--- a/artfynd/A 14354-2024 artfynd.xlsx
+++ b/artfynd/A 14354-2024 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY7"/>
+  <dimension ref="A1:AY8"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1430,6 +1430,126 @@
         </is>
       </c>
     </row>
+    <row r="8">
+      <c r="A8" t="n">
+        <v>118077514</v>
+      </c>
+      <c r="B8" t="n">
+        <v>42953</v>
+      </c>
+      <c r="C8" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D8" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E8" t="n">
+        <v>101242</v>
+      </c>
+      <c r="F8" t="inlineStr">
+        <is>
+          <t>Dårgräsfjäril</t>
+        </is>
+      </c>
+      <c r="G8" t="inlineStr">
+        <is>
+          <t>Lopinga achine</t>
+        </is>
+      </c>
+      <c r="H8" t="inlineStr">
+        <is>
+          <t>(Scopoli, 1763)</t>
+        </is>
+      </c>
+      <c r="I8" t="inlineStr">
+        <is>
+          <t>13</t>
+        </is>
+      </c>
+      <c r="J8" t="inlineStr"/>
+      <c r="K8" t="inlineStr">
+        <is>
+          <t>imago/adult</t>
+        </is>
+      </c>
+      <c r="L8" t="inlineStr"/>
+      <c r="M8" t="inlineStr"/>
+      <c r="N8" t="inlineStr"/>
+      <c r="P8" t="inlineStr">
+        <is>
+          <t>4. Botes Källmyr, Gtl</t>
+        </is>
+      </c>
+      <c r="Q8" t="n">
+        <v>700334</v>
+      </c>
+      <c r="R8" t="n">
+        <v>6359053</v>
+      </c>
+      <c r="S8" t="n">
+        <v>5</v>
+      </c>
+      <c r="T8" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="U8" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="V8" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="W8" t="inlineStr">
+        <is>
+          <t>Gerum</t>
+        </is>
+      </c>
+      <c r="Y8" t="inlineStr">
+        <is>
+          <t>2024-06-20</t>
+        </is>
+      </c>
+      <c r="AA8" t="inlineStr">
+        <is>
+          <t>2024-06-20</t>
+        </is>
+      </c>
+      <c r="AD8" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE8" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF8" t="inlineStr"/>
+      <c r="AG8" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT8" t="inlineStr"/>
+      <c r="AW8" t="inlineStr">
+        <is>
+          <t>Arne Pettersson</t>
+        </is>
+      </c>
+      <c r="AX8" t="inlineStr">
+        <is>
+          <t>Arne Pettersson</t>
+        </is>
+      </c>
+      <c r="AY8" t="inlineStr">
+        <is>
+          <t>Biogeografisk uppföljning av fjärilar</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/artfynd/A 14354-2024 artfynd.xlsx
+++ b/artfynd/A 14354-2024 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY8"/>
+  <dimension ref="A1:AY25"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1550,6 +1550,1792 @@
         </is>
       </c>
     </row>
+    <row r="9">
+      <c r="A9" t="n">
+        <v>126300260</v>
+      </c>
+      <c r="B9" t="n">
+        <v>43227</v>
+      </c>
+      <c r="D9" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E9" t="n">
+        <v>101242</v>
+      </c>
+      <c r="F9" t="inlineStr">
+        <is>
+          <t>Dårgräsfjäril</t>
+        </is>
+      </c>
+      <c r="G9" t="inlineStr">
+        <is>
+          <t>Lopinga achine</t>
+        </is>
+      </c>
+      <c r="H9" t="inlineStr">
+        <is>
+          <t>(Scopoli, 1763)</t>
+        </is>
+      </c>
+      <c r="I9" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="P9" t="inlineStr">
+        <is>
+          <t>Gerum, Likmunds 1:2 (4), Gtl</t>
+        </is>
+      </c>
+      <c r="Q9" t="n">
+        <v>700247</v>
+      </c>
+      <c r="R9" t="n">
+        <v>6359105</v>
+      </c>
+      <c r="S9" t="n">
+        <v>5</v>
+      </c>
+      <c r="T9" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="U9" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="V9" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="W9" t="inlineStr">
+        <is>
+          <t>Gerum</t>
+        </is>
+      </c>
+      <c r="Y9" t="inlineStr">
+        <is>
+          <t>2025-06-29</t>
+        </is>
+      </c>
+      <c r="AA9" t="inlineStr">
+        <is>
+          <t>2025-06-29</t>
+        </is>
+      </c>
+      <c r="AD9" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE9" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG9" t="b">
+        <v>0</v>
+      </c>
+      <c r="AI9" t="inlineStr">
+        <is>
+          <t>Hästbetad blandskog</t>
+        </is>
+      </c>
+      <c r="AT9" t="inlineStr"/>
+      <c r="AW9" t="inlineStr">
+        <is>
+          <t>Gun Ingmansson</t>
+        </is>
+      </c>
+      <c r="AX9" t="inlineStr">
+        <is>
+          <t>Gun Ingmansson, Jörgen Petersson, Björn Larsson</t>
+        </is>
+      </c>
+      <c r="AY9" t="inlineStr"/>
+    </row>
+    <row r="10">
+      <c r="A10" t="n">
+        <v>126300269</v>
+      </c>
+      <c r="B10" t="n">
+        <v>43227</v>
+      </c>
+      <c r="D10" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E10" t="n">
+        <v>101242</v>
+      </c>
+      <c r="F10" t="inlineStr">
+        <is>
+          <t>Dårgräsfjäril</t>
+        </is>
+      </c>
+      <c r="G10" t="inlineStr">
+        <is>
+          <t>Lopinga achine</t>
+        </is>
+      </c>
+      <c r="H10" t="inlineStr">
+        <is>
+          <t>(Scopoli, 1763)</t>
+        </is>
+      </c>
+      <c r="I10" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="P10" t="inlineStr">
+        <is>
+          <t>Gerum, Likmunds 1:2 (4), Gtl</t>
+        </is>
+      </c>
+      <c r="Q10" t="n">
+        <v>700265</v>
+      </c>
+      <c r="R10" t="n">
+        <v>6359056</v>
+      </c>
+      <c r="S10" t="n">
+        <v>4</v>
+      </c>
+      <c r="T10" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="U10" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="V10" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="W10" t="inlineStr">
+        <is>
+          <t>Gerum</t>
+        </is>
+      </c>
+      <c r="Y10" t="inlineStr">
+        <is>
+          <t>2025-06-29</t>
+        </is>
+      </c>
+      <c r="AA10" t="inlineStr">
+        <is>
+          <t>2025-06-29</t>
+        </is>
+      </c>
+      <c r="AD10" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE10" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG10" t="b">
+        <v>0</v>
+      </c>
+      <c r="AI10" t="inlineStr">
+        <is>
+          <t>Hästbetad blandskog</t>
+        </is>
+      </c>
+      <c r="AT10" t="inlineStr"/>
+      <c r="AW10" t="inlineStr">
+        <is>
+          <t>Gun Ingmansson</t>
+        </is>
+      </c>
+      <c r="AX10" t="inlineStr">
+        <is>
+          <t>Gun Ingmansson, Jörgen Petersson, Björn Larsson</t>
+        </is>
+      </c>
+      <c r="AY10" t="inlineStr"/>
+    </row>
+    <row r="11">
+      <c r="A11" t="n">
+        <v>126300254</v>
+      </c>
+      <c r="B11" t="n">
+        <v>98381</v>
+      </c>
+      <c r="D11" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E11" t="n">
+        <v>223621</v>
+      </c>
+      <c r="F11" t="inlineStr">
+        <is>
+          <t>Skogsnattviol</t>
+        </is>
+      </c>
+      <c r="G11" t="inlineStr">
+        <is>
+          <t>Platanthera bifolia subsp. latiflora</t>
+        </is>
+      </c>
+      <c r="H11" t="inlineStr">
+        <is>
+          <t>(Drejer) Løjtnant</t>
+        </is>
+      </c>
+      <c r="I11" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="P11" t="inlineStr">
+        <is>
+          <t>Gerum, Likmunds 1:2 (4), Gtl</t>
+        </is>
+      </c>
+      <c r="Q11" t="n">
+        <v>700231</v>
+      </c>
+      <c r="R11" t="n">
+        <v>6359136</v>
+      </c>
+      <c r="S11" t="n">
+        <v>4</v>
+      </c>
+      <c r="T11" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="U11" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="V11" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="W11" t="inlineStr">
+        <is>
+          <t>Gerum</t>
+        </is>
+      </c>
+      <c r="Y11" t="inlineStr">
+        <is>
+          <t>2025-06-29</t>
+        </is>
+      </c>
+      <c r="AA11" t="inlineStr">
+        <is>
+          <t>2025-06-29</t>
+        </is>
+      </c>
+      <c r="AD11" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE11" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG11" t="b">
+        <v>0</v>
+      </c>
+      <c r="AI11" t="inlineStr">
+        <is>
+          <t>Hästbetad blandskog</t>
+        </is>
+      </c>
+      <c r="AT11" t="inlineStr"/>
+      <c r="AW11" t="inlineStr">
+        <is>
+          <t>Gun Ingmansson</t>
+        </is>
+      </c>
+      <c r="AX11" t="inlineStr">
+        <is>
+          <t>Gun Ingmansson, Jörgen Petersson, Björn Larsson</t>
+        </is>
+      </c>
+      <c r="AY11" t="inlineStr"/>
+    </row>
+    <row r="12">
+      <c r="A12" t="n">
+        <v>126300262</v>
+      </c>
+      <c r="B12" t="n">
+        <v>43227</v>
+      </c>
+      <c r="D12" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E12" t="n">
+        <v>101242</v>
+      </c>
+      <c r="F12" t="inlineStr">
+        <is>
+          <t>Dårgräsfjäril</t>
+        </is>
+      </c>
+      <c r="G12" t="inlineStr">
+        <is>
+          <t>Lopinga achine</t>
+        </is>
+      </c>
+      <c r="H12" t="inlineStr">
+        <is>
+          <t>(Scopoli, 1763)</t>
+        </is>
+      </c>
+      <c r="I12" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="P12" t="inlineStr">
+        <is>
+          <t>Gerum, Likmunds 1:2 (4), Gtl</t>
+        </is>
+      </c>
+      <c r="Q12" t="n">
+        <v>700253</v>
+      </c>
+      <c r="R12" t="n">
+        <v>6359086</v>
+      </c>
+      <c r="S12" t="n">
+        <v>4</v>
+      </c>
+      <c r="T12" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="U12" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="V12" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="W12" t="inlineStr">
+        <is>
+          <t>Gerum</t>
+        </is>
+      </c>
+      <c r="Y12" t="inlineStr">
+        <is>
+          <t>2025-06-29</t>
+        </is>
+      </c>
+      <c r="AA12" t="inlineStr">
+        <is>
+          <t>2025-06-29</t>
+        </is>
+      </c>
+      <c r="AD12" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE12" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG12" t="b">
+        <v>0</v>
+      </c>
+      <c r="AI12" t="inlineStr">
+        <is>
+          <t>Hästbetad blandskog</t>
+        </is>
+      </c>
+      <c r="AT12" t="inlineStr"/>
+      <c r="AW12" t="inlineStr">
+        <is>
+          <t>Gun Ingmansson</t>
+        </is>
+      </c>
+      <c r="AX12" t="inlineStr">
+        <is>
+          <t>Gun Ingmansson, Jörgen Petersson, Björn Larsson</t>
+        </is>
+      </c>
+      <c r="AY12" t="inlineStr"/>
+    </row>
+    <row r="13">
+      <c r="A13" t="n">
+        <v>126300255</v>
+      </c>
+      <c r="B13" t="n">
+        <v>43227</v>
+      </c>
+      <c r="D13" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E13" t="n">
+        <v>101242</v>
+      </c>
+      <c r="F13" t="inlineStr">
+        <is>
+          <t>Dårgräsfjäril</t>
+        </is>
+      </c>
+      <c r="G13" t="inlineStr">
+        <is>
+          <t>Lopinga achine</t>
+        </is>
+      </c>
+      <c r="H13" t="inlineStr">
+        <is>
+          <t>(Scopoli, 1763)</t>
+        </is>
+      </c>
+      <c r="I13" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="P13" t="inlineStr">
+        <is>
+          <t>Gerum, Likmunds 1:2 (4), Gtl</t>
+        </is>
+      </c>
+      <c r="Q13" t="n">
+        <v>700243</v>
+      </c>
+      <c r="R13" t="n">
+        <v>6359125</v>
+      </c>
+      <c r="S13" t="n">
+        <v>5</v>
+      </c>
+      <c r="T13" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="U13" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="V13" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="W13" t="inlineStr">
+        <is>
+          <t>Gerum</t>
+        </is>
+      </c>
+      <c r="Y13" t="inlineStr">
+        <is>
+          <t>2025-06-29</t>
+        </is>
+      </c>
+      <c r="AA13" t="inlineStr">
+        <is>
+          <t>2025-06-29</t>
+        </is>
+      </c>
+      <c r="AD13" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE13" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG13" t="b">
+        <v>0</v>
+      </c>
+      <c r="AI13" t="inlineStr">
+        <is>
+          <t>Hästbetad blandskog</t>
+        </is>
+      </c>
+      <c r="AT13" t="inlineStr"/>
+      <c r="AW13" t="inlineStr">
+        <is>
+          <t>Gun Ingmansson</t>
+        </is>
+      </c>
+      <c r="AX13" t="inlineStr">
+        <is>
+          <t>Gun Ingmansson, Jörgen Petersson, Björn Larsson</t>
+        </is>
+      </c>
+      <c r="AY13" t="inlineStr"/>
+    </row>
+    <row r="14">
+      <c r="A14" t="n">
+        <v>126300264</v>
+      </c>
+      <c r="B14" t="n">
+        <v>43227</v>
+      </c>
+      <c r="D14" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E14" t="n">
+        <v>101242</v>
+      </c>
+      <c r="F14" t="inlineStr">
+        <is>
+          <t>Dårgräsfjäril</t>
+        </is>
+      </c>
+      <c r="G14" t="inlineStr">
+        <is>
+          <t>Lopinga achine</t>
+        </is>
+      </c>
+      <c r="H14" t="inlineStr">
+        <is>
+          <t>(Scopoli, 1763)</t>
+        </is>
+      </c>
+      <c r="I14" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="P14" t="inlineStr">
+        <is>
+          <t>Gerum, Likmunds 1:2 (4), Gtl</t>
+        </is>
+      </c>
+      <c r="Q14" t="n">
+        <v>700247</v>
+      </c>
+      <c r="R14" t="n">
+        <v>6359082</v>
+      </c>
+      <c r="S14" t="n">
+        <v>8</v>
+      </c>
+      <c r="T14" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="U14" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="V14" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="W14" t="inlineStr">
+        <is>
+          <t>Gerum</t>
+        </is>
+      </c>
+      <c r="Y14" t="inlineStr">
+        <is>
+          <t>2025-06-29</t>
+        </is>
+      </c>
+      <c r="AA14" t="inlineStr">
+        <is>
+          <t>2025-06-29</t>
+        </is>
+      </c>
+      <c r="AD14" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE14" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG14" t="b">
+        <v>0</v>
+      </c>
+      <c r="AI14" t="inlineStr">
+        <is>
+          <t>Hästbetad blandskog</t>
+        </is>
+      </c>
+      <c r="AT14" t="inlineStr"/>
+      <c r="AW14" t="inlineStr">
+        <is>
+          <t>Gun Ingmansson</t>
+        </is>
+      </c>
+      <c r="AX14" t="inlineStr">
+        <is>
+          <t>Gun Ingmansson, Jörgen Petersson, Björn Larsson</t>
+        </is>
+      </c>
+      <c r="AY14" t="inlineStr"/>
+    </row>
+    <row r="15">
+      <c r="A15" t="n">
+        <v>126300268</v>
+      </c>
+      <c r="B15" t="n">
+        <v>98368</v>
+      </c>
+      <c r="D15" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E15" t="n">
+        <v>219847</v>
+      </c>
+      <c r="F15" t="inlineStr">
+        <is>
+          <t>Tvåblad</t>
+        </is>
+      </c>
+      <c r="G15" t="inlineStr">
+        <is>
+          <t>Neottia ovata</t>
+        </is>
+      </c>
+      <c r="H15" t="inlineStr">
+        <is>
+          <t>(L.) Buff. &amp; Fingerh.</t>
+        </is>
+      </c>
+      <c r="I15" t="inlineStr"/>
+      <c r="P15" t="inlineStr">
+        <is>
+          <t>Gerum, Likmunds 1:2 (4), Gtl</t>
+        </is>
+      </c>
+      <c r="Q15" t="n">
+        <v>700265</v>
+      </c>
+      <c r="R15" t="n">
+        <v>6359056</v>
+      </c>
+      <c r="S15" t="n">
+        <v>4</v>
+      </c>
+      <c r="T15" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="U15" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="V15" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="W15" t="inlineStr">
+        <is>
+          <t>Gerum</t>
+        </is>
+      </c>
+      <c r="Y15" t="inlineStr">
+        <is>
+          <t>2025-06-29</t>
+        </is>
+      </c>
+      <c r="AA15" t="inlineStr">
+        <is>
+          <t>2025-06-29</t>
+        </is>
+      </c>
+      <c r="AD15" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE15" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG15" t="b">
+        <v>0</v>
+      </c>
+      <c r="AI15" t="inlineStr">
+        <is>
+          <t>Hästbetad blandskog</t>
+        </is>
+      </c>
+      <c r="AT15" t="inlineStr"/>
+      <c r="AW15" t="inlineStr">
+        <is>
+          <t>Gun Ingmansson</t>
+        </is>
+      </c>
+      <c r="AX15" t="inlineStr">
+        <is>
+          <t>Gun Ingmansson, Jörgen Petersson, Björn Larsson</t>
+        </is>
+      </c>
+      <c r="AY15" t="inlineStr"/>
+    </row>
+    <row r="16">
+      <c r="A16" t="n">
+        <v>126300258</v>
+      </c>
+      <c r="B16" t="n">
+        <v>98368</v>
+      </c>
+      <c r="D16" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E16" t="n">
+        <v>219847</v>
+      </c>
+      <c r="F16" t="inlineStr">
+        <is>
+          <t>Tvåblad</t>
+        </is>
+      </c>
+      <c r="G16" t="inlineStr">
+        <is>
+          <t>Neottia ovata</t>
+        </is>
+      </c>
+      <c r="H16" t="inlineStr">
+        <is>
+          <t>(L.) Buff. &amp; Fingerh.</t>
+        </is>
+      </c>
+      <c r="I16" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="P16" t="inlineStr">
+        <is>
+          <t>Gerum, Likmunds 1:2 (4), Gtl</t>
+        </is>
+      </c>
+      <c r="Q16" t="n">
+        <v>700247</v>
+      </c>
+      <c r="R16" t="n">
+        <v>6359105</v>
+      </c>
+      <c r="S16" t="n">
+        <v>5</v>
+      </c>
+      <c r="T16" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="U16" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="V16" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="W16" t="inlineStr">
+        <is>
+          <t>Gerum</t>
+        </is>
+      </c>
+      <c r="Y16" t="inlineStr">
+        <is>
+          <t>2025-06-29</t>
+        </is>
+      </c>
+      <c r="AA16" t="inlineStr">
+        <is>
+          <t>2025-06-29</t>
+        </is>
+      </c>
+      <c r="AD16" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE16" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG16" t="b">
+        <v>0</v>
+      </c>
+      <c r="AI16" t="inlineStr">
+        <is>
+          <t>Hästbetad blandskog</t>
+        </is>
+      </c>
+      <c r="AT16" t="inlineStr"/>
+      <c r="AW16" t="inlineStr">
+        <is>
+          <t>Gun Ingmansson</t>
+        </is>
+      </c>
+      <c r="AX16" t="inlineStr">
+        <is>
+          <t>Gun Ingmansson, Jörgen Petersson, Björn Larsson</t>
+        </is>
+      </c>
+      <c r="AY16" t="inlineStr"/>
+    </row>
+    <row r="17">
+      <c r="A17" t="n">
+        <v>126300256</v>
+      </c>
+      <c r="B17" t="n">
+        <v>98368</v>
+      </c>
+      <c r="D17" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E17" t="n">
+        <v>219847</v>
+      </c>
+      <c r="F17" t="inlineStr">
+        <is>
+          <t>Tvåblad</t>
+        </is>
+      </c>
+      <c r="G17" t="inlineStr">
+        <is>
+          <t>Neottia ovata</t>
+        </is>
+      </c>
+      <c r="H17" t="inlineStr">
+        <is>
+          <t>(L.) Buff. &amp; Fingerh.</t>
+        </is>
+      </c>
+      <c r="I17" t="inlineStr"/>
+      <c r="P17" t="inlineStr">
+        <is>
+          <t>Gerum, Likmunds 1:2 (4), Gtl</t>
+        </is>
+      </c>
+      <c r="Q17" t="n">
+        <v>700247</v>
+      </c>
+      <c r="R17" t="n">
+        <v>6359114</v>
+      </c>
+      <c r="S17" t="n">
+        <v>4</v>
+      </c>
+      <c r="T17" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="U17" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="V17" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="W17" t="inlineStr">
+        <is>
+          <t>Gerum</t>
+        </is>
+      </c>
+      <c r="Y17" t="inlineStr">
+        <is>
+          <t>2025-06-29</t>
+        </is>
+      </c>
+      <c r="AA17" t="inlineStr">
+        <is>
+          <t>2025-06-29</t>
+        </is>
+      </c>
+      <c r="AD17" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE17" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG17" t="b">
+        <v>0</v>
+      </c>
+      <c r="AI17" t="inlineStr">
+        <is>
+          <t>Hästbetad blandskog</t>
+        </is>
+      </c>
+      <c r="AT17" t="inlineStr"/>
+      <c r="AW17" t="inlineStr">
+        <is>
+          <t>Gun Ingmansson</t>
+        </is>
+      </c>
+      <c r="AX17" t="inlineStr">
+        <is>
+          <t>Gun Ingmansson, Jörgen Petersson, Björn Larsson</t>
+        </is>
+      </c>
+      <c r="AY17" t="inlineStr"/>
+    </row>
+    <row r="18">
+      <c r="A18" t="n">
+        <v>126300266</v>
+      </c>
+      <c r="B18" t="n">
+        <v>98263</v>
+      </c>
+      <c r="D18" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E18" t="n">
+        <v>223591</v>
+      </c>
+      <c r="F18" t="inlineStr">
+        <is>
+          <t>Skogsnycklar</t>
+        </is>
+      </c>
+      <c r="G18" t="inlineStr">
+        <is>
+          <t>Dactylorhiza maculata subsp. fuchsii</t>
+        </is>
+      </c>
+      <c r="H18" t="inlineStr">
+        <is>
+          <t>(Druce) Hyl.</t>
+        </is>
+      </c>
+      <c r="I18" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="P18" t="inlineStr">
+        <is>
+          <t>Gerum, Likmunds 1:2 (4), Gtl</t>
+        </is>
+      </c>
+      <c r="Q18" t="n">
+        <v>700247</v>
+      </c>
+      <c r="R18" t="n">
+        <v>6359082</v>
+      </c>
+      <c r="S18" t="n">
+        <v>8</v>
+      </c>
+      <c r="T18" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="U18" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="V18" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="W18" t="inlineStr">
+        <is>
+          <t>Gerum</t>
+        </is>
+      </c>
+      <c r="Y18" t="inlineStr">
+        <is>
+          <t>2025-06-29</t>
+        </is>
+      </c>
+      <c r="AA18" t="inlineStr">
+        <is>
+          <t>2025-06-29</t>
+        </is>
+      </c>
+      <c r="AD18" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE18" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG18" t="b">
+        <v>0</v>
+      </c>
+      <c r="AI18" t="inlineStr">
+        <is>
+          <t>Hästbetad blandskog</t>
+        </is>
+      </c>
+      <c r="AT18" t="inlineStr"/>
+      <c r="AW18" t="inlineStr">
+        <is>
+          <t>Gun Ingmansson</t>
+        </is>
+      </c>
+      <c r="AX18" t="inlineStr">
+        <is>
+          <t>Gun Ingmansson, Jörgen Petersson, Björn Larsson</t>
+        </is>
+      </c>
+      <c r="AY18" t="inlineStr"/>
+    </row>
+    <row r="19">
+      <c r="A19" t="n">
+        <v>126300263</v>
+      </c>
+      <c r="B19" t="n">
+        <v>98263</v>
+      </c>
+      <c r="D19" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E19" t="n">
+        <v>223591</v>
+      </c>
+      <c r="F19" t="inlineStr">
+        <is>
+          <t>Skogsnycklar</t>
+        </is>
+      </c>
+      <c r="G19" t="inlineStr">
+        <is>
+          <t>Dactylorhiza maculata subsp. fuchsii</t>
+        </is>
+      </c>
+      <c r="H19" t="inlineStr">
+        <is>
+          <t>(Druce) Hyl.</t>
+        </is>
+      </c>
+      <c r="I19" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="P19" t="inlineStr">
+        <is>
+          <t>Gerum, Likmunds 1:2 (4), Gtl</t>
+        </is>
+      </c>
+      <c r="Q19" t="n">
+        <v>700253</v>
+      </c>
+      <c r="R19" t="n">
+        <v>6359086</v>
+      </c>
+      <c r="S19" t="n">
+        <v>4</v>
+      </c>
+      <c r="T19" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="U19" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="V19" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="W19" t="inlineStr">
+        <is>
+          <t>Gerum</t>
+        </is>
+      </c>
+      <c r="Y19" t="inlineStr">
+        <is>
+          <t>2025-06-29</t>
+        </is>
+      </c>
+      <c r="AA19" t="inlineStr">
+        <is>
+          <t>2025-06-29</t>
+        </is>
+      </c>
+      <c r="AD19" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE19" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG19" t="b">
+        <v>0</v>
+      </c>
+      <c r="AI19" t="inlineStr">
+        <is>
+          <t>Hästbetad blandskog</t>
+        </is>
+      </c>
+      <c r="AT19" t="inlineStr"/>
+      <c r="AW19" t="inlineStr">
+        <is>
+          <t>Gun Ingmansson</t>
+        </is>
+      </c>
+      <c r="AX19" t="inlineStr">
+        <is>
+          <t>Gun Ingmansson, Jörgen Petersson, Björn Larsson</t>
+        </is>
+      </c>
+      <c r="AY19" t="inlineStr"/>
+    </row>
+    <row r="20">
+      <c r="A20" t="n">
+        <v>126300259</v>
+      </c>
+      <c r="B20" t="n">
+        <v>98263</v>
+      </c>
+      <c r="D20" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E20" t="n">
+        <v>223591</v>
+      </c>
+      <c r="F20" t="inlineStr">
+        <is>
+          <t>Skogsnycklar</t>
+        </is>
+      </c>
+      <c r="G20" t="inlineStr">
+        <is>
+          <t>Dactylorhiza maculata subsp. fuchsii</t>
+        </is>
+      </c>
+      <c r="H20" t="inlineStr">
+        <is>
+          <t>(Druce) Hyl.</t>
+        </is>
+      </c>
+      <c r="I20" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="P20" t="inlineStr">
+        <is>
+          <t>Gerum, Likmunds 1:2 (4), Gtl</t>
+        </is>
+      </c>
+      <c r="Q20" t="n">
+        <v>700247</v>
+      </c>
+      <c r="R20" t="n">
+        <v>6359105</v>
+      </c>
+      <c r="S20" t="n">
+        <v>5</v>
+      </c>
+      <c r="T20" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="U20" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="V20" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="W20" t="inlineStr">
+        <is>
+          <t>Gerum</t>
+        </is>
+      </c>
+      <c r="Y20" t="inlineStr">
+        <is>
+          <t>2025-06-29</t>
+        </is>
+      </c>
+      <c r="AA20" t="inlineStr">
+        <is>
+          <t>2025-06-29</t>
+        </is>
+      </c>
+      <c r="AD20" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE20" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG20" t="b">
+        <v>0</v>
+      </c>
+      <c r="AI20" t="inlineStr">
+        <is>
+          <t>Hästbetad blandskog</t>
+        </is>
+      </c>
+      <c r="AT20" t="inlineStr"/>
+      <c r="AW20" t="inlineStr">
+        <is>
+          <t>Gun Ingmansson</t>
+        </is>
+      </c>
+      <c r="AX20" t="inlineStr">
+        <is>
+          <t>Gun Ingmansson, Jörgen Petersson, Björn Larsson</t>
+        </is>
+      </c>
+      <c r="AY20" t="inlineStr"/>
+    </row>
+    <row r="21">
+      <c r="A21" t="n">
+        <v>126300253</v>
+      </c>
+      <c r="B21" t="n">
+        <v>43227</v>
+      </c>
+      <c r="D21" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E21" t="n">
+        <v>101242</v>
+      </c>
+      <c r="F21" t="inlineStr">
+        <is>
+          <t>Dårgräsfjäril</t>
+        </is>
+      </c>
+      <c r="G21" t="inlineStr">
+        <is>
+          <t>Lopinga achine</t>
+        </is>
+      </c>
+      <c r="H21" t="inlineStr">
+        <is>
+          <t>(Scopoli, 1763)</t>
+        </is>
+      </c>
+      <c r="I21" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="P21" t="inlineStr">
+        <is>
+          <t>Gerum, Likmunds 1:2 (4), Gtl</t>
+        </is>
+      </c>
+      <c r="Q21" t="n">
+        <v>700231</v>
+      </c>
+      <c r="R21" t="n">
+        <v>6359136</v>
+      </c>
+      <c r="S21" t="n">
+        <v>4</v>
+      </c>
+      <c r="T21" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="U21" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="V21" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="W21" t="inlineStr">
+        <is>
+          <t>Gerum</t>
+        </is>
+      </c>
+      <c r="Y21" t="inlineStr">
+        <is>
+          <t>2025-06-29</t>
+        </is>
+      </c>
+      <c r="AA21" t="inlineStr">
+        <is>
+          <t>2025-06-29</t>
+        </is>
+      </c>
+      <c r="AD21" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE21" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG21" t="b">
+        <v>0</v>
+      </c>
+      <c r="AI21" t="inlineStr">
+        <is>
+          <t>Hästbetad blandskog</t>
+        </is>
+      </c>
+      <c r="AT21" t="inlineStr"/>
+      <c r="AW21" t="inlineStr">
+        <is>
+          <t>Gun Ingmansson</t>
+        </is>
+      </c>
+      <c r="AX21" t="inlineStr">
+        <is>
+          <t>Gun Ingmansson, Jörgen Petersson, Björn Larsson</t>
+        </is>
+      </c>
+      <c r="AY21" t="inlineStr"/>
+    </row>
+    <row r="22">
+      <c r="A22" t="n">
+        <v>126300257</v>
+      </c>
+      <c r="B22" t="n">
+        <v>98323</v>
+      </c>
+      <c r="D22" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E22" t="n">
+        <v>219798</v>
+      </c>
+      <c r="F22" t="inlineStr">
+        <is>
+          <t>Skogsknipprot</t>
+        </is>
+      </c>
+      <c r="G22" t="inlineStr">
+        <is>
+          <t>Epipactis helleborine</t>
+        </is>
+      </c>
+      <c r="H22" t="inlineStr">
+        <is>
+          <t>(L.) Crantz</t>
+        </is>
+      </c>
+      <c r="I22" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="P22" t="inlineStr">
+        <is>
+          <t>Gerum, Likmunds 1:2 (4), Gtl</t>
+        </is>
+      </c>
+      <c r="Q22" t="n">
+        <v>700247</v>
+      </c>
+      <c r="R22" t="n">
+        <v>6359114</v>
+      </c>
+      <c r="S22" t="n">
+        <v>4</v>
+      </c>
+      <c r="T22" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="U22" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="V22" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="W22" t="inlineStr">
+        <is>
+          <t>Gerum</t>
+        </is>
+      </c>
+      <c r="Y22" t="inlineStr">
+        <is>
+          <t>2025-06-29</t>
+        </is>
+      </c>
+      <c r="AA22" t="inlineStr">
+        <is>
+          <t>2025-06-29</t>
+        </is>
+      </c>
+      <c r="AD22" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE22" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG22" t="b">
+        <v>0</v>
+      </c>
+      <c r="AI22" t="inlineStr">
+        <is>
+          <t>Hästbetad blandskog</t>
+        </is>
+      </c>
+      <c r="AT22" t="inlineStr"/>
+      <c r="AW22" t="inlineStr">
+        <is>
+          <t>Gun Ingmansson</t>
+        </is>
+      </c>
+      <c r="AX22" t="inlineStr">
+        <is>
+          <t>Gun Ingmansson, Jörgen Petersson, Björn Larsson</t>
+        </is>
+      </c>
+      <c r="AY22" t="inlineStr"/>
+    </row>
+    <row r="23">
+      <c r="A23" t="n">
+        <v>126300265</v>
+      </c>
+      <c r="B23" t="n">
+        <v>98368</v>
+      </c>
+      <c r="D23" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E23" t="n">
+        <v>219847</v>
+      </c>
+      <c r="F23" t="inlineStr">
+        <is>
+          <t>Tvåblad</t>
+        </is>
+      </c>
+      <c r="G23" t="inlineStr">
+        <is>
+          <t>Neottia ovata</t>
+        </is>
+      </c>
+      <c r="H23" t="inlineStr">
+        <is>
+          <t>(L.) Buff. &amp; Fingerh.</t>
+        </is>
+      </c>
+      <c r="I23" t="inlineStr"/>
+      <c r="P23" t="inlineStr">
+        <is>
+          <t>Gerum, Likmunds 1:2 (4), Gtl</t>
+        </is>
+      </c>
+      <c r="Q23" t="n">
+        <v>700247</v>
+      </c>
+      <c r="R23" t="n">
+        <v>6359082</v>
+      </c>
+      <c r="S23" t="n">
+        <v>8</v>
+      </c>
+      <c r="T23" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="U23" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="V23" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="W23" t="inlineStr">
+        <is>
+          <t>Gerum</t>
+        </is>
+      </c>
+      <c r="Y23" t="inlineStr">
+        <is>
+          <t>2025-06-29</t>
+        </is>
+      </c>
+      <c r="AA23" t="inlineStr">
+        <is>
+          <t>2025-06-29</t>
+        </is>
+      </c>
+      <c r="AD23" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE23" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG23" t="b">
+        <v>0</v>
+      </c>
+      <c r="AI23" t="inlineStr">
+        <is>
+          <t>Hästbetad blandskog</t>
+        </is>
+      </c>
+      <c r="AT23" t="inlineStr"/>
+      <c r="AW23" t="inlineStr">
+        <is>
+          <t>Gun Ingmansson</t>
+        </is>
+      </c>
+      <c r="AX23" t="inlineStr">
+        <is>
+          <t>Gun Ingmansson, Jörgen Petersson, Björn Larsson</t>
+        </is>
+      </c>
+      <c r="AY23" t="inlineStr"/>
+    </row>
+    <row r="24">
+      <c r="A24" t="n">
+        <v>126300267</v>
+      </c>
+      <c r="B24" t="n">
+        <v>98367</v>
+      </c>
+      <c r="D24" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E24" t="n">
+        <v>219862</v>
+      </c>
+      <c r="F24" t="inlineStr">
+        <is>
+          <t>Nästrot</t>
+        </is>
+      </c>
+      <c r="G24" t="inlineStr">
+        <is>
+          <t>Neottia nidus-avis</t>
+        </is>
+      </c>
+      <c r="H24" t="inlineStr">
+        <is>
+          <t>(L.) Rich.</t>
+        </is>
+      </c>
+      <c r="I24" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="P24" t="inlineStr">
+        <is>
+          <t>Gerum, Likmunds 1:2 (4), Gtl</t>
+        </is>
+      </c>
+      <c r="Q24" t="n">
+        <v>700257</v>
+      </c>
+      <c r="R24" t="n">
+        <v>6359067</v>
+      </c>
+      <c r="S24" t="n">
+        <v>10</v>
+      </c>
+      <c r="T24" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="U24" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="V24" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="W24" t="inlineStr">
+        <is>
+          <t>Gerum</t>
+        </is>
+      </c>
+      <c r="Y24" t="inlineStr">
+        <is>
+          <t>2025-06-29</t>
+        </is>
+      </c>
+      <c r="AA24" t="inlineStr">
+        <is>
+          <t>2025-06-29</t>
+        </is>
+      </c>
+      <c r="AD24" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE24" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG24" t="b">
+        <v>0</v>
+      </c>
+      <c r="AI24" t="inlineStr">
+        <is>
+          <t>Hästbetad blandskog</t>
+        </is>
+      </c>
+      <c r="AT24" t="inlineStr"/>
+      <c r="AW24" t="inlineStr">
+        <is>
+          <t>Gun Ingmansson</t>
+        </is>
+      </c>
+      <c r="AX24" t="inlineStr">
+        <is>
+          <t>Gun Ingmansson, Jörgen Petersson, Björn Larsson</t>
+        </is>
+      </c>
+      <c r="AY24" t="inlineStr"/>
+    </row>
+    <row r="25">
+      <c r="A25" t="n">
+        <v>126300270</v>
+      </c>
+      <c r="B25" t="n">
+        <v>98263</v>
+      </c>
+      <c r="D25" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E25" t="n">
+        <v>223591</v>
+      </c>
+      <c r="F25" t="inlineStr">
+        <is>
+          <t>Skogsnycklar</t>
+        </is>
+      </c>
+      <c r="G25" t="inlineStr">
+        <is>
+          <t>Dactylorhiza maculata subsp. fuchsii</t>
+        </is>
+      </c>
+      <c r="H25" t="inlineStr">
+        <is>
+          <t>(Druce) Hyl.</t>
+        </is>
+      </c>
+      <c r="I25" t="inlineStr"/>
+      <c r="P25" t="inlineStr">
+        <is>
+          <t>Gerum, Likmunds 1:2 (4), Gtl</t>
+        </is>
+      </c>
+      <c r="Q25" t="n">
+        <v>700265</v>
+      </c>
+      <c r="R25" t="n">
+        <v>6359056</v>
+      </c>
+      <c r="S25" t="n">
+        <v>4</v>
+      </c>
+      <c r="T25" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="U25" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="V25" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="W25" t="inlineStr">
+        <is>
+          <t>Gerum</t>
+        </is>
+      </c>
+      <c r="Y25" t="inlineStr">
+        <is>
+          <t>2025-06-29</t>
+        </is>
+      </c>
+      <c r="AA25" t="inlineStr">
+        <is>
+          <t>2025-06-29</t>
+        </is>
+      </c>
+      <c r="AD25" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE25" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG25" t="b">
+        <v>0</v>
+      </c>
+      <c r="AI25" t="inlineStr">
+        <is>
+          <t>Hästbetad blandskog</t>
+        </is>
+      </c>
+      <c r="AT25" t="inlineStr"/>
+      <c r="AW25" t="inlineStr">
+        <is>
+          <t>Gun Ingmansson</t>
+        </is>
+      </c>
+      <c r="AX25" t="inlineStr">
+        <is>
+          <t>Gun Ingmansson, Jörgen Petersson, Björn Larsson</t>
+        </is>
+      </c>
+      <c r="AY25" t="inlineStr"/>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/artfynd/A 14354-2024 artfynd.xlsx
+++ b/artfynd/A 14354-2024 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY25"/>
+  <dimension ref="A1:AY26"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -2290,7 +2290,7 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>126300258</v>
+        <v>126300256</v>
       </c>
       <c r="B16" t="n">
         <v>98368</v>
@@ -2318,11 +2318,7 @@
           <t>(L.) Buff. &amp; Fingerh.</t>
         </is>
       </c>
-      <c r="I16" t="inlineStr">
-        <is>
-          <t>7</t>
-        </is>
-      </c>
+      <c r="I16" t="inlineStr"/>
       <c r="P16" t="inlineStr">
         <is>
           <t>Gerum, Likmunds 1:2 (4), Gtl</t>
@@ -2332,10 +2328,10 @@
         <v>700247</v>
       </c>
       <c r="R16" t="n">
-        <v>6359105</v>
+        <v>6359114</v>
       </c>
       <c r="S16" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="T16" t="inlineStr">
         <is>
@@ -2396,7 +2392,7 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>126300256</v>
+        <v>126300258</v>
       </c>
       <c r="B17" t="n">
         <v>98368</v>
@@ -2424,7 +2420,11 @@
           <t>(L.) Buff. &amp; Fingerh.</t>
         </is>
       </c>
-      <c r="I17" t="inlineStr"/>
+      <c r="I17" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
       <c r="P17" t="inlineStr">
         <is>
           <t>Gerum, Likmunds 1:2 (4), Gtl</t>
@@ -2434,10 +2434,10 @@
         <v>700247</v>
       </c>
       <c r="R17" t="n">
-        <v>6359114</v>
+        <v>6359105</v>
       </c>
       <c r="S17" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="T17" t="inlineStr">
         <is>
@@ -3336,6 +3336,117 @@
       </c>
       <c r="AY25" t="inlineStr"/>
     </row>
+    <row r="26">
+      <c r="A26" t="n">
+        <v>126312506</v>
+      </c>
+      <c r="B26" t="n">
+        <v>109200</v>
+      </c>
+      <c r="D26" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E26" t="n">
+        <v>220320</v>
+      </c>
+      <c r="F26" t="inlineStr">
+        <is>
+          <t>Ängsskära</t>
+        </is>
+      </c>
+      <c r="G26" t="inlineStr">
+        <is>
+          <t>Serratula tinctoria</t>
+        </is>
+      </c>
+      <c r="H26" t="inlineStr">
+        <is>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I26" t="inlineStr">
+        <is>
+          <t>34</t>
+        </is>
+      </c>
+      <c r="J26" t="inlineStr">
+        <is>
+          <t>stjälkar/strån/skott</t>
+        </is>
+      </c>
+      <c r="K26" t="inlineStr">
+        <is>
+          <t>blomknopp</t>
+        </is>
+      </c>
+      <c r="P26" t="inlineStr">
+        <is>
+          <t>Lilla Korsgatan, Gtl</t>
+        </is>
+      </c>
+      <c r="Q26" t="n">
+        <v>700335</v>
+      </c>
+      <c r="R26" t="n">
+        <v>6359040</v>
+      </c>
+      <c r="S26" t="n">
+        <v>25</v>
+      </c>
+      <c r="T26" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="U26" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="V26" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="W26" t="inlineStr">
+        <is>
+          <t>Gerum</t>
+        </is>
+      </c>
+      <c r="Y26" t="inlineStr">
+        <is>
+          <t>2025-06-30</t>
+        </is>
+      </c>
+      <c r="AA26" t="inlineStr">
+        <is>
+          <t>2025-06-30</t>
+        </is>
+      </c>
+      <c r="AD26" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE26" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG26" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT26" t="inlineStr"/>
+      <c r="AW26" t="inlineStr">
+        <is>
+          <t>Felicia Wikinger</t>
+        </is>
+      </c>
+      <c r="AX26" t="inlineStr">
+        <is>
+          <t>Felicia Wikinger, Teo Jernkvist</t>
+        </is>
+      </c>
+      <c r="AY26" t="inlineStr"/>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/artfynd/A 14354-2024 artfynd.xlsx
+++ b/artfynd/A 14354-2024 artfynd.xlsx
@@ -1658,37 +1658,37 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>126300269</v>
+        <v>126300254</v>
       </c>
       <c r="B10" t="n">
-        <v>43227</v>
+        <v>98385</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E10" t="n">
-        <v>101242</v>
+        <v>223621</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Dårgräsfjäril</t>
+          <t>Skogsnattviol</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Lopinga achine</t>
+          <t>Platanthera bifolia subsp. latiflora</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(Scopoli, 1763)</t>
+          <t>(Drejer) Løjtnant</t>
         </is>
       </c>
       <c r="I10" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>1</t>
         </is>
       </c>
       <c r="P10" t="inlineStr">
@@ -1697,10 +1697,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>700265</v>
+        <v>700231</v>
       </c>
       <c r="R10" t="n">
-        <v>6359056</v>
+        <v>6359136</v>
       </c>
       <c r="S10" t="n">
         <v>4</v>
@@ -1764,37 +1764,37 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>126300254</v>
+        <v>126300269</v>
       </c>
       <c r="B11" t="n">
-        <v>98381</v>
+        <v>43227</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E11" t="n">
-        <v>223621</v>
+        <v>101242</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Skogsnattviol</t>
+          <t>Dårgräsfjäril</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Platanthera bifolia subsp. latiflora</t>
+          <t>Lopinga achine</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(Drejer) Løjtnant</t>
+          <t>(Scopoli, 1763)</t>
         </is>
       </c>
       <c r="I11" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="P11" t="inlineStr">
@@ -1803,10 +1803,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>700231</v>
+        <v>700265</v>
       </c>
       <c r="R11" t="n">
-        <v>6359136</v>
+        <v>6359056</v>
       </c>
       <c r="S11" t="n">
         <v>4</v>
@@ -2191,7 +2191,7 @@
         <v>126300268</v>
       </c>
       <c r="B15" t="n">
-        <v>98368</v>
+        <v>98372</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2290,10 +2290,10 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>126300256</v>
+        <v>126300258</v>
       </c>
       <c r="B16" t="n">
-        <v>98368</v>
+        <v>98372</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2318,7 +2318,11 @@
           <t>(L.) Buff. &amp; Fingerh.</t>
         </is>
       </c>
-      <c r="I16" t="inlineStr"/>
+      <c r="I16" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
       <c r="P16" t="inlineStr">
         <is>
           <t>Gerum, Likmunds 1:2 (4), Gtl</t>
@@ -2328,10 +2332,10 @@
         <v>700247</v>
       </c>
       <c r="R16" t="n">
-        <v>6359114</v>
+        <v>6359105</v>
       </c>
       <c r="S16" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="T16" t="inlineStr">
         <is>
@@ -2392,10 +2396,10 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>126300258</v>
+        <v>126300256</v>
       </c>
       <c r="B17" t="n">
-        <v>98368</v>
+        <v>98372</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2420,11 +2424,7 @@
           <t>(L.) Buff. &amp; Fingerh.</t>
         </is>
       </c>
-      <c r="I17" t="inlineStr">
-        <is>
-          <t>7</t>
-        </is>
-      </c>
+      <c r="I17" t="inlineStr"/>
       <c r="P17" t="inlineStr">
         <is>
           <t>Gerum, Likmunds 1:2 (4), Gtl</t>
@@ -2434,10 +2434,10 @@
         <v>700247</v>
       </c>
       <c r="R17" t="n">
-        <v>6359105</v>
+        <v>6359114</v>
       </c>
       <c r="S17" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="T17" t="inlineStr">
         <is>
@@ -2501,7 +2501,7 @@
         <v>126300266</v>
       </c>
       <c r="B18" t="n">
-        <v>98263</v>
+        <v>98267</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2607,7 +2607,7 @@
         <v>126300263</v>
       </c>
       <c r="B19" t="n">
-        <v>98263</v>
+        <v>98267</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2713,7 +2713,7 @@
         <v>126300259</v>
       </c>
       <c r="B20" t="n">
-        <v>98263</v>
+        <v>98267</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2925,7 +2925,7 @@
         <v>126300257</v>
       </c>
       <c r="B22" t="n">
-        <v>98323</v>
+        <v>98327</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -3031,7 +3031,7 @@
         <v>126300265</v>
       </c>
       <c r="B23" t="n">
-        <v>98368</v>
+        <v>98372</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -3133,7 +3133,7 @@
         <v>126300267</v>
       </c>
       <c r="B24" t="n">
-        <v>98367</v>
+        <v>98371</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -3239,7 +3239,7 @@
         <v>126300270</v>
       </c>
       <c r="B25" t="n">
-        <v>98263</v>
+        <v>98267</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -3341,7 +3341,7 @@
         <v>126312506</v>
       </c>
       <c r="B26" t="n">
-        <v>109200</v>
+        <v>109213</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>

--- a/artfynd/A 14354-2024 artfynd.xlsx
+++ b/artfynd/A 14354-2024 artfynd.xlsx
@@ -1658,37 +1658,37 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>126300254</v>
+        <v>126300269</v>
       </c>
       <c r="B10" t="n">
-        <v>98385</v>
+        <v>43227</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E10" t="n">
-        <v>223621</v>
+        <v>101242</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Skogsnattviol</t>
+          <t>Dårgräsfjäril</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Platanthera bifolia subsp. latiflora</t>
+          <t>Lopinga achine</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(Drejer) Løjtnant</t>
+          <t>(Scopoli, 1763)</t>
         </is>
       </c>
       <c r="I10" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="P10" t="inlineStr">
@@ -1697,10 +1697,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>700231</v>
+        <v>700265</v>
       </c>
       <c r="R10" t="n">
-        <v>6359136</v>
+        <v>6359056</v>
       </c>
       <c r="S10" t="n">
         <v>4</v>
@@ -1764,37 +1764,37 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>126300269</v>
+        <v>126300254</v>
       </c>
       <c r="B11" t="n">
-        <v>43227</v>
+        <v>98388</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E11" t="n">
-        <v>101242</v>
+        <v>223621</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Dårgräsfjäril</t>
+          <t>Skogsnattviol</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Lopinga achine</t>
+          <t>Platanthera bifolia subsp. latiflora</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(Scopoli, 1763)</t>
+          <t>(Drejer) Løjtnant</t>
         </is>
       </c>
       <c r="I11" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>1</t>
         </is>
       </c>
       <c r="P11" t="inlineStr">
@@ -1803,10 +1803,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>700265</v>
+        <v>700231</v>
       </c>
       <c r="R11" t="n">
-        <v>6359056</v>
+        <v>6359136</v>
       </c>
       <c r="S11" t="n">
         <v>4</v>
@@ -2191,7 +2191,7 @@
         <v>126300268</v>
       </c>
       <c r="B15" t="n">
-        <v>98372</v>
+        <v>98375</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2293,7 +2293,7 @@
         <v>126300258</v>
       </c>
       <c r="B16" t="n">
-        <v>98372</v>
+        <v>98375</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2399,7 +2399,7 @@
         <v>126300256</v>
       </c>
       <c r="B17" t="n">
-        <v>98372</v>
+        <v>98375</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2501,7 +2501,7 @@
         <v>126300266</v>
       </c>
       <c r="B18" t="n">
-        <v>98267</v>
+        <v>98270</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2607,7 +2607,7 @@
         <v>126300263</v>
       </c>
       <c r="B19" t="n">
-        <v>98267</v>
+        <v>98270</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2713,7 +2713,7 @@
         <v>126300259</v>
       </c>
       <c r="B20" t="n">
-        <v>98267</v>
+        <v>98270</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2925,7 +2925,7 @@
         <v>126300257</v>
       </c>
       <c r="B22" t="n">
-        <v>98327</v>
+        <v>98330</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -3031,7 +3031,7 @@
         <v>126300265</v>
       </c>
       <c r="B23" t="n">
-        <v>98372</v>
+        <v>98375</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -3133,7 +3133,7 @@
         <v>126300267</v>
       </c>
       <c r="B24" t="n">
-        <v>98371</v>
+        <v>98374</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -3239,7 +3239,7 @@
         <v>126300270</v>
       </c>
       <c r="B25" t="n">
-        <v>98267</v>
+        <v>98270</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -3341,7 +3341,7 @@
         <v>126312506</v>
       </c>
       <c r="B26" t="n">
-        <v>109213</v>
+        <v>109216</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>

--- a/artfynd/A 14354-2024 artfynd.xlsx
+++ b/artfynd/A 14354-2024 artfynd.xlsx
@@ -2290,7 +2290,7 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>126300258</v>
+        <v>126300256</v>
       </c>
       <c r="B16" t="n">
         <v>98375</v>
@@ -2318,11 +2318,7 @@
           <t>(L.) Buff. &amp; Fingerh.</t>
         </is>
       </c>
-      <c r="I16" t="inlineStr">
-        <is>
-          <t>7</t>
-        </is>
-      </c>
+      <c r="I16" t="inlineStr"/>
       <c r="P16" t="inlineStr">
         <is>
           <t>Gerum, Likmunds 1:2 (4), Gtl</t>
@@ -2332,10 +2328,10 @@
         <v>700247</v>
       </c>
       <c r="R16" t="n">
-        <v>6359105</v>
+        <v>6359114</v>
       </c>
       <c r="S16" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="T16" t="inlineStr">
         <is>
@@ -2396,7 +2392,7 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>126300256</v>
+        <v>126300258</v>
       </c>
       <c r="B17" t="n">
         <v>98375</v>
@@ -2424,7 +2420,11 @@
           <t>(L.) Buff. &amp; Fingerh.</t>
         </is>
       </c>
-      <c r="I17" t="inlineStr"/>
+      <c r="I17" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
       <c r="P17" t="inlineStr">
         <is>
           <t>Gerum, Likmunds 1:2 (4), Gtl</t>
@@ -2434,10 +2434,10 @@
         <v>700247</v>
       </c>
       <c r="R17" t="n">
-        <v>6359114</v>
+        <v>6359105</v>
       </c>
       <c r="S17" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="T17" t="inlineStr">
         <is>

--- a/artfynd/A 14354-2024 artfynd.xlsx
+++ b/artfynd/A 14354-2024 artfynd.xlsx
@@ -1555,7 +1555,7 @@
         <v>126300260</v>
       </c>
       <c r="B9" t="n">
-        <v>43227</v>
+        <v>43228</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1661,7 +1661,7 @@
         <v>126300269</v>
       </c>
       <c r="B10" t="n">
-        <v>43227</v>
+        <v>43228</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1767,7 +1767,7 @@
         <v>126300254</v>
       </c>
       <c r="B11" t="n">
-        <v>98388</v>
+        <v>98397</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1873,7 +1873,7 @@
         <v>126300262</v>
       </c>
       <c r="B12" t="n">
-        <v>43227</v>
+        <v>43228</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1979,7 +1979,7 @@
         <v>126300255</v>
       </c>
       <c r="B13" t="n">
-        <v>43227</v>
+        <v>43228</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -2085,7 +2085,7 @@
         <v>126300264</v>
       </c>
       <c r="B14" t="n">
-        <v>43227</v>
+        <v>43228</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2191,7 +2191,7 @@
         <v>126300268</v>
       </c>
       <c r="B15" t="n">
-        <v>98375</v>
+        <v>98384</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2293,7 +2293,7 @@
         <v>126300256</v>
       </c>
       <c r="B16" t="n">
-        <v>98375</v>
+        <v>98384</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2395,7 +2395,7 @@
         <v>126300258</v>
       </c>
       <c r="B17" t="n">
-        <v>98375</v>
+        <v>98384</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2501,7 +2501,7 @@
         <v>126300266</v>
       </c>
       <c r="B18" t="n">
-        <v>98270</v>
+        <v>98279</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2607,7 +2607,7 @@
         <v>126300263</v>
       </c>
       <c r="B19" t="n">
-        <v>98270</v>
+        <v>98279</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2713,7 +2713,7 @@
         <v>126300259</v>
       </c>
       <c r="B20" t="n">
-        <v>98270</v>
+        <v>98279</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2819,7 +2819,7 @@
         <v>126300253</v>
       </c>
       <c r="B21" t="n">
-        <v>43227</v>
+        <v>43228</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -2925,7 +2925,7 @@
         <v>126300257</v>
       </c>
       <c r="B22" t="n">
-        <v>98330</v>
+        <v>98339</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -3031,7 +3031,7 @@
         <v>126300265</v>
       </c>
       <c r="B23" t="n">
-        <v>98375</v>
+        <v>98384</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -3133,7 +3133,7 @@
         <v>126300267</v>
       </c>
       <c r="B24" t="n">
-        <v>98374</v>
+        <v>98383</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -3239,7 +3239,7 @@
         <v>126300270</v>
       </c>
       <c r="B25" t="n">
-        <v>98270</v>
+        <v>98279</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -3341,7 +3341,7 @@
         <v>126312506</v>
       </c>
       <c r="B26" t="n">
-        <v>109216</v>
+        <v>109225</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>

--- a/artfynd/A 14354-2024 artfynd.xlsx
+++ b/artfynd/A 14354-2024 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY26"/>
+  <dimension ref="A1:AY40"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -3447,6 +3447,1474 @@
       </c>
       <c r="AY26" t="inlineStr"/>
     </row>
+    <row r="27">
+      <c r="A27" t="n">
+        <v>126514045</v>
+      </c>
+      <c r="B27" t="n">
+        <v>98384</v>
+      </c>
+      <c r="D27" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E27" t="n">
+        <v>219847</v>
+      </c>
+      <c r="F27" t="inlineStr">
+        <is>
+          <t>Tvåblad</t>
+        </is>
+      </c>
+      <c r="G27" t="inlineStr">
+        <is>
+          <t>Neottia ovata</t>
+        </is>
+      </c>
+      <c r="H27" t="inlineStr">
+        <is>
+          <t>(L.) Buff. &amp; Fingerh.</t>
+        </is>
+      </c>
+      <c r="I27" t="inlineStr"/>
+      <c r="P27" t="inlineStr">
+        <is>
+          <t>Gerum, Likmunds 1:2 (4), Gtl</t>
+        </is>
+      </c>
+      <c r="Q27" t="n">
+        <v>700215</v>
+      </c>
+      <c r="R27" t="n">
+        <v>6359155</v>
+      </c>
+      <c r="S27" t="n">
+        <v>8</v>
+      </c>
+      <c r="T27" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="U27" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="V27" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="W27" t="inlineStr">
+        <is>
+          <t>Gerum</t>
+        </is>
+      </c>
+      <c r="Y27" t="inlineStr">
+        <is>
+          <t>2025-06-29</t>
+        </is>
+      </c>
+      <c r="AA27" t="inlineStr">
+        <is>
+          <t>2025-06-29</t>
+        </is>
+      </c>
+      <c r="AD27" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE27" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG27" t="b">
+        <v>0</v>
+      </c>
+      <c r="AI27" t="inlineStr">
+        <is>
+          <t>Hästbetad blandskog</t>
+        </is>
+      </c>
+      <c r="AT27" t="inlineStr"/>
+      <c r="AW27" t="inlineStr">
+        <is>
+          <t>Gun Ingmansson</t>
+        </is>
+      </c>
+      <c r="AX27" t="inlineStr">
+        <is>
+          <t>Gun Ingmansson, Jörgen Petersson, Björn Larsson</t>
+        </is>
+      </c>
+      <c r="AY27" t="inlineStr"/>
+    </row>
+    <row r="28">
+      <c r="A28" t="n">
+        <v>126514039</v>
+      </c>
+      <c r="B28" t="n">
+        <v>43228</v>
+      </c>
+      <c r="D28" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E28" t="n">
+        <v>101242</v>
+      </c>
+      <c r="F28" t="inlineStr">
+        <is>
+          <t>Dårgräsfjäril</t>
+        </is>
+      </c>
+      <c r="G28" t="inlineStr">
+        <is>
+          <t>Lopinga achine</t>
+        </is>
+      </c>
+      <c r="H28" t="inlineStr">
+        <is>
+          <t>(Scopoli, 1763)</t>
+        </is>
+      </c>
+      <c r="I28" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="P28" t="inlineStr">
+        <is>
+          <t>Gerum, Likmunds 1:2 (4), Gtl</t>
+        </is>
+      </c>
+      <c r="Q28" t="n">
+        <v>700289</v>
+      </c>
+      <c r="R28" t="n">
+        <v>6359104</v>
+      </c>
+      <c r="S28" t="n">
+        <v>4</v>
+      </c>
+      <c r="T28" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="U28" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="V28" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="W28" t="inlineStr">
+        <is>
+          <t>Gerum</t>
+        </is>
+      </c>
+      <c r="Y28" t="inlineStr">
+        <is>
+          <t>2025-06-29</t>
+        </is>
+      </c>
+      <c r="AA28" t="inlineStr">
+        <is>
+          <t>2025-06-29</t>
+        </is>
+      </c>
+      <c r="AD28" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE28" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG28" t="b">
+        <v>0</v>
+      </c>
+      <c r="AI28" t="inlineStr">
+        <is>
+          <t>Hästbetad blandskog</t>
+        </is>
+      </c>
+      <c r="AT28" t="inlineStr"/>
+      <c r="AW28" t="inlineStr">
+        <is>
+          <t>Gun Ingmansson</t>
+        </is>
+      </c>
+      <c r="AX28" t="inlineStr">
+        <is>
+          <t>Gun Ingmansson, Jörgen Petersson, Björn Larsson</t>
+        </is>
+      </c>
+      <c r="AY28" t="inlineStr"/>
+    </row>
+    <row r="29">
+      <c r="A29" t="n">
+        <v>126514034</v>
+      </c>
+      <c r="B29" t="n">
+        <v>43228</v>
+      </c>
+      <c r="D29" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E29" t="n">
+        <v>101242</v>
+      </c>
+      <c r="F29" t="inlineStr">
+        <is>
+          <t>Dårgräsfjäril</t>
+        </is>
+      </c>
+      <c r="G29" t="inlineStr">
+        <is>
+          <t>Lopinga achine</t>
+        </is>
+      </c>
+      <c r="H29" t="inlineStr">
+        <is>
+          <t>(Scopoli, 1763)</t>
+        </is>
+      </c>
+      <c r="I29" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="P29" t="inlineStr">
+        <is>
+          <t>Gerum, Likmunds 1:2 (4), Gtl</t>
+        </is>
+      </c>
+      <c r="Q29" t="n">
+        <v>700296</v>
+      </c>
+      <c r="R29" t="n">
+        <v>6359059</v>
+      </c>
+      <c r="S29" t="n">
+        <v>4</v>
+      </c>
+      <c r="T29" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="U29" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="V29" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="W29" t="inlineStr">
+        <is>
+          <t>Gerum</t>
+        </is>
+      </c>
+      <c r="Y29" t="inlineStr">
+        <is>
+          <t>2025-06-29</t>
+        </is>
+      </c>
+      <c r="AA29" t="inlineStr">
+        <is>
+          <t>2025-06-29</t>
+        </is>
+      </c>
+      <c r="AD29" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE29" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG29" t="b">
+        <v>0</v>
+      </c>
+      <c r="AI29" t="inlineStr">
+        <is>
+          <t>Hästbetad blandskog</t>
+        </is>
+      </c>
+      <c r="AT29" t="inlineStr"/>
+      <c r="AW29" t="inlineStr">
+        <is>
+          <t>Gun Ingmansson</t>
+        </is>
+      </c>
+      <c r="AX29" t="inlineStr">
+        <is>
+          <t>Gun Ingmansson, Jörgen Petersson, Björn Larsson</t>
+        </is>
+      </c>
+      <c r="AY29" t="inlineStr"/>
+    </row>
+    <row r="30">
+      <c r="A30" t="n">
+        <v>126514036</v>
+      </c>
+      <c r="B30" t="n">
+        <v>43228</v>
+      </c>
+      <c r="D30" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E30" t="n">
+        <v>101242</v>
+      </c>
+      <c r="F30" t="inlineStr">
+        <is>
+          <t>Dårgräsfjäril</t>
+        </is>
+      </c>
+      <c r="G30" t="inlineStr">
+        <is>
+          <t>Lopinga achine</t>
+        </is>
+      </c>
+      <c r="H30" t="inlineStr">
+        <is>
+          <t>(Scopoli, 1763)</t>
+        </is>
+      </c>
+      <c r="I30" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="P30" t="inlineStr">
+        <is>
+          <t>Gerum, Likmunds 1:2 (4), Gtl</t>
+        </is>
+      </c>
+      <c r="Q30" t="n">
+        <v>700296</v>
+      </c>
+      <c r="R30" t="n">
+        <v>6359084</v>
+      </c>
+      <c r="S30" t="n">
+        <v>4</v>
+      </c>
+      <c r="T30" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="U30" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="V30" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="W30" t="inlineStr">
+        <is>
+          <t>Gerum</t>
+        </is>
+      </c>
+      <c r="Y30" t="inlineStr">
+        <is>
+          <t>2025-06-29</t>
+        </is>
+      </c>
+      <c r="AA30" t="inlineStr">
+        <is>
+          <t>2025-06-29</t>
+        </is>
+      </c>
+      <c r="AD30" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE30" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG30" t="b">
+        <v>0</v>
+      </c>
+      <c r="AI30" t="inlineStr">
+        <is>
+          <t>Hästbetad blandskog</t>
+        </is>
+      </c>
+      <c r="AT30" t="inlineStr"/>
+      <c r="AW30" t="inlineStr">
+        <is>
+          <t>Gun Ingmansson</t>
+        </is>
+      </c>
+      <c r="AX30" t="inlineStr">
+        <is>
+          <t>Gun Ingmansson, Jörgen Petersson, Björn Larsson</t>
+        </is>
+      </c>
+      <c r="AY30" t="inlineStr"/>
+    </row>
+    <row r="31">
+      <c r="A31" t="n">
+        <v>126514044</v>
+      </c>
+      <c r="B31" t="n">
+        <v>98339</v>
+      </c>
+      <c r="D31" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E31" t="n">
+        <v>219798</v>
+      </c>
+      <c r="F31" t="inlineStr">
+        <is>
+          <t>Skogsknipprot</t>
+        </is>
+      </c>
+      <c r="G31" t="inlineStr">
+        <is>
+          <t>Epipactis helleborine</t>
+        </is>
+      </c>
+      <c r="H31" t="inlineStr">
+        <is>
+          <t>(L.) Crantz</t>
+        </is>
+      </c>
+      <c r="I31" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="P31" t="inlineStr">
+        <is>
+          <t>Gerum, Likmunds 1:2 (4), Gtl</t>
+        </is>
+      </c>
+      <c r="Q31" t="n">
+        <v>700215</v>
+      </c>
+      <c r="R31" t="n">
+        <v>6359155</v>
+      </c>
+      <c r="S31" t="n">
+        <v>8</v>
+      </c>
+      <c r="T31" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="U31" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="V31" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="W31" t="inlineStr">
+        <is>
+          <t>Gerum</t>
+        </is>
+      </c>
+      <c r="Y31" t="inlineStr">
+        <is>
+          <t>2025-06-29</t>
+        </is>
+      </c>
+      <c r="AA31" t="inlineStr">
+        <is>
+          <t>2025-06-29</t>
+        </is>
+      </c>
+      <c r="AD31" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE31" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG31" t="b">
+        <v>0</v>
+      </c>
+      <c r="AI31" t="inlineStr">
+        <is>
+          <t>Hästbetad blandskog</t>
+        </is>
+      </c>
+      <c r="AT31" t="inlineStr"/>
+      <c r="AW31" t="inlineStr">
+        <is>
+          <t>Gun Ingmansson</t>
+        </is>
+      </c>
+      <c r="AX31" t="inlineStr">
+        <is>
+          <t>Gun Ingmansson, Jörgen Petersson, Björn Larsson</t>
+        </is>
+      </c>
+      <c r="AY31" t="inlineStr"/>
+    </row>
+    <row r="32">
+      <c r="A32" t="n">
+        <v>126514049</v>
+      </c>
+      <c r="B32" t="n">
+        <v>98384</v>
+      </c>
+      <c r="D32" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E32" t="n">
+        <v>219847</v>
+      </c>
+      <c r="F32" t="inlineStr">
+        <is>
+          <t>Tvåblad</t>
+        </is>
+      </c>
+      <c r="G32" t="inlineStr">
+        <is>
+          <t>Neottia ovata</t>
+        </is>
+      </c>
+      <c r="H32" t="inlineStr">
+        <is>
+          <t>(L.) Buff. &amp; Fingerh.</t>
+        </is>
+      </c>
+      <c r="I32" t="inlineStr"/>
+      <c r="P32" t="inlineStr">
+        <is>
+          <t>Gerum, Likmunds 1:2 (4), Gtl</t>
+        </is>
+      </c>
+      <c r="Q32" t="n">
+        <v>700235</v>
+      </c>
+      <c r="R32" t="n">
+        <v>6359147</v>
+      </c>
+      <c r="S32" t="n">
+        <v>10</v>
+      </c>
+      <c r="T32" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="U32" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="V32" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="W32" t="inlineStr">
+        <is>
+          <t>Gerum</t>
+        </is>
+      </c>
+      <c r="Y32" t="inlineStr">
+        <is>
+          <t>2025-06-29</t>
+        </is>
+      </c>
+      <c r="AA32" t="inlineStr">
+        <is>
+          <t>2025-06-29</t>
+        </is>
+      </c>
+      <c r="AD32" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE32" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG32" t="b">
+        <v>0</v>
+      </c>
+      <c r="AI32" t="inlineStr">
+        <is>
+          <t>Hästbetad blandskog</t>
+        </is>
+      </c>
+      <c r="AT32" t="inlineStr"/>
+      <c r="AW32" t="inlineStr">
+        <is>
+          <t>Gun Ingmansson</t>
+        </is>
+      </c>
+      <c r="AX32" t="inlineStr">
+        <is>
+          <t>Gun Ingmansson, Jörgen Petersson, Björn Larsson</t>
+        </is>
+      </c>
+      <c r="AY32" t="inlineStr"/>
+    </row>
+    <row r="33">
+      <c r="A33" t="n">
+        <v>126514041</v>
+      </c>
+      <c r="B33" t="n">
+        <v>95964</v>
+      </c>
+      <c r="D33" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E33" t="n">
+        <v>2180</v>
+      </c>
+      <c r="F33" t="inlineStr">
+        <is>
+          <t>Blåmossa</t>
+        </is>
+      </c>
+      <c r="G33" t="inlineStr">
+        <is>
+          <t>Leucobryum glaucum</t>
+        </is>
+      </c>
+      <c r="H33" t="inlineStr">
+        <is>
+          <t>(Hedw.) Ångstr.</t>
+        </is>
+      </c>
+      <c r="I33" t="inlineStr"/>
+      <c r="P33" t="inlineStr">
+        <is>
+          <t>Gerum, Likmunds 1:2 (4), Gtl</t>
+        </is>
+      </c>
+      <c r="Q33" t="n">
+        <v>700275</v>
+      </c>
+      <c r="R33" t="n">
+        <v>6359146</v>
+      </c>
+      <c r="S33" t="n">
+        <v>10</v>
+      </c>
+      <c r="T33" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="U33" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="V33" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="W33" t="inlineStr">
+        <is>
+          <t>Gerum</t>
+        </is>
+      </c>
+      <c r="Y33" t="inlineStr">
+        <is>
+          <t>2025-06-29</t>
+        </is>
+      </c>
+      <c r="AA33" t="inlineStr">
+        <is>
+          <t>2025-06-29</t>
+        </is>
+      </c>
+      <c r="AD33" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE33" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG33" t="b">
+        <v>0</v>
+      </c>
+      <c r="AI33" t="inlineStr">
+        <is>
+          <t>Hästbetad blandskog</t>
+        </is>
+      </c>
+      <c r="AT33" t="inlineStr"/>
+      <c r="AW33" t="inlineStr">
+        <is>
+          <t>Gun Ingmansson</t>
+        </is>
+      </c>
+      <c r="AX33" t="inlineStr">
+        <is>
+          <t>Gun Ingmansson, Jörgen Petersson, Björn Larsson</t>
+        </is>
+      </c>
+      <c r="AY33" t="inlineStr"/>
+    </row>
+    <row r="34">
+      <c r="A34" t="n">
+        <v>126514038</v>
+      </c>
+      <c r="B34" t="n">
+        <v>43228</v>
+      </c>
+      <c r="D34" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E34" t="n">
+        <v>101242</v>
+      </c>
+      <c r="F34" t="inlineStr">
+        <is>
+          <t>Dårgräsfjäril</t>
+        </is>
+      </c>
+      <c r="G34" t="inlineStr">
+        <is>
+          <t>Lopinga achine</t>
+        </is>
+      </c>
+      <c r="H34" t="inlineStr">
+        <is>
+          <t>(Scopoli, 1763)</t>
+        </is>
+      </c>
+      <c r="I34" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="P34" t="inlineStr">
+        <is>
+          <t>Gerum, Likmunds 1:2 (4), Gtl</t>
+        </is>
+      </c>
+      <c r="Q34" t="n">
+        <v>700305</v>
+      </c>
+      <c r="R34" t="n">
+        <v>6359105</v>
+      </c>
+      <c r="S34" t="n">
+        <v>4</v>
+      </c>
+      <c r="T34" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="U34" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="V34" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="W34" t="inlineStr">
+        <is>
+          <t>Gerum</t>
+        </is>
+      </c>
+      <c r="Y34" t="inlineStr">
+        <is>
+          <t>2025-06-29</t>
+        </is>
+      </c>
+      <c r="AA34" t="inlineStr">
+        <is>
+          <t>2025-06-29</t>
+        </is>
+      </c>
+      <c r="AD34" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE34" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG34" t="b">
+        <v>0</v>
+      </c>
+      <c r="AI34" t="inlineStr">
+        <is>
+          <t>Hästbetad blandskog</t>
+        </is>
+      </c>
+      <c r="AT34" t="inlineStr"/>
+      <c r="AW34" t="inlineStr">
+        <is>
+          <t>Gun Ingmansson</t>
+        </is>
+      </c>
+      <c r="AX34" t="inlineStr">
+        <is>
+          <t>Gun Ingmansson, Jörgen Petersson, Björn Larsson</t>
+        </is>
+      </c>
+      <c r="AY34" t="inlineStr"/>
+    </row>
+    <row r="35">
+      <c r="A35" t="n">
+        <v>126514043</v>
+      </c>
+      <c r="B35" t="n">
+        <v>43228</v>
+      </c>
+      <c r="D35" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E35" t="n">
+        <v>101242</v>
+      </c>
+      <c r="F35" t="inlineStr">
+        <is>
+          <t>Dårgräsfjäril</t>
+        </is>
+      </c>
+      <c r="G35" t="inlineStr">
+        <is>
+          <t>Lopinga achine</t>
+        </is>
+      </c>
+      <c r="H35" t="inlineStr">
+        <is>
+          <t>(Scopoli, 1763)</t>
+        </is>
+      </c>
+      <c r="I35" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="P35" t="inlineStr">
+        <is>
+          <t>Gerum, Likmunds 1:2 (4), Gtl</t>
+        </is>
+      </c>
+      <c r="Q35" t="n">
+        <v>700228</v>
+      </c>
+      <c r="R35" t="n">
+        <v>6359179</v>
+      </c>
+      <c r="S35" t="n">
+        <v>4</v>
+      </c>
+      <c r="T35" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="U35" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="V35" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="W35" t="inlineStr">
+        <is>
+          <t>Gerum</t>
+        </is>
+      </c>
+      <c r="Y35" t="inlineStr">
+        <is>
+          <t>2025-06-29</t>
+        </is>
+      </c>
+      <c r="AA35" t="inlineStr">
+        <is>
+          <t>2025-06-29</t>
+        </is>
+      </c>
+      <c r="AD35" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE35" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG35" t="b">
+        <v>0</v>
+      </c>
+      <c r="AI35" t="inlineStr">
+        <is>
+          <t>Hästbetad blandskog</t>
+        </is>
+      </c>
+      <c r="AT35" t="inlineStr"/>
+      <c r="AW35" t="inlineStr">
+        <is>
+          <t>Gun Ingmansson</t>
+        </is>
+      </c>
+      <c r="AX35" t="inlineStr">
+        <is>
+          <t>Gun Ingmansson, Jörgen Petersson, Björn Larsson</t>
+        </is>
+      </c>
+      <c r="AY35" t="inlineStr"/>
+    </row>
+    <row r="36">
+      <c r="A36" t="n">
+        <v>126514046</v>
+      </c>
+      <c r="B36" t="n">
+        <v>43228</v>
+      </c>
+      <c r="D36" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E36" t="n">
+        <v>101242</v>
+      </c>
+      <c r="F36" t="inlineStr">
+        <is>
+          <t>Dårgräsfjäril</t>
+        </is>
+      </c>
+      <c r="G36" t="inlineStr">
+        <is>
+          <t>Lopinga achine</t>
+        </is>
+      </c>
+      <c r="H36" t="inlineStr">
+        <is>
+          <t>(Scopoli, 1763)</t>
+        </is>
+      </c>
+      <c r="I36" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="P36" t="inlineStr">
+        <is>
+          <t>Gerum, Likmunds 1:2 (4), Gtl</t>
+        </is>
+      </c>
+      <c r="Q36" t="n">
+        <v>700215</v>
+      </c>
+      <c r="R36" t="n">
+        <v>6359155</v>
+      </c>
+      <c r="S36" t="n">
+        <v>8</v>
+      </c>
+      <c r="T36" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="U36" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="V36" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="W36" t="inlineStr">
+        <is>
+          <t>Gerum</t>
+        </is>
+      </c>
+      <c r="Y36" t="inlineStr">
+        <is>
+          <t>2025-06-29</t>
+        </is>
+      </c>
+      <c r="AA36" t="inlineStr">
+        <is>
+          <t>2025-06-29</t>
+        </is>
+      </c>
+      <c r="AD36" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE36" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG36" t="b">
+        <v>0</v>
+      </c>
+      <c r="AI36" t="inlineStr">
+        <is>
+          <t>Hästbetad blandskog</t>
+        </is>
+      </c>
+      <c r="AT36" t="inlineStr"/>
+      <c r="AW36" t="inlineStr">
+        <is>
+          <t>Gun Ingmansson</t>
+        </is>
+      </c>
+      <c r="AX36" t="inlineStr">
+        <is>
+          <t>Gun Ingmansson, Jörgen Petersson, Björn Larsson</t>
+        </is>
+      </c>
+      <c r="AY36" t="inlineStr"/>
+    </row>
+    <row r="37">
+      <c r="A37" t="n">
+        <v>126514042</v>
+      </c>
+      <c r="B37" t="n">
+        <v>43228</v>
+      </c>
+      <c r="D37" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E37" t="n">
+        <v>101242</v>
+      </c>
+      <c r="F37" t="inlineStr">
+        <is>
+          <t>Dårgräsfjäril</t>
+        </is>
+      </c>
+      <c r="G37" t="inlineStr">
+        <is>
+          <t>Lopinga achine</t>
+        </is>
+      </c>
+      <c r="H37" t="inlineStr">
+        <is>
+          <t>(Scopoli, 1763)</t>
+        </is>
+      </c>
+      <c r="I37" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="P37" t="inlineStr">
+        <is>
+          <t>Gerum, Likmunds 1:2 (4), Gtl</t>
+        </is>
+      </c>
+      <c r="Q37" t="n">
+        <v>700275</v>
+      </c>
+      <c r="R37" t="n">
+        <v>6359146</v>
+      </c>
+      <c r="S37" t="n">
+        <v>10</v>
+      </c>
+      <c r="T37" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="U37" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="V37" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="W37" t="inlineStr">
+        <is>
+          <t>Gerum</t>
+        </is>
+      </c>
+      <c r="Y37" t="inlineStr">
+        <is>
+          <t>2025-06-29</t>
+        </is>
+      </c>
+      <c r="AA37" t="inlineStr">
+        <is>
+          <t>2025-06-29</t>
+        </is>
+      </c>
+      <c r="AD37" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE37" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG37" t="b">
+        <v>0</v>
+      </c>
+      <c r="AI37" t="inlineStr">
+        <is>
+          <t>Hästbetad blandskog</t>
+        </is>
+      </c>
+      <c r="AT37" t="inlineStr"/>
+      <c r="AW37" t="inlineStr">
+        <is>
+          <t>Gun Ingmansson</t>
+        </is>
+      </c>
+      <c r="AX37" t="inlineStr">
+        <is>
+          <t>Gun Ingmansson, Jörgen Petersson, Björn Larsson</t>
+        </is>
+      </c>
+      <c r="AY37" t="inlineStr"/>
+    </row>
+    <row r="38">
+      <c r="A38" t="n">
+        <v>126514040</v>
+      </c>
+      <c r="B38" t="n">
+        <v>43228</v>
+      </c>
+      <c r="D38" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E38" t="n">
+        <v>101242</v>
+      </c>
+      <c r="F38" t="inlineStr">
+        <is>
+          <t>Dårgräsfjäril</t>
+        </is>
+      </c>
+      <c r="G38" t="inlineStr">
+        <is>
+          <t>Lopinga achine</t>
+        </is>
+      </c>
+      <c r="H38" t="inlineStr">
+        <is>
+          <t>(Scopoli, 1763)</t>
+        </is>
+      </c>
+      <c r="I38" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="P38" t="inlineStr">
+        <is>
+          <t>Gerum, Likmunds 1:2 (4), Gtl</t>
+        </is>
+      </c>
+      <c r="Q38" t="n">
+        <v>700278</v>
+      </c>
+      <c r="R38" t="n">
+        <v>6359138</v>
+      </c>
+      <c r="S38" t="n">
+        <v>4</v>
+      </c>
+      <c r="T38" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="U38" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="V38" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="W38" t="inlineStr">
+        <is>
+          <t>Gerum</t>
+        </is>
+      </c>
+      <c r="Y38" t="inlineStr">
+        <is>
+          <t>2025-06-29</t>
+        </is>
+      </c>
+      <c r="AA38" t="inlineStr">
+        <is>
+          <t>2025-06-29</t>
+        </is>
+      </c>
+      <c r="AD38" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE38" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG38" t="b">
+        <v>0</v>
+      </c>
+      <c r="AI38" t="inlineStr">
+        <is>
+          <t>Hästbetad blandskog</t>
+        </is>
+      </c>
+      <c r="AT38" t="inlineStr"/>
+      <c r="AW38" t="inlineStr">
+        <is>
+          <t>Gun Ingmansson</t>
+        </is>
+      </c>
+      <c r="AX38" t="inlineStr">
+        <is>
+          <t>Gun Ingmansson, Jörgen Petersson, Björn Larsson</t>
+        </is>
+      </c>
+      <c r="AY38" t="inlineStr"/>
+    </row>
+    <row r="39">
+      <c r="A39" t="n">
+        <v>126514047</v>
+      </c>
+      <c r="B39" t="n">
+        <v>98279</v>
+      </c>
+      <c r="D39" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E39" t="n">
+        <v>223591</v>
+      </c>
+      <c r="F39" t="inlineStr">
+        <is>
+          <t>Skogsnycklar</t>
+        </is>
+      </c>
+      <c r="G39" t="inlineStr">
+        <is>
+          <t>Dactylorhiza maculata subsp. fuchsii</t>
+        </is>
+      </c>
+      <c r="H39" t="inlineStr">
+        <is>
+          <t>(Druce) Hyl.</t>
+        </is>
+      </c>
+      <c r="I39" t="inlineStr"/>
+      <c r="P39" t="inlineStr">
+        <is>
+          <t>Gerum, Likmunds 1:2 (4), Gtl</t>
+        </is>
+      </c>
+      <c r="Q39" t="n">
+        <v>700215</v>
+      </c>
+      <c r="R39" t="n">
+        <v>6359155</v>
+      </c>
+      <c r="S39" t="n">
+        <v>8</v>
+      </c>
+      <c r="T39" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="U39" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="V39" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="W39" t="inlineStr">
+        <is>
+          <t>Gerum</t>
+        </is>
+      </c>
+      <c r="Y39" t="inlineStr">
+        <is>
+          <t>2025-06-29</t>
+        </is>
+      </c>
+      <c r="AA39" t="inlineStr">
+        <is>
+          <t>2025-06-29</t>
+        </is>
+      </c>
+      <c r="AD39" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE39" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG39" t="b">
+        <v>0</v>
+      </c>
+      <c r="AI39" t="inlineStr">
+        <is>
+          <t>Hästbetad blandskog</t>
+        </is>
+      </c>
+      <c r="AT39" t="inlineStr"/>
+      <c r="AW39" t="inlineStr">
+        <is>
+          <t>Gun Ingmansson</t>
+        </is>
+      </c>
+      <c r="AX39" t="inlineStr">
+        <is>
+          <t>Gun Ingmansson, Jörgen Petersson, Björn Larsson</t>
+        </is>
+      </c>
+      <c r="AY39" t="inlineStr"/>
+    </row>
+    <row r="40">
+      <c r="A40" t="n">
+        <v>126514037</v>
+      </c>
+      <c r="B40" t="n">
+        <v>43228</v>
+      </c>
+      <c r="D40" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E40" t="n">
+        <v>101242</v>
+      </c>
+      <c r="F40" t="inlineStr">
+        <is>
+          <t>Dårgräsfjäril</t>
+        </is>
+      </c>
+      <c r="G40" t="inlineStr">
+        <is>
+          <t>Lopinga achine</t>
+        </is>
+      </c>
+      <c r="H40" t="inlineStr">
+        <is>
+          <t>(Scopoli, 1763)</t>
+        </is>
+      </c>
+      <c r="I40" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="P40" t="inlineStr">
+        <is>
+          <t>Gerum, Likmunds 1:2 (4), Gtl</t>
+        </is>
+      </c>
+      <c r="Q40" t="n">
+        <v>700290</v>
+      </c>
+      <c r="R40" t="n">
+        <v>6359078</v>
+      </c>
+      <c r="S40" t="n">
+        <v>5</v>
+      </c>
+      <c r="T40" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="U40" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="V40" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="W40" t="inlineStr">
+        <is>
+          <t>Gerum</t>
+        </is>
+      </c>
+      <c r="Y40" t="inlineStr">
+        <is>
+          <t>2025-06-29</t>
+        </is>
+      </c>
+      <c r="AA40" t="inlineStr">
+        <is>
+          <t>2025-06-29</t>
+        </is>
+      </c>
+      <c r="AD40" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE40" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG40" t="b">
+        <v>0</v>
+      </c>
+      <c r="AI40" t="inlineStr">
+        <is>
+          <t>Hästbetad blandskog</t>
+        </is>
+      </c>
+      <c r="AT40" t="inlineStr"/>
+      <c r="AW40" t="inlineStr">
+        <is>
+          <t>Gun Ingmansson</t>
+        </is>
+      </c>
+      <c r="AX40" t="inlineStr">
+        <is>
+          <t>Gun Ingmansson, Jörgen Petersson, Björn Larsson</t>
+        </is>
+      </c>
+      <c r="AY40" t="inlineStr"/>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/artfynd/A 14354-2024 artfynd.xlsx
+++ b/artfynd/A 14354-2024 artfynd.xlsx
@@ -3449,48 +3449,52 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>126514045</v>
+        <v>126514039</v>
       </c>
       <c r="B27" t="n">
-        <v>98384</v>
+        <v>43228</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E27" t="n">
-        <v>219847</v>
+        <v>101242</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Tvåblad</t>
+          <t>Dårgräsfjäril</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>Neottia ovata</t>
+          <t>Lopinga achine</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>(L.) Buff. &amp; Fingerh.</t>
-        </is>
-      </c>
-      <c r="I27" t="inlineStr"/>
+          <t>(Scopoli, 1763)</t>
+        </is>
+      </c>
+      <c r="I27" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="P27" t="inlineStr">
         <is>
           <t>Gerum, Likmunds 1:2 (4), Gtl</t>
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>700215</v>
+        <v>700289</v>
       </c>
       <c r="R27" t="n">
-        <v>6359155</v>
+        <v>6359104</v>
       </c>
       <c r="S27" t="n">
-        <v>8</v>
+        <v>4</v>
       </c>
       <c r="T27" t="inlineStr">
         <is>
@@ -3551,52 +3555,48 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>126514039</v>
+        <v>126514045</v>
       </c>
       <c r="B28" t="n">
-        <v>43228</v>
+        <v>98384</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E28" t="n">
-        <v>101242</v>
+        <v>219847</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Dårgräsfjäril</t>
+          <t>Tvåblad</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>Lopinga achine</t>
+          <t>Neottia ovata</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>(Scopoli, 1763)</t>
-        </is>
-      </c>
-      <c r="I28" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+          <t>(L.) Buff. &amp; Fingerh.</t>
+        </is>
+      </c>
+      <c r="I28" t="inlineStr"/>
       <c r="P28" t="inlineStr">
         <is>
           <t>Gerum, Likmunds 1:2 (4), Gtl</t>
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>700289</v>
+        <v>700215</v>
       </c>
       <c r="R28" t="n">
-        <v>6359104</v>
+        <v>6359155</v>
       </c>
       <c r="S28" t="n">
-        <v>4</v>
+        <v>8</v>
       </c>
       <c r="T28" t="inlineStr">
         <is>
@@ -3756,7 +3756,7 @@
       </c>
       <c r="AX29" t="inlineStr">
         <is>
-          <t>Gun Ingmansson, Jörgen Petersson, Björn Larsson</t>
+          <t>Jörgen Petersson, Gun Ingmansson, Björn Larsson</t>
         </is>
       </c>
       <c r="AY29" t="inlineStr"/>
@@ -3862,7 +3862,7 @@
       </c>
       <c r="AX30" t="inlineStr">
         <is>
-          <t>Gun Ingmansson, Jörgen Petersson, Björn Larsson</t>
+          <t>Jörgen Petersson, Gun Ingmansson, Björn Larsson</t>
         </is>
       </c>
       <c r="AY30" t="inlineStr"/>
@@ -3975,10 +3975,10 @@
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>126514049</v>
+        <v>126514041</v>
       </c>
       <c r="B32" t="n">
-        <v>98384</v>
+        <v>95964</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
@@ -3986,21 +3986,21 @@
         </is>
       </c>
       <c r="E32" t="n">
-        <v>219847</v>
+        <v>2180</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Tvåblad</t>
+          <t>Blåmossa</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>Neottia ovata</t>
+          <t>Leucobryum glaucum</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>(L.) Buff. &amp; Fingerh.</t>
+          <t>(Hedw.) Ångstr.</t>
         </is>
       </c>
       <c r="I32" t="inlineStr"/>
@@ -4010,10 +4010,10 @@
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>700235</v>
+        <v>700275</v>
       </c>
       <c r="R32" t="n">
-        <v>6359147</v>
+        <v>6359146</v>
       </c>
       <c r="S32" t="n">
         <v>10</v>
@@ -4077,10 +4077,10 @@
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>126514041</v>
+        <v>126514049</v>
       </c>
       <c r="B33" t="n">
-        <v>95964</v>
+        <v>98384</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
@@ -4088,21 +4088,21 @@
         </is>
       </c>
       <c r="E33" t="n">
-        <v>2180</v>
+        <v>219847</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Blåmossa</t>
+          <t>Tvåblad</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>Leucobryum glaucum</t>
+          <t>Neottia ovata</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>(Hedw.) Ångstr.</t>
+          <t>(L.) Buff. &amp; Fingerh.</t>
         </is>
       </c>
       <c r="I33" t="inlineStr"/>
@@ -4112,10 +4112,10 @@
         </is>
       </c>
       <c r="Q33" t="n">
-        <v>700275</v>
+        <v>700235</v>
       </c>
       <c r="R33" t="n">
-        <v>6359146</v>
+        <v>6359147</v>
       </c>
       <c r="S33" t="n">
         <v>10</v>
@@ -4179,7 +4179,7 @@
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>126514038</v>
+        <v>126514043</v>
       </c>
       <c r="B34" t="n">
         <v>43228</v>
@@ -4218,10 +4218,10 @@
         </is>
       </c>
       <c r="Q34" t="n">
-        <v>700305</v>
+        <v>700228</v>
       </c>
       <c r="R34" t="n">
-        <v>6359105</v>
+        <v>6359179</v>
       </c>
       <c r="S34" t="n">
         <v>4</v>
@@ -4285,7 +4285,7 @@
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>126514043</v>
+        <v>126514046</v>
       </c>
       <c r="B35" t="n">
         <v>43228</v>
@@ -4324,13 +4324,13 @@
         </is>
       </c>
       <c r="Q35" t="n">
-        <v>700228</v>
+        <v>700215</v>
       </c>
       <c r="R35" t="n">
-        <v>6359179</v>
+        <v>6359155</v>
       </c>
       <c r="S35" t="n">
-        <v>4</v>
+        <v>8</v>
       </c>
       <c r="T35" t="inlineStr">
         <is>
@@ -4391,7 +4391,7 @@
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>126514046</v>
+        <v>126514038</v>
       </c>
       <c r="B36" t="n">
         <v>43228</v>
@@ -4430,13 +4430,13 @@
         </is>
       </c>
       <c r="Q36" t="n">
-        <v>700215</v>
+        <v>700305</v>
       </c>
       <c r="R36" t="n">
-        <v>6359155</v>
+        <v>6359105</v>
       </c>
       <c r="S36" t="n">
-        <v>8</v>
+        <v>4</v>
       </c>
       <c r="T36" t="inlineStr">
         <is>
@@ -4490,14 +4490,14 @@
       </c>
       <c r="AX36" t="inlineStr">
         <is>
-          <t>Gun Ingmansson, Jörgen Petersson, Björn Larsson</t>
+          <t>Jörgen Petersson, Gun Ingmansson, Björn Larsson</t>
         </is>
       </c>
       <c r="AY36" t="inlineStr"/>
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>126514042</v>
+        <v>126514040</v>
       </c>
       <c r="B37" t="n">
         <v>43228</v>
@@ -4536,13 +4536,13 @@
         </is>
       </c>
       <c r="Q37" t="n">
-        <v>700275</v>
+        <v>700278</v>
       </c>
       <c r="R37" t="n">
-        <v>6359146</v>
+        <v>6359138</v>
       </c>
       <c r="S37" t="n">
-        <v>10</v>
+        <v>4</v>
       </c>
       <c r="T37" t="inlineStr">
         <is>
@@ -4603,7 +4603,7 @@
     </row>
     <row r="38">
       <c r="A38" t="n">
-        <v>126514040</v>
+        <v>126514042</v>
       </c>
       <c r="B38" t="n">
         <v>43228</v>
@@ -4642,13 +4642,13 @@
         </is>
       </c>
       <c r="Q38" t="n">
-        <v>700278</v>
+        <v>700275</v>
       </c>
       <c r="R38" t="n">
-        <v>6359138</v>
+        <v>6359146</v>
       </c>
       <c r="S38" t="n">
-        <v>4</v>
+        <v>10</v>
       </c>
       <c r="T38" t="inlineStr">
         <is>
@@ -4910,7 +4910,7 @@
       </c>
       <c r="AX40" t="inlineStr">
         <is>
-          <t>Gun Ingmansson, Jörgen Petersson, Björn Larsson</t>
+          <t>Jörgen Petersson, Gun Ingmansson, Björn Larsson</t>
         </is>
       </c>
       <c r="AY40" t="inlineStr"/>

--- a/artfynd/A 14354-2024 artfynd.xlsx
+++ b/artfynd/A 14354-2024 artfynd.xlsx
@@ -1658,37 +1658,37 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>126300269</v>
+        <v>126300254</v>
       </c>
       <c r="B10" t="n">
-        <v>43228</v>
+        <v>98397</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E10" t="n">
-        <v>101242</v>
+        <v>223621</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Dårgräsfjäril</t>
+          <t>Skogsnattviol</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Lopinga achine</t>
+          <t>Platanthera bifolia subsp. latiflora</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(Scopoli, 1763)</t>
+          <t>(Drejer) Løjtnant</t>
         </is>
       </c>
       <c r="I10" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>1</t>
         </is>
       </c>
       <c r="P10" t="inlineStr">
@@ -1697,10 +1697,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>700265</v>
+        <v>700231</v>
       </c>
       <c r="R10" t="n">
-        <v>6359056</v>
+        <v>6359136</v>
       </c>
       <c r="S10" t="n">
         <v>4</v>
@@ -1764,37 +1764,37 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>126300254</v>
+        <v>126300269</v>
       </c>
       <c r="B11" t="n">
-        <v>98397</v>
+        <v>43228</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E11" t="n">
-        <v>223621</v>
+        <v>101242</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Skogsnattviol</t>
+          <t>Dårgräsfjäril</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Platanthera bifolia subsp. latiflora</t>
+          <t>Lopinga achine</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(Drejer) Løjtnant</t>
+          <t>(Scopoli, 1763)</t>
         </is>
       </c>
       <c r="I11" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="P11" t="inlineStr">
@@ -1803,10 +1803,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>700231</v>
+        <v>700265</v>
       </c>
       <c r="R11" t="n">
-        <v>6359136</v>
+        <v>6359056</v>
       </c>
       <c r="S11" t="n">
         <v>4</v>
@@ -4179,7 +4179,7 @@
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>126514043</v>
+        <v>126514038</v>
       </c>
       <c r="B34" t="n">
         <v>43228</v>
@@ -4218,10 +4218,10 @@
         </is>
       </c>
       <c r="Q34" t="n">
-        <v>700228</v>
+        <v>700305</v>
       </c>
       <c r="R34" t="n">
-        <v>6359179</v>
+        <v>6359105</v>
       </c>
       <c r="S34" t="n">
         <v>4</v>
@@ -4278,14 +4278,14 @@
       </c>
       <c r="AX34" t="inlineStr">
         <is>
-          <t>Gun Ingmansson, Jörgen Petersson, Björn Larsson</t>
+          <t>Jörgen Petersson, Gun Ingmansson, Björn Larsson</t>
         </is>
       </c>
       <c r="AY34" t="inlineStr"/>
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>126514046</v>
+        <v>126514043</v>
       </c>
       <c r="B35" t="n">
         <v>43228</v>
@@ -4324,13 +4324,13 @@
         </is>
       </c>
       <c r="Q35" t="n">
-        <v>700215</v>
+        <v>700228</v>
       </c>
       <c r="R35" t="n">
-        <v>6359155</v>
+        <v>6359179</v>
       </c>
       <c r="S35" t="n">
-        <v>8</v>
+        <v>4</v>
       </c>
       <c r="T35" t="inlineStr">
         <is>
@@ -4391,7 +4391,7 @@
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>126514038</v>
+        <v>126514046</v>
       </c>
       <c r="B36" t="n">
         <v>43228</v>
@@ -4430,13 +4430,13 @@
         </is>
       </c>
       <c r="Q36" t="n">
-        <v>700305</v>
+        <v>700215</v>
       </c>
       <c r="R36" t="n">
-        <v>6359105</v>
+        <v>6359155</v>
       </c>
       <c r="S36" t="n">
-        <v>4</v>
+        <v>8</v>
       </c>
       <c r="T36" t="inlineStr">
         <is>
@@ -4490,7 +4490,7 @@
       </c>
       <c r="AX36" t="inlineStr">
         <is>
-          <t>Jörgen Petersson, Gun Ingmansson, Björn Larsson</t>
+          <t>Gun Ingmansson, Jörgen Petersson, Björn Larsson</t>
         </is>
       </c>
       <c r="AY36" t="inlineStr"/>

--- a/artfynd/A 14354-2024 artfynd.xlsx
+++ b/artfynd/A 14354-2024 artfynd.xlsx
@@ -1658,37 +1658,37 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>126300254</v>
+        <v>126300269</v>
       </c>
       <c r="B10" t="n">
-        <v>98397</v>
+        <v>43228</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E10" t="n">
-        <v>223621</v>
+        <v>101242</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Skogsnattviol</t>
+          <t>Dårgräsfjäril</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Platanthera bifolia subsp. latiflora</t>
+          <t>Lopinga achine</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(Drejer) Løjtnant</t>
+          <t>(Scopoli, 1763)</t>
         </is>
       </c>
       <c r="I10" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="P10" t="inlineStr">
@@ -1697,10 +1697,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>700231</v>
+        <v>700265</v>
       </c>
       <c r="R10" t="n">
-        <v>6359136</v>
+        <v>6359056</v>
       </c>
       <c r="S10" t="n">
         <v>4</v>
@@ -1764,37 +1764,37 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>126300269</v>
+        <v>126300254</v>
       </c>
       <c r="B11" t="n">
-        <v>43228</v>
+        <v>98397</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E11" t="n">
-        <v>101242</v>
+        <v>223621</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Dårgräsfjäril</t>
+          <t>Skogsnattviol</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Lopinga achine</t>
+          <t>Platanthera bifolia subsp. latiflora</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(Scopoli, 1763)</t>
+          <t>(Drejer) Løjtnant</t>
         </is>
       </c>
       <c r="I11" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>1</t>
         </is>
       </c>
       <c r="P11" t="inlineStr">
@@ -1803,10 +1803,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>700265</v>
+        <v>700231</v>
       </c>
       <c r="R11" t="n">
-        <v>6359056</v>
+        <v>6359136</v>
       </c>
       <c r="S11" t="n">
         <v>4</v>

--- a/artfynd/A 14354-2024 artfynd.xlsx
+++ b/artfynd/A 14354-2024 artfynd.xlsx
@@ -3449,52 +3449,48 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>126514039</v>
+        <v>126514045</v>
       </c>
       <c r="B27" t="n">
-        <v>43228</v>
+        <v>98384</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E27" t="n">
-        <v>101242</v>
+        <v>219847</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Dårgräsfjäril</t>
+          <t>Tvåblad</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>Lopinga achine</t>
+          <t>Neottia ovata</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>(Scopoli, 1763)</t>
-        </is>
-      </c>
-      <c r="I27" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+          <t>(L.) Buff. &amp; Fingerh.</t>
+        </is>
+      </c>
+      <c r="I27" t="inlineStr"/>
       <c r="P27" t="inlineStr">
         <is>
           <t>Gerum, Likmunds 1:2 (4), Gtl</t>
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>700289</v>
+        <v>700215</v>
       </c>
       <c r="R27" t="n">
-        <v>6359104</v>
+        <v>6359155</v>
       </c>
       <c r="S27" t="n">
-        <v>4</v>
+        <v>8</v>
       </c>
       <c r="T27" t="inlineStr">
         <is>
@@ -3555,48 +3551,52 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>126514045</v>
+        <v>126514039</v>
       </c>
       <c r="B28" t="n">
-        <v>98384</v>
+        <v>43228</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E28" t="n">
-        <v>219847</v>
+        <v>101242</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Tvåblad</t>
+          <t>Dårgräsfjäril</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>Neottia ovata</t>
+          <t>Lopinga achine</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>(L.) Buff. &amp; Fingerh.</t>
-        </is>
-      </c>
-      <c r="I28" t="inlineStr"/>
+          <t>(Scopoli, 1763)</t>
+        </is>
+      </c>
+      <c r="I28" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="P28" t="inlineStr">
         <is>
           <t>Gerum, Likmunds 1:2 (4), Gtl</t>
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>700215</v>
+        <v>700289</v>
       </c>
       <c r="R28" t="n">
-        <v>6359155</v>
+        <v>6359104</v>
       </c>
       <c r="S28" t="n">
-        <v>8</v>
+        <v>4</v>
       </c>
       <c r="T28" t="inlineStr">
         <is>
@@ -4179,7 +4179,7 @@
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>126514038</v>
+        <v>126514043</v>
       </c>
       <c r="B34" t="n">
         <v>43228</v>
@@ -4218,10 +4218,10 @@
         </is>
       </c>
       <c r="Q34" t="n">
-        <v>700305</v>
+        <v>700228</v>
       </c>
       <c r="R34" t="n">
-        <v>6359105</v>
+        <v>6359179</v>
       </c>
       <c r="S34" t="n">
         <v>4</v>
@@ -4278,14 +4278,14 @@
       </c>
       <c r="AX34" t="inlineStr">
         <is>
-          <t>Jörgen Petersson, Gun Ingmansson, Björn Larsson</t>
+          <t>Gun Ingmansson, Jörgen Petersson, Björn Larsson</t>
         </is>
       </c>
       <c r="AY34" t="inlineStr"/>
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>126514043</v>
+        <v>126514046</v>
       </c>
       <c r="B35" t="n">
         <v>43228</v>
@@ -4324,13 +4324,13 @@
         </is>
       </c>
       <c r="Q35" t="n">
-        <v>700228</v>
+        <v>700215</v>
       </c>
       <c r="R35" t="n">
-        <v>6359179</v>
+        <v>6359155</v>
       </c>
       <c r="S35" t="n">
-        <v>4</v>
+        <v>8</v>
       </c>
       <c r="T35" t="inlineStr">
         <is>
@@ -4391,7 +4391,7 @@
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>126514046</v>
+        <v>126514038</v>
       </c>
       <c r="B36" t="n">
         <v>43228</v>
@@ -4430,13 +4430,13 @@
         </is>
       </c>
       <c r="Q36" t="n">
-        <v>700215</v>
+        <v>700305</v>
       </c>
       <c r="R36" t="n">
-        <v>6359155</v>
+        <v>6359105</v>
       </c>
       <c r="S36" t="n">
-        <v>8</v>
+        <v>4</v>
       </c>
       <c r="T36" t="inlineStr">
         <is>
@@ -4490,7 +4490,7 @@
       </c>
       <c r="AX36" t="inlineStr">
         <is>
-          <t>Gun Ingmansson, Jörgen Petersson, Björn Larsson</t>
+          <t>Jörgen Petersson, Gun Ingmansson, Björn Larsson</t>
         </is>
       </c>
       <c r="AY36" t="inlineStr"/>

--- a/artfynd/A 14354-2024 artfynd.xlsx
+++ b/artfynd/A 14354-2024 artfynd.xlsx
@@ -4920,7 +4920,7 @@
         <v>126992159</v>
       </c>
       <c r="B41" t="n">
-        <v>43228</v>
+        <v>43232</v>
       </c>
       <c r="D41" t="inlineStr">
         <is>

--- a/artfynd/A 14354-2024 artfynd.xlsx
+++ b/artfynd/A 14354-2024 artfynd.xlsx
@@ -4920,7 +4920,7 @@
         <v>126992159</v>
       </c>
       <c r="B41" t="n">
-        <v>43232</v>
+        <v>43234</v>
       </c>
       <c r="D41" t="inlineStr">
         <is>

--- a/artfynd/A 14354-2024 artfynd.xlsx
+++ b/artfynd/A 14354-2024 artfynd.xlsx
@@ -4920,7 +4920,7 @@
         <v>126992159</v>
       </c>
       <c r="B41" t="n">
-        <v>43234</v>
+        <v>43228</v>
       </c>
       <c r="D41" t="inlineStr">
         <is>

--- a/artfynd/A 14354-2024 artfynd.xlsx
+++ b/artfynd/A 14354-2024 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY41"/>
+  <dimension ref="A1:AY64"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -675,60 +675,48 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>16230167</v>
+        <v>126514041</v>
       </c>
       <c r="B2" t="n">
-        <v>107008</v>
-      </c>
-      <c r="C2" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>96708</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>220320</v>
+        <v>2180</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Ängsskära</t>
+          <t>Blåmossa</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Serratula tinctoria</t>
+          <t>Leucobryum glaucum</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(Hedw.) Ångstr.</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
-      <c r="J2" t="inlineStr"/>
-      <c r="K2" t="inlineStr">
-        <is>
-          <t>blomning</t>
-        </is>
-      </c>
-      <c r="L2" t="inlineStr"/>
       <c r="P2" t="inlineStr">
         <is>
-          <t>Russparken, parkeringen 100m N, Gtl</t>
+          <t>Gerum, Likmunds 1:2 (4), Gtl</t>
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>700332.6694781327</v>
+        <v>700275</v>
       </c>
       <c r="R2" t="n">
-        <v>6359040.312721097</v>
+        <v>6359146</v>
       </c>
       <c r="S2" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T2" t="inlineStr">
         <is>
@@ -752,22 +740,12 @@
       </c>
       <c r="Y2" t="inlineStr">
         <is>
-          <t>2014-07-21</t>
-        </is>
-      </c>
-      <c r="Z2" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2025-06-29</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
         <is>
-          <t>2014-07-21</t>
-        </is>
-      </c>
-      <c r="AB2" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2025-06-29</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -778,83 +756,75 @@
       </c>
       <c r="AG2" t="b">
         <v>0</v>
+      </c>
+      <c r="AI2" t="inlineStr">
+        <is>
+          <t>Hästbetad blandskog</t>
+        </is>
       </c>
       <c r="AT2" t="inlineStr"/>
       <c r="AW2" t="inlineStr">
         <is>
-          <t>Dennis Nyström</t>
+          <t>Gun Ingmansson</t>
         </is>
       </c>
       <c r="AX2" t="inlineStr">
         <is>
-          <t>Dennis Nyström</t>
+          <t>Gun Ingmansson, Jörgen Petersson, Björn Larsson</t>
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>60293979</v>
+        <v>116259490</v>
       </c>
       <c r="B3" t="n">
-        <v>42760</v>
-      </c>
-      <c r="C3" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>57950</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>101242</v>
+        <v>100049</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Dårgräsfjäril</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Lopinga achine</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Scopoli, 1763)</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>6</t>
-        </is>
-      </c>
-      <c r="J3" t="inlineStr"/>
-      <c r="K3" t="inlineStr">
-        <is>
-          <t>imago/adult</t>
-        </is>
-      </c>
-      <c r="L3" t="inlineStr"/>
+          <t>1</t>
+        </is>
+      </c>
       <c r="M3" t="inlineStr">
         <is>
-          <t>friflygande</t>
-        </is>
-      </c>
-      <c r="N3" t="inlineStr"/>
+          <t>spel/sång</t>
+        </is>
+      </c>
       <c r="P3" t="inlineStr">
         <is>
-          <t>Russparken, parkeringen 100m N, Gtl</t>
+          <t>Gerum Likmunds 1:2 (4), Gtl</t>
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>700332.6694781327</v>
+        <v>700268</v>
       </c>
       <c r="R3" t="n">
-        <v>6359040.312721097</v>
+        <v>6359044</v>
       </c>
       <c r="S3" t="n">
         <v>25</v>
@@ -881,22 +851,12 @@
       </c>
       <c r="Y3" t="inlineStr">
         <is>
-          <t>2016-06-26</t>
-        </is>
-      </c>
-      <c r="Z3" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2024-04-23</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
         <is>
-          <t>2016-06-26</t>
-        </is>
-      </c>
-      <c r="AB3" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2024-04-23</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -907,31 +867,31 @@
       </c>
       <c r="AG3" t="b">
         <v>0</v>
+      </c>
+      <c r="AI3" t="inlineStr">
+        <is>
+          <t>Kalktallskog, hästbetad.</t>
+        </is>
       </c>
       <c r="AT3" t="inlineStr"/>
       <c r="AW3" t="inlineStr">
         <is>
-          <t>Dennis Nyström</t>
+          <t>Jörgen Petersson</t>
         </is>
       </c>
       <c r="AX3" t="inlineStr">
         <is>
-          <t>Dennis Nyström, Sanne Svensson</t>
+          <t>Jörgen Petersson</t>
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>95822757</v>
+        <v>60293979</v>
       </c>
       <c r="B4" t="n">
-        <v>42760</v>
-      </c>
-      <c r="C4" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>43467</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -958,7 +918,7 @@
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>6</t>
         </is>
       </c>
       <c r="J4" t="inlineStr"/>
@@ -968,21 +928,25 @@
         </is>
       </c>
       <c r="L4" t="inlineStr"/>
-      <c r="M4" t="inlineStr"/>
+      <c r="M4" t="inlineStr">
+        <is>
+          <t>friflygande</t>
+        </is>
+      </c>
       <c r="N4" t="inlineStr"/>
       <c r="P4" t="inlineStr">
         <is>
-          <t>4. Botes källmyr, Gtl</t>
+          <t>Russparken, parkeringen 100m N, Gtl</t>
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>700319.6838455767</v>
+        <v>700333</v>
       </c>
       <c r="R4" t="n">
-        <v>6359051.032133494</v>
+        <v>6359040</v>
       </c>
       <c r="S4" t="n">
-        <v>5</v>
+        <v>25</v>
       </c>
       <c r="T4" t="inlineStr">
         <is>
@@ -1006,22 +970,12 @@
       </c>
       <c r="Y4" t="inlineStr">
         <is>
-          <t>2021-06-28</t>
-        </is>
-      </c>
-      <c r="Z4" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2016-06-26</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
         <is>
-          <t>2021-06-28</t>
-        </is>
-      </c>
-      <c r="AB4" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2016-06-26</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -1030,38 +984,28 @@
       <c r="AE4" t="b">
         <v>0</v>
       </c>
-      <c r="AF4" t="inlineStr"/>
       <c r="AG4" t="b">
         <v>0</v>
       </c>
       <c r="AT4" t="inlineStr"/>
       <c r="AW4" t="inlineStr">
         <is>
-          <t>Arne Pettersson</t>
+          <t>Dennis Nyström</t>
         </is>
       </c>
       <c r="AX4" t="inlineStr">
         <is>
-          <t>Arne Pettersson</t>
-        </is>
-      </c>
-      <c r="AY4" t="inlineStr">
-        <is>
-          <t>Biogeografisk uppföljning av fjärilar</t>
-        </is>
-      </c>
+          <t>Dennis Nyström, Sanne Svensson</t>
+        </is>
+      </c>
+      <c r="AY4" t="inlineStr"/>
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>97960624</v>
+        <v>68587789</v>
       </c>
       <c r="B5" t="n">
-        <v>106964</v>
-      </c>
-      <c r="C5" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>43467</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1069,45 +1013,54 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>220299</v>
+        <v>101242</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Svinrot</t>
+          <t>Dårgräsfjäril</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Scorzonera humilis</t>
+          <t>Lopinga achine</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>L.</t>
-        </is>
-      </c>
-      <c r="I5" t="inlineStr"/>
-      <c r="J5" t="inlineStr"/>
+          <t>(Scopoli, 1763)</t>
+        </is>
+      </c>
+      <c r="I5" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="J5" t="inlineStr">
+        <is>
+          <t>ex.</t>
+        </is>
+      </c>
       <c r="K5" t="inlineStr">
         <is>
-          <t>vinterståndare</t>
+          <t>imago/adult</t>
         </is>
       </c>
       <c r="L5" t="inlineStr"/>
+      <c r="M5" t="inlineStr"/>
       <c r="N5" t="inlineStr"/>
       <c r="P5" t="inlineStr">
         <is>
-          <t>Russparken, parkeringen 100m N, Gtl</t>
+          <t>4. Vägen till Botes källmyr, Gtl</t>
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>700332.6694781327</v>
+        <v>700330</v>
       </c>
       <c r="R5" t="n">
-        <v>6359040.312721097</v>
+        <v>6359020</v>
       </c>
       <c r="S5" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T5" t="inlineStr">
         <is>
@@ -1131,22 +1084,12 @@
       </c>
       <c r="Y5" t="inlineStr">
         <is>
-          <t>2022-01-06</t>
-        </is>
-      </c>
-      <c r="Z5" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2017-07-02</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
         <is>
-          <t>2022-01-06</t>
-        </is>
-      </c>
-      <c r="AB5" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2017-07-02</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1155,34 +1098,32 @@
       <c r="AE5" t="b">
         <v>0</v>
       </c>
-      <c r="AF5" t="inlineStr"/>
       <c r="AG5" t="b">
         <v>0</v>
       </c>
       <c r="AT5" t="inlineStr"/>
       <c r="AW5" t="inlineStr">
         <is>
-          <t>Dennis Nyström</t>
+          <t>Arne Pettersson</t>
         </is>
       </c>
       <c r="AX5" t="inlineStr">
         <is>
-          <t>Dennis Nyström</t>
-        </is>
-      </c>
-      <c r="AY5" t="inlineStr"/>
+          <t>Arne Pettersson</t>
+        </is>
+      </c>
+      <c r="AY5" t="inlineStr">
+        <is>
+          <t>Biogeografisk uppföljning av fjärilar</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>111589164</v>
+        <v>88866474</v>
       </c>
       <c r="B6" t="n">
-        <v>5410</v>
-      </c>
-      <c r="C6" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>43467</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1190,62 +1131,50 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>105894</v>
+        <v>101242</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Smedbock</t>
+          <t>Dårgräsfjäril</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Ergates faber</t>
+          <t>Lopinga achine</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1761)</t>
+          <t>(Scopoli, 1763)</t>
         </is>
       </c>
       <c r="I6" t="inlineStr">
         <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="J6" t="inlineStr">
-        <is>
-          <t>ex.</t>
-        </is>
-      </c>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="J6" t="inlineStr"/>
       <c r="K6" t="inlineStr">
         <is>
           <t>imago/adult</t>
         </is>
       </c>
-      <c r="L6" t="inlineStr">
-        <is>
-          <t>hona</t>
-        </is>
-      </c>
-      <c r="M6" t="inlineStr">
-        <is>
-          <t>frispringande/krypande</t>
-        </is>
-      </c>
+      <c r="L6" t="inlineStr"/>
+      <c r="M6" t="inlineStr"/>
       <c r="N6" t="inlineStr"/>
       <c r="P6" t="inlineStr">
         <is>
-          <t>Botes källmyr, vägen, Gtl</t>
+          <t>4. Botes Källmyr, Gtl</t>
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>700322.1717818696</v>
+        <v>700334</v>
       </c>
       <c r="R6" t="n">
-        <v>6359099.818101731</v>
+        <v>6359032</v>
       </c>
       <c r="S6" t="n">
-        <v>50</v>
+        <v>5</v>
       </c>
       <c r="T6" t="inlineStr">
         <is>
@@ -1269,22 +1198,12 @@
       </c>
       <c r="Y6" t="inlineStr">
         <is>
-          <t>2023-08-15</t>
-        </is>
-      </c>
-      <c r="Z6" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2020-06-28</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
         <is>
-          <t>2023-08-15</t>
-        </is>
-      </c>
-      <c r="AB6" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2020-06-28</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1300,27 +1219,26 @@
       <c r="AT6" t="inlineStr"/>
       <c r="AW6" t="inlineStr">
         <is>
-          <t>Kjell Eriksson</t>
+          <t>Arne Pettersson</t>
         </is>
       </c>
       <c r="AX6" t="inlineStr">
         <is>
-          <t>Kjell Eriksson, Ulla Eriksson</t>
-        </is>
-      </c>
-      <c r="AY6" t="inlineStr"/>
+          <t>Arne Pettersson</t>
+        </is>
+      </c>
+      <c r="AY6" t="inlineStr">
+        <is>
+          <t>Biogeografisk uppföljning av fjärilar</t>
+        </is>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>111758817</v>
+        <v>95822755</v>
       </c>
       <c r="B7" t="n">
-        <v>42763</v>
-      </c>
-      <c r="C7" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>43467</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1347,7 +1265,7 @@
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>11</t>
+          <t>7</t>
         </is>
       </c>
       <c r="J7" t="inlineStr"/>
@@ -1365,10 +1283,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>700336</v>
+        <v>700332</v>
       </c>
       <c r="R7" t="n">
-        <v>6359048</v>
+        <v>6359027</v>
       </c>
       <c r="S7" t="n">
         <v>5</v>
@@ -1395,12 +1313,12 @@
       </c>
       <c r="Y7" t="inlineStr">
         <is>
-          <t>2023-06-26</t>
+          <t>2021-06-28</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
         <is>
-          <t>2023-06-26</t>
+          <t>2021-06-28</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1432,15 +1350,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>118077514</v>
+        <v>95822757</v>
       </c>
       <c r="B8" t="n">
-        <v>42955</v>
-      </c>
-      <c r="C8" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>43467</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1467,7 +1380,7 @@
       </c>
       <c r="I8" t="inlineStr">
         <is>
-          <t>13</t>
+          <t>4</t>
         </is>
       </c>
       <c r="J8" t="inlineStr"/>
@@ -1481,14 +1394,14 @@
       <c r="N8" t="inlineStr"/>
       <c r="P8" t="inlineStr">
         <is>
-          <t>4. Botes Källmyr, Gtl</t>
+          <t>4. Botes källmyr, Gtl</t>
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>700334</v>
+        <v>700320</v>
       </c>
       <c r="R8" t="n">
-        <v>6359053</v>
+        <v>6359051</v>
       </c>
       <c r="S8" t="n">
         <v>5</v>
@@ -1515,12 +1428,12 @@
       </c>
       <c r="Y8" t="inlineStr">
         <is>
-          <t>2024-06-20</t>
+          <t>2021-06-28</t>
         </is>
       </c>
       <c r="AA8" t="inlineStr">
         <is>
-          <t>2024-06-20</t>
+          <t>2021-06-28</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1552,10 +1465,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>126300260</v>
+        <v>111758809</v>
       </c>
       <c r="B9" t="n">
-        <v>43228</v>
+        <v>43467</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1582,19 +1495,28 @@
       </c>
       <c r="I9" t="inlineStr">
         <is>
-          <t>2</t>
-        </is>
-      </c>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="J9" t="inlineStr"/>
+      <c r="K9" t="inlineStr">
+        <is>
+          <t>imago/adult</t>
+        </is>
+      </c>
+      <c r="L9" t="inlineStr"/>
+      <c r="M9" t="inlineStr"/>
+      <c r="N9" t="inlineStr"/>
       <c r="P9" t="inlineStr">
         <is>
-          <t>Gerum, Likmunds 1:2 (4), Gtl</t>
+          <t>4. Botes källmyr, Gtl</t>
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>700247</v>
+        <v>700336</v>
       </c>
       <c r="R9" t="n">
-        <v>6359105</v>
+        <v>6359031</v>
       </c>
       <c r="S9" t="n">
         <v>5</v>
@@ -1621,12 +1543,12 @@
       </c>
       <c r="Y9" t="inlineStr">
         <is>
-          <t>2025-06-29</t>
+          <t>2023-06-26</t>
         </is>
       </c>
       <c r="AA9" t="inlineStr">
         <is>
-          <t>2025-06-29</t>
+          <t>2023-06-26</t>
         </is>
       </c>
       <c r="AD9" t="b">
@@ -1635,33 +1557,33 @@
       <c r="AE9" t="b">
         <v>0</v>
       </c>
+      <c r="AF9" t="inlineStr"/>
       <c r="AG9" t="b">
         <v>0</v>
-      </c>
-      <c r="AI9" t="inlineStr">
-        <is>
-          <t>Hästbetad blandskog</t>
-        </is>
       </c>
       <c r="AT9" t="inlineStr"/>
       <c r="AW9" t="inlineStr">
         <is>
-          <t>Gun Ingmansson</t>
+          <t>Arne Pettersson</t>
         </is>
       </c>
       <c r="AX9" t="inlineStr">
         <is>
-          <t>Gun Ingmansson, Jörgen Petersson, Björn Larsson</t>
-        </is>
-      </c>
-      <c r="AY9" t="inlineStr"/>
+          <t>Arne Pettersson</t>
+        </is>
+      </c>
+      <c r="AY9" t="inlineStr">
+        <is>
+          <t>Biogeografisk uppföljning av fjärilar</t>
+        </is>
+      </c>
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>126300269</v>
+        <v>111758817</v>
       </c>
       <c r="B10" t="n">
-        <v>43228</v>
+        <v>43467</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1688,22 +1610,31 @@
       </c>
       <c r="I10" t="inlineStr">
         <is>
-          <t>2</t>
-        </is>
-      </c>
+          <t>11</t>
+        </is>
+      </c>
+      <c r="J10" t="inlineStr"/>
+      <c r="K10" t="inlineStr">
+        <is>
+          <t>imago/adult</t>
+        </is>
+      </c>
+      <c r="L10" t="inlineStr"/>
+      <c r="M10" t="inlineStr"/>
+      <c r="N10" t="inlineStr"/>
       <c r="P10" t="inlineStr">
         <is>
-          <t>Gerum, Likmunds 1:2 (4), Gtl</t>
+          <t>4. Botes källmyr, Gtl</t>
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>700265</v>
+        <v>700336</v>
       </c>
       <c r="R10" t="n">
-        <v>6359056</v>
+        <v>6359048</v>
       </c>
       <c r="S10" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="T10" t="inlineStr">
         <is>
@@ -1727,12 +1658,12 @@
       </c>
       <c r="Y10" t="inlineStr">
         <is>
-          <t>2025-06-29</t>
+          <t>2023-06-26</t>
         </is>
       </c>
       <c r="AA10" t="inlineStr">
         <is>
-          <t>2025-06-29</t>
+          <t>2023-06-26</t>
         </is>
       </c>
       <c r="AD10" t="b">
@@ -1741,55 +1672,55 @@
       <c r="AE10" t="b">
         <v>0</v>
       </c>
+      <c r="AF10" t="inlineStr"/>
       <c r="AG10" t="b">
         <v>0</v>
-      </c>
-      <c r="AI10" t="inlineStr">
-        <is>
-          <t>Hästbetad blandskog</t>
-        </is>
       </c>
       <c r="AT10" t="inlineStr"/>
       <c r="AW10" t="inlineStr">
         <is>
-          <t>Gun Ingmansson</t>
+          <t>Arne Pettersson</t>
         </is>
       </c>
       <c r="AX10" t="inlineStr">
         <is>
-          <t>Gun Ingmansson, Jörgen Petersson, Björn Larsson</t>
-        </is>
-      </c>
-      <c r="AY10" t="inlineStr"/>
+          <t>Arne Pettersson</t>
+        </is>
+      </c>
+      <c r="AY10" t="inlineStr">
+        <is>
+          <t>Biogeografisk uppföljning av fjärilar</t>
+        </is>
+      </c>
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>126300254</v>
+        <v>111758822</v>
       </c>
       <c r="B11" t="n">
-        <v>98397</v>
+        <v>43467</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E11" t="n">
-        <v>223621</v>
+        <v>101242</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Skogsnattviol</t>
+          <t>Dårgräsfjäril</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Platanthera bifolia subsp. latiflora</t>
+          <t>Lopinga achine</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(Drejer) Løjtnant</t>
+          <t>(Scopoli, 1763)</t>
         </is>
       </c>
       <c r="I11" t="inlineStr">
@@ -1797,19 +1728,28 @@
           <t>1</t>
         </is>
       </c>
+      <c r="J11" t="inlineStr"/>
+      <c r="K11" t="inlineStr">
+        <is>
+          <t>imago/adult</t>
+        </is>
+      </c>
+      <c r="L11" t="inlineStr"/>
+      <c r="M11" t="inlineStr"/>
+      <c r="N11" t="inlineStr"/>
       <c r="P11" t="inlineStr">
         <is>
-          <t>Gerum, Likmunds 1:2 (4), Gtl</t>
+          <t>4. Botes källmyr, Gtl</t>
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>700231</v>
+        <v>700333</v>
       </c>
       <c r="R11" t="n">
-        <v>6359136</v>
+        <v>6359065</v>
       </c>
       <c r="S11" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="T11" t="inlineStr">
         <is>
@@ -1828,17 +1768,17 @@
       </c>
       <c r="W11" t="inlineStr">
         <is>
-          <t>Gerum</t>
+          <t>Fardhem</t>
         </is>
       </c>
       <c r="Y11" t="inlineStr">
         <is>
-          <t>2025-06-29</t>
+          <t>2023-06-26</t>
         </is>
       </c>
       <c r="AA11" t="inlineStr">
         <is>
-          <t>2025-06-29</t>
+          <t>2023-06-26</t>
         </is>
       </c>
       <c r="AD11" t="b">
@@ -1847,33 +1787,33 @@
       <c r="AE11" t="b">
         <v>0</v>
       </c>
+      <c r="AF11" t="inlineStr"/>
       <c r="AG11" t="b">
         <v>0</v>
-      </c>
-      <c r="AI11" t="inlineStr">
-        <is>
-          <t>Hästbetad blandskog</t>
-        </is>
       </c>
       <c r="AT11" t="inlineStr"/>
       <c r="AW11" t="inlineStr">
         <is>
-          <t>Gun Ingmansson</t>
+          <t>Arne Pettersson</t>
         </is>
       </c>
       <c r="AX11" t="inlineStr">
         <is>
-          <t>Gun Ingmansson, Jörgen Petersson, Björn Larsson</t>
-        </is>
-      </c>
-      <c r="AY11" t="inlineStr"/>
+          <t>Arne Pettersson</t>
+        </is>
+      </c>
+      <c r="AY11" t="inlineStr">
+        <is>
+          <t>Biogeografisk uppföljning av fjärilar</t>
+        </is>
+      </c>
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>126300262</v>
+        <v>118077502</v>
       </c>
       <c r="B12" t="n">
-        <v>43228</v>
+        <v>43467</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1900,22 +1840,31 @@
       </c>
       <c r="I12" t="inlineStr">
         <is>
-          <t>3</t>
-        </is>
-      </c>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="J12" t="inlineStr"/>
+      <c r="K12" t="inlineStr">
+        <is>
+          <t>imago/adult</t>
+        </is>
+      </c>
+      <c r="L12" t="inlineStr"/>
+      <c r="M12" t="inlineStr"/>
+      <c r="N12" t="inlineStr"/>
       <c r="P12" t="inlineStr">
         <is>
-          <t>Gerum, Likmunds 1:2 (4), Gtl</t>
+          <t>4. Botes Källmyr, Gtl</t>
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>700253</v>
+        <v>700337</v>
       </c>
       <c r="R12" t="n">
-        <v>6359086</v>
+        <v>6359034</v>
       </c>
       <c r="S12" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="T12" t="inlineStr">
         <is>
@@ -1939,12 +1888,12 @@
       </c>
       <c r="Y12" t="inlineStr">
         <is>
-          <t>2025-06-29</t>
+          <t>2024-06-20</t>
         </is>
       </c>
       <c r="AA12" t="inlineStr">
         <is>
-          <t>2025-06-29</t>
+          <t>2024-06-20</t>
         </is>
       </c>
       <c r="AD12" t="b">
@@ -1953,33 +1902,33 @@
       <c r="AE12" t="b">
         <v>0</v>
       </c>
+      <c r="AF12" t="inlineStr"/>
       <c r="AG12" t="b">
         <v>0</v>
-      </c>
-      <c r="AI12" t="inlineStr">
-        <is>
-          <t>Hästbetad blandskog</t>
-        </is>
       </c>
       <c r="AT12" t="inlineStr"/>
       <c r="AW12" t="inlineStr">
         <is>
-          <t>Gun Ingmansson</t>
+          <t>Arne Pettersson</t>
         </is>
       </c>
       <c r="AX12" t="inlineStr">
         <is>
-          <t>Gun Ingmansson, Jörgen Petersson, Björn Larsson</t>
-        </is>
-      </c>
-      <c r="AY12" t="inlineStr"/>
+          <t>Arne Pettersson</t>
+        </is>
+      </c>
+      <c r="AY12" t="inlineStr">
+        <is>
+          <t>Biogeografisk uppföljning av fjärilar</t>
+        </is>
+      </c>
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>126300255</v>
+        <v>118077514</v>
       </c>
       <c r="B13" t="n">
-        <v>43228</v>
+        <v>43467</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -2006,19 +1955,28 @@
       </c>
       <c r="I13" t="inlineStr">
         <is>
-          <t>1</t>
-        </is>
-      </c>
+          <t>13</t>
+        </is>
+      </c>
+      <c r="J13" t="inlineStr"/>
+      <c r="K13" t="inlineStr">
+        <is>
+          <t>imago/adult</t>
+        </is>
+      </c>
+      <c r="L13" t="inlineStr"/>
+      <c r="M13" t="inlineStr"/>
+      <c r="N13" t="inlineStr"/>
       <c r="P13" t="inlineStr">
         <is>
-          <t>Gerum, Likmunds 1:2 (4), Gtl</t>
+          <t>4. Botes Källmyr, Gtl</t>
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>700243</v>
+        <v>700334</v>
       </c>
       <c r="R13" t="n">
-        <v>6359125</v>
+        <v>6359053</v>
       </c>
       <c r="S13" t="n">
         <v>5</v>
@@ -2045,12 +2003,12 @@
       </c>
       <c r="Y13" t="inlineStr">
         <is>
-          <t>2025-06-29</t>
+          <t>2024-06-20</t>
         </is>
       </c>
       <c r="AA13" t="inlineStr">
         <is>
-          <t>2025-06-29</t>
+          <t>2024-06-20</t>
         </is>
       </c>
       <c r="AD13" t="b">
@@ -2059,33 +2017,33 @@
       <c r="AE13" t="b">
         <v>0</v>
       </c>
+      <c r="AF13" t="inlineStr"/>
       <c r="AG13" t="b">
         <v>0</v>
-      </c>
-      <c r="AI13" t="inlineStr">
-        <is>
-          <t>Hästbetad blandskog</t>
-        </is>
       </c>
       <c r="AT13" t="inlineStr"/>
       <c r="AW13" t="inlineStr">
         <is>
-          <t>Gun Ingmansson</t>
+          <t>Arne Pettersson</t>
         </is>
       </c>
       <c r="AX13" t="inlineStr">
         <is>
-          <t>Gun Ingmansson, Jörgen Petersson, Björn Larsson</t>
-        </is>
-      </c>
-      <c r="AY13" t="inlineStr"/>
+          <t>Arne Pettersson</t>
+        </is>
+      </c>
+      <c r="AY13" t="inlineStr">
+        <is>
+          <t>Biogeografisk uppföljning av fjärilar</t>
+        </is>
+      </c>
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>126300264</v>
+        <v>126300253</v>
       </c>
       <c r="B14" t="n">
-        <v>43228</v>
+        <v>43467</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2121,13 +2079,13 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>700247</v>
+        <v>700231</v>
       </c>
       <c r="R14" t="n">
-        <v>6359082</v>
+        <v>6359136</v>
       </c>
       <c r="S14" t="n">
-        <v>8</v>
+        <v>4</v>
       </c>
       <c r="T14" t="inlineStr">
         <is>
@@ -2188,48 +2146,52 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>126300268</v>
+        <v>126300255</v>
       </c>
       <c r="B15" t="n">
-        <v>98384</v>
+        <v>43467</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E15" t="n">
-        <v>219847</v>
+        <v>101242</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Tvåblad</t>
+          <t>Dårgräsfjäril</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Neottia ovata</t>
+          <t>Lopinga achine</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(L.) Buff. &amp; Fingerh.</t>
-        </is>
-      </c>
-      <c r="I15" t="inlineStr"/>
+          <t>(Scopoli, 1763)</t>
+        </is>
+      </c>
+      <c r="I15" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="P15" t="inlineStr">
         <is>
           <t>Gerum, Likmunds 1:2 (4), Gtl</t>
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>700265</v>
+        <v>700243</v>
       </c>
       <c r="R15" t="n">
-        <v>6359056</v>
+        <v>6359125</v>
       </c>
       <c r="S15" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="T15" t="inlineStr">
         <is>
@@ -2290,35 +2252,39 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>126300256</v>
+        <v>126300260</v>
       </c>
       <c r="B16" t="n">
-        <v>98384</v>
+        <v>43467</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E16" t="n">
-        <v>219847</v>
+        <v>101242</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Tvåblad</t>
+          <t>Dårgräsfjäril</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Neottia ovata</t>
+          <t>Lopinga achine</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(L.) Buff. &amp; Fingerh.</t>
-        </is>
-      </c>
-      <c r="I16" t="inlineStr"/>
+          <t>(Scopoli, 1763)</t>
+        </is>
+      </c>
+      <c r="I16" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
       <c r="P16" t="inlineStr">
         <is>
           <t>Gerum, Likmunds 1:2 (4), Gtl</t>
@@ -2328,10 +2294,10 @@
         <v>700247</v>
       </c>
       <c r="R16" t="n">
-        <v>6359114</v>
+        <v>6359105</v>
       </c>
       <c r="S16" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="T16" t="inlineStr">
         <is>
@@ -2392,37 +2358,37 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>126300258</v>
+        <v>126300262</v>
       </c>
       <c r="B17" t="n">
-        <v>98384</v>
+        <v>43467</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E17" t="n">
-        <v>219847</v>
+        <v>101242</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Tvåblad</t>
+          <t>Dårgräsfjäril</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Neottia ovata</t>
+          <t>Lopinga achine</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(L.) Buff. &amp; Fingerh.</t>
+          <t>(Scopoli, 1763)</t>
         </is>
       </c>
       <c r="I17" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>3</t>
         </is>
       </c>
       <c r="P17" t="inlineStr">
@@ -2431,13 +2397,13 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>700247</v>
+        <v>700253</v>
       </c>
       <c r="R17" t="n">
-        <v>6359105</v>
+        <v>6359086</v>
       </c>
       <c r="S17" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="T17" t="inlineStr">
         <is>
@@ -2498,37 +2464,37 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>126300266</v>
+        <v>126300264</v>
       </c>
       <c r="B18" t="n">
-        <v>98279</v>
+        <v>43467</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E18" t="n">
-        <v>223591</v>
+        <v>101242</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Skogsnycklar</t>
+          <t>Dårgräsfjäril</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Dactylorhiza maculata subsp. fuchsii</t>
+          <t>Lopinga achine</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(Druce) Hyl.</t>
+          <t>(Scopoli, 1763)</t>
         </is>
       </c>
       <c r="I18" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>1</t>
         </is>
       </c>
       <c r="P18" t="inlineStr">
@@ -2604,37 +2570,37 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>126300263</v>
+        <v>126300269</v>
       </c>
       <c r="B19" t="n">
-        <v>98279</v>
+        <v>43467</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E19" t="n">
-        <v>223591</v>
+        <v>101242</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Skogsnycklar</t>
+          <t>Dårgräsfjäril</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Dactylorhiza maculata subsp. fuchsii</t>
+          <t>Lopinga achine</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>(Druce) Hyl.</t>
+          <t>(Scopoli, 1763)</t>
         </is>
       </c>
       <c r="I19" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>2</t>
         </is>
       </c>
       <c r="P19" t="inlineStr">
@@ -2643,10 +2609,10 @@
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>700253</v>
+        <v>700265</v>
       </c>
       <c r="R19" t="n">
-        <v>6359086</v>
+        <v>6359056</v>
       </c>
       <c r="S19" t="n">
         <v>4</v>
@@ -2710,37 +2676,37 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>126300259</v>
+        <v>126300274</v>
       </c>
       <c r="B20" t="n">
-        <v>98279</v>
+        <v>43467</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E20" t="n">
-        <v>223591</v>
+        <v>101242</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Skogsnycklar</t>
+          <t>Dårgräsfjäril</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Dactylorhiza maculata subsp. fuchsii</t>
+          <t>Lopinga achine</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>(Druce) Hyl.</t>
+          <t>(Scopoli, 1763)</t>
         </is>
       </c>
       <c r="I20" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>4</t>
         </is>
       </c>
       <c r="P20" t="inlineStr">
@@ -2749,13 +2715,13 @@
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>700247</v>
+        <v>700275</v>
       </c>
       <c r="R20" t="n">
-        <v>6359105</v>
+        <v>6359045</v>
       </c>
       <c r="S20" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="T20" t="inlineStr">
         <is>
@@ -2816,10 +2782,10 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>126300253</v>
+        <v>126300275</v>
       </c>
       <c r="B21" t="n">
-        <v>43228</v>
+        <v>43467</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -2846,7 +2812,7 @@
       </c>
       <c r="I21" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="P21" t="inlineStr">
@@ -2855,10 +2821,10 @@
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>700231</v>
+        <v>700276</v>
       </c>
       <c r="R21" t="n">
-        <v>6359136</v>
+        <v>6359028</v>
       </c>
       <c r="S21" t="n">
         <v>4</v>
@@ -2922,37 +2888,37 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>126300257</v>
+        <v>126300276</v>
       </c>
       <c r="B22" t="n">
-        <v>98339</v>
+        <v>43467</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E22" t="n">
-        <v>219798</v>
+        <v>101242</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Skogsknipprot</t>
+          <t>Dårgräsfjäril</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Epipactis helleborine</t>
+          <t>Lopinga achine</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>(L.) Crantz</t>
+          <t>(Scopoli, 1763)</t>
         </is>
       </c>
       <c r="I22" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>3</t>
         </is>
       </c>
       <c r="P22" t="inlineStr">
@@ -2961,10 +2927,10 @@
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>700247</v>
+        <v>700295</v>
       </c>
       <c r="R22" t="n">
-        <v>6359114</v>
+        <v>6359022</v>
       </c>
       <c r="S22" t="n">
         <v>4</v>
@@ -3028,48 +2994,52 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>126300265</v>
+        <v>126514033</v>
       </c>
       <c r="B23" t="n">
-        <v>98384</v>
+        <v>43467</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E23" t="n">
-        <v>219847</v>
+        <v>101242</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Tvåblad</t>
+          <t>Dårgräsfjäril</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Neottia ovata</t>
+          <t>Lopinga achine</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>(L.) Buff. &amp; Fingerh.</t>
-        </is>
-      </c>
-      <c r="I23" t="inlineStr"/>
+          <t>(Scopoli, 1763)</t>
+        </is>
+      </c>
+      <c r="I23" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="P23" t="inlineStr">
         <is>
           <t>Gerum, Likmunds 1:2 (4), Gtl</t>
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>700247</v>
+        <v>700302</v>
       </c>
       <c r="R23" t="n">
-        <v>6359082</v>
+        <v>6359030</v>
       </c>
       <c r="S23" t="n">
-        <v>8</v>
+        <v>4</v>
       </c>
       <c r="T23" t="inlineStr">
         <is>
@@ -3130,37 +3100,37 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>126300267</v>
+        <v>126514034</v>
       </c>
       <c r="B24" t="n">
-        <v>98383</v>
+        <v>43467</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E24" t="n">
-        <v>219862</v>
+        <v>101242</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Nästrot</t>
+          <t>Dårgräsfjäril</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Neottia nidus-avis</t>
+          <t>Lopinga achine</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>(L.) Rich.</t>
+          <t>(Scopoli, 1763)</t>
         </is>
       </c>
       <c r="I24" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>6</t>
         </is>
       </c>
       <c r="P24" t="inlineStr">
@@ -3169,13 +3139,13 @@
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>700257</v>
+        <v>700296</v>
       </c>
       <c r="R24" t="n">
-        <v>6359067</v>
+        <v>6359059</v>
       </c>
       <c r="S24" t="n">
-        <v>10</v>
+        <v>4</v>
       </c>
       <c r="T24" t="inlineStr">
         <is>
@@ -3236,45 +3206,49 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>126300270</v>
+        <v>126514036</v>
       </c>
       <c r="B25" t="n">
-        <v>98279</v>
+        <v>43467</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E25" t="n">
-        <v>223591</v>
+        <v>101242</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Skogsnycklar</t>
+          <t>Dårgräsfjäril</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Dactylorhiza maculata subsp. fuchsii</t>
+          <t>Lopinga achine</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>(Druce) Hyl.</t>
-        </is>
-      </c>
-      <c r="I25" t="inlineStr"/>
+          <t>(Scopoli, 1763)</t>
+        </is>
+      </c>
+      <c r="I25" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
       <c r="P25" t="inlineStr">
         <is>
           <t>Gerum, Likmunds 1:2 (4), Gtl</t>
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>700265</v>
+        <v>700296</v>
       </c>
       <c r="R25" t="n">
-        <v>6359056</v>
+        <v>6359084</v>
       </c>
       <c r="S25" t="n">
         <v>4</v>
@@ -3338,10 +3312,10 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>126312506</v>
+        <v>126514037</v>
       </c>
       <c r="B26" t="n">
-        <v>109225</v>
+        <v>43467</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -3349,51 +3323,41 @@
         </is>
       </c>
       <c r="E26" t="n">
-        <v>220320</v>
+        <v>101242</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Ängsskära</t>
+          <t>Dårgräsfjäril</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Serratula tinctoria</t>
+          <t>Lopinga achine</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(Scopoli, 1763)</t>
         </is>
       </c>
       <c r="I26" t="inlineStr">
         <is>
-          <t>34</t>
-        </is>
-      </c>
-      <c r="J26" t="inlineStr">
-        <is>
-          <t>stjälkar/strån/skott</t>
-        </is>
-      </c>
-      <c r="K26" t="inlineStr">
-        <is>
-          <t>blomknopp</t>
+          <t>3</t>
         </is>
       </c>
       <c r="P26" t="inlineStr">
         <is>
-          <t>Lilla Korsgatan, Gtl</t>
+          <t>Gerum, Likmunds 1:2 (4), Gtl</t>
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>700335</v>
+        <v>700290</v>
       </c>
       <c r="R26" t="n">
-        <v>6359040</v>
+        <v>6359078</v>
       </c>
       <c r="S26" t="n">
-        <v>25</v>
+        <v>5</v>
       </c>
       <c r="T26" t="inlineStr">
         <is>
@@ -3417,12 +3381,12 @@
       </c>
       <c r="Y26" t="inlineStr">
         <is>
-          <t>2025-06-30</t>
+          <t>2025-06-29</t>
         </is>
       </c>
       <c r="AA26" t="inlineStr">
         <is>
-          <t>2025-06-30</t>
+          <t>2025-06-29</t>
         </is>
       </c>
       <c r="AD26" t="b">
@@ -3433,64 +3397,73 @@
       </c>
       <c r="AG26" t="b">
         <v>0</v>
+      </c>
+      <c r="AI26" t="inlineStr">
+        <is>
+          <t>Hästbetad blandskog</t>
+        </is>
       </c>
       <c r="AT26" t="inlineStr"/>
       <c r="AW26" t="inlineStr">
         <is>
-          <t>Felicia Wikinger</t>
+          <t>Gun Ingmansson</t>
         </is>
       </c>
       <c r="AX26" t="inlineStr">
         <is>
-          <t>Felicia Wikinger, Teo Jernkvist</t>
+          <t>Gun Ingmansson, Jörgen Petersson, Björn Larsson</t>
         </is>
       </c>
       <c r="AY26" t="inlineStr"/>
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>126514045</v>
+        <v>126514038</v>
       </c>
       <c r="B27" t="n">
-        <v>98384</v>
+        <v>43467</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E27" t="n">
-        <v>219847</v>
+        <v>101242</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Tvåblad</t>
+          <t>Dårgräsfjäril</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>Neottia ovata</t>
+          <t>Lopinga achine</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>(L.) Buff. &amp; Fingerh.</t>
-        </is>
-      </c>
-      <c r="I27" t="inlineStr"/>
+          <t>(Scopoli, 1763)</t>
+        </is>
+      </c>
+      <c r="I27" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="P27" t="inlineStr">
         <is>
           <t>Gerum, Likmunds 1:2 (4), Gtl</t>
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>700215</v>
+        <v>700305</v>
       </c>
       <c r="R27" t="n">
-        <v>6359155</v>
+        <v>6359105</v>
       </c>
       <c r="S27" t="n">
-        <v>8</v>
+        <v>4</v>
       </c>
       <c r="T27" t="inlineStr">
         <is>
@@ -3554,7 +3527,7 @@
         <v>126514039</v>
       </c>
       <c r="B28" t="n">
-        <v>43228</v>
+        <v>43467</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
@@ -3657,10 +3630,10 @@
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>126514034</v>
+        <v>126514040</v>
       </c>
       <c r="B29" t="n">
-        <v>43228</v>
+        <v>43467</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
@@ -3687,7 +3660,7 @@
       </c>
       <c r="I29" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>1</t>
         </is>
       </c>
       <c r="P29" t="inlineStr">
@@ -3696,10 +3669,10 @@
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>700296</v>
+        <v>700278</v>
       </c>
       <c r="R29" t="n">
-        <v>6359059</v>
+        <v>6359138</v>
       </c>
       <c r="S29" t="n">
         <v>4</v>
@@ -3763,10 +3736,10 @@
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>126514036</v>
+        <v>126514042</v>
       </c>
       <c r="B30" t="n">
-        <v>43228</v>
+        <v>43467</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
@@ -3793,7 +3766,7 @@
       </c>
       <c r="I30" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>1</t>
         </is>
       </c>
       <c r="P30" t="inlineStr">
@@ -3802,13 +3775,13 @@
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>700296</v>
+        <v>700275</v>
       </c>
       <c r="R30" t="n">
-        <v>6359084</v>
+        <v>6359146</v>
       </c>
       <c r="S30" t="n">
-        <v>4</v>
+        <v>10</v>
       </c>
       <c r="T30" t="inlineStr">
         <is>
@@ -3869,32 +3842,32 @@
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>126514044</v>
+        <v>126514043</v>
       </c>
       <c r="B31" t="n">
-        <v>98339</v>
+        <v>43467</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E31" t="n">
-        <v>219798</v>
+        <v>101242</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Skogsknipprot</t>
+          <t>Dårgräsfjäril</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>Epipactis helleborine</t>
+          <t>Lopinga achine</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>(L.) Crantz</t>
+          <t>(Scopoli, 1763)</t>
         </is>
       </c>
       <c r="I31" t="inlineStr">
@@ -3908,13 +3881,13 @@
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>700215</v>
+        <v>700228</v>
       </c>
       <c r="R31" t="n">
-        <v>6359155</v>
+        <v>6359179</v>
       </c>
       <c r="S31" t="n">
-        <v>8</v>
+        <v>4</v>
       </c>
       <c r="T31" t="inlineStr">
         <is>
@@ -3975,48 +3948,52 @@
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>126514041</v>
+        <v>126514046</v>
       </c>
       <c r="B32" t="n">
-        <v>95964</v>
+        <v>43467</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E32" t="n">
-        <v>2180</v>
+        <v>101242</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Blåmossa</t>
+          <t>Dårgräsfjäril</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>Leucobryum glaucum</t>
+          <t>Lopinga achine</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>(Hedw.) Ångstr.</t>
-        </is>
-      </c>
-      <c r="I32" t="inlineStr"/>
+          <t>(Scopoli, 1763)</t>
+        </is>
+      </c>
+      <c r="I32" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="P32" t="inlineStr">
         <is>
           <t>Gerum, Likmunds 1:2 (4), Gtl</t>
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>700275</v>
+        <v>700215</v>
       </c>
       <c r="R32" t="n">
-        <v>6359146</v>
+        <v>6359155</v>
       </c>
       <c r="S32" t="n">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="T32" t="inlineStr">
         <is>
@@ -4077,48 +4054,61 @@
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>126514049</v>
+        <v>126992149</v>
       </c>
       <c r="B33" t="n">
-        <v>98384</v>
+        <v>43467</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E33" t="n">
-        <v>219847</v>
+        <v>101242</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Tvåblad</t>
+          <t>Dårgräsfjäril</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>Neottia ovata</t>
+          <t>Lopinga achine</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>(L.) Buff. &amp; Fingerh.</t>
-        </is>
-      </c>
-      <c r="I33" t="inlineStr"/>
+          <t>(Scopoli, 1763)</t>
+        </is>
+      </c>
+      <c r="I33" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="J33" t="inlineStr"/>
+      <c r="K33" t="inlineStr">
+        <is>
+          <t>imago/adult</t>
+        </is>
+      </c>
+      <c r="L33" t="inlineStr"/>
+      <c r="M33" t="inlineStr"/>
+      <c r="N33" t="inlineStr"/>
       <c r="P33" t="inlineStr">
         <is>
-          <t>Gerum, Likmunds 1:2 (4), Gtl</t>
+          <t>4. Botes källmyr, Gtl</t>
         </is>
       </c>
       <c r="Q33" t="n">
-        <v>700235</v>
+        <v>700333</v>
       </c>
       <c r="R33" t="n">
-        <v>6359147</v>
+        <v>6359029</v>
       </c>
       <c r="S33" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T33" t="inlineStr">
         <is>
@@ -4156,33 +4146,33 @@
       <c r="AE33" t="b">
         <v>0</v>
       </c>
+      <c r="AF33" t="inlineStr"/>
       <c r="AG33" t="b">
         <v>0</v>
-      </c>
-      <c r="AI33" t="inlineStr">
-        <is>
-          <t>Hästbetad blandskog</t>
-        </is>
       </c>
       <c r="AT33" t="inlineStr"/>
       <c r="AW33" t="inlineStr">
         <is>
-          <t>Gun Ingmansson</t>
+          <t>Arne Pettersson</t>
         </is>
       </c>
       <c r="AX33" t="inlineStr">
         <is>
-          <t>Gun Ingmansson, Jörgen Petersson, Björn Larsson</t>
-        </is>
-      </c>
-      <c r="AY33" t="inlineStr"/>
+          <t>Arne Pettersson</t>
+        </is>
+      </c>
+      <c r="AY33" t="inlineStr">
+        <is>
+          <t>Biogeografisk uppföljning av fjärilar</t>
+        </is>
+      </c>
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>126514038</v>
+        <v>126992159</v>
       </c>
       <c r="B34" t="n">
-        <v>43228</v>
+        <v>43467</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
@@ -4209,22 +4199,31 @@
       </c>
       <c r="I34" t="inlineStr">
         <is>
-          <t>1</t>
-        </is>
-      </c>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="J34" t="inlineStr"/>
+      <c r="K34" t="inlineStr">
+        <is>
+          <t>imago/adult</t>
+        </is>
+      </c>
+      <c r="L34" t="inlineStr"/>
+      <c r="M34" t="inlineStr"/>
+      <c r="N34" t="inlineStr"/>
       <c r="P34" t="inlineStr">
         <is>
-          <t>Gerum, Likmunds 1:2 (4), Gtl</t>
+          <t>4. Botes källmyr, Gtl</t>
         </is>
       </c>
       <c r="Q34" t="n">
-        <v>700305</v>
+        <v>700334</v>
       </c>
       <c r="R34" t="n">
-        <v>6359105</v>
+        <v>6359040</v>
       </c>
       <c r="S34" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="T34" t="inlineStr">
         <is>
@@ -4262,33 +4261,33 @@
       <c r="AE34" t="b">
         <v>0</v>
       </c>
+      <c r="AF34" t="inlineStr"/>
       <c r="AG34" t="b">
         <v>0</v>
-      </c>
-      <c r="AI34" t="inlineStr">
-        <is>
-          <t>Hästbetad blandskog</t>
-        </is>
       </c>
       <c r="AT34" t="inlineStr"/>
       <c r="AW34" t="inlineStr">
         <is>
-          <t>Gun Ingmansson</t>
+          <t>Arne Pettersson</t>
         </is>
       </c>
       <c r="AX34" t="inlineStr">
         <is>
-          <t>Gun Ingmansson, Jörgen Petersson, Björn Larsson</t>
-        </is>
-      </c>
-      <c r="AY34" t="inlineStr"/>
+          <t>Arne Pettersson</t>
+        </is>
+      </c>
+      <c r="AY34" t="inlineStr">
+        <is>
+          <t>Biogeografisk uppföljning av fjärilar</t>
+        </is>
+      </c>
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>126514043</v>
+        <v>111589164</v>
       </c>
       <c r="B35" t="n">
-        <v>43228</v>
+        <v>5479</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
@@ -4296,21 +4295,21 @@
         </is>
       </c>
       <c r="E35" t="n">
-        <v>101242</v>
+        <v>105894</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Dårgräsfjäril</t>
+          <t>Smedbock</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>Lopinga achine</t>
+          <t>Ergates faber</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>(Scopoli, 1763)</t>
+          <t>(Linnaeus, 1761)</t>
         </is>
       </c>
       <c r="I35" t="inlineStr">
@@ -4318,19 +4317,40 @@
           <t>1</t>
         </is>
       </c>
+      <c r="J35" t="inlineStr">
+        <is>
+          <t>ex.</t>
+        </is>
+      </c>
+      <c r="K35" t="inlineStr">
+        <is>
+          <t>imago/adult</t>
+        </is>
+      </c>
+      <c r="L35" t="inlineStr">
+        <is>
+          <t>hona</t>
+        </is>
+      </c>
+      <c r="M35" t="inlineStr">
+        <is>
+          <t>frispringande/krypande</t>
+        </is>
+      </c>
+      <c r="N35" t="inlineStr"/>
       <c r="P35" t="inlineStr">
         <is>
-          <t>Gerum, Likmunds 1:2 (4), Gtl</t>
+          <t>Botes källmyr, vägen, Gtl</t>
         </is>
       </c>
       <c r="Q35" t="n">
-        <v>700228</v>
+        <v>700322</v>
       </c>
       <c r="R35" t="n">
-        <v>6359179</v>
+        <v>6359100</v>
       </c>
       <c r="S35" t="n">
-        <v>4</v>
+        <v>50</v>
       </c>
       <c r="T35" t="inlineStr">
         <is>
@@ -4354,12 +4374,12 @@
       </c>
       <c r="Y35" t="inlineStr">
         <is>
-          <t>2025-06-29</t>
+          <t>2023-08-15</t>
         </is>
       </c>
       <c r="AA35" t="inlineStr">
         <is>
-          <t>2025-06-29</t>
+          <t>2023-08-15</t>
         </is>
       </c>
       <c r="AD35" t="b">
@@ -4368,55 +4388,51 @@
       <c r="AE35" t="b">
         <v>0</v>
       </c>
+      <c r="AF35" t="inlineStr"/>
       <c r="AG35" t="b">
         <v>0</v>
-      </c>
-      <c r="AI35" t="inlineStr">
-        <is>
-          <t>Hästbetad blandskog</t>
-        </is>
       </c>
       <c r="AT35" t="inlineStr"/>
       <c r="AW35" t="inlineStr">
         <is>
-          <t>Gun Ingmansson</t>
+          <t>Kjell Eriksson</t>
         </is>
       </c>
       <c r="AX35" t="inlineStr">
         <is>
-          <t>Gun Ingmansson, Jörgen Petersson, Björn Larsson</t>
+          <t>Kjell Eriksson, Ulla Eriksson</t>
         </is>
       </c>
       <c r="AY35" t="inlineStr"/>
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>126514046</v>
+        <v>116259087</v>
       </c>
       <c r="B36" t="n">
-        <v>43228</v>
+        <v>99035</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E36" t="n">
-        <v>101242</v>
+        <v>219790</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Dårgräsfjäril</t>
+          <t>Fläcknycklar</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>Lopinga achine</t>
+          <t>Dactylorhiza maculata</t>
         </is>
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>(Scopoli, 1763)</t>
+          <t>(L.) Soó</t>
         </is>
       </c>
       <c r="I36" t="inlineStr">
@@ -4424,19 +4440,29 @@
           <t>1</t>
         </is>
       </c>
+      <c r="J36" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="K36" t="inlineStr">
+        <is>
+          <t>fullt utvecklade blad</t>
+        </is>
+      </c>
       <c r="P36" t="inlineStr">
         <is>
-          <t>Gerum, Likmunds 1:2 (4), Gtl</t>
+          <t>Gerum Likmunds 1:2 (4), Gtl</t>
         </is>
       </c>
       <c r="Q36" t="n">
-        <v>700215</v>
+        <v>700256</v>
       </c>
       <c r="R36" t="n">
-        <v>6359155</v>
+        <v>6359045</v>
       </c>
       <c r="S36" t="n">
-        <v>8</v>
+        <v>3</v>
       </c>
       <c r="T36" t="inlineStr">
         <is>
@@ -4460,12 +4486,12 @@
       </c>
       <c r="Y36" t="inlineStr">
         <is>
-          <t>2025-06-29</t>
+          <t>2024-04-23</t>
         </is>
       </c>
       <c r="AA36" t="inlineStr">
         <is>
-          <t>2025-06-29</t>
+          <t>2024-04-23</t>
         </is>
       </c>
       <c r="AD36" t="b">
@@ -4479,50 +4505,50 @@
       </c>
       <c r="AI36" t="inlineStr">
         <is>
-          <t>Hästbetad blandskog</t>
+          <t>Kalktallskog något fuktigare, träd på socklar, hästbetad.</t>
         </is>
       </c>
       <c r="AT36" t="inlineStr"/>
       <c r="AW36" t="inlineStr">
         <is>
-          <t>Gun Ingmansson</t>
+          <t>Jörgen Petersson</t>
         </is>
       </c>
       <c r="AX36" t="inlineStr">
         <is>
-          <t>Gun Ingmansson, Jörgen Petersson, Björn Larsson</t>
+          <t>Jörgen Petersson</t>
         </is>
       </c>
       <c r="AY36" t="inlineStr"/>
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>126514042</v>
+        <v>126300257</v>
       </c>
       <c r="B37" t="n">
-        <v>43228</v>
+        <v>99096</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E37" t="n">
-        <v>101242</v>
+        <v>219798</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Dårgräsfjäril</t>
+          <t>Skogsknipprot</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>Lopinga achine</t>
+          <t>Epipactis helleborine</t>
         </is>
       </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t>(Scopoli, 1763)</t>
+          <t>(L.) Crantz</t>
         </is>
       </c>
       <c r="I37" t="inlineStr">
@@ -4536,13 +4562,13 @@
         </is>
       </c>
       <c r="Q37" t="n">
-        <v>700275</v>
+        <v>700247</v>
       </c>
       <c r="R37" t="n">
-        <v>6359146</v>
+        <v>6359114</v>
       </c>
       <c r="S37" t="n">
-        <v>10</v>
+        <v>4</v>
       </c>
       <c r="T37" t="inlineStr">
         <is>
@@ -4603,32 +4629,32 @@
     </row>
     <row r="38">
       <c r="A38" t="n">
-        <v>126514040</v>
+        <v>126514044</v>
       </c>
       <c r="B38" t="n">
-        <v>43228</v>
+        <v>99096</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E38" t="n">
-        <v>101242</v>
+        <v>219798</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Dårgräsfjäril</t>
+          <t>Skogsknipprot</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>Lopinga achine</t>
+          <t>Epipactis helleborine</t>
         </is>
       </c>
       <c r="H38" t="inlineStr">
         <is>
-          <t>(Scopoli, 1763)</t>
+          <t>(L.) Crantz</t>
         </is>
       </c>
       <c r="I38" t="inlineStr">
@@ -4642,13 +4668,13 @@
         </is>
       </c>
       <c r="Q38" t="n">
-        <v>700278</v>
+        <v>700215</v>
       </c>
       <c r="R38" t="n">
-        <v>6359138</v>
+        <v>6359155</v>
       </c>
       <c r="S38" t="n">
-        <v>4</v>
+        <v>8</v>
       </c>
       <c r="T38" t="inlineStr">
         <is>
@@ -4709,10 +4735,10 @@
     </row>
     <row r="39">
       <c r="A39" t="n">
-        <v>126514047</v>
+        <v>126300256</v>
       </c>
       <c r="B39" t="n">
-        <v>98279</v>
+        <v>99142</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
@@ -4720,21 +4746,21 @@
         </is>
       </c>
       <c r="E39" t="n">
-        <v>223591</v>
+        <v>219847</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Skogsnycklar</t>
+          <t>Tvåblad</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>Dactylorhiza maculata subsp. fuchsii</t>
+          <t>Neottia ovata</t>
         </is>
       </c>
       <c r="H39" t="inlineStr">
         <is>
-          <t>(Druce) Hyl.</t>
+          <t>(L.) Buff. &amp; Fingerh.</t>
         </is>
       </c>
       <c r="I39" t="inlineStr"/>
@@ -4744,13 +4770,13 @@
         </is>
       </c>
       <c r="Q39" t="n">
-        <v>700215</v>
+        <v>700247</v>
       </c>
       <c r="R39" t="n">
-        <v>6359155</v>
+        <v>6359114</v>
       </c>
       <c r="S39" t="n">
-        <v>8</v>
+        <v>4</v>
       </c>
       <c r="T39" t="inlineStr">
         <is>
@@ -4811,37 +4837,37 @@
     </row>
     <row r="40">
       <c r="A40" t="n">
-        <v>126514037</v>
+        <v>126300258</v>
       </c>
       <c r="B40" t="n">
-        <v>43228</v>
+        <v>99142</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E40" t="n">
-        <v>101242</v>
+        <v>219847</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Dårgräsfjäril</t>
+          <t>Tvåblad</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>Lopinga achine</t>
+          <t>Neottia ovata</t>
         </is>
       </c>
       <c r="H40" t="inlineStr">
         <is>
-          <t>(Scopoli, 1763)</t>
+          <t>(L.) Buff. &amp; Fingerh.</t>
         </is>
       </c>
       <c r="I40" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>7</t>
         </is>
       </c>
       <c r="P40" t="inlineStr">
@@ -4850,10 +4876,10 @@
         </is>
       </c>
       <c r="Q40" t="n">
-        <v>700290</v>
+        <v>700247</v>
       </c>
       <c r="R40" t="n">
-        <v>6359078</v>
+        <v>6359105</v>
       </c>
       <c r="S40" t="n">
         <v>5</v>
@@ -4917,61 +4943,48 @@
     </row>
     <row r="41">
       <c r="A41" t="n">
-        <v>126992159</v>
+        <v>126300265</v>
       </c>
       <c r="B41" t="n">
-        <v>43234</v>
+        <v>99142</v>
       </c>
       <c r="D41" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E41" t="n">
-        <v>101242</v>
+        <v>219847</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Dårgräsfjäril</t>
+          <t>Tvåblad</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>Lopinga achine</t>
+          <t>Neottia ovata</t>
         </is>
       </c>
       <c r="H41" t="inlineStr">
         <is>
-          <t>(Scopoli, 1763)</t>
-        </is>
-      </c>
-      <c r="I41" t="inlineStr">
-        <is>
-          <t>8</t>
-        </is>
-      </c>
-      <c r="J41" t="inlineStr"/>
-      <c r="K41" t="inlineStr">
-        <is>
-          <t>imago/adult</t>
-        </is>
-      </c>
-      <c r="L41" t="inlineStr"/>
-      <c r="M41" t="inlineStr"/>
-      <c r="N41" t="inlineStr"/>
+          <t>(L.) Buff. &amp; Fingerh.</t>
+        </is>
+      </c>
+      <c r="I41" t="inlineStr"/>
       <c r="P41" t="inlineStr">
         <is>
-          <t>4. Botes källmyr, Gtl</t>
+          <t>Gerum, Likmunds 1:2 (4), Gtl</t>
         </is>
       </c>
       <c r="Q41" t="n">
-        <v>700334</v>
+        <v>700247</v>
       </c>
       <c r="R41" t="n">
-        <v>6359040</v>
+        <v>6359082</v>
       </c>
       <c r="S41" t="n">
-        <v>5</v>
+        <v>8</v>
       </c>
       <c r="T41" t="inlineStr">
         <is>
@@ -5009,26 +5022,2493 @@
       <c r="AE41" t="b">
         <v>0</v>
       </c>
-      <c r="AF41" t="inlineStr"/>
       <c r="AG41" t="b">
         <v>0</v>
+      </c>
+      <c r="AI41" t="inlineStr">
+        <is>
+          <t>Hästbetad blandskog</t>
+        </is>
       </c>
       <c r="AT41" t="inlineStr"/>
       <c r="AW41" t="inlineStr">
         <is>
-          <t>Arne Pettersson</t>
+          <t>Gun Ingmansson</t>
         </is>
       </c>
       <c r="AX41" t="inlineStr">
         <is>
-          <t>Arne Pettersson</t>
-        </is>
-      </c>
-      <c r="AY41" t="inlineStr">
-        <is>
-          <t>Biogeografisk uppföljning av fjärilar</t>
-        </is>
-      </c>
+          <t>Gun Ingmansson, Jörgen Petersson, Björn Larsson</t>
+        </is>
+      </c>
+      <c r="AY41" t="inlineStr"/>
+    </row>
+    <row r="42">
+      <c r="A42" t="n">
+        <v>126300268</v>
+      </c>
+      <c r="B42" t="n">
+        <v>99142</v>
+      </c>
+      <c r="D42" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E42" t="n">
+        <v>219847</v>
+      </c>
+      <c r="F42" t="inlineStr">
+        <is>
+          <t>Tvåblad</t>
+        </is>
+      </c>
+      <c r="G42" t="inlineStr">
+        <is>
+          <t>Neottia ovata</t>
+        </is>
+      </c>
+      <c r="H42" t="inlineStr">
+        <is>
+          <t>(L.) Buff. &amp; Fingerh.</t>
+        </is>
+      </c>
+      <c r="I42" t="inlineStr"/>
+      <c r="P42" t="inlineStr">
+        <is>
+          <t>Gerum, Likmunds 1:2 (4), Gtl</t>
+        </is>
+      </c>
+      <c r="Q42" t="n">
+        <v>700265</v>
+      </c>
+      <c r="R42" t="n">
+        <v>6359056</v>
+      </c>
+      <c r="S42" t="n">
+        <v>4</v>
+      </c>
+      <c r="T42" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="U42" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="V42" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="W42" t="inlineStr">
+        <is>
+          <t>Gerum</t>
+        </is>
+      </c>
+      <c r="Y42" t="inlineStr">
+        <is>
+          <t>2025-06-29</t>
+        </is>
+      </c>
+      <c r="AA42" t="inlineStr">
+        <is>
+          <t>2025-06-29</t>
+        </is>
+      </c>
+      <c r="AD42" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE42" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG42" t="b">
+        <v>0</v>
+      </c>
+      <c r="AI42" t="inlineStr">
+        <is>
+          <t>Hästbetad blandskog</t>
+        </is>
+      </c>
+      <c r="AT42" t="inlineStr"/>
+      <c r="AW42" t="inlineStr">
+        <is>
+          <t>Gun Ingmansson</t>
+        </is>
+      </c>
+      <c r="AX42" t="inlineStr">
+        <is>
+          <t>Gun Ingmansson, Jörgen Petersson, Björn Larsson</t>
+        </is>
+      </c>
+      <c r="AY42" t="inlineStr"/>
+    </row>
+    <row r="43">
+      <c r="A43" t="n">
+        <v>126300273</v>
+      </c>
+      <c r="B43" t="n">
+        <v>99142</v>
+      </c>
+      <c r="D43" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E43" t="n">
+        <v>219847</v>
+      </c>
+      <c r="F43" t="inlineStr">
+        <is>
+          <t>Tvåblad</t>
+        </is>
+      </c>
+      <c r="G43" t="inlineStr">
+        <is>
+          <t>Neottia ovata</t>
+        </is>
+      </c>
+      <c r="H43" t="inlineStr">
+        <is>
+          <t>(L.) Buff. &amp; Fingerh.</t>
+        </is>
+      </c>
+      <c r="I43" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="P43" t="inlineStr">
+        <is>
+          <t>Gerum, Likmunds 1:2 (4), Gtl</t>
+        </is>
+      </c>
+      <c r="Q43" t="n">
+        <v>700275</v>
+      </c>
+      <c r="R43" t="n">
+        <v>6359045</v>
+      </c>
+      <c r="S43" t="n">
+        <v>4</v>
+      </c>
+      <c r="T43" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="U43" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="V43" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="W43" t="inlineStr">
+        <is>
+          <t>Gerum</t>
+        </is>
+      </c>
+      <c r="Y43" t="inlineStr">
+        <is>
+          <t>2025-06-29</t>
+        </is>
+      </c>
+      <c r="AA43" t="inlineStr">
+        <is>
+          <t>2025-06-29</t>
+        </is>
+      </c>
+      <c r="AD43" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE43" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG43" t="b">
+        <v>0</v>
+      </c>
+      <c r="AI43" t="inlineStr">
+        <is>
+          <t>Hästbetad blandskog</t>
+        </is>
+      </c>
+      <c r="AT43" t="inlineStr"/>
+      <c r="AW43" t="inlineStr">
+        <is>
+          <t>Gun Ingmansson</t>
+        </is>
+      </c>
+      <c r="AX43" t="inlineStr">
+        <is>
+          <t>Gun Ingmansson, Jörgen Petersson, Björn Larsson</t>
+        </is>
+      </c>
+      <c r="AY43" t="inlineStr"/>
+    </row>
+    <row r="44">
+      <c r="A44" t="n">
+        <v>126514045</v>
+      </c>
+      <c r="B44" t="n">
+        <v>99142</v>
+      </c>
+      <c r="D44" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E44" t="n">
+        <v>219847</v>
+      </c>
+      <c r="F44" t="inlineStr">
+        <is>
+          <t>Tvåblad</t>
+        </is>
+      </c>
+      <c r="G44" t="inlineStr">
+        <is>
+          <t>Neottia ovata</t>
+        </is>
+      </c>
+      <c r="H44" t="inlineStr">
+        <is>
+          <t>(L.) Buff. &amp; Fingerh.</t>
+        </is>
+      </c>
+      <c r="I44" t="inlineStr"/>
+      <c r="P44" t="inlineStr">
+        <is>
+          <t>Gerum, Likmunds 1:2 (4), Gtl</t>
+        </is>
+      </c>
+      <c r="Q44" t="n">
+        <v>700215</v>
+      </c>
+      <c r="R44" t="n">
+        <v>6359155</v>
+      </c>
+      <c r="S44" t="n">
+        <v>8</v>
+      </c>
+      <c r="T44" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="U44" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="V44" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="W44" t="inlineStr">
+        <is>
+          <t>Gerum</t>
+        </is>
+      </c>
+      <c r="Y44" t="inlineStr">
+        <is>
+          <t>2025-06-29</t>
+        </is>
+      </c>
+      <c r="AA44" t="inlineStr">
+        <is>
+          <t>2025-06-29</t>
+        </is>
+      </c>
+      <c r="AD44" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE44" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG44" t="b">
+        <v>0</v>
+      </c>
+      <c r="AI44" t="inlineStr">
+        <is>
+          <t>Hästbetad blandskog</t>
+        </is>
+      </c>
+      <c r="AT44" t="inlineStr"/>
+      <c r="AW44" t="inlineStr">
+        <is>
+          <t>Gun Ingmansson</t>
+        </is>
+      </c>
+      <c r="AX44" t="inlineStr">
+        <is>
+          <t>Gun Ingmansson, Jörgen Petersson, Björn Larsson</t>
+        </is>
+      </c>
+      <c r="AY44" t="inlineStr"/>
+    </row>
+    <row r="45">
+      <c r="A45" t="n">
+        <v>126514049</v>
+      </c>
+      <c r="B45" t="n">
+        <v>99142</v>
+      </c>
+      <c r="D45" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E45" t="n">
+        <v>219847</v>
+      </c>
+      <c r="F45" t="inlineStr">
+        <is>
+          <t>Tvåblad</t>
+        </is>
+      </c>
+      <c r="G45" t="inlineStr">
+        <is>
+          <t>Neottia ovata</t>
+        </is>
+      </c>
+      <c r="H45" t="inlineStr">
+        <is>
+          <t>(L.) Buff. &amp; Fingerh.</t>
+        </is>
+      </c>
+      <c r="I45" t="inlineStr"/>
+      <c r="P45" t="inlineStr">
+        <is>
+          <t>Gerum, Likmunds 1:2 (4), Gtl</t>
+        </is>
+      </c>
+      <c r="Q45" t="n">
+        <v>700235</v>
+      </c>
+      <c r="R45" t="n">
+        <v>6359147</v>
+      </c>
+      <c r="S45" t="n">
+        <v>10</v>
+      </c>
+      <c r="T45" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="U45" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="V45" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="W45" t="inlineStr">
+        <is>
+          <t>Gerum</t>
+        </is>
+      </c>
+      <c r="Y45" t="inlineStr">
+        <is>
+          <t>2025-06-29</t>
+        </is>
+      </c>
+      <c r="AA45" t="inlineStr">
+        <is>
+          <t>2025-06-29</t>
+        </is>
+      </c>
+      <c r="AD45" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE45" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG45" t="b">
+        <v>0</v>
+      </c>
+      <c r="AI45" t="inlineStr">
+        <is>
+          <t>Hästbetad blandskog</t>
+        </is>
+      </c>
+      <c r="AT45" t="inlineStr"/>
+      <c r="AW45" t="inlineStr">
+        <is>
+          <t>Gun Ingmansson</t>
+        </is>
+      </c>
+      <c r="AX45" t="inlineStr">
+        <is>
+          <t>Gun Ingmansson, Jörgen Petersson, Björn Larsson</t>
+        </is>
+      </c>
+      <c r="AY45" t="inlineStr"/>
+    </row>
+    <row r="46">
+      <c r="A46" t="n">
+        <v>126300267</v>
+      </c>
+      <c r="B46" t="n">
+        <v>99141</v>
+      </c>
+      <c r="D46" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E46" t="n">
+        <v>219862</v>
+      </c>
+      <c r="F46" t="inlineStr">
+        <is>
+          <t>Nästrot</t>
+        </is>
+      </c>
+      <c r="G46" t="inlineStr">
+        <is>
+          <t>Neottia nidus-avis</t>
+        </is>
+      </c>
+      <c r="H46" t="inlineStr">
+        <is>
+          <t>(L.) Rich.</t>
+        </is>
+      </c>
+      <c r="I46" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="P46" t="inlineStr">
+        <is>
+          <t>Gerum, Likmunds 1:2 (4), Gtl</t>
+        </is>
+      </c>
+      <c r="Q46" t="n">
+        <v>700257</v>
+      </c>
+      <c r="R46" t="n">
+        <v>6359067</v>
+      </c>
+      <c r="S46" t="n">
+        <v>10</v>
+      </c>
+      <c r="T46" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="U46" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="V46" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="W46" t="inlineStr">
+        <is>
+          <t>Gerum</t>
+        </is>
+      </c>
+      <c r="Y46" t="inlineStr">
+        <is>
+          <t>2025-06-29</t>
+        </is>
+      </c>
+      <c r="AA46" t="inlineStr">
+        <is>
+          <t>2025-06-29</t>
+        </is>
+      </c>
+      <c r="AD46" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE46" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG46" t="b">
+        <v>0</v>
+      </c>
+      <c r="AI46" t="inlineStr">
+        <is>
+          <t>Hästbetad blandskog</t>
+        </is>
+      </c>
+      <c r="AT46" t="inlineStr"/>
+      <c r="AW46" t="inlineStr">
+        <is>
+          <t>Gun Ingmansson</t>
+        </is>
+      </c>
+      <c r="AX46" t="inlineStr">
+        <is>
+          <t>Gun Ingmansson, Jörgen Petersson, Björn Larsson</t>
+        </is>
+      </c>
+      <c r="AY46" t="inlineStr"/>
+    </row>
+    <row r="47">
+      <c r="A47" t="n">
+        <v>97960624</v>
+      </c>
+      <c r="B47" t="n">
+        <v>110078</v>
+      </c>
+      <c r="D47" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E47" t="n">
+        <v>220299</v>
+      </c>
+      <c r="F47" t="inlineStr">
+        <is>
+          <t>Svinrot</t>
+        </is>
+      </c>
+      <c r="G47" t="inlineStr">
+        <is>
+          <t>Scorzonera humilis</t>
+        </is>
+      </c>
+      <c r="H47" t="inlineStr">
+        <is>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I47" t="inlineStr"/>
+      <c r="J47" t="inlineStr"/>
+      <c r="K47" t="inlineStr">
+        <is>
+          <t>vinterståndare</t>
+        </is>
+      </c>
+      <c r="L47" t="inlineStr"/>
+      <c r="N47" t="inlineStr"/>
+      <c r="P47" t="inlineStr">
+        <is>
+          <t>Russparken, parkeringen 100m N, Gtl</t>
+        </is>
+      </c>
+      <c r="Q47" t="n">
+        <v>700333</v>
+      </c>
+      <c r="R47" t="n">
+        <v>6359040</v>
+      </c>
+      <c r="S47" t="n">
+        <v>25</v>
+      </c>
+      <c r="T47" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="U47" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="V47" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="W47" t="inlineStr">
+        <is>
+          <t>Gerum</t>
+        </is>
+      </c>
+      <c r="Y47" t="inlineStr">
+        <is>
+          <t>2022-01-06</t>
+        </is>
+      </c>
+      <c r="AA47" t="inlineStr">
+        <is>
+          <t>2022-01-06</t>
+        </is>
+      </c>
+      <c r="AD47" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE47" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF47" t="inlineStr"/>
+      <c r="AG47" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT47" t="inlineStr"/>
+      <c r="AW47" t="inlineStr">
+        <is>
+          <t>Dennis Nyström</t>
+        </is>
+      </c>
+      <c r="AX47" t="inlineStr">
+        <is>
+          <t>Dennis Nyström</t>
+        </is>
+      </c>
+      <c r="AY47" t="inlineStr"/>
+    </row>
+    <row r="48">
+      <c r="A48" t="n">
+        <v>2760594</v>
+      </c>
+      <c r="B48" t="n">
+        <v>110117</v>
+      </c>
+      <c r="D48" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E48" t="n">
+        <v>220320</v>
+      </c>
+      <c r="F48" t="inlineStr">
+        <is>
+          <t>Ängsskära</t>
+        </is>
+      </c>
+      <c r="G48" t="inlineStr">
+        <is>
+          <t>Serratula tinctoria</t>
+        </is>
+      </c>
+      <c r="H48" t="inlineStr">
+        <is>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I48" t="inlineStr">
+        <is>
+          <t>49</t>
+        </is>
+      </c>
+      <c r="J48" t="inlineStr">
+        <is>
+          <t>stjälkar/strån/skott</t>
+        </is>
+      </c>
+      <c r="K48" t="inlineStr">
+        <is>
+          <t>frukt-/fröspridning</t>
+        </is>
+      </c>
+      <c r="P48" t="inlineStr">
+        <is>
+          <t>Lojsta hed, Botes källmyr S-ut, Gtl</t>
+        </is>
+      </c>
+      <c r="Q48" t="n">
+        <v>700332</v>
+      </c>
+      <c r="R48" t="n">
+        <v>6359036</v>
+      </c>
+      <c r="S48" t="n">
+        <v>5</v>
+      </c>
+      <c r="T48" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="U48" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="V48" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="W48" t="inlineStr">
+        <is>
+          <t>Gerum</t>
+        </is>
+      </c>
+      <c r="Y48" t="inlineStr">
+        <is>
+          <t>2008-09-04</t>
+        </is>
+      </c>
+      <c r="AA48" t="inlineStr">
+        <is>
+          <t>2008-09-04</t>
+        </is>
+      </c>
+      <c r="AC48" t="inlineStr">
+        <is>
+          <t>Återfynd.</t>
+        </is>
+      </c>
+      <c r="AD48" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE48" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG48" t="b">
+        <v>0</v>
+      </c>
+      <c r="AI48" t="inlineStr">
+        <is>
+          <t>Stigkant</t>
+        </is>
+      </c>
+      <c r="AT48" t="inlineStr"/>
+      <c r="AW48" t="inlineStr">
+        <is>
+          <t>Joakim Ekman</t>
+        </is>
+      </c>
+      <c r="AX48" t="inlineStr">
+        <is>
+          <t>Joakim Ekman, Gabriel Ekman</t>
+        </is>
+      </c>
+      <c r="AY48" t="inlineStr"/>
+    </row>
+    <row r="49">
+      <c r="A49" t="n">
+        <v>16230167</v>
+      </c>
+      <c r="B49" t="n">
+        <v>110117</v>
+      </c>
+      <c r="D49" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E49" t="n">
+        <v>220320</v>
+      </c>
+      <c r="F49" t="inlineStr">
+        <is>
+          <t>Ängsskära</t>
+        </is>
+      </c>
+      <c r="G49" t="inlineStr">
+        <is>
+          <t>Serratula tinctoria</t>
+        </is>
+      </c>
+      <c r="H49" t="inlineStr">
+        <is>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I49" t="inlineStr"/>
+      <c r="J49" t="inlineStr"/>
+      <c r="K49" t="inlineStr">
+        <is>
+          <t>blomning</t>
+        </is>
+      </c>
+      <c r="L49" t="inlineStr"/>
+      <c r="P49" t="inlineStr">
+        <is>
+          <t>Russparken, parkeringen 100m N, Gtl</t>
+        </is>
+      </c>
+      <c r="Q49" t="n">
+        <v>700333</v>
+      </c>
+      <c r="R49" t="n">
+        <v>6359040</v>
+      </c>
+      <c r="S49" t="n">
+        <v>25</v>
+      </c>
+      <c r="T49" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="U49" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="V49" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="W49" t="inlineStr">
+        <is>
+          <t>Gerum</t>
+        </is>
+      </c>
+      <c r="Y49" t="inlineStr">
+        <is>
+          <t>2014-07-21</t>
+        </is>
+      </c>
+      <c r="AA49" t="inlineStr">
+        <is>
+          <t>2014-07-21</t>
+        </is>
+      </c>
+      <c r="AD49" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE49" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG49" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT49" t="inlineStr"/>
+      <c r="AW49" t="inlineStr">
+        <is>
+          <t>Dennis Nyström</t>
+        </is>
+      </c>
+      <c r="AX49" t="inlineStr">
+        <is>
+          <t>Dennis Nyström</t>
+        </is>
+      </c>
+      <c r="AY49" t="inlineStr"/>
+    </row>
+    <row r="50">
+      <c r="A50" t="n">
+        <v>16500486</v>
+      </c>
+      <c r="B50" t="n">
+        <v>110117</v>
+      </c>
+      <c r="D50" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E50" t="n">
+        <v>220320</v>
+      </c>
+      <c r="F50" t="inlineStr">
+        <is>
+          <t>Ängsskära</t>
+        </is>
+      </c>
+      <c r="G50" t="inlineStr">
+        <is>
+          <t>Serratula tinctoria</t>
+        </is>
+      </c>
+      <c r="H50" t="inlineStr">
+        <is>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I50" t="inlineStr"/>
+      <c r="J50" t="inlineStr"/>
+      <c r="K50" t="inlineStr"/>
+      <c r="L50" t="inlineStr"/>
+      <c r="P50" t="inlineStr">
+        <is>
+          <t>Lojsta, Gtl</t>
+        </is>
+      </c>
+      <c r="Q50" t="n">
+        <v>700339</v>
+      </c>
+      <c r="R50" t="n">
+        <v>6359017</v>
+      </c>
+      <c r="S50" t="n">
+        <v>25</v>
+      </c>
+      <c r="T50" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="U50" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="V50" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="W50" t="inlineStr">
+        <is>
+          <t>Fardhem</t>
+        </is>
+      </c>
+      <c r="Y50" t="inlineStr">
+        <is>
+          <t>2014-08-12</t>
+        </is>
+      </c>
+      <c r="AA50" t="inlineStr">
+        <is>
+          <t>2014-08-12</t>
+        </is>
+      </c>
+      <c r="AD50" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE50" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG50" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT50" t="inlineStr"/>
+      <c r="AW50" t="inlineStr">
+        <is>
+          <t>Thomas Strid</t>
+        </is>
+      </c>
+      <c r="AX50" t="inlineStr">
+        <is>
+          <t>Thomas Strid, Tiina Laantee, Melica Strid</t>
+        </is>
+      </c>
+      <c r="AY50" t="inlineStr"/>
+    </row>
+    <row r="51">
+      <c r="A51" t="n">
+        <v>69716937</v>
+      </c>
+      <c r="B51" t="n">
+        <v>110117</v>
+      </c>
+      <c r="D51" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E51" t="n">
+        <v>220320</v>
+      </c>
+      <c r="F51" t="inlineStr">
+        <is>
+          <t>Ängsskära</t>
+        </is>
+      </c>
+      <c r="G51" t="inlineStr">
+        <is>
+          <t>Serratula tinctoria</t>
+        </is>
+      </c>
+      <c r="H51" t="inlineStr">
+        <is>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I51" t="inlineStr"/>
+      <c r="K51" t="inlineStr">
+        <is>
+          <t>blomning</t>
+        </is>
+      </c>
+      <c r="P51" t="inlineStr">
+        <is>
+          <t>Lojsta hed, S om Botes källmyrs NR, Gtl</t>
+        </is>
+      </c>
+      <c r="Q51" t="n">
+        <v>700329</v>
+      </c>
+      <c r="R51" t="n">
+        <v>6359034</v>
+      </c>
+      <c r="S51" t="n">
+        <v>10</v>
+      </c>
+      <c r="T51" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="U51" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="V51" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="W51" t="inlineStr">
+        <is>
+          <t>Gerum</t>
+        </is>
+      </c>
+      <c r="Y51" t="inlineStr">
+        <is>
+          <t>2009-07-23</t>
+        </is>
+      </c>
+      <c r="AA51" t="inlineStr">
+        <is>
+          <t>2009-07-23</t>
+        </is>
+      </c>
+      <c r="AD51" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE51" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG51" t="b">
+        <v>0</v>
+      </c>
+      <c r="AI51" t="inlineStr">
+        <is>
+          <t>Fuktig ängsmark</t>
+        </is>
+      </c>
+      <c r="AT51" t="inlineStr"/>
+      <c r="AW51" t="inlineStr">
+        <is>
+          <t>Jan Yngve Andersson</t>
+        </is>
+      </c>
+      <c r="AX51" t="inlineStr">
+        <is>
+          <t>Jan Yngve Andersson</t>
+        </is>
+      </c>
+      <c r="AY51" t="inlineStr"/>
+    </row>
+    <row r="52">
+      <c r="A52" t="n">
+        <v>105024185</v>
+      </c>
+      <c r="B52" t="n">
+        <v>110117</v>
+      </c>
+      <c r="D52" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E52" t="n">
+        <v>220320</v>
+      </c>
+      <c r="F52" t="inlineStr">
+        <is>
+          <t>Ängsskära</t>
+        </is>
+      </c>
+      <c r="G52" t="inlineStr">
+        <is>
+          <t>Serratula tinctoria</t>
+        </is>
+      </c>
+      <c r="H52" t="inlineStr">
+        <is>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I52" t="inlineStr">
+        <is>
+          <t>57</t>
+        </is>
+      </c>
+      <c r="J52" t="inlineStr">
+        <is>
+          <t>stjälkar/strån/skott</t>
+        </is>
+      </c>
+      <c r="P52" t="inlineStr">
+        <is>
+          <t>Lilla Korsgatan N, Gtl</t>
+        </is>
+      </c>
+      <c r="Q52" t="n">
+        <v>700333</v>
+      </c>
+      <c r="R52" t="n">
+        <v>6359035</v>
+      </c>
+      <c r="S52" t="n">
+        <v>10</v>
+      </c>
+      <c r="T52" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="U52" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="V52" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="W52" t="inlineStr">
+        <is>
+          <t>Gerum</t>
+        </is>
+      </c>
+      <c r="Y52" t="inlineStr">
+        <is>
+          <t>2008-07-26</t>
+        </is>
+      </c>
+      <c r="AA52" t="inlineStr">
+        <is>
+          <t>2008-07-26</t>
+        </is>
+      </c>
+      <c r="AC52" t="inlineStr">
+        <is>
+          <t>57 stänglar, ca 25 ex. Tidigare känd lokal. - xkoord = 1651946, ykoord = 6358867</t>
+        </is>
+      </c>
+      <c r="AD52" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE52" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG52" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT52" t="inlineStr"/>
+      <c r="AW52" t="inlineStr">
+        <is>
+          <t>Jörgen Petersson</t>
+        </is>
+      </c>
+      <c r="AX52" t="inlineStr">
+        <is>
+          <t>Jörgen Petersson</t>
+        </is>
+      </c>
+      <c r="AY52" t="inlineStr">
+        <is>
+          <t>Projekt Gotlands Flora</t>
+        </is>
+      </c>
+    </row>
+    <row r="53">
+      <c r="A53" t="n">
+        <v>105024186</v>
+      </c>
+      <c r="B53" t="n">
+        <v>110117</v>
+      </c>
+      <c r="D53" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E53" t="n">
+        <v>220320</v>
+      </c>
+      <c r="F53" t="inlineStr">
+        <is>
+          <t>Ängsskära</t>
+        </is>
+      </c>
+      <c r="G53" t="inlineStr">
+        <is>
+          <t>Serratula tinctoria</t>
+        </is>
+      </c>
+      <c r="H53" t="inlineStr">
+        <is>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I53" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J53" t="inlineStr">
+        <is>
+          <t>m²</t>
+        </is>
+      </c>
+      <c r="P53" t="inlineStr">
+        <is>
+          <t>Lilla Korsgatan 100 m N, vid stig mot Botes källmyr, Gtl</t>
+        </is>
+      </c>
+      <c r="Q53" t="n">
+        <v>700323</v>
+      </c>
+      <c r="R53" t="n">
+        <v>6359035</v>
+      </c>
+      <c r="S53" t="n">
+        <v>10</v>
+      </c>
+      <c r="T53" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="U53" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="V53" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="W53" t="inlineStr">
+        <is>
+          <t>Gerum</t>
+        </is>
+      </c>
+      <c r="Y53" t="inlineStr">
+        <is>
+          <t>2003-08-30</t>
+        </is>
+      </c>
+      <c r="AA53" t="inlineStr">
+        <is>
+          <t>2003-08-30</t>
+        </is>
+      </c>
+      <c r="AD53" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE53" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG53" t="b">
+        <v>0</v>
+      </c>
+      <c r="AI53" t="inlineStr">
+        <is>
+          <t>Körvägkant.</t>
+        </is>
+      </c>
+      <c r="AT53" t="inlineStr"/>
+      <c r="AW53" t="inlineStr">
+        <is>
+          <t>Jörgen Petersson</t>
+        </is>
+      </c>
+      <c r="AX53" t="inlineStr">
+        <is>
+          <t>Jörgen Petersson</t>
+        </is>
+      </c>
+      <c r="AY53" t="inlineStr">
+        <is>
+          <t>Projekt Gotlands Flora</t>
+        </is>
+      </c>
+    </row>
+    <row r="54">
+      <c r="A54" t="n">
+        <v>105024198</v>
+      </c>
+      <c r="B54" t="n">
+        <v>110117</v>
+      </c>
+      <c r="D54" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E54" t="n">
+        <v>220320</v>
+      </c>
+      <c r="F54" t="inlineStr">
+        <is>
+          <t>Ängsskära</t>
+        </is>
+      </c>
+      <c r="G54" t="inlineStr">
+        <is>
+          <t>Serratula tinctoria</t>
+        </is>
+      </c>
+      <c r="H54" t="inlineStr">
+        <is>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I54" t="inlineStr">
+        <is>
+          <t>57</t>
+        </is>
+      </c>
+      <c r="J54" t="inlineStr">
+        <is>
+          <t>stjälkar/strån/skott</t>
+        </is>
+      </c>
+      <c r="P54" t="inlineStr">
+        <is>
+          <t>Lilla Korsgatan N, vid stig mot Botes källmyr, Gtl</t>
+        </is>
+      </c>
+      <c r="Q54" t="n">
+        <v>700333</v>
+      </c>
+      <c r="R54" t="n">
+        <v>6359015</v>
+      </c>
+      <c r="S54" t="n">
+        <v>25</v>
+      </c>
+      <c r="T54" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="U54" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="V54" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="W54" t="inlineStr">
+        <is>
+          <t>Fardhem</t>
+        </is>
+      </c>
+      <c r="Y54" t="inlineStr">
+        <is>
+          <t>2006-07-04</t>
+        </is>
+      </c>
+      <c r="AA54" t="inlineStr">
+        <is>
+          <t>2006-07-04</t>
+        </is>
+      </c>
+      <c r="AC54" t="inlineStr">
+        <is>
+          <t>57 stänglar. Ungefärlig koordinat.</t>
+        </is>
+      </c>
+      <c r="AD54" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE54" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG54" t="b">
+        <v>0</v>
+      </c>
+      <c r="AI54" t="inlineStr">
+        <is>
+          <t>Stig i kalktallskog, delvis sandunderlag</t>
+        </is>
+      </c>
+      <c r="AT54" t="inlineStr"/>
+      <c r="AW54" t="inlineStr">
+        <is>
+          <t>Jörgen Petersson</t>
+        </is>
+      </c>
+      <c r="AX54" t="inlineStr">
+        <is>
+          <t>Jörgen Petersson</t>
+        </is>
+      </c>
+      <c r="AY54" t="inlineStr">
+        <is>
+          <t>Projekt Gotlands Flora</t>
+        </is>
+      </c>
+    </row>
+    <row r="55">
+      <c r="A55" t="n">
+        <v>111587690</v>
+      </c>
+      <c r="B55" t="n">
+        <v>110117</v>
+      </c>
+      <c r="D55" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E55" t="n">
+        <v>220320</v>
+      </c>
+      <c r="F55" t="inlineStr">
+        <is>
+          <t>Ängsskära</t>
+        </is>
+      </c>
+      <c r="G55" t="inlineStr">
+        <is>
+          <t>Serratula tinctoria</t>
+        </is>
+      </c>
+      <c r="H55" t="inlineStr">
+        <is>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I55" t="inlineStr">
+        <is>
+          <t>37</t>
+        </is>
+      </c>
+      <c r="J55" t="inlineStr">
+        <is>
+          <t>stjälkar/strån/skott</t>
+        </is>
+      </c>
+      <c r="K55" t="inlineStr">
+        <is>
+          <t>överblommad</t>
+        </is>
+      </c>
+      <c r="L55" t="inlineStr"/>
+      <c r="N55" t="inlineStr"/>
+      <c r="P55" t="inlineStr">
+        <is>
+          <t>Botes källmyr, vägen, Gtl</t>
+        </is>
+      </c>
+      <c r="Q55" t="n">
+        <v>700319</v>
+      </c>
+      <c r="R55" t="n">
+        <v>6359038</v>
+      </c>
+      <c r="S55" t="n">
+        <v>25</v>
+      </c>
+      <c r="T55" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="U55" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="V55" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="W55" t="inlineStr">
+        <is>
+          <t>Gerum</t>
+        </is>
+      </c>
+      <c r="Y55" t="inlineStr">
+        <is>
+          <t>2023-08-15</t>
+        </is>
+      </c>
+      <c r="AA55" t="inlineStr">
+        <is>
+          <t>2023-08-15</t>
+        </is>
+      </c>
+      <c r="AD55" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE55" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF55" t="inlineStr"/>
+      <c r="AG55" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT55" t="inlineStr"/>
+      <c r="AW55" t="inlineStr">
+        <is>
+          <t>Kjell Eriksson</t>
+        </is>
+      </c>
+      <c r="AX55" t="inlineStr">
+        <is>
+          <t>Kjell Eriksson, Ulla Eriksson</t>
+        </is>
+      </c>
+      <c r="AY55" t="inlineStr"/>
+    </row>
+    <row r="56">
+      <c r="A56" t="n">
+        <v>126312506</v>
+      </c>
+      <c r="B56" t="n">
+        <v>110117</v>
+      </c>
+      <c r="D56" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E56" t="n">
+        <v>220320</v>
+      </c>
+      <c r="F56" t="inlineStr">
+        <is>
+          <t>Ängsskära</t>
+        </is>
+      </c>
+      <c r="G56" t="inlineStr">
+        <is>
+          <t>Serratula tinctoria</t>
+        </is>
+      </c>
+      <c r="H56" t="inlineStr">
+        <is>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I56" t="inlineStr">
+        <is>
+          <t>34</t>
+        </is>
+      </c>
+      <c r="J56" t="inlineStr">
+        <is>
+          <t>stjälkar/strån/skott</t>
+        </is>
+      </c>
+      <c r="K56" t="inlineStr">
+        <is>
+          <t>blomknopp</t>
+        </is>
+      </c>
+      <c r="P56" t="inlineStr">
+        <is>
+          <t>Lilla Korsgatan, Gtl</t>
+        </is>
+      </c>
+      <c r="Q56" t="n">
+        <v>700335</v>
+      </c>
+      <c r="R56" t="n">
+        <v>6359040</v>
+      </c>
+      <c r="S56" t="n">
+        <v>25</v>
+      </c>
+      <c r="T56" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="U56" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="V56" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="W56" t="inlineStr">
+        <is>
+          <t>Gerum</t>
+        </is>
+      </c>
+      <c r="Y56" t="inlineStr">
+        <is>
+          <t>2025-06-30</t>
+        </is>
+      </c>
+      <c r="AA56" t="inlineStr">
+        <is>
+          <t>2025-06-30</t>
+        </is>
+      </c>
+      <c r="AD56" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE56" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG56" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT56" t="inlineStr"/>
+      <c r="AW56" t="inlineStr">
+        <is>
+          <t>Felicia Wikinger</t>
+        </is>
+      </c>
+      <c r="AX56" t="inlineStr">
+        <is>
+          <t>Felicia Wikinger, Teo Jernkvist</t>
+        </is>
+      </c>
+      <c r="AY56" t="inlineStr"/>
+    </row>
+    <row r="57">
+      <c r="A57" t="n">
+        <v>116259105</v>
+      </c>
+      <c r="B57" t="n">
+        <v>101326</v>
+      </c>
+      <c r="D57" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E57" t="n">
+        <v>222498</v>
+      </c>
+      <c r="F57" t="inlineStr">
+        <is>
+          <t>Blåsippa</t>
+        </is>
+      </c>
+      <c r="G57" t="inlineStr">
+        <is>
+          <t>Hepatica nobilis</t>
+        </is>
+      </c>
+      <c r="H57" t="inlineStr">
+        <is>
+          <t>Schreb.</t>
+        </is>
+      </c>
+      <c r="I57" t="inlineStr"/>
+      <c r="P57" t="inlineStr">
+        <is>
+          <t>Gerum Likmunds 1:2 (4), Gtl</t>
+        </is>
+      </c>
+      <c r="Q57" t="n">
+        <v>700330</v>
+      </c>
+      <c r="R57" t="n">
+        <v>6359014</v>
+      </c>
+      <c r="S57" t="n">
+        <v>5</v>
+      </c>
+      <c r="T57" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="U57" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="V57" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="W57" t="inlineStr">
+        <is>
+          <t>Gerum</t>
+        </is>
+      </c>
+      <c r="Y57" t="inlineStr">
+        <is>
+          <t>2024-04-23</t>
+        </is>
+      </c>
+      <c r="AA57" t="inlineStr">
+        <is>
+          <t>2024-04-23</t>
+        </is>
+      </c>
+      <c r="AC57" t="inlineStr">
+        <is>
+          <t>Spridd i hela skogen.</t>
+        </is>
+      </c>
+      <c r="AD57" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE57" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG57" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT57" t="inlineStr"/>
+      <c r="AW57" t="inlineStr">
+        <is>
+          <t>Jörgen Petersson</t>
+        </is>
+      </c>
+      <c r="AX57" t="inlineStr">
+        <is>
+          <t>Jörgen Petersson</t>
+        </is>
+      </c>
+      <c r="AY57" t="inlineStr"/>
+    </row>
+    <row r="58">
+      <c r="A58" t="n">
+        <v>126300259</v>
+      </c>
+      <c r="B58" t="n">
+        <v>99036</v>
+      </c>
+      <c r="D58" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E58" t="n">
+        <v>223591</v>
+      </c>
+      <c r="F58" t="inlineStr">
+        <is>
+          <t>Skogsnycklar</t>
+        </is>
+      </c>
+      <c r="G58" t="inlineStr">
+        <is>
+          <t>Dactylorhiza maculata subsp. fuchsii</t>
+        </is>
+      </c>
+      <c r="H58" t="inlineStr">
+        <is>
+          <t>(Druce) Hyl.</t>
+        </is>
+      </c>
+      <c r="I58" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="P58" t="inlineStr">
+        <is>
+          <t>Gerum, Likmunds 1:2 (4), Gtl</t>
+        </is>
+      </c>
+      <c r="Q58" t="n">
+        <v>700247</v>
+      </c>
+      <c r="R58" t="n">
+        <v>6359105</v>
+      </c>
+      <c r="S58" t="n">
+        <v>5</v>
+      </c>
+      <c r="T58" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="U58" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="V58" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="W58" t="inlineStr">
+        <is>
+          <t>Gerum</t>
+        </is>
+      </c>
+      <c r="Y58" t="inlineStr">
+        <is>
+          <t>2025-06-29</t>
+        </is>
+      </c>
+      <c r="AA58" t="inlineStr">
+        <is>
+          <t>2025-06-29</t>
+        </is>
+      </c>
+      <c r="AD58" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE58" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG58" t="b">
+        <v>0</v>
+      </c>
+      <c r="AI58" t="inlineStr">
+        <is>
+          <t>Hästbetad blandskog</t>
+        </is>
+      </c>
+      <c r="AT58" t="inlineStr"/>
+      <c r="AW58" t="inlineStr">
+        <is>
+          <t>Gun Ingmansson</t>
+        </is>
+      </c>
+      <c r="AX58" t="inlineStr">
+        <is>
+          <t>Gun Ingmansson, Jörgen Petersson, Björn Larsson</t>
+        </is>
+      </c>
+      <c r="AY58" t="inlineStr"/>
+    </row>
+    <row r="59">
+      <c r="A59" t="n">
+        <v>126300263</v>
+      </c>
+      <c r="B59" t="n">
+        <v>99036</v>
+      </c>
+      <c r="D59" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E59" t="n">
+        <v>223591</v>
+      </c>
+      <c r="F59" t="inlineStr">
+        <is>
+          <t>Skogsnycklar</t>
+        </is>
+      </c>
+      <c r="G59" t="inlineStr">
+        <is>
+          <t>Dactylorhiza maculata subsp. fuchsii</t>
+        </is>
+      </c>
+      <c r="H59" t="inlineStr">
+        <is>
+          <t>(Druce) Hyl.</t>
+        </is>
+      </c>
+      <c r="I59" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="P59" t="inlineStr">
+        <is>
+          <t>Gerum, Likmunds 1:2 (4), Gtl</t>
+        </is>
+      </c>
+      <c r="Q59" t="n">
+        <v>700253</v>
+      </c>
+      <c r="R59" t="n">
+        <v>6359086</v>
+      </c>
+      <c r="S59" t="n">
+        <v>4</v>
+      </c>
+      <c r="T59" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="U59" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="V59" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="W59" t="inlineStr">
+        <is>
+          <t>Gerum</t>
+        </is>
+      </c>
+      <c r="Y59" t="inlineStr">
+        <is>
+          <t>2025-06-29</t>
+        </is>
+      </c>
+      <c r="AA59" t="inlineStr">
+        <is>
+          <t>2025-06-29</t>
+        </is>
+      </c>
+      <c r="AD59" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE59" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG59" t="b">
+        <v>0</v>
+      </c>
+      <c r="AI59" t="inlineStr">
+        <is>
+          <t>Hästbetad blandskog</t>
+        </is>
+      </c>
+      <c r="AT59" t="inlineStr"/>
+      <c r="AW59" t="inlineStr">
+        <is>
+          <t>Gun Ingmansson</t>
+        </is>
+      </c>
+      <c r="AX59" t="inlineStr">
+        <is>
+          <t>Gun Ingmansson, Jörgen Petersson, Björn Larsson</t>
+        </is>
+      </c>
+      <c r="AY59" t="inlineStr"/>
+    </row>
+    <row r="60">
+      <c r="A60" t="n">
+        <v>126300266</v>
+      </c>
+      <c r="B60" t="n">
+        <v>99036</v>
+      </c>
+      <c r="D60" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E60" t="n">
+        <v>223591</v>
+      </c>
+      <c r="F60" t="inlineStr">
+        <is>
+          <t>Skogsnycklar</t>
+        </is>
+      </c>
+      <c r="G60" t="inlineStr">
+        <is>
+          <t>Dactylorhiza maculata subsp. fuchsii</t>
+        </is>
+      </c>
+      <c r="H60" t="inlineStr">
+        <is>
+          <t>(Druce) Hyl.</t>
+        </is>
+      </c>
+      <c r="I60" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="P60" t="inlineStr">
+        <is>
+          <t>Gerum, Likmunds 1:2 (4), Gtl</t>
+        </is>
+      </c>
+      <c r="Q60" t="n">
+        <v>700247</v>
+      </c>
+      <c r="R60" t="n">
+        <v>6359082</v>
+      </c>
+      <c r="S60" t="n">
+        <v>8</v>
+      </c>
+      <c r="T60" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="U60" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="V60" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="W60" t="inlineStr">
+        <is>
+          <t>Gerum</t>
+        </is>
+      </c>
+      <c r="Y60" t="inlineStr">
+        <is>
+          <t>2025-06-29</t>
+        </is>
+      </c>
+      <c r="AA60" t="inlineStr">
+        <is>
+          <t>2025-06-29</t>
+        </is>
+      </c>
+      <c r="AD60" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE60" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG60" t="b">
+        <v>0</v>
+      </c>
+      <c r="AI60" t="inlineStr">
+        <is>
+          <t>Hästbetad blandskog</t>
+        </is>
+      </c>
+      <c r="AT60" t="inlineStr"/>
+      <c r="AW60" t="inlineStr">
+        <is>
+          <t>Gun Ingmansson</t>
+        </is>
+      </c>
+      <c r="AX60" t="inlineStr">
+        <is>
+          <t>Gun Ingmansson, Jörgen Petersson, Björn Larsson</t>
+        </is>
+      </c>
+      <c r="AY60" t="inlineStr"/>
+    </row>
+    <row r="61">
+      <c r="A61" t="n">
+        <v>126300270</v>
+      </c>
+      <c r="B61" t="n">
+        <v>99036</v>
+      </c>
+      <c r="D61" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E61" t="n">
+        <v>223591</v>
+      </c>
+      <c r="F61" t="inlineStr">
+        <is>
+          <t>Skogsnycklar</t>
+        </is>
+      </c>
+      <c r="G61" t="inlineStr">
+        <is>
+          <t>Dactylorhiza maculata subsp. fuchsii</t>
+        </is>
+      </c>
+      <c r="H61" t="inlineStr">
+        <is>
+          <t>(Druce) Hyl.</t>
+        </is>
+      </c>
+      <c r="I61" t="inlineStr"/>
+      <c r="P61" t="inlineStr">
+        <is>
+          <t>Gerum, Likmunds 1:2 (4), Gtl</t>
+        </is>
+      </c>
+      <c r="Q61" t="n">
+        <v>700265</v>
+      </c>
+      <c r="R61" t="n">
+        <v>6359056</v>
+      </c>
+      <c r="S61" t="n">
+        <v>4</v>
+      </c>
+      <c r="T61" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="U61" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="V61" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="W61" t="inlineStr">
+        <is>
+          <t>Gerum</t>
+        </is>
+      </c>
+      <c r="Y61" t="inlineStr">
+        <is>
+          <t>2025-06-29</t>
+        </is>
+      </c>
+      <c r="AA61" t="inlineStr">
+        <is>
+          <t>2025-06-29</t>
+        </is>
+      </c>
+      <c r="AD61" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE61" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG61" t="b">
+        <v>0</v>
+      </c>
+      <c r="AI61" t="inlineStr">
+        <is>
+          <t>Hästbetad blandskog</t>
+        </is>
+      </c>
+      <c r="AT61" t="inlineStr"/>
+      <c r="AW61" t="inlineStr">
+        <is>
+          <t>Gun Ingmansson</t>
+        </is>
+      </c>
+      <c r="AX61" t="inlineStr">
+        <is>
+          <t>Gun Ingmansson, Jörgen Petersson, Björn Larsson</t>
+        </is>
+      </c>
+      <c r="AY61" t="inlineStr"/>
+    </row>
+    <row r="62">
+      <c r="A62" t="n">
+        <v>126300272</v>
+      </c>
+      <c r="B62" t="n">
+        <v>99036</v>
+      </c>
+      <c r="D62" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E62" t="n">
+        <v>223591</v>
+      </c>
+      <c r="F62" t="inlineStr">
+        <is>
+          <t>Skogsnycklar</t>
+        </is>
+      </c>
+      <c r="G62" t="inlineStr">
+        <is>
+          <t>Dactylorhiza maculata subsp. fuchsii</t>
+        </is>
+      </c>
+      <c r="H62" t="inlineStr">
+        <is>
+          <t>(Druce) Hyl.</t>
+        </is>
+      </c>
+      <c r="I62" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="P62" t="inlineStr">
+        <is>
+          <t>Gerum, Likmunds 1:2 (4), Gtl</t>
+        </is>
+      </c>
+      <c r="Q62" t="n">
+        <v>700275</v>
+      </c>
+      <c r="R62" t="n">
+        <v>6359045</v>
+      </c>
+      <c r="S62" t="n">
+        <v>4</v>
+      </c>
+      <c r="T62" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="U62" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="V62" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="W62" t="inlineStr">
+        <is>
+          <t>Gerum</t>
+        </is>
+      </c>
+      <c r="Y62" t="inlineStr">
+        <is>
+          <t>2025-06-29</t>
+        </is>
+      </c>
+      <c r="AA62" t="inlineStr">
+        <is>
+          <t>2025-06-29</t>
+        </is>
+      </c>
+      <c r="AD62" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE62" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG62" t="b">
+        <v>0</v>
+      </c>
+      <c r="AI62" t="inlineStr">
+        <is>
+          <t>Hästbetad blandskog</t>
+        </is>
+      </c>
+      <c r="AT62" t="inlineStr"/>
+      <c r="AW62" t="inlineStr">
+        <is>
+          <t>Gun Ingmansson</t>
+        </is>
+      </c>
+      <c r="AX62" t="inlineStr">
+        <is>
+          <t>Gun Ingmansson, Jörgen Petersson, Björn Larsson</t>
+        </is>
+      </c>
+      <c r="AY62" t="inlineStr"/>
+    </row>
+    <row r="63">
+      <c r="A63" t="n">
+        <v>126514047</v>
+      </c>
+      <c r="B63" t="n">
+        <v>99036</v>
+      </c>
+      <c r="D63" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E63" t="n">
+        <v>223591</v>
+      </c>
+      <c r="F63" t="inlineStr">
+        <is>
+          <t>Skogsnycklar</t>
+        </is>
+      </c>
+      <c r="G63" t="inlineStr">
+        <is>
+          <t>Dactylorhiza maculata subsp. fuchsii</t>
+        </is>
+      </c>
+      <c r="H63" t="inlineStr">
+        <is>
+          <t>(Druce) Hyl.</t>
+        </is>
+      </c>
+      <c r="I63" t="inlineStr"/>
+      <c r="P63" t="inlineStr">
+        <is>
+          <t>Gerum, Likmunds 1:2 (4), Gtl</t>
+        </is>
+      </c>
+      <c r="Q63" t="n">
+        <v>700215</v>
+      </c>
+      <c r="R63" t="n">
+        <v>6359155</v>
+      </c>
+      <c r="S63" t="n">
+        <v>8</v>
+      </c>
+      <c r="T63" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="U63" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="V63" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="W63" t="inlineStr">
+        <is>
+          <t>Gerum</t>
+        </is>
+      </c>
+      <c r="Y63" t="inlineStr">
+        <is>
+          <t>2025-06-29</t>
+        </is>
+      </c>
+      <c r="AA63" t="inlineStr">
+        <is>
+          <t>2025-06-29</t>
+        </is>
+      </c>
+      <c r="AD63" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE63" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG63" t="b">
+        <v>0</v>
+      </c>
+      <c r="AI63" t="inlineStr">
+        <is>
+          <t>Hästbetad blandskog</t>
+        </is>
+      </c>
+      <c r="AT63" t="inlineStr"/>
+      <c r="AW63" t="inlineStr">
+        <is>
+          <t>Gun Ingmansson</t>
+        </is>
+      </c>
+      <c r="AX63" t="inlineStr">
+        <is>
+          <t>Gun Ingmansson, Jörgen Petersson, Björn Larsson</t>
+        </is>
+      </c>
+      <c r="AY63" t="inlineStr"/>
+    </row>
+    <row r="64">
+      <c r="A64" t="n">
+        <v>126300254</v>
+      </c>
+      <c r="B64" t="n">
+        <v>99155</v>
+      </c>
+      <c r="D64" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E64" t="n">
+        <v>223621</v>
+      </c>
+      <c r="F64" t="inlineStr">
+        <is>
+          <t>Skogsnattviol</t>
+        </is>
+      </c>
+      <c r="G64" t="inlineStr">
+        <is>
+          <t>Platanthera bifolia subsp. latiflora</t>
+        </is>
+      </c>
+      <c r="H64" t="inlineStr">
+        <is>
+          <t>(Drejer) Løjtnant</t>
+        </is>
+      </c>
+      <c r="I64" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="P64" t="inlineStr">
+        <is>
+          <t>Gerum, Likmunds 1:2 (4), Gtl</t>
+        </is>
+      </c>
+      <c r="Q64" t="n">
+        <v>700231</v>
+      </c>
+      <c r="R64" t="n">
+        <v>6359136</v>
+      </c>
+      <c r="S64" t="n">
+        <v>4</v>
+      </c>
+      <c r="T64" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="U64" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="V64" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="W64" t="inlineStr">
+        <is>
+          <t>Gerum</t>
+        </is>
+      </c>
+      <c r="Y64" t="inlineStr">
+        <is>
+          <t>2025-06-29</t>
+        </is>
+      </c>
+      <c r="AA64" t="inlineStr">
+        <is>
+          <t>2025-06-29</t>
+        </is>
+      </c>
+      <c r="AD64" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE64" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG64" t="b">
+        <v>0</v>
+      </c>
+      <c r="AI64" t="inlineStr">
+        <is>
+          <t>Hästbetad blandskog</t>
+        </is>
+      </c>
+      <c r="AT64" t="inlineStr"/>
+      <c r="AW64" t="inlineStr">
+        <is>
+          <t>Gun Ingmansson</t>
+        </is>
+      </c>
+      <c r="AX64" t="inlineStr">
+        <is>
+          <t>Gun Ingmansson, Jörgen Petersson, Björn Larsson</t>
+        </is>
+      </c>
+      <c r="AY64" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/artfynd/A 14354-2024 artfynd.xlsx
+++ b/artfynd/A 14354-2024 artfynd.xlsx
@@ -4389,7 +4389,7 @@
       </c>
       <c r="AX35" t="inlineStr">
         <is>
-          <t>Anna Helmersson, Margaret Rainey, Esmeralda  Svanberg</t>
+          <t>Anna Helmersson, Margaret Rainey, Esmeralda Svanberg</t>
         </is>
       </c>
       <c r="AY35" t="inlineStr"/>
@@ -4496,7 +4496,7 @@
       </c>
       <c r="AX36" t="inlineStr">
         <is>
-          <t>Anna Helmersson, Margaret Rainey, Esmeralda  Svanberg</t>
+          <t>Anna Helmersson, Margaret Rainey, Esmeralda Svanberg</t>
         </is>
       </c>
       <c r="AY36" t="inlineStr"/>
@@ -4608,7 +4608,7 @@
       </c>
       <c r="AX37" t="inlineStr">
         <is>
-          <t>Anna Helmersson, Margaret Rainey, Esmeralda  Svanberg</t>
+          <t>Anna Helmersson, Margaret Rainey, Esmeralda Svanberg</t>
         </is>
       </c>
       <c r="AY37" t="inlineStr"/>
@@ -4715,7 +4715,7 @@
       </c>
       <c r="AX38" t="inlineStr">
         <is>
-          <t>Anna Helmersson, Margaret Rainey, Esmeralda  Svanberg</t>
+          <t>Anna Helmersson, Margaret Rainey, Esmeralda Svanberg</t>
         </is>
       </c>
       <c r="AY38" t="inlineStr"/>
@@ -4822,7 +4822,7 @@
       </c>
       <c r="AX39" t="inlineStr">
         <is>
-          <t>Anna Helmersson, Margaret Rainey, Esmeralda  Svanberg</t>
+          <t>Anna Helmersson, Margaret Rainey, Esmeralda Svanberg</t>
         </is>
       </c>
       <c r="AY39" t="inlineStr"/>
@@ -4934,7 +4934,7 @@
       </c>
       <c r="AX40" t="inlineStr">
         <is>
-          <t>Anna Helmersson, Margaret Rainey, Esmeralda  Svanberg</t>
+          <t>Anna Helmersson, Margaret Rainey, Esmeralda Svanberg</t>
         </is>
       </c>
       <c r="AY40" t="inlineStr"/>
@@ -5041,7 +5041,7 @@
       </c>
       <c r="AX41" t="inlineStr">
         <is>
-          <t>Anna Helmersson, Margaret Rainey, Esmeralda  Svanberg</t>
+          <t>Anna Helmersson, Margaret Rainey, Esmeralda Svanberg</t>
         </is>
       </c>
       <c r="AY41" t="inlineStr"/>
@@ -5153,7 +5153,7 @@
       </c>
       <c r="AX42" t="inlineStr">
         <is>
-          <t>Anna Helmersson, Margaret Rainey, Esmeralda  Svanberg</t>
+          <t>Anna Helmersson, Margaret Rainey, Esmeralda Svanberg</t>
         </is>
       </c>
       <c r="AY42" t="inlineStr"/>
@@ -5260,7 +5260,7 @@
       </c>
       <c r="AX43" t="inlineStr">
         <is>
-          <t>Anna Helmersson, Margaret Rainey, Esmeralda  Svanberg</t>
+          <t>Anna Helmersson, Margaret Rainey, Esmeralda Svanberg</t>
         </is>
       </c>
       <c r="AY43" t="inlineStr"/>
@@ -5367,7 +5367,7 @@
       </c>
       <c r="AX44" t="inlineStr">
         <is>
-          <t>Anna Helmersson, Margaret Rainey, Esmeralda  Svanberg</t>
+          <t>Anna Helmersson, Margaret Rainey, Esmeralda Svanberg</t>
         </is>
       </c>
       <c r="AY44" t="inlineStr"/>
@@ -5479,7 +5479,7 @@
       </c>
       <c r="AX45" t="inlineStr">
         <is>
-          <t>Anna Helmersson, Margaret Rainey, Esmeralda  Svanberg</t>
+          <t>Anna Helmersson, Margaret Rainey, Esmeralda Svanberg</t>
         </is>
       </c>
       <c r="AY45" t="inlineStr"/>
@@ -5591,7 +5591,7 @@
       </c>
       <c r="AX46" t="inlineStr">
         <is>
-          <t>Anna Helmersson, Margaret Rainey, Esmeralda  Svanberg</t>
+          <t>Anna Helmersson, Margaret Rainey, Esmeralda Svanberg</t>
         </is>
       </c>
       <c r="AY46" t="inlineStr"/>
@@ -5703,7 +5703,7 @@
       </c>
       <c r="AX47" t="inlineStr">
         <is>
-          <t>Anna Helmersson, Margaret Rainey, Esmeralda  Svanberg</t>
+          <t>Anna Helmersson, Margaret Rainey, Esmeralda Svanberg</t>
         </is>
       </c>
       <c r="AY47" t="inlineStr"/>
@@ -5815,7 +5815,7 @@
       </c>
       <c r="AX48" t="inlineStr">
         <is>
-          <t>Anna Helmersson, Margaret Rainey, Esmeralda  Svanberg</t>
+          <t>Anna Helmersson, Margaret Rainey, Esmeralda Svanberg</t>
         </is>
       </c>
       <c r="AY48" t="inlineStr"/>
@@ -7221,12 +7221,12 @@
       <c r="AT61" t="inlineStr"/>
       <c r="AW61" t="inlineStr">
         <is>
-          <t>Esmeralda  Svanberg</t>
+          <t>Esmeralda Svanberg</t>
         </is>
       </c>
       <c r="AX61" t="inlineStr">
         <is>
-          <t>Esmeralda  Svanberg</t>
+          <t>Esmeralda Svanberg</t>
         </is>
       </c>
       <c r="AY61" t="inlineStr"/>
@@ -7333,12 +7333,12 @@
       <c r="AT62" t="inlineStr"/>
       <c r="AW62" t="inlineStr">
         <is>
-          <t>Esmeralda  Svanberg</t>
+          <t>Esmeralda Svanberg</t>
         </is>
       </c>
       <c r="AX62" t="inlineStr">
         <is>
-          <t>Esmeralda  Svanberg</t>
+          <t>Esmeralda Svanberg</t>
         </is>
       </c>
       <c r="AY62" t="inlineStr"/>
@@ -7445,12 +7445,12 @@
       <c r="AT63" t="inlineStr"/>
       <c r="AW63" t="inlineStr">
         <is>
-          <t>Esmeralda  Svanberg</t>
+          <t>Esmeralda Svanberg</t>
         </is>
       </c>
       <c r="AX63" t="inlineStr">
         <is>
-          <t>Esmeralda  Svanberg</t>
+          <t>Esmeralda Svanberg</t>
         </is>
       </c>
       <c r="AY63" t="inlineStr"/>
@@ -7557,12 +7557,12 @@
       <c r="AT64" t="inlineStr"/>
       <c r="AW64" t="inlineStr">
         <is>
-          <t>Esmeralda  Svanberg</t>
+          <t>Esmeralda Svanberg</t>
         </is>
       </c>
       <c r="AX64" t="inlineStr">
         <is>
-          <t>Esmeralda  Svanberg</t>
+          <t>Esmeralda Svanberg</t>
         </is>
       </c>
       <c r="AY64" t="inlineStr"/>
@@ -7669,12 +7669,12 @@
       <c r="AT65" t="inlineStr"/>
       <c r="AW65" t="inlineStr">
         <is>
-          <t>Esmeralda  Svanberg</t>
+          <t>Esmeralda Svanberg</t>
         </is>
       </c>
       <c r="AX65" t="inlineStr">
         <is>
-          <t>Esmeralda  Svanberg</t>
+          <t>Esmeralda Svanberg</t>
         </is>
       </c>
       <c r="AY65" t="inlineStr"/>
@@ -7781,12 +7781,12 @@
       <c r="AT66" t="inlineStr"/>
       <c r="AW66" t="inlineStr">
         <is>
-          <t>Esmeralda  Svanberg</t>
+          <t>Esmeralda Svanberg</t>
         </is>
       </c>
       <c r="AX66" t="inlineStr">
         <is>
-          <t>Esmeralda  Svanberg</t>
+          <t>Esmeralda Svanberg</t>
         </is>
       </c>
       <c r="AY66" t="inlineStr"/>
@@ -7893,12 +7893,12 @@
       <c r="AT67" t="inlineStr"/>
       <c r="AW67" t="inlineStr">
         <is>
-          <t>Esmeralda  Svanberg</t>
+          <t>Esmeralda Svanberg</t>
         </is>
       </c>
       <c r="AX67" t="inlineStr">
         <is>
-          <t>Esmeralda  Svanberg</t>
+          <t>Esmeralda Svanberg</t>
         </is>
       </c>
       <c r="AY67" t="inlineStr"/>
@@ -8005,12 +8005,12 @@
       <c r="AT68" t="inlineStr"/>
       <c r="AW68" t="inlineStr">
         <is>
-          <t>Esmeralda  Svanberg</t>
+          <t>Esmeralda Svanberg</t>
         </is>
       </c>
       <c r="AX68" t="inlineStr">
         <is>
-          <t>Esmeralda  Svanberg</t>
+          <t>Esmeralda Svanberg</t>
         </is>
       </c>
       <c r="AY68" t="inlineStr"/>
@@ -8117,12 +8117,12 @@
       <c r="AT69" t="inlineStr"/>
       <c r="AW69" t="inlineStr">
         <is>
-          <t>Esmeralda  Svanberg</t>
+          <t>Esmeralda Svanberg</t>
         </is>
       </c>
       <c r="AX69" t="inlineStr">
         <is>
-          <t>Esmeralda  Svanberg</t>
+          <t>Esmeralda Svanberg</t>
         </is>
       </c>
       <c r="AY69" t="inlineStr"/>
@@ -8229,12 +8229,12 @@
       <c r="AT70" t="inlineStr"/>
       <c r="AW70" t="inlineStr">
         <is>
-          <t>Esmeralda  Svanberg</t>
+          <t>Esmeralda Svanberg</t>
         </is>
       </c>
       <c r="AX70" t="inlineStr">
         <is>
-          <t>Esmeralda  Svanberg</t>
+          <t>Esmeralda Svanberg</t>
         </is>
       </c>
       <c r="AY70" t="inlineStr"/>
@@ -8341,12 +8341,12 @@
       <c r="AT71" t="inlineStr"/>
       <c r="AW71" t="inlineStr">
         <is>
-          <t>Esmeralda  Svanberg</t>
+          <t>Esmeralda Svanberg</t>
         </is>
       </c>
       <c r="AX71" t="inlineStr">
         <is>
-          <t>Esmeralda  Svanberg</t>
+          <t>Esmeralda Svanberg</t>
         </is>
       </c>
       <c r="AY71" t="inlineStr"/>
@@ -8453,12 +8453,12 @@
       <c r="AT72" t="inlineStr"/>
       <c r="AW72" t="inlineStr">
         <is>
-          <t>Esmeralda  Svanberg</t>
+          <t>Esmeralda Svanberg</t>
         </is>
       </c>
       <c r="AX72" t="inlineStr">
         <is>
-          <t>Esmeralda  Svanberg</t>
+          <t>Esmeralda Svanberg</t>
         </is>
       </c>
       <c r="AY72" t="inlineStr"/>
@@ -8565,12 +8565,12 @@
       <c r="AT73" t="inlineStr"/>
       <c r="AW73" t="inlineStr">
         <is>
-          <t>Esmeralda  Svanberg</t>
+          <t>Esmeralda Svanberg</t>
         </is>
       </c>
       <c r="AX73" t="inlineStr">
         <is>
-          <t>Esmeralda  Svanberg</t>
+          <t>Esmeralda Svanberg</t>
         </is>
       </c>
       <c r="AY73" t="inlineStr"/>
@@ -8677,12 +8677,12 @@
       <c r="AT74" t="inlineStr"/>
       <c r="AW74" t="inlineStr">
         <is>
-          <t>Esmeralda  Svanberg</t>
+          <t>Esmeralda Svanberg</t>
         </is>
       </c>
       <c r="AX74" t="inlineStr">
         <is>
-          <t>Esmeralda  Svanberg</t>
+          <t>Esmeralda Svanberg</t>
         </is>
       </c>
       <c r="AY74" t="inlineStr"/>
@@ -8789,12 +8789,12 @@
       <c r="AT75" t="inlineStr"/>
       <c r="AW75" t="inlineStr">
         <is>
-          <t>Esmeralda  Svanberg</t>
+          <t>Esmeralda Svanberg</t>
         </is>
       </c>
       <c r="AX75" t="inlineStr">
         <is>
-          <t>Esmeralda  Svanberg</t>
+          <t>Esmeralda Svanberg</t>
         </is>
       </c>
       <c r="AY75" t="inlineStr"/>
@@ -8901,12 +8901,12 @@
       <c r="AT76" t="inlineStr"/>
       <c r="AW76" t="inlineStr">
         <is>
-          <t>Esmeralda  Svanberg</t>
+          <t>Esmeralda Svanberg</t>
         </is>
       </c>
       <c r="AX76" t="inlineStr">
         <is>
-          <t>Esmeralda  Svanberg</t>
+          <t>Esmeralda Svanberg</t>
         </is>
       </c>
       <c r="AY76" t="inlineStr"/>
@@ -9013,12 +9013,12 @@
       <c r="AT77" t="inlineStr"/>
       <c r="AW77" t="inlineStr">
         <is>
-          <t>Esmeralda  Svanberg</t>
+          <t>Esmeralda Svanberg</t>
         </is>
       </c>
       <c r="AX77" t="inlineStr">
         <is>
-          <t>Esmeralda  Svanberg</t>
+          <t>Esmeralda Svanberg</t>
         </is>
       </c>
       <c r="AY77" t="inlineStr"/>
@@ -9125,12 +9125,12 @@
       <c r="AT78" t="inlineStr"/>
       <c r="AW78" t="inlineStr">
         <is>
-          <t>Esmeralda  Svanberg</t>
+          <t>Esmeralda Svanberg</t>
         </is>
       </c>
       <c r="AX78" t="inlineStr">
         <is>
-          <t>Esmeralda  Svanberg</t>
+          <t>Esmeralda Svanberg</t>
         </is>
       </c>
       <c r="AY78" t="inlineStr"/>
@@ -9237,12 +9237,12 @@
       <c r="AT79" t="inlineStr"/>
       <c r="AW79" t="inlineStr">
         <is>
-          <t>Esmeralda  Svanberg</t>
+          <t>Esmeralda Svanberg</t>
         </is>
       </c>
       <c r="AX79" t="inlineStr">
         <is>
-          <t>Esmeralda  Svanberg</t>
+          <t>Esmeralda Svanberg</t>
         </is>
       </c>
       <c r="AY79" t="inlineStr"/>
@@ -9349,12 +9349,12 @@
       <c r="AT80" t="inlineStr"/>
       <c r="AW80" t="inlineStr">
         <is>
-          <t>Esmeralda  Svanberg</t>
+          <t>Esmeralda Svanberg</t>
         </is>
       </c>
       <c r="AX80" t="inlineStr">
         <is>
-          <t>Esmeralda  Svanberg</t>
+          <t>Esmeralda Svanberg</t>
         </is>
       </c>
       <c r="AY80" t="inlineStr"/>
@@ -9461,12 +9461,12 @@
       <c r="AT81" t="inlineStr"/>
       <c r="AW81" t="inlineStr">
         <is>
-          <t>Esmeralda  Svanberg</t>
+          <t>Esmeralda Svanberg</t>
         </is>
       </c>
       <c r="AX81" t="inlineStr">
         <is>
-          <t>Esmeralda  Svanberg</t>
+          <t>Esmeralda Svanberg</t>
         </is>
       </c>
       <c r="AY81" t="inlineStr"/>
@@ -9573,12 +9573,12 @@
       <c r="AT82" t="inlineStr"/>
       <c r="AW82" t="inlineStr">
         <is>
-          <t>Esmeralda  Svanberg</t>
+          <t>Esmeralda Svanberg</t>
         </is>
       </c>
       <c r="AX82" t="inlineStr">
         <is>
-          <t>Esmeralda  Svanberg</t>
+          <t>Esmeralda Svanberg</t>
         </is>
       </c>
       <c r="AY82" t="inlineStr"/>
@@ -11072,7 +11072,7 @@
       </c>
       <c r="AX96" t="inlineStr">
         <is>
-          <t>Anna Helmersson, Margaret Rainey, Esmeralda  Svanberg</t>
+          <t>Anna Helmersson, Margaret Rainey, Esmeralda Svanberg</t>
         </is>
       </c>
       <c r="AY96" t="inlineStr"/>
@@ -13561,7 +13561,7 @@
       </c>
       <c r="AX119" t="inlineStr">
         <is>
-          <t>Anna Helmersson, Margaret Rainey, Esmeralda  Svanberg</t>
+          <t>Anna Helmersson, Margaret Rainey, Esmeralda Svanberg</t>
         </is>
       </c>
       <c r="AY119" t="inlineStr"/>

--- a/artfynd/A 14354-2024 artfynd.xlsx
+++ b/artfynd/A 14354-2024 artfynd.xlsx
@@ -4389,7 +4389,7 @@
       </c>
       <c r="AX35" t="inlineStr">
         <is>
-          <t>Anna Helmersson, Margaret Rainey, Esmeralda Svanberg</t>
+          <t>Anna Helmersson, Margaret Rainey, Esmeralda  Svanberg</t>
         </is>
       </c>
       <c r="AY35" t="inlineStr"/>
@@ -4496,7 +4496,7 @@
       </c>
       <c r="AX36" t="inlineStr">
         <is>
-          <t>Anna Helmersson, Margaret Rainey, Esmeralda Svanberg</t>
+          <t>Anna Helmersson, Margaret Rainey, Esmeralda  Svanberg</t>
         </is>
       </c>
       <c r="AY36" t="inlineStr"/>
@@ -4608,7 +4608,7 @@
       </c>
       <c r="AX37" t="inlineStr">
         <is>
-          <t>Anna Helmersson, Margaret Rainey, Esmeralda Svanberg</t>
+          <t>Anna Helmersson, Margaret Rainey, Esmeralda  Svanberg</t>
         </is>
       </c>
       <c r="AY37" t="inlineStr"/>
@@ -4715,7 +4715,7 @@
       </c>
       <c r="AX38" t="inlineStr">
         <is>
-          <t>Anna Helmersson, Margaret Rainey, Esmeralda Svanberg</t>
+          <t>Anna Helmersson, Margaret Rainey, Esmeralda  Svanberg</t>
         </is>
       </c>
       <c r="AY38" t="inlineStr"/>
@@ -4822,7 +4822,7 @@
       </c>
       <c r="AX39" t="inlineStr">
         <is>
-          <t>Anna Helmersson, Margaret Rainey, Esmeralda Svanberg</t>
+          <t>Anna Helmersson, Margaret Rainey, Esmeralda  Svanberg</t>
         </is>
       </c>
       <c r="AY39" t="inlineStr"/>
@@ -4934,7 +4934,7 @@
       </c>
       <c r="AX40" t="inlineStr">
         <is>
-          <t>Anna Helmersson, Margaret Rainey, Esmeralda Svanberg</t>
+          <t>Anna Helmersson, Margaret Rainey, Esmeralda  Svanberg</t>
         </is>
       </c>
       <c r="AY40" t="inlineStr"/>
@@ -5041,7 +5041,7 @@
       </c>
       <c r="AX41" t="inlineStr">
         <is>
-          <t>Anna Helmersson, Margaret Rainey, Esmeralda Svanberg</t>
+          <t>Anna Helmersson, Margaret Rainey, Esmeralda  Svanberg</t>
         </is>
       </c>
       <c r="AY41" t="inlineStr"/>
@@ -5153,7 +5153,7 @@
       </c>
       <c r="AX42" t="inlineStr">
         <is>
-          <t>Anna Helmersson, Margaret Rainey, Esmeralda Svanberg</t>
+          <t>Anna Helmersson, Margaret Rainey, Esmeralda  Svanberg</t>
         </is>
       </c>
       <c r="AY42" t="inlineStr"/>
@@ -5260,7 +5260,7 @@
       </c>
       <c r="AX43" t="inlineStr">
         <is>
-          <t>Anna Helmersson, Margaret Rainey, Esmeralda Svanberg</t>
+          <t>Anna Helmersson, Margaret Rainey, Esmeralda  Svanberg</t>
         </is>
       </c>
       <c r="AY43" t="inlineStr"/>
@@ -5367,7 +5367,7 @@
       </c>
       <c r="AX44" t="inlineStr">
         <is>
-          <t>Anna Helmersson, Margaret Rainey, Esmeralda Svanberg</t>
+          <t>Anna Helmersson, Margaret Rainey, Esmeralda  Svanberg</t>
         </is>
       </c>
       <c r="AY44" t="inlineStr"/>
@@ -5479,7 +5479,7 @@
       </c>
       <c r="AX45" t="inlineStr">
         <is>
-          <t>Anna Helmersson, Margaret Rainey, Esmeralda Svanberg</t>
+          <t>Anna Helmersson, Margaret Rainey, Esmeralda  Svanberg</t>
         </is>
       </c>
       <c r="AY45" t="inlineStr"/>
@@ -5591,7 +5591,7 @@
       </c>
       <c r="AX46" t="inlineStr">
         <is>
-          <t>Anna Helmersson, Margaret Rainey, Esmeralda Svanberg</t>
+          <t>Anna Helmersson, Margaret Rainey, Esmeralda  Svanberg</t>
         </is>
       </c>
       <c r="AY46" t="inlineStr"/>
@@ -5703,7 +5703,7 @@
       </c>
       <c r="AX47" t="inlineStr">
         <is>
-          <t>Anna Helmersson, Margaret Rainey, Esmeralda Svanberg</t>
+          <t>Anna Helmersson, Margaret Rainey, Esmeralda  Svanberg</t>
         </is>
       </c>
       <c r="AY47" t="inlineStr"/>
@@ -5815,7 +5815,7 @@
       </c>
       <c r="AX48" t="inlineStr">
         <is>
-          <t>Anna Helmersson, Margaret Rainey, Esmeralda Svanberg</t>
+          <t>Anna Helmersson, Margaret Rainey, Esmeralda  Svanberg</t>
         </is>
       </c>
       <c r="AY48" t="inlineStr"/>
@@ -7221,12 +7221,12 @@
       <c r="AT61" t="inlineStr"/>
       <c r="AW61" t="inlineStr">
         <is>
-          <t>Esmeralda Svanberg</t>
+          <t>Esmeralda  Svanberg</t>
         </is>
       </c>
       <c r="AX61" t="inlineStr">
         <is>
-          <t>Esmeralda Svanberg</t>
+          <t>Esmeralda  Svanberg</t>
         </is>
       </c>
       <c r="AY61" t="inlineStr"/>
@@ -7333,12 +7333,12 @@
       <c r="AT62" t="inlineStr"/>
       <c r="AW62" t="inlineStr">
         <is>
-          <t>Esmeralda Svanberg</t>
+          <t>Esmeralda  Svanberg</t>
         </is>
       </c>
       <c r="AX62" t="inlineStr">
         <is>
-          <t>Esmeralda Svanberg</t>
+          <t>Esmeralda  Svanberg</t>
         </is>
       </c>
       <c r="AY62" t="inlineStr"/>
@@ -7445,12 +7445,12 @@
       <c r="AT63" t="inlineStr"/>
       <c r="AW63" t="inlineStr">
         <is>
-          <t>Esmeralda Svanberg</t>
+          <t>Esmeralda  Svanberg</t>
         </is>
       </c>
       <c r="AX63" t="inlineStr">
         <is>
-          <t>Esmeralda Svanberg</t>
+          <t>Esmeralda  Svanberg</t>
         </is>
       </c>
       <c r="AY63" t="inlineStr"/>
@@ -7557,12 +7557,12 @@
       <c r="AT64" t="inlineStr"/>
       <c r="AW64" t="inlineStr">
         <is>
-          <t>Esmeralda Svanberg</t>
+          <t>Esmeralda  Svanberg</t>
         </is>
       </c>
       <c r="AX64" t="inlineStr">
         <is>
-          <t>Esmeralda Svanberg</t>
+          <t>Esmeralda  Svanberg</t>
         </is>
       </c>
       <c r="AY64" t="inlineStr"/>
@@ -7669,12 +7669,12 @@
       <c r="AT65" t="inlineStr"/>
       <c r="AW65" t="inlineStr">
         <is>
-          <t>Esmeralda Svanberg</t>
+          <t>Esmeralda  Svanberg</t>
         </is>
       </c>
       <c r="AX65" t="inlineStr">
         <is>
-          <t>Esmeralda Svanberg</t>
+          <t>Esmeralda  Svanberg</t>
         </is>
       </c>
       <c r="AY65" t="inlineStr"/>
@@ -7781,12 +7781,12 @@
       <c r="AT66" t="inlineStr"/>
       <c r="AW66" t="inlineStr">
         <is>
-          <t>Esmeralda Svanberg</t>
+          <t>Esmeralda  Svanberg</t>
         </is>
       </c>
       <c r="AX66" t="inlineStr">
         <is>
-          <t>Esmeralda Svanberg</t>
+          <t>Esmeralda  Svanberg</t>
         </is>
       </c>
       <c r="AY66" t="inlineStr"/>
@@ -7893,12 +7893,12 @@
       <c r="AT67" t="inlineStr"/>
       <c r="AW67" t="inlineStr">
         <is>
-          <t>Esmeralda Svanberg</t>
+          <t>Esmeralda  Svanberg</t>
         </is>
       </c>
       <c r="AX67" t="inlineStr">
         <is>
-          <t>Esmeralda Svanberg</t>
+          <t>Esmeralda  Svanberg</t>
         </is>
       </c>
       <c r="AY67" t="inlineStr"/>
@@ -8005,12 +8005,12 @@
       <c r="AT68" t="inlineStr"/>
       <c r="AW68" t="inlineStr">
         <is>
-          <t>Esmeralda Svanberg</t>
+          <t>Esmeralda  Svanberg</t>
         </is>
       </c>
       <c r="AX68" t="inlineStr">
         <is>
-          <t>Esmeralda Svanberg</t>
+          <t>Esmeralda  Svanberg</t>
         </is>
       </c>
       <c r="AY68" t="inlineStr"/>
@@ -8117,12 +8117,12 @@
       <c r="AT69" t="inlineStr"/>
       <c r="AW69" t="inlineStr">
         <is>
-          <t>Esmeralda Svanberg</t>
+          <t>Esmeralda  Svanberg</t>
         </is>
       </c>
       <c r="AX69" t="inlineStr">
         <is>
-          <t>Esmeralda Svanberg</t>
+          <t>Esmeralda  Svanberg</t>
         </is>
       </c>
       <c r="AY69" t="inlineStr"/>
@@ -8229,12 +8229,12 @@
       <c r="AT70" t="inlineStr"/>
       <c r="AW70" t="inlineStr">
         <is>
-          <t>Esmeralda Svanberg</t>
+          <t>Esmeralda  Svanberg</t>
         </is>
       </c>
       <c r="AX70" t="inlineStr">
         <is>
-          <t>Esmeralda Svanberg</t>
+          <t>Esmeralda  Svanberg</t>
         </is>
       </c>
       <c r="AY70" t="inlineStr"/>
@@ -8341,12 +8341,12 @@
       <c r="AT71" t="inlineStr"/>
       <c r="AW71" t="inlineStr">
         <is>
-          <t>Esmeralda Svanberg</t>
+          <t>Esmeralda  Svanberg</t>
         </is>
       </c>
       <c r="AX71" t="inlineStr">
         <is>
-          <t>Esmeralda Svanberg</t>
+          <t>Esmeralda  Svanberg</t>
         </is>
       </c>
       <c r="AY71" t="inlineStr"/>
@@ -8453,12 +8453,12 @@
       <c r="AT72" t="inlineStr"/>
       <c r="AW72" t="inlineStr">
         <is>
-          <t>Esmeralda Svanberg</t>
+          <t>Esmeralda  Svanberg</t>
         </is>
       </c>
       <c r="AX72" t="inlineStr">
         <is>
-          <t>Esmeralda Svanberg</t>
+          <t>Esmeralda  Svanberg</t>
         </is>
       </c>
       <c r="AY72" t="inlineStr"/>
@@ -8565,12 +8565,12 @@
       <c r="AT73" t="inlineStr"/>
       <c r="AW73" t="inlineStr">
         <is>
-          <t>Esmeralda Svanberg</t>
+          <t>Esmeralda  Svanberg</t>
         </is>
       </c>
       <c r="AX73" t="inlineStr">
         <is>
-          <t>Esmeralda Svanberg</t>
+          <t>Esmeralda  Svanberg</t>
         </is>
       </c>
       <c r="AY73" t="inlineStr"/>
@@ -8677,12 +8677,12 @@
       <c r="AT74" t="inlineStr"/>
       <c r="AW74" t="inlineStr">
         <is>
-          <t>Esmeralda Svanberg</t>
+          <t>Esmeralda  Svanberg</t>
         </is>
       </c>
       <c r="AX74" t="inlineStr">
         <is>
-          <t>Esmeralda Svanberg</t>
+          <t>Esmeralda  Svanberg</t>
         </is>
       </c>
       <c r="AY74" t="inlineStr"/>
@@ -8789,12 +8789,12 @@
       <c r="AT75" t="inlineStr"/>
       <c r="AW75" t="inlineStr">
         <is>
-          <t>Esmeralda Svanberg</t>
+          <t>Esmeralda  Svanberg</t>
         </is>
       </c>
       <c r="AX75" t="inlineStr">
         <is>
-          <t>Esmeralda Svanberg</t>
+          <t>Esmeralda  Svanberg</t>
         </is>
       </c>
       <c r="AY75" t="inlineStr"/>
@@ -8901,12 +8901,12 @@
       <c r="AT76" t="inlineStr"/>
       <c r="AW76" t="inlineStr">
         <is>
-          <t>Esmeralda Svanberg</t>
+          <t>Esmeralda  Svanberg</t>
         </is>
       </c>
       <c r="AX76" t="inlineStr">
         <is>
-          <t>Esmeralda Svanberg</t>
+          <t>Esmeralda  Svanberg</t>
         </is>
       </c>
       <c r="AY76" t="inlineStr"/>
@@ -9013,12 +9013,12 @@
       <c r="AT77" t="inlineStr"/>
       <c r="AW77" t="inlineStr">
         <is>
-          <t>Esmeralda Svanberg</t>
+          <t>Esmeralda  Svanberg</t>
         </is>
       </c>
       <c r="AX77" t="inlineStr">
         <is>
-          <t>Esmeralda Svanberg</t>
+          <t>Esmeralda  Svanberg</t>
         </is>
       </c>
       <c r="AY77" t="inlineStr"/>
@@ -9125,12 +9125,12 @@
       <c r="AT78" t="inlineStr"/>
       <c r="AW78" t="inlineStr">
         <is>
-          <t>Esmeralda Svanberg</t>
+          <t>Esmeralda  Svanberg</t>
         </is>
       </c>
       <c r="AX78" t="inlineStr">
         <is>
-          <t>Esmeralda Svanberg</t>
+          <t>Esmeralda  Svanberg</t>
         </is>
       </c>
       <c r="AY78" t="inlineStr"/>
@@ -9237,12 +9237,12 @@
       <c r="AT79" t="inlineStr"/>
       <c r="AW79" t="inlineStr">
         <is>
-          <t>Esmeralda Svanberg</t>
+          <t>Esmeralda  Svanberg</t>
         </is>
       </c>
       <c r="AX79" t="inlineStr">
         <is>
-          <t>Esmeralda Svanberg</t>
+          <t>Esmeralda  Svanberg</t>
         </is>
       </c>
       <c r="AY79" t="inlineStr"/>
@@ -9349,12 +9349,12 @@
       <c r="AT80" t="inlineStr"/>
       <c r="AW80" t="inlineStr">
         <is>
-          <t>Esmeralda Svanberg</t>
+          <t>Esmeralda  Svanberg</t>
         </is>
       </c>
       <c r="AX80" t="inlineStr">
         <is>
-          <t>Esmeralda Svanberg</t>
+          <t>Esmeralda  Svanberg</t>
         </is>
       </c>
       <c r="AY80" t="inlineStr"/>
@@ -9461,12 +9461,12 @@
       <c r="AT81" t="inlineStr"/>
       <c r="AW81" t="inlineStr">
         <is>
-          <t>Esmeralda Svanberg</t>
+          <t>Esmeralda  Svanberg</t>
         </is>
       </c>
       <c r="AX81" t="inlineStr">
         <is>
-          <t>Esmeralda Svanberg</t>
+          <t>Esmeralda  Svanberg</t>
         </is>
       </c>
       <c r="AY81" t="inlineStr"/>
@@ -9573,12 +9573,12 @@
       <c r="AT82" t="inlineStr"/>
       <c r="AW82" t="inlineStr">
         <is>
-          <t>Esmeralda Svanberg</t>
+          <t>Esmeralda  Svanberg</t>
         </is>
       </c>
       <c r="AX82" t="inlineStr">
         <is>
-          <t>Esmeralda Svanberg</t>
+          <t>Esmeralda  Svanberg</t>
         </is>
       </c>
       <c r="AY82" t="inlineStr"/>
@@ -11072,7 +11072,7 @@
       </c>
       <c r="AX96" t="inlineStr">
         <is>
-          <t>Anna Helmersson, Margaret Rainey, Esmeralda Svanberg</t>
+          <t>Anna Helmersson, Margaret Rainey, Esmeralda  Svanberg</t>
         </is>
       </c>
       <c r="AY96" t="inlineStr"/>
@@ -13561,7 +13561,7 @@
       </c>
       <c r="AX119" t="inlineStr">
         <is>
-          <t>Anna Helmersson, Margaret Rainey, Esmeralda Svanberg</t>
+          <t>Anna Helmersson, Margaret Rainey, Esmeralda  Svanberg</t>
         </is>
       </c>
       <c r="AY119" t="inlineStr"/>

--- a/artfynd/A 14354-2024 artfynd.xlsx
+++ b/artfynd/A 14354-2024 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY124"/>
+  <dimension ref="A1:AY123"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -9025,7 +9025,7 @@
     </row>
     <row r="78">
       <c r="A78" t="n">
-        <v>134629667</v>
+        <v>134629668</v>
       </c>
       <c r="B78" t="n">
         <v>43472</v>
@@ -9060,13 +9060,13 @@
         </is>
       </c>
       <c r="Q78" t="n">
-        <v>700275</v>
+        <v>700247</v>
       </c>
       <c r="R78" t="n">
-        <v>6359145</v>
+        <v>6359174</v>
       </c>
       <c r="S78" t="n">
-        <v>12</v>
+        <v>5</v>
       </c>
       <c r="T78" t="inlineStr">
         <is>
@@ -9095,7 +9095,7 @@
       </c>
       <c r="Z78" t="inlineStr">
         <is>
-          <t>16:09</t>
+          <t>16:12</t>
         </is>
       </c>
       <c r="AA78" t="inlineStr">
@@ -9105,7 +9105,7 @@
       </c>
       <c r="AB78" t="inlineStr">
         <is>
-          <t>16:09</t>
+          <t>16:12</t>
         </is>
       </c>
       <c r="AC78" t="inlineStr">
@@ -9137,7 +9137,7 @@
     </row>
     <row r="79">
       <c r="A79" t="n">
-        <v>134629668</v>
+        <v>134629671</v>
       </c>
       <c r="B79" t="n">
         <v>43472</v>
@@ -9172,13 +9172,13 @@
         </is>
       </c>
       <c r="Q79" t="n">
-        <v>700247</v>
+        <v>700257</v>
       </c>
       <c r="R79" t="n">
-        <v>6359174</v>
+        <v>6359107</v>
       </c>
       <c r="S79" t="n">
-        <v>5</v>
+        <v>17</v>
       </c>
       <c r="T79" t="inlineStr">
         <is>
@@ -9207,7 +9207,7 @@
       </c>
       <c r="Z79" t="inlineStr">
         <is>
-          <t>16:12</t>
+          <t>16:24</t>
         </is>
       </c>
       <c r="AA79" t="inlineStr">
@@ -9217,12 +9217,12 @@
       </c>
       <c r="AB79" t="inlineStr">
         <is>
-          <t>16:12</t>
+          <t>16:24</t>
         </is>
       </c>
       <c r="AC79" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AD79" t="b">
@@ -9249,7 +9249,7 @@
     </row>
     <row r="80">
       <c r="A80" t="n">
-        <v>134629671</v>
+        <v>134629673</v>
       </c>
       <c r="B80" t="n">
         <v>43472</v>
@@ -9284,13 +9284,13 @@
         </is>
       </c>
       <c r="Q80" t="n">
-        <v>700257</v>
+        <v>700317</v>
       </c>
       <c r="R80" t="n">
-        <v>6359107</v>
+        <v>6359124</v>
       </c>
       <c r="S80" t="n">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="T80" t="inlineStr">
         <is>
@@ -9319,7 +9319,7 @@
       </c>
       <c r="Z80" t="inlineStr">
         <is>
-          <t>16:24</t>
+          <t>16:28</t>
         </is>
       </c>
       <c r="AA80" t="inlineStr">
@@ -9329,12 +9329,12 @@
       </c>
       <c r="AB80" t="inlineStr">
         <is>
-          <t>16:24</t>
+          <t>16:28</t>
         </is>
       </c>
       <c r="AC80" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AD80" t="b">
@@ -9361,7 +9361,7 @@
     </row>
     <row r="81">
       <c r="A81" t="n">
-        <v>134629673</v>
+        <v>134629674</v>
       </c>
       <c r="B81" t="n">
         <v>43472</v>
@@ -9396,13 +9396,13 @@
         </is>
       </c>
       <c r="Q81" t="n">
-        <v>700317</v>
+        <v>700265</v>
       </c>
       <c r="R81" t="n">
-        <v>6359124</v>
+        <v>6359164</v>
       </c>
       <c r="S81" t="n">
-        <v>16</v>
+        <v>5</v>
       </c>
       <c r="T81" t="inlineStr">
         <is>
@@ -9431,7 +9431,7 @@
       </c>
       <c r="Z81" t="inlineStr">
         <is>
-          <t>16:28</t>
+          <t>16:29</t>
         </is>
       </c>
       <c r="AA81" t="inlineStr">
@@ -9441,12 +9441,12 @@
       </c>
       <c r="AB81" t="inlineStr">
         <is>
-          <t>16:28</t>
+          <t>16:29</t>
         </is>
       </c>
       <c r="AC81" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AD81" t="b">
@@ -9473,10 +9473,10 @@
     </row>
     <row r="82">
       <c r="A82" t="n">
-        <v>134629674</v>
+        <v>134629192</v>
       </c>
       <c r="B82" t="n">
-        <v>43472</v>
+        <v>58260</v>
       </c>
       <c r="D82" t="inlineStr">
         <is>
@@ -9484,37 +9484,37 @@
         </is>
       </c>
       <c r="E82" t="n">
-        <v>101242</v>
+        <v>103012</v>
       </c>
       <c r="F82" t="inlineStr">
         <is>
-          <t>Dårgräsfjäril</t>
+          <t>Grönsångare</t>
         </is>
       </c>
       <c r="G82" t="inlineStr">
         <is>
-          <t>Lopinga achine</t>
+          <t>Phylloscopus sibilatrix</t>
         </is>
       </c>
       <c r="H82" t="inlineStr">
         <is>
-          <t>(Scopoli, 1763)</t>
+          <t>(Bechstein, 1793)</t>
         </is>
       </c>
       <c r="I82" t="inlineStr"/>
       <c r="P82" t="inlineStr">
         <is>
-          <t>Hästar, Gtl</t>
+          <t>Gerums Likmunds, Gtl</t>
         </is>
       </c>
       <c r="Q82" t="n">
-        <v>700265</v>
+        <v>700257</v>
       </c>
       <c r="R82" t="n">
-        <v>6359164</v>
+        <v>6359091</v>
       </c>
       <c r="S82" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="T82" t="inlineStr">
         <is>
@@ -9543,7 +9543,7 @@
       </c>
       <c r="Z82" t="inlineStr">
         <is>
-          <t>16:29</t>
+          <t>16:24</t>
         </is>
       </c>
       <c r="AA82" t="inlineStr">
@@ -9553,12 +9553,7 @@
       </c>
       <c r="AB82" t="inlineStr">
         <is>
-          <t>16:29</t>
-        </is>
-      </c>
-      <c r="AC82" t="inlineStr">
-        <is>
-          <t>2</t>
+          <t>16:24</t>
         </is>
       </c>
       <c r="AD82" t="b">
@@ -9573,22 +9568,22 @@
       <c r="AT82" t="inlineStr"/>
       <c r="AW82" t="inlineStr">
         <is>
-          <t>Esmeralda  Svanberg</t>
+          <t>Margaret Rainey</t>
         </is>
       </c>
       <c r="AX82" t="inlineStr">
         <is>
-          <t>Esmeralda  Svanberg</t>
+          <t>Margaret Rainey</t>
         </is>
       </c>
       <c r="AY82" t="inlineStr"/>
     </row>
     <row r="83">
       <c r="A83" t="n">
-        <v>134629192</v>
+        <v>134629189</v>
       </c>
       <c r="B83" t="n">
-        <v>58260</v>
+        <v>58134</v>
       </c>
       <c r="D83" t="inlineStr">
         <is>
@@ -9596,21 +9591,21 @@
         </is>
       </c>
       <c r="E83" t="n">
-        <v>103012</v>
+        <v>103020</v>
       </c>
       <c r="F83" t="inlineStr">
         <is>
-          <t>Grönsångare</t>
+          <t>Entita</t>
         </is>
       </c>
       <c r="G83" t="inlineStr">
         <is>
-          <t>Phylloscopus sibilatrix</t>
+          <t>Poecile palustris</t>
         </is>
       </c>
       <c r="H83" t="inlineStr">
         <is>
-          <t>(Bechstein, 1793)</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I83" t="inlineStr"/>
@@ -9620,10 +9615,10 @@
         </is>
       </c>
       <c r="Q83" t="n">
-        <v>700257</v>
+        <v>700255</v>
       </c>
       <c r="R83" t="n">
-        <v>6359091</v>
+        <v>6359112</v>
       </c>
       <c r="S83" t="n">
         <v>6</v>
@@ -9655,7 +9650,7 @@
       </c>
       <c r="Z83" t="inlineStr">
         <is>
-          <t>16:24</t>
+          <t>16:20</t>
         </is>
       </c>
       <c r="AA83" t="inlineStr">
@@ -9665,7 +9660,7 @@
       </c>
       <c r="AB83" t="inlineStr">
         <is>
-          <t>16:24</t>
+          <t>16:20</t>
         </is>
       </c>
       <c r="AD83" t="b">
@@ -9685,17 +9680,17 @@
       </c>
       <c r="AX83" t="inlineStr">
         <is>
-          <t>Margaret Rainey</t>
+          <t>Via Margaret Rainey</t>
         </is>
       </c>
       <c r="AY83" t="inlineStr"/>
     </row>
     <row r="84">
       <c r="A84" t="n">
-        <v>134629189</v>
+        <v>111589164</v>
       </c>
       <c r="B84" t="n">
-        <v>58134</v>
+        <v>5479</v>
       </c>
       <c r="D84" t="inlineStr">
         <is>
@@ -9703,37 +9698,62 @@
         </is>
       </c>
       <c r="E84" t="n">
-        <v>103020</v>
+        <v>105894</v>
       </c>
       <c r="F84" t="inlineStr">
         <is>
-          <t>Entita</t>
+          <t>Smedbock</t>
         </is>
       </c>
       <c r="G84" t="inlineStr">
         <is>
-          <t>Poecile palustris</t>
+          <t>Ergates faber</t>
         </is>
       </c>
       <c r="H84" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I84" t="inlineStr"/>
+          <t>(Linnaeus, 1761)</t>
+        </is>
+      </c>
+      <c r="I84" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J84" t="inlineStr">
+        <is>
+          <t>ex.</t>
+        </is>
+      </c>
+      <c r="K84" t="inlineStr">
+        <is>
+          <t>imago/adult</t>
+        </is>
+      </c>
+      <c r="L84" t="inlineStr">
+        <is>
+          <t>hona</t>
+        </is>
+      </c>
+      <c r="M84" t="inlineStr">
+        <is>
+          <t>frispringande/krypande</t>
+        </is>
+      </c>
+      <c r="N84" t="inlineStr"/>
       <c r="P84" t="inlineStr">
         <is>
-          <t>Gerums Likmunds, Gtl</t>
+          <t>Botes källmyr, vägen, Gtl</t>
         </is>
       </c>
       <c r="Q84" t="n">
-        <v>700255</v>
+        <v>700322</v>
       </c>
       <c r="R84" t="n">
-        <v>6359112</v>
+        <v>6359100</v>
       </c>
       <c r="S84" t="n">
-        <v>6</v>
+        <v>50</v>
       </c>
       <c r="T84" t="inlineStr">
         <is>
@@ -9757,22 +9777,12 @@
       </c>
       <c r="Y84" t="inlineStr">
         <is>
-          <t>2026-06-24</t>
-        </is>
-      </c>
-      <c r="Z84" t="inlineStr">
-        <is>
-          <t>16:20</t>
+          <t>2023-08-15</t>
         </is>
       </c>
       <c r="AA84" t="inlineStr">
         <is>
-          <t>2026-06-24</t>
-        </is>
-      </c>
-      <c r="AB84" t="inlineStr">
-        <is>
-          <t>16:20</t>
+          <t>2023-08-15</t>
         </is>
       </c>
       <c r="AD84" t="b">
@@ -9781,50 +9791,51 @@
       <c r="AE84" t="b">
         <v>0</v>
       </c>
+      <c r="AF84" t="inlineStr"/>
       <c r="AG84" t="b">
         <v>0</v>
       </c>
       <c r="AT84" t="inlineStr"/>
       <c r="AW84" t="inlineStr">
         <is>
-          <t>Margaret Rainey</t>
+          <t>Kjell Eriksson</t>
         </is>
       </c>
       <c r="AX84" t="inlineStr">
         <is>
-          <t>Via Margaret Rainey</t>
+          <t>Kjell Eriksson, Ulla Eriksson</t>
         </is>
       </c>
       <c r="AY84" t="inlineStr"/>
     </row>
     <row r="85">
       <c r="A85" t="n">
-        <v>111589164</v>
+        <v>116259087</v>
       </c>
       <c r="B85" t="n">
-        <v>5479</v>
+        <v>99035</v>
       </c>
       <c r="D85" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E85" t="n">
-        <v>105894</v>
+        <v>219790</v>
       </c>
       <c r="F85" t="inlineStr">
         <is>
-          <t>Smedbock</t>
+          <t>Fläcknycklar</t>
         </is>
       </c>
       <c r="G85" t="inlineStr">
         <is>
-          <t>Ergates faber</t>
+          <t>Dactylorhiza maculata</t>
         </is>
       </c>
       <c r="H85" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1761)</t>
+          <t>(L.) Soó</t>
         </is>
       </c>
       <c r="I85" t="inlineStr">
@@ -9834,38 +9845,27 @@
       </c>
       <c r="J85" t="inlineStr">
         <is>
-          <t>ex.</t>
+          <t>plantor/tuvor</t>
         </is>
       </c>
       <c r="K85" t="inlineStr">
         <is>
-          <t>imago/adult</t>
-        </is>
-      </c>
-      <c r="L85" t="inlineStr">
-        <is>
-          <t>hona</t>
-        </is>
-      </c>
-      <c r="M85" t="inlineStr">
-        <is>
-          <t>frispringande/krypande</t>
-        </is>
-      </c>
-      <c r="N85" t="inlineStr"/>
+          <t>fullt utvecklade blad</t>
+        </is>
+      </c>
       <c r="P85" t="inlineStr">
         <is>
-          <t>Botes källmyr, vägen, Gtl</t>
+          <t>Gerum Likmunds 1:2 (4), Gtl</t>
         </is>
       </c>
       <c r="Q85" t="n">
-        <v>700322</v>
+        <v>700256</v>
       </c>
       <c r="R85" t="n">
-        <v>6359100</v>
+        <v>6359045</v>
       </c>
       <c r="S85" t="n">
-        <v>50</v>
+        <v>3</v>
       </c>
       <c r="T85" t="inlineStr">
         <is>
@@ -9889,12 +9889,12 @@
       </c>
       <c r="Y85" t="inlineStr">
         <is>
-          <t>2023-08-15</t>
+          <t>2024-04-23</t>
         </is>
       </c>
       <c r="AA85" t="inlineStr">
         <is>
-          <t>2023-08-15</t>
+          <t>2024-04-23</t>
         </is>
       </c>
       <c r="AD85" t="b">
@@ -9903,29 +9903,33 @@
       <c r="AE85" t="b">
         <v>0</v>
       </c>
-      <c r="AF85" t="inlineStr"/>
       <c r="AG85" t="b">
         <v>0</v>
+      </c>
+      <c r="AI85" t="inlineStr">
+        <is>
+          <t>Kalktallskog något fuktigare, träd på socklar, hästbetad.</t>
+        </is>
       </c>
       <c r="AT85" t="inlineStr"/>
       <c r="AW85" t="inlineStr">
         <is>
-          <t>Kjell Eriksson</t>
+          <t>Jörgen Petersson</t>
         </is>
       </c>
       <c r="AX85" t="inlineStr">
         <is>
-          <t>Kjell Eriksson, Ulla Eriksson</t>
+          <t>Jörgen Petersson</t>
         </is>
       </c>
       <c r="AY85" t="inlineStr"/>
     </row>
     <row r="86">
       <c r="A86" t="n">
-        <v>116259087</v>
+        <v>126300257</v>
       </c>
       <c r="B86" t="n">
-        <v>99035</v>
+        <v>99096</v>
       </c>
       <c r="D86" t="inlineStr">
         <is>
@@ -9933,21 +9937,21 @@
         </is>
       </c>
       <c r="E86" t="n">
-        <v>219790</v>
+        <v>219798</v>
       </c>
       <c r="F86" t="inlineStr">
         <is>
-          <t>Fläcknycklar</t>
+          <t>Skogsknipprot</t>
         </is>
       </c>
       <c r="G86" t="inlineStr">
         <is>
-          <t>Dactylorhiza maculata</t>
+          <t>Epipactis helleborine</t>
         </is>
       </c>
       <c r="H86" t="inlineStr">
         <is>
-          <t>(L.) Soó</t>
+          <t>(L.) Crantz</t>
         </is>
       </c>
       <c r="I86" t="inlineStr">
@@ -9955,29 +9959,19 @@
           <t>1</t>
         </is>
       </c>
-      <c r="J86" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
-      <c r="K86" t="inlineStr">
-        <is>
-          <t>fullt utvecklade blad</t>
-        </is>
-      </c>
       <c r="P86" t="inlineStr">
         <is>
-          <t>Gerum Likmunds 1:2 (4), Gtl</t>
+          <t>Gerum, Likmunds 1:2 (4), Gtl</t>
         </is>
       </c>
       <c r="Q86" t="n">
-        <v>700256</v>
+        <v>700247</v>
       </c>
       <c r="R86" t="n">
-        <v>6359045</v>
+        <v>6359114</v>
       </c>
       <c r="S86" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="T86" t="inlineStr">
         <is>
@@ -10001,12 +9995,12 @@
       </c>
       <c r="Y86" t="inlineStr">
         <is>
-          <t>2024-04-23</t>
+          <t>2025-06-29</t>
         </is>
       </c>
       <c r="AA86" t="inlineStr">
         <is>
-          <t>2024-04-23</t>
+          <t>2025-06-29</t>
         </is>
       </c>
       <c r="AD86" t="b">
@@ -10020,25 +10014,25 @@
       </c>
       <c r="AI86" t="inlineStr">
         <is>
-          <t>Kalktallskog något fuktigare, träd på socklar, hästbetad.</t>
+          <t>Hästbetad blandskog</t>
         </is>
       </c>
       <c r="AT86" t="inlineStr"/>
       <c r="AW86" t="inlineStr">
         <is>
-          <t>Jörgen Petersson</t>
+          <t>Gun Ingmansson</t>
         </is>
       </c>
       <c r="AX86" t="inlineStr">
         <is>
-          <t>Jörgen Petersson</t>
+          <t>Gun Ingmansson, Jörgen Petersson, Björn Larsson</t>
         </is>
       </c>
       <c r="AY86" t="inlineStr"/>
     </row>
     <row r="87">
       <c r="A87" t="n">
-        <v>126300257</v>
+        <v>126514044</v>
       </c>
       <c r="B87" t="n">
         <v>99096</v>
@@ -10077,13 +10071,13 @@
         </is>
       </c>
       <c r="Q87" t="n">
-        <v>700247</v>
+        <v>700215</v>
       </c>
       <c r="R87" t="n">
-        <v>6359114</v>
+        <v>6359155</v>
       </c>
       <c r="S87" t="n">
-        <v>4</v>
+        <v>8</v>
       </c>
       <c r="T87" t="inlineStr">
         <is>
@@ -10144,10 +10138,10 @@
     </row>
     <row r="88">
       <c r="A88" t="n">
-        <v>126514044</v>
+        <v>126300256</v>
       </c>
       <c r="B88" t="n">
-        <v>99096</v>
+        <v>99142</v>
       </c>
       <c r="D88" t="inlineStr">
         <is>
@@ -10155,41 +10149,37 @@
         </is>
       </c>
       <c r="E88" t="n">
-        <v>219798</v>
+        <v>219847</v>
       </c>
       <c r="F88" t="inlineStr">
         <is>
-          <t>Skogsknipprot</t>
+          <t>Tvåblad</t>
         </is>
       </c>
       <c r="G88" t="inlineStr">
         <is>
-          <t>Epipactis helleborine</t>
+          <t>Neottia ovata</t>
         </is>
       </c>
       <c r="H88" t="inlineStr">
         <is>
-          <t>(L.) Crantz</t>
-        </is>
-      </c>
-      <c r="I88" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+          <t>(L.) Buff. &amp; Fingerh.</t>
+        </is>
+      </c>
+      <c r="I88" t="inlineStr"/>
       <c r="P88" t="inlineStr">
         <is>
           <t>Gerum, Likmunds 1:2 (4), Gtl</t>
         </is>
       </c>
       <c r="Q88" t="n">
-        <v>700215</v>
+        <v>700247</v>
       </c>
       <c r="R88" t="n">
-        <v>6359155</v>
+        <v>6359114</v>
       </c>
       <c r="S88" t="n">
-        <v>8</v>
+        <v>4</v>
       </c>
       <c r="T88" t="inlineStr">
         <is>
@@ -10250,7 +10240,7 @@
     </row>
     <row r="89">
       <c r="A89" t="n">
-        <v>126300256</v>
+        <v>126300258</v>
       </c>
       <c r="B89" t="n">
         <v>99142</v>
@@ -10278,7 +10268,11 @@
           <t>(L.) Buff. &amp; Fingerh.</t>
         </is>
       </c>
-      <c r="I89" t="inlineStr"/>
+      <c r="I89" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
       <c r="P89" t="inlineStr">
         <is>
           <t>Gerum, Likmunds 1:2 (4), Gtl</t>
@@ -10288,10 +10282,10 @@
         <v>700247</v>
       </c>
       <c r="R89" t="n">
-        <v>6359114</v>
+        <v>6359105</v>
       </c>
       <c r="S89" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="T89" t="inlineStr">
         <is>
@@ -10352,7 +10346,7 @@
     </row>
     <row r="90">
       <c r="A90" t="n">
-        <v>126300258</v>
+        <v>126300265</v>
       </c>
       <c r="B90" t="n">
         <v>99142</v>
@@ -10380,11 +10374,7 @@
           <t>(L.) Buff. &amp; Fingerh.</t>
         </is>
       </c>
-      <c r="I90" t="inlineStr">
-        <is>
-          <t>7</t>
-        </is>
-      </c>
+      <c r="I90" t="inlineStr"/>
       <c r="P90" t="inlineStr">
         <is>
           <t>Gerum, Likmunds 1:2 (4), Gtl</t>
@@ -10394,10 +10384,10 @@
         <v>700247</v>
       </c>
       <c r="R90" t="n">
-        <v>6359105</v>
+        <v>6359082</v>
       </c>
       <c r="S90" t="n">
-        <v>5</v>
+        <v>8</v>
       </c>
       <c r="T90" t="inlineStr">
         <is>
@@ -10458,7 +10448,7 @@
     </row>
     <row r="91">
       <c r="A91" t="n">
-        <v>126300265</v>
+        <v>126300268</v>
       </c>
       <c r="B91" t="n">
         <v>99142</v>
@@ -10493,13 +10483,13 @@
         </is>
       </c>
       <c r="Q91" t="n">
-        <v>700247</v>
+        <v>700265</v>
       </c>
       <c r="R91" t="n">
-        <v>6359082</v>
+        <v>6359056</v>
       </c>
       <c r="S91" t="n">
-        <v>8</v>
+        <v>4</v>
       </c>
       <c r="T91" t="inlineStr">
         <is>
@@ -10560,7 +10550,7 @@
     </row>
     <row r="92">
       <c r="A92" t="n">
-        <v>126300268</v>
+        <v>126300273</v>
       </c>
       <c r="B92" t="n">
         <v>99142</v>
@@ -10588,17 +10578,21 @@
           <t>(L.) Buff. &amp; Fingerh.</t>
         </is>
       </c>
-      <c r="I92" t="inlineStr"/>
+      <c r="I92" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
       <c r="P92" t="inlineStr">
         <is>
           <t>Gerum, Likmunds 1:2 (4), Gtl</t>
         </is>
       </c>
       <c r="Q92" t="n">
-        <v>700265</v>
+        <v>700275</v>
       </c>
       <c r="R92" t="n">
-        <v>6359056</v>
+        <v>6359045</v>
       </c>
       <c r="S92" t="n">
         <v>4</v>
@@ -10662,7 +10656,7 @@
     </row>
     <row r="93">
       <c r="A93" t="n">
-        <v>126300273</v>
+        <v>126514045</v>
       </c>
       <c r="B93" t="n">
         <v>99142</v>
@@ -10690,24 +10684,20 @@
           <t>(L.) Buff. &amp; Fingerh.</t>
         </is>
       </c>
-      <c r="I93" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
+      <c r="I93" t="inlineStr"/>
       <c r="P93" t="inlineStr">
         <is>
           <t>Gerum, Likmunds 1:2 (4), Gtl</t>
         </is>
       </c>
       <c r="Q93" t="n">
-        <v>700275</v>
+        <v>700215</v>
       </c>
       <c r="R93" t="n">
-        <v>6359045</v>
+        <v>6359155</v>
       </c>
       <c r="S93" t="n">
-        <v>4</v>
+        <v>8</v>
       </c>
       <c r="T93" t="inlineStr">
         <is>
@@ -10768,7 +10758,7 @@
     </row>
     <row r="94">
       <c r="A94" t="n">
-        <v>126514045</v>
+        <v>126514049</v>
       </c>
       <c r="B94" t="n">
         <v>99142</v>
@@ -10803,13 +10793,13 @@
         </is>
       </c>
       <c r="Q94" t="n">
-        <v>700215</v>
+        <v>700235</v>
       </c>
       <c r="R94" t="n">
-        <v>6359155</v>
+        <v>6359147</v>
       </c>
       <c r="S94" t="n">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="T94" t="inlineStr">
         <is>
@@ -10870,10 +10860,10 @@
     </row>
     <row r="95">
       <c r="A95" t="n">
-        <v>126514049</v>
+        <v>134628528</v>
       </c>
       <c r="B95" t="n">
-        <v>99142</v>
+        <v>99219</v>
       </c>
       <c r="D95" t="inlineStr">
         <is>
@@ -10901,17 +10891,17 @@
       <c r="I95" t="inlineStr"/>
       <c r="P95" t="inlineStr">
         <is>
-          <t>Gerum, Likmunds 1:2 (4), Gtl</t>
+          <t>Gerum Likmunds, Gtl</t>
         </is>
       </c>
       <c r="Q95" t="n">
-        <v>700235</v>
+        <v>700250</v>
       </c>
       <c r="R95" t="n">
-        <v>6359147</v>
+        <v>6359173</v>
       </c>
       <c r="S95" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T95" t="inlineStr">
         <is>
@@ -10935,12 +10925,22 @@
       </c>
       <c r="Y95" t="inlineStr">
         <is>
-          <t>2025-06-29</t>
+          <t>2026-06-24</t>
+        </is>
+      </c>
+      <c r="Z95" t="inlineStr">
+        <is>
+          <t>15:58</t>
         </is>
       </c>
       <c r="AA95" t="inlineStr">
         <is>
-          <t>2025-06-29</t>
+          <t>2026-06-24</t>
+        </is>
+      </c>
+      <c r="AB95" t="inlineStr">
+        <is>
+          <t>15:58</t>
         </is>
       </c>
       <c r="AD95" t="b">
@@ -10951,28 +10951,23 @@
       </c>
       <c r="AG95" t="b">
         <v>0</v>
-      </c>
-      <c r="AI95" t="inlineStr">
-        <is>
-          <t>Hästbetad blandskog</t>
-        </is>
       </c>
       <c r="AT95" t="inlineStr"/>
       <c r="AW95" t="inlineStr">
         <is>
-          <t>Gun Ingmansson</t>
+          <t>Anna Helmersson</t>
         </is>
       </c>
       <c r="AX95" t="inlineStr">
         <is>
-          <t>Gun Ingmansson, Jörgen Petersson, Björn Larsson</t>
+          <t>Anna Helmersson, Margaret Rainey, Esmeralda  Svanberg</t>
         </is>
       </c>
       <c r="AY95" t="inlineStr"/>
     </row>
     <row r="96">
       <c r="A96" t="n">
-        <v>134628528</v>
+        <v>134629174</v>
       </c>
       <c r="B96" t="n">
         <v>99219</v>
@@ -11003,14 +10998,14 @@
       <c r="I96" t="inlineStr"/>
       <c r="P96" t="inlineStr">
         <is>
-          <t>Gerum Likmunds, Gtl</t>
+          <t>Gerums Likmunds, Gtl</t>
         </is>
       </c>
       <c r="Q96" t="n">
-        <v>700250</v>
+        <v>700262</v>
       </c>
       <c r="R96" t="n">
-        <v>6359173</v>
+        <v>6359042</v>
       </c>
       <c r="S96" t="n">
         <v>5</v>
@@ -11042,7 +11037,7 @@
       </c>
       <c r="Z96" t="inlineStr">
         <is>
-          <t>15:58</t>
+          <t>15:53</t>
         </is>
       </c>
       <c r="AA96" t="inlineStr">
@@ -11052,7 +11047,7 @@
       </c>
       <c r="AB96" t="inlineStr">
         <is>
-          <t>15:58</t>
+          <t>15:53</t>
         </is>
       </c>
       <c r="AD96" t="b">
@@ -11067,19 +11062,19 @@
       <c r="AT96" t="inlineStr"/>
       <c r="AW96" t="inlineStr">
         <is>
-          <t>Anna Helmersson</t>
+          <t>Margaret Rainey</t>
         </is>
       </c>
       <c r="AX96" t="inlineStr">
         <is>
-          <t>Anna Helmersson, Margaret Rainey, Esmeralda  Svanberg</t>
+          <t>Margaret Rainey</t>
         </is>
       </c>
       <c r="AY96" t="inlineStr"/>
     </row>
     <row r="97">
       <c r="A97" t="n">
-        <v>134629174</v>
+        <v>134629183</v>
       </c>
       <c r="B97" t="n">
         <v>99219</v>
@@ -11114,10 +11109,10 @@
         </is>
       </c>
       <c r="Q97" t="n">
-        <v>700262</v>
+        <v>700205</v>
       </c>
       <c r="R97" t="n">
-        <v>6359042</v>
+        <v>6359141</v>
       </c>
       <c r="S97" t="n">
         <v>5</v>
@@ -11149,7 +11144,7 @@
       </c>
       <c r="Z97" t="inlineStr">
         <is>
-          <t>15:53</t>
+          <t>16:11</t>
         </is>
       </c>
       <c r="AA97" t="inlineStr">
@@ -11159,7 +11154,7 @@
       </c>
       <c r="AB97" t="inlineStr">
         <is>
-          <t>15:53</t>
+          <t>16:11</t>
         </is>
       </c>
       <c r="AD97" t="b">
@@ -11186,7 +11181,7 @@
     </row>
     <row r="98">
       <c r="A98" t="n">
-        <v>134629183</v>
+        <v>134629187</v>
       </c>
       <c r="B98" t="n">
         <v>99219</v>
@@ -11221,10 +11216,10 @@
         </is>
       </c>
       <c r="Q98" t="n">
-        <v>700205</v>
+        <v>700230</v>
       </c>
       <c r="R98" t="n">
-        <v>6359141</v>
+        <v>6359151</v>
       </c>
       <c r="S98" t="n">
         <v>5</v>
@@ -11256,7 +11251,7 @@
       </c>
       <c r="Z98" t="inlineStr">
         <is>
-          <t>16:11</t>
+          <t>16:16</t>
         </is>
       </c>
       <c r="AA98" t="inlineStr">
@@ -11266,7 +11261,12 @@
       </c>
       <c r="AB98" t="inlineStr">
         <is>
-          <t>16:11</t>
+          <t>16:16</t>
+        </is>
+      </c>
+      <c r="AC98" t="inlineStr">
+        <is>
+          <t>3 st</t>
         </is>
       </c>
       <c r="AD98" t="b">
@@ -11293,10 +11293,10 @@
     </row>
     <row r="99">
       <c r="A99" t="n">
-        <v>134629187</v>
+        <v>126300267</v>
       </c>
       <c r="B99" t="n">
-        <v>99219</v>
+        <v>99141</v>
       </c>
       <c r="D99" t="inlineStr">
         <is>
@@ -11304,37 +11304,41 @@
         </is>
       </c>
       <c r="E99" t="n">
-        <v>219847</v>
+        <v>219862</v>
       </c>
       <c r="F99" t="inlineStr">
         <is>
-          <t>Tvåblad</t>
+          <t>Nästrot</t>
         </is>
       </c>
       <c r="G99" t="inlineStr">
         <is>
-          <t>Neottia ovata</t>
+          <t>Neottia nidus-avis</t>
         </is>
       </c>
       <c r="H99" t="inlineStr">
         <is>
-          <t>(L.) Buff. &amp; Fingerh.</t>
-        </is>
-      </c>
-      <c r="I99" t="inlineStr"/>
+          <t>(L.) Rich.</t>
+        </is>
+      </c>
+      <c r="I99" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
       <c r="P99" t="inlineStr">
         <is>
-          <t>Gerums Likmunds, Gtl</t>
+          <t>Gerum, Likmunds 1:2 (4), Gtl</t>
         </is>
       </c>
       <c r="Q99" t="n">
-        <v>700230</v>
+        <v>700257</v>
       </c>
       <c r="R99" t="n">
-        <v>6359151</v>
+        <v>6359067</v>
       </c>
       <c r="S99" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T99" t="inlineStr">
         <is>
@@ -11358,27 +11362,12 @@
       </c>
       <c r="Y99" t="inlineStr">
         <is>
-          <t>2026-06-24</t>
-        </is>
-      </c>
-      <c r="Z99" t="inlineStr">
-        <is>
-          <t>16:16</t>
+          <t>2025-06-29</t>
         </is>
       </c>
       <c r="AA99" t="inlineStr">
         <is>
-          <t>2026-06-24</t>
-        </is>
-      </c>
-      <c r="AB99" t="inlineStr">
-        <is>
-          <t>16:16</t>
-        </is>
-      </c>
-      <c r="AC99" t="inlineStr">
-        <is>
-          <t>3 st</t>
+          <t>2025-06-29</t>
         </is>
       </c>
       <c r="AD99" t="b">
@@ -11389,26 +11378,31 @@
       </c>
       <c r="AG99" t="b">
         <v>0</v>
+      </c>
+      <c r="AI99" t="inlineStr">
+        <is>
+          <t>Hästbetad blandskog</t>
+        </is>
       </c>
       <c r="AT99" t="inlineStr"/>
       <c r="AW99" t="inlineStr">
         <is>
-          <t>Margaret Rainey</t>
+          <t>Gun Ingmansson</t>
         </is>
       </c>
       <c r="AX99" t="inlineStr">
         <is>
-          <t>Margaret Rainey</t>
+          <t>Gun Ingmansson, Jörgen Petersson, Björn Larsson</t>
         </is>
       </c>
       <c r="AY99" t="inlineStr"/>
     </row>
     <row r="100">
       <c r="A100" t="n">
-        <v>126300267</v>
+        <v>134629170</v>
       </c>
       <c r="B100" t="n">
-        <v>99141</v>
+        <v>99230</v>
       </c>
       <c r="D100" t="inlineStr">
         <is>
@@ -11416,16 +11410,16 @@
         </is>
       </c>
       <c r="E100" t="n">
-        <v>219862</v>
+        <v>219874</v>
       </c>
       <c r="F100" t="inlineStr">
         <is>
-          <t>Nästrot</t>
+          <t>Nattviol</t>
         </is>
       </c>
       <c r="G100" t="inlineStr">
         <is>
-          <t>Neottia nidus-avis</t>
+          <t>Platanthera bifolia</t>
         </is>
       </c>
       <c r="H100" t="inlineStr">
@@ -11433,24 +11427,20 @@
           <t>(L.) Rich.</t>
         </is>
       </c>
-      <c r="I100" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
+      <c r="I100" t="inlineStr"/>
       <c r="P100" t="inlineStr">
         <is>
-          <t>Gerum, Likmunds 1:2 (4), Gtl</t>
+          <t>Gerums Likmunds, Gtl</t>
         </is>
       </c>
       <c r="Q100" t="n">
-        <v>700257</v>
+        <v>700270</v>
       </c>
       <c r="R100" t="n">
-        <v>6359067</v>
+        <v>6359038</v>
       </c>
       <c r="S100" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T100" t="inlineStr">
         <is>
@@ -11474,12 +11464,22 @@
       </c>
       <c r="Y100" t="inlineStr">
         <is>
-          <t>2025-06-29</t>
+          <t>2026-06-24</t>
+        </is>
+      </c>
+      <c r="Z100" t="inlineStr">
+        <is>
+          <t>15:48</t>
         </is>
       </c>
       <c r="AA100" t="inlineStr">
         <is>
-          <t>2025-06-29</t>
+          <t>2026-06-24</t>
+        </is>
+      </c>
+      <c r="AB100" t="inlineStr">
+        <is>
+          <t>15:48</t>
         </is>
       </c>
       <c r="AD100" t="b">
@@ -11490,69 +11490,72 @@
       </c>
       <c r="AG100" t="b">
         <v>0</v>
-      </c>
-      <c r="AI100" t="inlineStr">
-        <is>
-          <t>Hästbetad blandskog</t>
-        </is>
       </c>
       <c r="AT100" t="inlineStr"/>
       <c r="AW100" t="inlineStr">
         <is>
-          <t>Gun Ingmansson</t>
+          <t>Margaret Rainey</t>
         </is>
       </c>
       <c r="AX100" t="inlineStr">
         <is>
-          <t>Gun Ingmansson, Jörgen Petersson, Björn Larsson</t>
+          <t>Margaret Rainey</t>
         </is>
       </c>
       <c r="AY100" t="inlineStr"/>
     </row>
     <row r="101">
       <c r="A101" t="n">
-        <v>134629170</v>
+        <v>97960624</v>
       </c>
       <c r="B101" t="n">
-        <v>99230</v>
+        <v>110078</v>
       </c>
       <c r="D101" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E101" t="n">
-        <v>219874</v>
+        <v>220299</v>
       </c>
       <c r="F101" t="inlineStr">
         <is>
-          <t>Nattviol</t>
+          <t>Svinrot</t>
         </is>
       </c>
       <c r="G101" t="inlineStr">
         <is>
-          <t>Platanthera bifolia</t>
+          <t>Scorzonera humilis</t>
         </is>
       </c>
       <c r="H101" t="inlineStr">
         <is>
-          <t>(L.) Rich.</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I101" t="inlineStr"/>
+      <c r="J101" t="inlineStr"/>
+      <c r="K101" t="inlineStr">
+        <is>
+          <t>vinterståndare</t>
+        </is>
+      </c>
+      <c r="L101" t="inlineStr"/>
+      <c r="N101" t="inlineStr"/>
       <c r="P101" t="inlineStr">
         <is>
-          <t>Gerums Likmunds, Gtl</t>
+          <t>Russparken, parkeringen 100m N, Gtl</t>
         </is>
       </c>
       <c r="Q101" t="n">
-        <v>700270</v>
+        <v>700333</v>
       </c>
       <c r="R101" t="n">
-        <v>6359038</v>
+        <v>6359040</v>
       </c>
       <c r="S101" t="n">
-        <v>5</v>
+        <v>25</v>
       </c>
       <c r="T101" t="inlineStr">
         <is>
@@ -11576,22 +11579,12 @@
       </c>
       <c r="Y101" t="inlineStr">
         <is>
-          <t>2026-06-24</t>
-        </is>
-      </c>
-      <c r="Z101" t="inlineStr">
-        <is>
-          <t>15:48</t>
+          <t>2022-01-06</t>
         </is>
       </c>
       <c r="AA101" t="inlineStr">
         <is>
-          <t>2026-06-24</t>
-        </is>
-      </c>
-      <c r="AB101" t="inlineStr">
-        <is>
-          <t>15:48</t>
+          <t>2022-01-06</t>
         </is>
       </c>
       <c r="AD101" t="b">
@@ -11600,28 +11593,29 @@
       <c r="AE101" t="b">
         <v>0</v>
       </c>
+      <c r="AF101" t="inlineStr"/>
       <c r="AG101" t="b">
         <v>0</v>
       </c>
       <c r="AT101" t="inlineStr"/>
       <c r="AW101" t="inlineStr">
         <is>
-          <t>Margaret Rainey</t>
+          <t>Dennis Nyström</t>
         </is>
       </c>
       <c r="AX101" t="inlineStr">
         <is>
-          <t>Margaret Rainey</t>
+          <t>Dennis Nyström</t>
         </is>
       </c>
       <c r="AY101" t="inlineStr"/>
     </row>
     <row r="102">
       <c r="A102" t="n">
-        <v>97960624</v>
+        <v>2760594</v>
       </c>
       <c r="B102" t="n">
-        <v>110078</v>
+        <v>110117</v>
       </c>
       <c r="D102" t="inlineStr">
         <is>
@@ -11629,16 +11623,16 @@
         </is>
       </c>
       <c r="E102" t="n">
-        <v>220299</v>
+        <v>220320</v>
       </c>
       <c r="F102" t="inlineStr">
         <is>
-          <t>Svinrot</t>
+          <t>Ängsskära</t>
         </is>
       </c>
       <c r="G102" t="inlineStr">
         <is>
-          <t>Scorzonera humilis</t>
+          <t>Serratula tinctoria</t>
         </is>
       </c>
       <c r="H102" t="inlineStr">
@@ -11646,28 +11640,34 @@
           <t>L.</t>
         </is>
       </c>
-      <c r="I102" t="inlineStr"/>
-      <c r="J102" t="inlineStr"/>
+      <c r="I102" t="inlineStr">
+        <is>
+          <t>49</t>
+        </is>
+      </c>
+      <c r="J102" t="inlineStr">
+        <is>
+          <t>stjälkar/strån/skott</t>
+        </is>
+      </c>
       <c r="K102" t="inlineStr">
         <is>
-          <t>vinterståndare</t>
-        </is>
-      </c>
-      <c r="L102" t="inlineStr"/>
-      <c r="N102" t="inlineStr"/>
+          <t>frukt-/fröspridning</t>
+        </is>
+      </c>
       <c r="P102" t="inlineStr">
         <is>
-          <t>Russparken, parkeringen 100m N, Gtl</t>
+          <t>Lojsta hed, Botes källmyr S-ut, Gtl</t>
         </is>
       </c>
       <c r="Q102" t="n">
-        <v>700333</v>
+        <v>700332</v>
       </c>
       <c r="R102" t="n">
-        <v>6359040</v>
+        <v>6359036</v>
       </c>
       <c r="S102" t="n">
-        <v>25</v>
+        <v>5</v>
       </c>
       <c r="T102" t="inlineStr">
         <is>
@@ -11691,12 +11691,17 @@
       </c>
       <c r="Y102" t="inlineStr">
         <is>
-          <t>2022-01-06</t>
+          <t>2008-09-04</t>
         </is>
       </c>
       <c r="AA102" t="inlineStr">
         <is>
-          <t>2022-01-06</t>
+          <t>2008-09-04</t>
+        </is>
+      </c>
+      <c r="AC102" t="inlineStr">
+        <is>
+          <t>Återfynd.</t>
         </is>
       </c>
       <c r="AD102" t="b">
@@ -11705,26 +11710,30 @@
       <c r="AE102" t="b">
         <v>0</v>
       </c>
-      <c r="AF102" t="inlineStr"/>
       <c r="AG102" t="b">
         <v>0</v>
+      </c>
+      <c r="AI102" t="inlineStr">
+        <is>
+          <t>Stigkant</t>
+        </is>
       </c>
       <c r="AT102" t="inlineStr"/>
       <c r="AW102" t="inlineStr">
         <is>
-          <t>Dennis Nyström</t>
+          <t>Joakim Ekman</t>
         </is>
       </c>
       <c r="AX102" t="inlineStr">
         <is>
-          <t>Dennis Nyström</t>
+          <t>Joakim Ekman, Gabriel Ekman</t>
         </is>
       </c>
       <c r="AY102" t="inlineStr"/>
     </row>
     <row r="103">
       <c r="A103" t="n">
-        <v>2760594</v>
+        <v>16230167</v>
       </c>
       <c r="B103" t="n">
         <v>110117</v>
@@ -11752,34 +11761,27 @@
           <t>L.</t>
         </is>
       </c>
-      <c r="I103" t="inlineStr">
-        <is>
-          <t>49</t>
-        </is>
-      </c>
-      <c r="J103" t="inlineStr">
-        <is>
-          <t>stjälkar/strån/skott</t>
-        </is>
-      </c>
+      <c r="I103" t="inlineStr"/>
+      <c r="J103" t="inlineStr"/>
       <c r="K103" t="inlineStr">
         <is>
-          <t>frukt-/fröspridning</t>
-        </is>
-      </c>
+          <t>blomning</t>
+        </is>
+      </c>
+      <c r="L103" t="inlineStr"/>
       <c r="P103" t="inlineStr">
         <is>
-          <t>Lojsta hed, Botes källmyr S-ut, Gtl</t>
+          <t>Russparken, parkeringen 100m N, Gtl</t>
         </is>
       </c>
       <c r="Q103" t="n">
-        <v>700332</v>
+        <v>700333</v>
       </c>
       <c r="R103" t="n">
-        <v>6359036</v>
+        <v>6359040</v>
       </c>
       <c r="S103" t="n">
-        <v>5</v>
+        <v>25</v>
       </c>
       <c r="T103" t="inlineStr">
         <is>
@@ -11803,17 +11805,12 @@
       </c>
       <c r="Y103" t="inlineStr">
         <is>
-          <t>2008-09-04</t>
+          <t>2014-07-21</t>
         </is>
       </c>
       <c r="AA103" t="inlineStr">
         <is>
-          <t>2008-09-04</t>
-        </is>
-      </c>
-      <c r="AC103" t="inlineStr">
-        <is>
-          <t>Återfynd.</t>
+          <t>2014-07-21</t>
         </is>
       </c>
       <c r="AD103" t="b">
@@ -11824,28 +11821,23 @@
       </c>
       <c r="AG103" t="b">
         <v>0</v>
-      </c>
-      <c r="AI103" t="inlineStr">
-        <is>
-          <t>Stigkant</t>
-        </is>
       </c>
       <c r="AT103" t="inlineStr"/>
       <c r="AW103" t="inlineStr">
         <is>
-          <t>Joakim Ekman</t>
+          <t>Dennis Nyström</t>
         </is>
       </c>
       <c r="AX103" t="inlineStr">
         <is>
-          <t>Joakim Ekman, Gabriel Ekman</t>
+          <t>Dennis Nyström</t>
         </is>
       </c>
       <c r="AY103" t="inlineStr"/>
     </row>
     <row r="104">
       <c r="A104" t="n">
-        <v>16230167</v>
+        <v>16500486</v>
       </c>
       <c r="B104" t="n">
         <v>110117</v>
@@ -11875,22 +11867,18 @@
       </c>
       <c r="I104" t="inlineStr"/>
       <c r="J104" t="inlineStr"/>
-      <c r="K104" t="inlineStr">
-        <is>
-          <t>blomning</t>
-        </is>
-      </c>
+      <c r="K104" t="inlineStr"/>
       <c r="L104" t="inlineStr"/>
       <c r="P104" t="inlineStr">
         <is>
-          <t>Russparken, parkeringen 100m N, Gtl</t>
+          <t>Lojsta, Gtl</t>
         </is>
       </c>
       <c r="Q104" t="n">
-        <v>700333</v>
+        <v>700339</v>
       </c>
       <c r="R104" t="n">
-        <v>6359040</v>
+        <v>6359017</v>
       </c>
       <c r="S104" t="n">
         <v>25</v>
@@ -11912,17 +11900,17 @@
       </c>
       <c r="W104" t="inlineStr">
         <is>
-          <t>Gerum</t>
+          <t>Fardhem</t>
         </is>
       </c>
       <c r="Y104" t="inlineStr">
         <is>
-          <t>2014-07-21</t>
+          <t>2014-08-12</t>
         </is>
       </c>
       <c r="AA104" t="inlineStr">
         <is>
-          <t>2014-07-21</t>
+          <t>2014-08-12</t>
         </is>
       </c>
       <c r="AD104" t="b">
@@ -11937,19 +11925,19 @@
       <c r="AT104" t="inlineStr"/>
       <c r="AW104" t="inlineStr">
         <is>
-          <t>Dennis Nyström</t>
+          <t>Thomas Strid</t>
         </is>
       </c>
       <c r="AX104" t="inlineStr">
         <is>
-          <t>Dennis Nyström</t>
+          <t>Thomas Strid, Tiina Laantee, Melica Strid</t>
         </is>
       </c>
       <c r="AY104" t="inlineStr"/>
     </row>
     <row r="105">
       <c r="A105" t="n">
-        <v>16500486</v>
+        <v>69716937</v>
       </c>
       <c r="B105" t="n">
         <v>110117</v>
@@ -11978,22 +11966,24 @@
         </is>
       </c>
       <c r="I105" t="inlineStr"/>
-      <c r="J105" t="inlineStr"/>
-      <c r="K105" t="inlineStr"/>
-      <c r="L105" t="inlineStr"/>
+      <c r="K105" t="inlineStr">
+        <is>
+          <t>blomning</t>
+        </is>
+      </c>
       <c r="P105" t="inlineStr">
         <is>
-          <t>Lojsta, Gtl</t>
+          <t>Lojsta hed, S om Botes källmyrs NR, Gtl</t>
         </is>
       </c>
       <c r="Q105" t="n">
-        <v>700339</v>
+        <v>700329</v>
       </c>
       <c r="R105" t="n">
-        <v>6359017</v>
+        <v>6359034</v>
       </c>
       <c r="S105" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T105" t="inlineStr">
         <is>
@@ -12012,17 +12002,17 @@
       </c>
       <c r="W105" t="inlineStr">
         <is>
-          <t>Fardhem</t>
+          <t>Gerum</t>
         </is>
       </c>
       <c r="Y105" t="inlineStr">
         <is>
-          <t>2014-08-12</t>
+          <t>2009-07-23</t>
         </is>
       </c>
       <c r="AA105" t="inlineStr">
         <is>
-          <t>2014-08-12</t>
+          <t>2009-07-23</t>
         </is>
       </c>
       <c r="AD105" t="b">
@@ -12033,23 +12023,28 @@
       </c>
       <c r="AG105" t="b">
         <v>0</v>
+      </c>
+      <c r="AI105" t="inlineStr">
+        <is>
+          <t>Fuktig ängsmark</t>
+        </is>
       </c>
       <c r="AT105" t="inlineStr"/>
       <c r="AW105" t="inlineStr">
         <is>
-          <t>Thomas Strid</t>
+          <t>Jan Yngve Andersson</t>
         </is>
       </c>
       <c r="AX105" t="inlineStr">
         <is>
-          <t>Thomas Strid, Tiina Laantee, Melica Strid</t>
+          <t>Jan Yngve Andersson</t>
         </is>
       </c>
       <c r="AY105" t="inlineStr"/>
     </row>
     <row r="106">
       <c r="A106" t="n">
-        <v>69716937</v>
+        <v>105024185</v>
       </c>
       <c r="B106" t="n">
         <v>110117</v>
@@ -12077,22 +12072,26 @@
           <t>L.</t>
         </is>
       </c>
-      <c r="I106" t="inlineStr"/>
-      <c r="K106" t="inlineStr">
-        <is>
-          <t>blomning</t>
+      <c r="I106" t="inlineStr">
+        <is>
+          <t>57</t>
+        </is>
+      </c>
+      <c r="J106" t="inlineStr">
+        <is>
+          <t>stjälkar/strån/skott</t>
         </is>
       </c>
       <c r="P106" t="inlineStr">
         <is>
-          <t>Lojsta hed, S om Botes källmyrs NR, Gtl</t>
+          <t>Lilla Korsgatan N, Gtl</t>
         </is>
       </c>
       <c r="Q106" t="n">
-        <v>700329</v>
+        <v>700333</v>
       </c>
       <c r="R106" t="n">
-        <v>6359034</v>
+        <v>6359035</v>
       </c>
       <c r="S106" t="n">
         <v>10</v>
@@ -12119,12 +12118,17 @@
       </c>
       <c r="Y106" t="inlineStr">
         <is>
-          <t>2009-07-23</t>
+          <t>2008-07-26</t>
         </is>
       </c>
       <c r="AA106" t="inlineStr">
         <is>
-          <t>2009-07-23</t>
+          <t>2008-07-26</t>
+        </is>
+      </c>
+      <c r="AC106" t="inlineStr">
+        <is>
+          <t>57 stänglar, ca 25 ex. Tidigare känd lokal. - xkoord = 1651946, ykoord = 6358867</t>
         </is>
       </c>
       <c r="AD106" t="b">
@@ -12135,28 +12139,27 @@
       </c>
       <c r="AG106" t="b">
         <v>0</v>
-      </c>
-      <c r="AI106" t="inlineStr">
-        <is>
-          <t>Fuktig ängsmark</t>
-        </is>
       </c>
       <c r="AT106" t="inlineStr"/>
       <c r="AW106" t="inlineStr">
         <is>
-          <t>Jan Yngve Andersson</t>
+          <t>Jörgen Petersson</t>
         </is>
       </c>
       <c r="AX106" t="inlineStr">
         <is>
-          <t>Jan Yngve Andersson</t>
-        </is>
-      </c>
-      <c r="AY106" t="inlineStr"/>
+          <t>Jörgen Petersson</t>
+        </is>
+      </c>
+      <c r="AY106" t="inlineStr">
+        <is>
+          <t>Projekt Gotlands Flora</t>
+        </is>
+      </c>
     </row>
     <row r="107">
       <c r="A107" t="n">
-        <v>105024185</v>
+        <v>105024186</v>
       </c>
       <c r="B107" t="n">
         <v>110117</v>
@@ -12186,21 +12189,21 @@
       </c>
       <c r="I107" t="inlineStr">
         <is>
-          <t>57</t>
+          <t>1</t>
         </is>
       </c>
       <c r="J107" t="inlineStr">
         <is>
-          <t>stjälkar/strån/skott</t>
+          <t>m²</t>
         </is>
       </c>
       <c r="P107" t="inlineStr">
         <is>
-          <t>Lilla Korsgatan N, Gtl</t>
+          <t>Lilla Korsgatan 100 m N, vid stig mot Botes källmyr, Gtl</t>
         </is>
       </c>
       <c r="Q107" t="n">
-        <v>700333</v>
+        <v>700323</v>
       </c>
       <c r="R107" t="n">
         <v>6359035</v>
@@ -12230,17 +12233,12 @@
       </c>
       <c r="Y107" t="inlineStr">
         <is>
-          <t>2008-07-26</t>
+          <t>2003-08-30</t>
         </is>
       </c>
       <c r="AA107" t="inlineStr">
         <is>
-          <t>2008-07-26</t>
-        </is>
-      </c>
-      <c r="AC107" t="inlineStr">
-        <is>
-          <t>57 stänglar, ca 25 ex. Tidigare känd lokal. - xkoord = 1651946, ykoord = 6358867</t>
+          <t>2003-08-30</t>
         </is>
       </c>
       <c r="AD107" t="b">
@@ -12251,6 +12249,11 @@
       </c>
       <c r="AG107" t="b">
         <v>0</v>
+      </c>
+      <c r="AI107" t="inlineStr">
+        <is>
+          <t>Körvägkant.</t>
+        </is>
       </c>
       <c r="AT107" t="inlineStr"/>
       <c r="AW107" t="inlineStr">
@@ -12271,7 +12274,7 @@
     </row>
     <row r="108">
       <c r="A108" t="n">
-        <v>105024186</v>
+        <v>105024198</v>
       </c>
       <c r="B108" t="n">
         <v>110117</v>
@@ -12301,27 +12304,27 @@
       </c>
       <c r="I108" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>57</t>
         </is>
       </c>
       <c r="J108" t="inlineStr">
         <is>
-          <t>m²</t>
+          <t>stjälkar/strån/skott</t>
         </is>
       </c>
       <c r="P108" t="inlineStr">
         <is>
-          <t>Lilla Korsgatan 100 m N, vid stig mot Botes källmyr, Gtl</t>
+          <t>Lilla Korsgatan N, vid stig mot Botes källmyr, Gtl</t>
         </is>
       </c>
       <c r="Q108" t="n">
-        <v>700323</v>
+        <v>700333</v>
       </c>
       <c r="R108" t="n">
-        <v>6359035</v>
+        <v>6359015</v>
       </c>
       <c r="S108" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T108" t="inlineStr">
         <is>
@@ -12340,17 +12343,22 @@
       </c>
       <c r="W108" t="inlineStr">
         <is>
-          <t>Gerum</t>
+          <t>Fardhem</t>
         </is>
       </c>
       <c r="Y108" t="inlineStr">
         <is>
-          <t>2003-08-30</t>
+          <t>2006-07-04</t>
         </is>
       </c>
       <c r="AA108" t="inlineStr">
         <is>
-          <t>2003-08-30</t>
+          <t>2006-07-04</t>
+        </is>
+      </c>
+      <c r="AC108" t="inlineStr">
+        <is>
+          <t>57 stänglar. Ungefärlig koordinat.</t>
         </is>
       </c>
       <c r="AD108" t="b">
@@ -12364,7 +12372,7 @@
       </c>
       <c r="AI108" t="inlineStr">
         <is>
-          <t>Körvägkant.</t>
+          <t>Stig i kalktallskog, delvis sandunderlag</t>
         </is>
       </c>
       <c r="AT108" t="inlineStr"/>
@@ -12386,7 +12394,7 @@
     </row>
     <row r="109">
       <c r="A109" t="n">
-        <v>105024198</v>
+        <v>111587690</v>
       </c>
       <c r="B109" t="n">
         <v>110117</v>
@@ -12416,7 +12424,7 @@
       </c>
       <c r="I109" t="inlineStr">
         <is>
-          <t>57</t>
+          <t>37</t>
         </is>
       </c>
       <c r="J109" t="inlineStr">
@@ -12424,16 +12432,23 @@
           <t>stjälkar/strån/skott</t>
         </is>
       </c>
+      <c r="K109" t="inlineStr">
+        <is>
+          <t>överblommad</t>
+        </is>
+      </c>
+      <c r="L109" t="inlineStr"/>
+      <c r="N109" t="inlineStr"/>
       <c r="P109" t="inlineStr">
         <is>
-          <t>Lilla Korsgatan N, vid stig mot Botes källmyr, Gtl</t>
+          <t>Botes källmyr, vägen, Gtl</t>
         </is>
       </c>
       <c r="Q109" t="n">
-        <v>700333</v>
+        <v>700319</v>
       </c>
       <c r="R109" t="n">
-        <v>6359015</v>
+        <v>6359038</v>
       </c>
       <c r="S109" t="n">
         <v>25</v>
@@ -12455,22 +12470,17 @@
       </c>
       <c r="W109" t="inlineStr">
         <is>
-          <t>Fardhem</t>
+          <t>Gerum</t>
         </is>
       </c>
       <c r="Y109" t="inlineStr">
         <is>
-          <t>2006-07-04</t>
+          <t>2023-08-15</t>
         </is>
       </c>
       <c r="AA109" t="inlineStr">
         <is>
-          <t>2006-07-04</t>
-        </is>
-      </c>
-      <c r="AC109" t="inlineStr">
-        <is>
-          <t>57 stänglar. Ungefärlig koordinat.</t>
+          <t>2023-08-15</t>
         </is>
       </c>
       <c r="AD109" t="b">
@@ -12479,34 +12489,26 @@
       <c r="AE109" t="b">
         <v>0</v>
       </c>
+      <c r="AF109" t="inlineStr"/>
       <c r="AG109" t="b">
         <v>0</v>
-      </c>
-      <c r="AI109" t="inlineStr">
-        <is>
-          <t>Stig i kalktallskog, delvis sandunderlag</t>
-        </is>
       </c>
       <c r="AT109" t="inlineStr"/>
       <c r="AW109" t="inlineStr">
         <is>
-          <t>Jörgen Petersson</t>
+          <t>Kjell Eriksson</t>
         </is>
       </c>
       <c r="AX109" t="inlineStr">
         <is>
-          <t>Jörgen Petersson</t>
-        </is>
-      </c>
-      <c r="AY109" t="inlineStr">
-        <is>
-          <t>Projekt Gotlands Flora</t>
-        </is>
-      </c>
+          <t>Kjell Eriksson, Ulla Eriksson</t>
+        </is>
+      </c>
+      <c r="AY109" t="inlineStr"/>
     </row>
     <row r="110">
       <c r="A110" t="n">
-        <v>111587690</v>
+        <v>126312506</v>
       </c>
       <c r="B110" t="n">
         <v>110117</v>
@@ -12536,7 +12538,7 @@
       </c>
       <c r="I110" t="inlineStr">
         <is>
-          <t>37</t>
+          <t>34</t>
         </is>
       </c>
       <c r="J110" t="inlineStr">
@@ -12546,21 +12548,19 @@
       </c>
       <c r="K110" t="inlineStr">
         <is>
-          <t>överblommad</t>
-        </is>
-      </c>
-      <c r="L110" t="inlineStr"/>
-      <c r="N110" t="inlineStr"/>
+          <t>blomknopp</t>
+        </is>
+      </c>
       <c r="P110" t="inlineStr">
         <is>
-          <t>Botes källmyr, vägen, Gtl</t>
+          <t>Lilla Korsgatan, Gtl</t>
         </is>
       </c>
       <c r="Q110" t="n">
-        <v>700319</v>
+        <v>700335</v>
       </c>
       <c r="R110" t="n">
-        <v>6359038</v>
+        <v>6359040</v>
       </c>
       <c r="S110" t="n">
         <v>25</v>
@@ -12587,12 +12587,12 @@
       </c>
       <c r="Y110" t="inlineStr">
         <is>
-          <t>2023-08-15</t>
+          <t>2025-06-30</t>
         </is>
       </c>
       <c r="AA110" t="inlineStr">
         <is>
-          <t>2023-08-15</t>
+          <t>2025-06-30</t>
         </is>
       </c>
       <c r="AD110" t="b">
@@ -12601,81 +12601,66 @@
       <c r="AE110" t="b">
         <v>0</v>
       </c>
-      <c r="AF110" t="inlineStr"/>
       <c r="AG110" t="b">
         <v>0</v>
       </c>
       <c r="AT110" t="inlineStr"/>
       <c r="AW110" t="inlineStr">
         <is>
-          <t>Kjell Eriksson</t>
+          <t>Felicia Wikinger</t>
         </is>
       </c>
       <c r="AX110" t="inlineStr">
         <is>
-          <t>Kjell Eriksson, Ulla Eriksson</t>
+          <t>Felicia Wikinger, Teo Jernkvist</t>
         </is>
       </c>
       <c r="AY110" t="inlineStr"/>
     </row>
     <row r="111">
       <c r="A111" t="n">
-        <v>126312506</v>
+        <v>116259105</v>
       </c>
       <c r="B111" t="n">
-        <v>110117</v>
+        <v>101326</v>
       </c>
       <c r="D111" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E111" t="n">
-        <v>220320</v>
+        <v>222498</v>
       </c>
       <c r="F111" t="inlineStr">
         <is>
-          <t>Ängsskära</t>
+          <t>Blåsippa</t>
         </is>
       </c>
       <c r="G111" t="inlineStr">
         <is>
-          <t>Serratula tinctoria</t>
+          <t>Hepatica nobilis</t>
         </is>
       </c>
       <c r="H111" t="inlineStr">
         <is>
-          <t>L.</t>
-        </is>
-      </c>
-      <c r="I111" t="inlineStr">
-        <is>
-          <t>34</t>
-        </is>
-      </c>
-      <c r="J111" t="inlineStr">
-        <is>
-          <t>stjälkar/strån/skott</t>
-        </is>
-      </c>
-      <c r="K111" t="inlineStr">
-        <is>
-          <t>blomknopp</t>
-        </is>
-      </c>
+          <t>Schreb.</t>
+        </is>
+      </c>
+      <c r="I111" t="inlineStr"/>
       <c r="P111" t="inlineStr">
         <is>
-          <t>Lilla Korsgatan, Gtl</t>
+          <t>Gerum Likmunds 1:2 (4), Gtl</t>
         </is>
       </c>
       <c r="Q111" t="n">
-        <v>700335</v>
+        <v>700330</v>
       </c>
       <c r="R111" t="n">
-        <v>6359040</v>
+        <v>6359014</v>
       </c>
       <c r="S111" t="n">
-        <v>25</v>
+        <v>5</v>
       </c>
       <c r="T111" t="inlineStr">
         <is>
@@ -12699,12 +12684,17 @@
       </c>
       <c r="Y111" t="inlineStr">
         <is>
-          <t>2025-06-30</t>
+          <t>2024-04-23</t>
         </is>
       </c>
       <c r="AA111" t="inlineStr">
         <is>
-          <t>2025-06-30</t>
+          <t>2024-04-23</t>
+        </is>
+      </c>
+      <c r="AC111" t="inlineStr">
+        <is>
+          <t>Spridd i hela skogen.</t>
         </is>
       </c>
       <c r="AD111" t="b">
@@ -12719,22 +12709,22 @@
       <c r="AT111" t="inlineStr"/>
       <c r="AW111" t="inlineStr">
         <is>
-          <t>Felicia Wikinger</t>
+          <t>Jörgen Petersson</t>
         </is>
       </c>
       <c r="AX111" t="inlineStr">
         <is>
-          <t>Felicia Wikinger, Teo Jernkvist</t>
+          <t>Jörgen Petersson</t>
         </is>
       </c>
       <c r="AY111" t="inlineStr"/>
     </row>
     <row r="112">
       <c r="A112" t="n">
-        <v>116259105</v>
+        <v>126300259</v>
       </c>
       <c r="B112" t="n">
-        <v>101326</v>
+        <v>99036</v>
       </c>
       <c r="D112" t="inlineStr">
         <is>
@@ -12742,34 +12732,38 @@
         </is>
       </c>
       <c r="E112" t="n">
-        <v>222498</v>
+        <v>223591</v>
       </c>
       <c r="F112" t="inlineStr">
         <is>
-          <t>Blåsippa</t>
+          <t>Skogsnycklar</t>
         </is>
       </c>
       <c r="G112" t="inlineStr">
         <is>
-          <t>Hepatica nobilis</t>
+          <t>Dactylorhiza maculata subsp. fuchsii</t>
         </is>
       </c>
       <c r="H112" t="inlineStr">
         <is>
-          <t>Schreb.</t>
-        </is>
-      </c>
-      <c r="I112" t="inlineStr"/>
+          <t>(Druce) Hyl.</t>
+        </is>
+      </c>
+      <c r="I112" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
       <c r="P112" t="inlineStr">
         <is>
-          <t>Gerum Likmunds 1:2 (4), Gtl</t>
+          <t>Gerum, Likmunds 1:2 (4), Gtl</t>
         </is>
       </c>
       <c r="Q112" t="n">
-        <v>700330</v>
+        <v>700247</v>
       </c>
       <c r="R112" t="n">
-        <v>6359014</v>
+        <v>6359105</v>
       </c>
       <c r="S112" t="n">
         <v>5</v>
@@ -12796,17 +12790,12 @@
       </c>
       <c r="Y112" t="inlineStr">
         <is>
-          <t>2024-04-23</t>
+          <t>2025-06-29</t>
         </is>
       </c>
       <c r="AA112" t="inlineStr">
         <is>
-          <t>2024-04-23</t>
-        </is>
-      </c>
-      <c r="AC112" t="inlineStr">
-        <is>
-          <t>Spridd i hela skogen.</t>
+          <t>2025-06-29</t>
         </is>
       </c>
       <c r="AD112" t="b">
@@ -12817,23 +12806,28 @@
       </c>
       <c r="AG112" t="b">
         <v>0</v>
+      </c>
+      <c r="AI112" t="inlineStr">
+        <is>
+          <t>Hästbetad blandskog</t>
+        </is>
       </c>
       <c r="AT112" t="inlineStr"/>
       <c r="AW112" t="inlineStr">
         <is>
-          <t>Jörgen Petersson</t>
+          <t>Gun Ingmansson</t>
         </is>
       </c>
       <c r="AX112" t="inlineStr">
         <is>
-          <t>Jörgen Petersson</t>
+          <t>Gun Ingmansson, Jörgen Petersson, Björn Larsson</t>
         </is>
       </c>
       <c r="AY112" t="inlineStr"/>
     </row>
     <row r="113">
       <c r="A113" t="n">
-        <v>126300259</v>
+        <v>126300263</v>
       </c>
       <c r="B113" t="n">
         <v>99036</v>
@@ -12863,7 +12857,7 @@
       </c>
       <c r="I113" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>10</t>
         </is>
       </c>
       <c r="P113" t="inlineStr">
@@ -12872,13 +12866,13 @@
         </is>
       </c>
       <c r="Q113" t="n">
-        <v>700247</v>
+        <v>700253</v>
       </c>
       <c r="R113" t="n">
-        <v>6359105</v>
+        <v>6359086</v>
       </c>
       <c r="S113" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="T113" t="inlineStr">
         <is>
@@ -12939,7 +12933,7 @@
     </row>
     <row r="114">
       <c r="A114" t="n">
-        <v>126300263</v>
+        <v>126300266</v>
       </c>
       <c r="B114" t="n">
         <v>99036</v>
@@ -12969,7 +12963,7 @@
       </c>
       <c r="I114" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>3</t>
         </is>
       </c>
       <c r="P114" t="inlineStr">
@@ -12978,13 +12972,13 @@
         </is>
       </c>
       <c r="Q114" t="n">
-        <v>700253</v>
+        <v>700247</v>
       </c>
       <c r="R114" t="n">
-        <v>6359086</v>
+        <v>6359082</v>
       </c>
       <c r="S114" t="n">
-        <v>4</v>
+        <v>8</v>
       </c>
       <c r="T114" t="inlineStr">
         <is>
@@ -13045,7 +13039,7 @@
     </row>
     <row r="115">
       <c r="A115" t="n">
-        <v>126300266</v>
+        <v>126300270</v>
       </c>
       <c r="B115" t="n">
         <v>99036</v>
@@ -13073,24 +13067,20 @@
           <t>(Druce) Hyl.</t>
         </is>
       </c>
-      <c r="I115" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
+      <c r="I115" t="inlineStr"/>
       <c r="P115" t="inlineStr">
         <is>
           <t>Gerum, Likmunds 1:2 (4), Gtl</t>
         </is>
       </c>
       <c r="Q115" t="n">
-        <v>700247</v>
+        <v>700265</v>
       </c>
       <c r="R115" t="n">
-        <v>6359082</v>
+        <v>6359056</v>
       </c>
       <c r="S115" t="n">
-        <v>8</v>
+        <v>4</v>
       </c>
       <c r="T115" t="inlineStr">
         <is>
@@ -13151,7 +13141,7 @@
     </row>
     <row r="116">
       <c r="A116" t="n">
-        <v>126300270</v>
+        <v>126300272</v>
       </c>
       <c r="B116" t="n">
         <v>99036</v>
@@ -13179,17 +13169,21 @@
           <t>(Druce) Hyl.</t>
         </is>
       </c>
-      <c r="I116" t="inlineStr"/>
+      <c r="I116" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
       <c r="P116" t="inlineStr">
         <is>
           <t>Gerum, Likmunds 1:2 (4), Gtl</t>
         </is>
       </c>
       <c r="Q116" t="n">
-        <v>700265</v>
+        <v>700275</v>
       </c>
       <c r="R116" t="n">
-        <v>6359056</v>
+        <v>6359045</v>
       </c>
       <c r="S116" t="n">
         <v>4</v>
@@ -13253,7 +13247,7 @@
     </row>
     <row r="117">
       <c r="A117" t="n">
-        <v>126300272</v>
+        <v>126514047</v>
       </c>
       <c r="B117" t="n">
         <v>99036</v>
@@ -13281,24 +13275,20 @@
           <t>(Druce) Hyl.</t>
         </is>
       </c>
-      <c r="I117" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
-      </c>
+      <c r="I117" t="inlineStr"/>
       <c r="P117" t="inlineStr">
         <is>
           <t>Gerum, Likmunds 1:2 (4), Gtl</t>
         </is>
       </c>
       <c r="Q117" t="n">
-        <v>700275</v>
+        <v>700215</v>
       </c>
       <c r="R117" t="n">
-        <v>6359045</v>
+        <v>6359155</v>
       </c>
       <c r="S117" t="n">
-        <v>4</v>
+        <v>8</v>
       </c>
       <c r="T117" t="inlineStr">
         <is>
@@ -13359,10 +13349,10 @@
     </row>
     <row r="118">
       <c r="A118" t="n">
-        <v>126514047</v>
+        <v>134628531</v>
       </c>
       <c r="B118" t="n">
-        <v>99036</v>
+        <v>99113</v>
       </c>
       <c r="D118" t="inlineStr">
         <is>
@@ -13390,17 +13380,17 @@
       <c r="I118" t="inlineStr"/>
       <c r="P118" t="inlineStr">
         <is>
-          <t>Gerum, Likmunds 1:2 (4), Gtl</t>
+          <t>Gerum Likmunds, Gtl</t>
         </is>
       </c>
       <c r="Q118" t="n">
-        <v>700215</v>
+        <v>700192</v>
       </c>
       <c r="R118" t="n">
-        <v>6359155</v>
+        <v>6359150</v>
       </c>
       <c r="S118" t="n">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="T118" t="inlineStr">
         <is>
@@ -13424,12 +13414,22 @@
       </c>
       <c r="Y118" t="inlineStr">
         <is>
-          <t>2025-06-29</t>
+          <t>2026-06-24</t>
+        </is>
+      </c>
+      <c r="Z118" t="inlineStr">
+        <is>
+          <t>16:09</t>
         </is>
       </c>
       <c r="AA118" t="inlineStr">
         <is>
-          <t>2025-06-29</t>
+          <t>2026-06-24</t>
+        </is>
+      </c>
+      <c r="AB118" t="inlineStr">
+        <is>
+          <t>16:09</t>
         </is>
       </c>
       <c r="AD118" t="b">
@@ -13440,28 +13440,23 @@
       </c>
       <c r="AG118" t="b">
         <v>0</v>
-      </c>
-      <c r="AI118" t="inlineStr">
-        <is>
-          <t>Hästbetad blandskog</t>
-        </is>
       </c>
       <c r="AT118" t="inlineStr"/>
       <c r="AW118" t="inlineStr">
         <is>
-          <t>Gun Ingmansson</t>
+          <t>Anna Helmersson</t>
         </is>
       </c>
       <c r="AX118" t="inlineStr">
         <is>
-          <t>Gun Ingmansson, Jörgen Petersson, Björn Larsson</t>
+          <t>Anna Helmersson, Margaret Rainey, Esmeralda  Svanberg</t>
         </is>
       </c>
       <c r="AY118" t="inlineStr"/>
     </row>
     <row r="119">
       <c r="A119" t="n">
-        <v>134628531</v>
+        <v>134629175</v>
       </c>
       <c r="B119" t="n">
         <v>99113</v>
@@ -13492,17 +13487,17 @@
       <c r="I119" t="inlineStr"/>
       <c r="P119" t="inlineStr">
         <is>
-          <t>Gerum Likmunds, Gtl</t>
+          <t>Gerums Likmunds, Gtl</t>
         </is>
       </c>
       <c r="Q119" t="n">
-        <v>700192</v>
+        <v>700259</v>
       </c>
       <c r="R119" t="n">
-        <v>6359150</v>
+        <v>6359029</v>
       </c>
       <c r="S119" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="T119" t="inlineStr">
         <is>
@@ -13531,7 +13526,7 @@
       </c>
       <c r="Z119" t="inlineStr">
         <is>
-          <t>16:09</t>
+          <t>15:54</t>
         </is>
       </c>
       <c r="AA119" t="inlineStr">
@@ -13541,7 +13536,7 @@
       </c>
       <c r="AB119" t="inlineStr">
         <is>
-          <t>16:09</t>
+          <t>15:54</t>
         </is>
       </c>
       <c r="AD119" t="b">
@@ -13556,19 +13551,19 @@
       <c r="AT119" t="inlineStr"/>
       <c r="AW119" t="inlineStr">
         <is>
-          <t>Anna Helmersson</t>
+          <t>Margaret Rainey</t>
         </is>
       </c>
       <c r="AX119" t="inlineStr">
         <is>
-          <t>Anna Helmersson, Margaret Rainey, Esmeralda  Svanberg</t>
+          <t>Margaret Rainey</t>
         </is>
       </c>
       <c r="AY119" t="inlineStr"/>
     </row>
     <row r="120">
       <c r="A120" t="n">
-        <v>134629175</v>
+        <v>134629176</v>
       </c>
       <c r="B120" t="n">
         <v>99113</v>
@@ -13603,13 +13598,13 @@
         </is>
       </c>
       <c r="Q120" t="n">
-        <v>700259</v>
+        <v>700225</v>
       </c>
       <c r="R120" t="n">
-        <v>6359029</v>
+        <v>6359027</v>
       </c>
       <c r="S120" t="n">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="T120" t="inlineStr">
         <is>
@@ -13638,7 +13633,7 @@
       </c>
       <c r="Z120" t="inlineStr">
         <is>
-          <t>15:54</t>
+          <t>15:57</t>
         </is>
       </c>
       <c r="AA120" t="inlineStr">
@@ -13648,7 +13643,7 @@
       </c>
       <c r="AB120" t="inlineStr">
         <is>
-          <t>15:54</t>
+          <t>15:57</t>
         </is>
       </c>
       <c r="AD120" t="b">
@@ -13675,7 +13670,7 @@
     </row>
     <row r="121">
       <c r="A121" t="n">
-        <v>134629176</v>
+        <v>134629180</v>
       </c>
       <c r="B121" t="n">
         <v>99113</v>
@@ -13710,13 +13705,13 @@
         </is>
       </c>
       <c r="Q121" t="n">
-        <v>700225</v>
+        <v>700189</v>
       </c>
       <c r="R121" t="n">
-        <v>6359027</v>
+        <v>6359091</v>
       </c>
       <c r="S121" t="n">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="T121" t="inlineStr">
         <is>
@@ -13745,7 +13740,7 @@
       </c>
       <c r="Z121" t="inlineStr">
         <is>
-          <t>15:57</t>
+          <t>16:04</t>
         </is>
       </c>
       <c r="AA121" t="inlineStr">
@@ -13755,7 +13750,7 @@
       </c>
       <c r="AB121" t="inlineStr">
         <is>
-          <t>15:57</t>
+          <t>16:04</t>
         </is>
       </c>
       <c r="AD121" t="b">
@@ -13782,7 +13777,7 @@
     </row>
     <row r="122">
       <c r="A122" t="n">
-        <v>134629180</v>
+        <v>134629194</v>
       </c>
       <c r="B122" t="n">
         <v>99113</v>
@@ -13817,13 +13812,13 @@
         </is>
       </c>
       <c r="Q122" t="n">
-        <v>700189</v>
+        <v>700257</v>
       </c>
       <c r="R122" t="n">
         <v>6359091</v>
       </c>
       <c r="S122" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="T122" t="inlineStr">
         <is>
@@ -13852,7 +13847,7 @@
       </c>
       <c r="Z122" t="inlineStr">
         <is>
-          <t>16:04</t>
+          <t>16:24</t>
         </is>
       </c>
       <c r="AA122" t="inlineStr">
@@ -13862,7 +13857,7 @@
       </c>
       <c r="AB122" t="inlineStr">
         <is>
-          <t>16:04</t>
+          <t>16:24</t>
         </is>
       </c>
       <c r="AD122" t="b">
@@ -13889,10 +13884,10 @@
     </row>
     <row r="123">
       <c r="A123" t="n">
-        <v>134629194</v>
+        <v>126300254</v>
       </c>
       <c r="B123" t="n">
-        <v>99113</v>
+        <v>99155</v>
       </c>
       <c r="D123" t="inlineStr">
         <is>
@@ -13900,37 +13895,41 @@
         </is>
       </c>
       <c r="E123" t="n">
-        <v>223591</v>
+        <v>223621</v>
       </c>
       <c r="F123" t="inlineStr">
         <is>
-          <t>Skogsnycklar</t>
+          <t>Skogsnattviol</t>
         </is>
       </c>
       <c r="G123" t="inlineStr">
         <is>
-          <t>Dactylorhiza maculata subsp. fuchsii</t>
+          <t>Platanthera bifolia subsp. latiflora</t>
         </is>
       </c>
       <c r="H123" t="inlineStr">
         <is>
-          <t>(Druce) Hyl.</t>
-        </is>
-      </c>
-      <c r="I123" t="inlineStr"/>
+          <t>(Drejer) Løjtnant</t>
+        </is>
+      </c>
+      <c r="I123" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="P123" t="inlineStr">
         <is>
-          <t>Gerums Likmunds, Gtl</t>
+          <t>Gerum, Likmunds 1:2 (4), Gtl</t>
         </is>
       </c>
       <c r="Q123" t="n">
-        <v>700257</v>
+        <v>700231</v>
       </c>
       <c r="R123" t="n">
-        <v>6359091</v>
+        <v>6359136</v>
       </c>
       <c r="S123" t="n">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="T123" t="inlineStr">
         <is>
@@ -13954,22 +13953,12 @@
       </c>
       <c r="Y123" t="inlineStr">
         <is>
-          <t>2026-06-24</t>
-        </is>
-      </c>
-      <c r="Z123" t="inlineStr">
-        <is>
-          <t>16:24</t>
+          <t>2025-06-29</t>
         </is>
       </c>
       <c r="AA123" t="inlineStr">
         <is>
-          <t>2026-06-24</t>
-        </is>
-      </c>
-      <c r="AB123" t="inlineStr">
-        <is>
-          <t>16:24</t>
+          <t>2025-06-29</t>
         </is>
       </c>
       <c r="AD123" t="b">
@@ -13980,125 +13969,24 @@
       </c>
       <c r="AG123" t="b">
         <v>0</v>
+      </c>
+      <c r="AI123" t="inlineStr">
+        <is>
+          <t>Hästbetad blandskog</t>
+        </is>
       </c>
       <c r="AT123" t="inlineStr"/>
       <c r="AW123" t="inlineStr">
         <is>
-          <t>Margaret Rainey</t>
+          <t>Gun Ingmansson</t>
         </is>
       </c>
       <c r="AX123" t="inlineStr">
         <is>
-          <t>Margaret Rainey</t>
+          <t>Gun Ingmansson, Jörgen Petersson, Björn Larsson</t>
         </is>
       </c>
       <c r="AY123" t="inlineStr"/>
-    </row>
-    <row r="124">
-      <c r="A124" t="n">
-        <v>126300254</v>
-      </c>
-      <c r="B124" t="n">
-        <v>99155</v>
-      </c>
-      <c r="D124" t="inlineStr">
-        <is>
-          <t>LC</t>
-        </is>
-      </c>
-      <c r="E124" t="n">
-        <v>223621</v>
-      </c>
-      <c r="F124" t="inlineStr">
-        <is>
-          <t>Skogsnattviol</t>
-        </is>
-      </c>
-      <c r="G124" t="inlineStr">
-        <is>
-          <t>Platanthera bifolia subsp. latiflora</t>
-        </is>
-      </c>
-      <c r="H124" t="inlineStr">
-        <is>
-          <t>(Drejer) Løjtnant</t>
-        </is>
-      </c>
-      <c r="I124" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="P124" t="inlineStr">
-        <is>
-          <t>Gerum, Likmunds 1:2 (4), Gtl</t>
-        </is>
-      </c>
-      <c r="Q124" t="n">
-        <v>700231</v>
-      </c>
-      <c r="R124" t="n">
-        <v>6359136</v>
-      </c>
-      <c r="S124" t="n">
-        <v>4</v>
-      </c>
-      <c r="T124" t="inlineStr">
-        <is>
-          <t>Gotland</t>
-        </is>
-      </c>
-      <c r="U124" t="inlineStr">
-        <is>
-          <t>Gotland</t>
-        </is>
-      </c>
-      <c r="V124" t="inlineStr">
-        <is>
-          <t>Gotland</t>
-        </is>
-      </c>
-      <c r="W124" t="inlineStr">
-        <is>
-          <t>Gerum</t>
-        </is>
-      </c>
-      <c r="Y124" t="inlineStr">
-        <is>
-          <t>2025-06-29</t>
-        </is>
-      </c>
-      <c r="AA124" t="inlineStr">
-        <is>
-          <t>2025-06-29</t>
-        </is>
-      </c>
-      <c r="AD124" t="b">
-        <v>0</v>
-      </c>
-      <c r="AE124" t="b">
-        <v>0</v>
-      </c>
-      <c r="AG124" t="b">
-        <v>0</v>
-      </c>
-      <c r="AI124" t="inlineStr">
-        <is>
-          <t>Hästbetad blandskog</t>
-        </is>
-      </c>
-      <c r="AT124" t="inlineStr"/>
-      <c r="AW124" t="inlineStr">
-        <is>
-          <t>Gun Ingmansson</t>
-        </is>
-      </c>
-      <c r="AX124" t="inlineStr">
-        <is>
-          <t>Gun Ingmansson, Jörgen Petersson, Björn Larsson</t>
-        </is>
-      </c>
-      <c r="AY124" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/artfynd/A 14354-2024 artfynd.xlsx
+++ b/artfynd/A 14354-2024 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY123"/>
+  <dimension ref="A1:AY124"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -9025,7 +9025,7 @@
     </row>
     <row r="78">
       <c r="A78" t="n">
-        <v>134629668</v>
+        <v>134629667</v>
       </c>
       <c r="B78" t="n">
         <v>43472</v>
@@ -9060,13 +9060,13 @@
         </is>
       </c>
       <c r="Q78" t="n">
-        <v>700247</v>
+        <v>700275</v>
       </c>
       <c r="R78" t="n">
-        <v>6359174</v>
+        <v>6359145</v>
       </c>
       <c r="S78" t="n">
-        <v>5</v>
+        <v>12</v>
       </c>
       <c r="T78" t="inlineStr">
         <is>
@@ -9095,7 +9095,7 @@
       </c>
       <c r="Z78" t="inlineStr">
         <is>
-          <t>16:12</t>
+          <t>16:09</t>
         </is>
       </c>
       <c r="AA78" t="inlineStr">
@@ -9105,7 +9105,7 @@
       </c>
       <c r="AB78" t="inlineStr">
         <is>
-          <t>16:12</t>
+          <t>16:09</t>
         </is>
       </c>
       <c r="AC78" t="inlineStr">
@@ -9137,7 +9137,7 @@
     </row>
     <row r="79">
       <c r="A79" t="n">
-        <v>134629671</v>
+        <v>134629668</v>
       </c>
       <c r="B79" t="n">
         <v>43472</v>
@@ -9172,13 +9172,13 @@
         </is>
       </c>
       <c r="Q79" t="n">
-        <v>700257</v>
+        <v>700247</v>
       </c>
       <c r="R79" t="n">
-        <v>6359107</v>
+        <v>6359174</v>
       </c>
       <c r="S79" t="n">
-        <v>17</v>
+        <v>5</v>
       </c>
       <c r="T79" t="inlineStr">
         <is>
@@ -9207,7 +9207,7 @@
       </c>
       <c r="Z79" t="inlineStr">
         <is>
-          <t>16:24</t>
+          <t>16:12</t>
         </is>
       </c>
       <c r="AA79" t="inlineStr">
@@ -9217,12 +9217,12 @@
       </c>
       <c r="AB79" t="inlineStr">
         <is>
-          <t>16:24</t>
+          <t>16:12</t>
         </is>
       </c>
       <c r="AC79" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>1</t>
         </is>
       </c>
       <c r="AD79" t="b">
@@ -9249,7 +9249,7 @@
     </row>
     <row r="80">
       <c r="A80" t="n">
-        <v>134629673</v>
+        <v>134629671</v>
       </c>
       <c r="B80" t="n">
         <v>43472</v>
@@ -9284,13 +9284,13 @@
         </is>
       </c>
       <c r="Q80" t="n">
-        <v>700317</v>
+        <v>700257</v>
       </c>
       <c r="R80" t="n">
-        <v>6359124</v>
+        <v>6359107</v>
       </c>
       <c r="S80" t="n">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="T80" t="inlineStr">
         <is>
@@ -9319,7 +9319,7 @@
       </c>
       <c r="Z80" t="inlineStr">
         <is>
-          <t>16:28</t>
+          <t>16:24</t>
         </is>
       </c>
       <c r="AA80" t="inlineStr">
@@ -9329,12 +9329,12 @@
       </c>
       <c r="AB80" t="inlineStr">
         <is>
-          <t>16:28</t>
+          <t>16:24</t>
         </is>
       </c>
       <c r="AC80" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AD80" t="b">
@@ -9361,7 +9361,7 @@
     </row>
     <row r="81">
       <c r="A81" t="n">
-        <v>134629674</v>
+        <v>134629673</v>
       </c>
       <c r="B81" t="n">
         <v>43472</v>
@@ -9396,13 +9396,13 @@
         </is>
       </c>
       <c r="Q81" t="n">
-        <v>700265</v>
+        <v>700317</v>
       </c>
       <c r="R81" t="n">
-        <v>6359164</v>
+        <v>6359124</v>
       </c>
       <c r="S81" t="n">
-        <v>5</v>
+        <v>16</v>
       </c>
       <c r="T81" t="inlineStr">
         <is>
@@ -9431,7 +9431,7 @@
       </c>
       <c r="Z81" t="inlineStr">
         <is>
-          <t>16:29</t>
+          <t>16:28</t>
         </is>
       </c>
       <c r="AA81" t="inlineStr">
@@ -9441,12 +9441,12 @@
       </c>
       <c r="AB81" t="inlineStr">
         <is>
-          <t>16:29</t>
+          <t>16:28</t>
         </is>
       </c>
       <c r="AC81" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AD81" t="b">
@@ -9473,10 +9473,10 @@
     </row>
     <row r="82">
       <c r="A82" t="n">
-        <v>134629192</v>
+        <v>134629674</v>
       </c>
       <c r="B82" t="n">
-        <v>58260</v>
+        <v>43472</v>
       </c>
       <c r="D82" t="inlineStr">
         <is>
@@ -9484,37 +9484,37 @@
         </is>
       </c>
       <c r="E82" t="n">
-        <v>103012</v>
+        <v>101242</v>
       </c>
       <c r="F82" t="inlineStr">
         <is>
-          <t>Grönsångare</t>
+          <t>Dårgräsfjäril</t>
         </is>
       </c>
       <c r="G82" t="inlineStr">
         <is>
-          <t>Phylloscopus sibilatrix</t>
+          <t>Lopinga achine</t>
         </is>
       </c>
       <c r="H82" t="inlineStr">
         <is>
-          <t>(Bechstein, 1793)</t>
+          <t>(Scopoli, 1763)</t>
         </is>
       </c>
       <c r="I82" t="inlineStr"/>
       <c r="P82" t="inlineStr">
         <is>
-          <t>Gerums Likmunds, Gtl</t>
+          <t>Hästar, Gtl</t>
         </is>
       </c>
       <c r="Q82" t="n">
-        <v>700257</v>
+        <v>700265</v>
       </c>
       <c r="R82" t="n">
-        <v>6359091</v>
+        <v>6359164</v>
       </c>
       <c r="S82" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="T82" t="inlineStr">
         <is>
@@ -9543,7 +9543,7 @@
       </c>
       <c r="Z82" t="inlineStr">
         <is>
-          <t>16:24</t>
+          <t>16:29</t>
         </is>
       </c>
       <c r="AA82" t="inlineStr">
@@ -9553,7 +9553,12 @@
       </c>
       <c r="AB82" t="inlineStr">
         <is>
-          <t>16:24</t>
+          <t>16:29</t>
+        </is>
+      </c>
+      <c r="AC82" t="inlineStr">
+        <is>
+          <t>2</t>
         </is>
       </c>
       <c r="AD82" t="b">
@@ -9568,22 +9573,22 @@
       <c r="AT82" t="inlineStr"/>
       <c r="AW82" t="inlineStr">
         <is>
-          <t>Margaret Rainey</t>
+          <t>Esmeralda  Svanberg</t>
         </is>
       </c>
       <c r="AX82" t="inlineStr">
         <is>
-          <t>Margaret Rainey</t>
+          <t>Esmeralda  Svanberg</t>
         </is>
       </c>
       <c r="AY82" t="inlineStr"/>
     </row>
     <row r="83">
       <c r="A83" t="n">
-        <v>134629189</v>
+        <v>134629192</v>
       </c>
       <c r="B83" t="n">
-        <v>58134</v>
+        <v>58260</v>
       </c>
       <c r="D83" t="inlineStr">
         <is>
@@ -9591,21 +9596,21 @@
         </is>
       </c>
       <c r="E83" t="n">
-        <v>103020</v>
+        <v>103012</v>
       </c>
       <c r="F83" t="inlineStr">
         <is>
-          <t>Entita</t>
+          <t>Grönsångare</t>
         </is>
       </c>
       <c r="G83" t="inlineStr">
         <is>
-          <t>Poecile palustris</t>
+          <t>Phylloscopus sibilatrix</t>
         </is>
       </c>
       <c r="H83" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Bechstein, 1793)</t>
         </is>
       </c>
       <c r="I83" t="inlineStr"/>
@@ -9615,10 +9620,10 @@
         </is>
       </c>
       <c r="Q83" t="n">
-        <v>700255</v>
+        <v>700257</v>
       </c>
       <c r="R83" t="n">
-        <v>6359112</v>
+        <v>6359091</v>
       </c>
       <c r="S83" t="n">
         <v>6</v>
@@ -9650,7 +9655,7 @@
       </c>
       <c r="Z83" t="inlineStr">
         <is>
-          <t>16:20</t>
+          <t>16:24</t>
         </is>
       </c>
       <c r="AA83" t="inlineStr">
@@ -9660,7 +9665,7 @@
       </c>
       <c r="AB83" t="inlineStr">
         <is>
-          <t>16:20</t>
+          <t>16:24</t>
         </is>
       </c>
       <c r="AD83" t="b">
@@ -9680,17 +9685,17 @@
       </c>
       <c r="AX83" t="inlineStr">
         <is>
-          <t>Via Margaret Rainey</t>
+          <t>Margaret Rainey</t>
         </is>
       </c>
       <c r="AY83" t="inlineStr"/>
     </row>
     <row r="84">
       <c r="A84" t="n">
-        <v>111589164</v>
+        <v>134629189</v>
       </c>
       <c r="B84" t="n">
-        <v>5479</v>
+        <v>58134</v>
       </c>
       <c r="D84" t="inlineStr">
         <is>
@@ -9698,62 +9703,37 @@
         </is>
       </c>
       <c r="E84" t="n">
-        <v>105894</v>
+        <v>103020</v>
       </c>
       <c r="F84" t="inlineStr">
         <is>
-          <t>Smedbock</t>
+          <t>Entita</t>
         </is>
       </c>
       <c r="G84" t="inlineStr">
         <is>
-          <t>Ergates faber</t>
+          <t>Poecile palustris</t>
         </is>
       </c>
       <c r="H84" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1761)</t>
-        </is>
-      </c>
-      <c r="I84" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="J84" t="inlineStr">
-        <is>
-          <t>ex.</t>
-        </is>
-      </c>
-      <c r="K84" t="inlineStr">
-        <is>
-          <t>imago/adult</t>
-        </is>
-      </c>
-      <c r="L84" t="inlineStr">
-        <is>
-          <t>hona</t>
-        </is>
-      </c>
-      <c r="M84" t="inlineStr">
-        <is>
-          <t>frispringande/krypande</t>
-        </is>
-      </c>
-      <c r="N84" t="inlineStr"/>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I84" t="inlineStr"/>
       <c r="P84" t="inlineStr">
         <is>
-          <t>Botes källmyr, vägen, Gtl</t>
+          <t>Gerums Likmunds, Gtl</t>
         </is>
       </c>
       <c r="Q84" t="n">
-        <v>700322</v>
+        <v>700255</v>
       </c>
       <c r="R84" t="n">
-        <v>6359100</v>
+        <v>6359112</v>
       </c>
       <c r="S84" t="n">
-        <v>50</v>
+        <v>6</v>
       </c>
       <c r="T84" t="inlineStr">
         <is>
@@ -9777,12 +9757,22 @@
       </c>
       <c r="Y84" t="inlineStr">
         <is>
-          <t>2023-08-15</t>
+          <t>2026-06-24</t>
+        </is>
+      </c>
+      <c r="Z84" t="inlineStr">
+        <is>
+          <t>16:20</t>
         </is>
       </c>
       <c r="AA84" t="inlineStr">
         <is>
-          <t>2023-08-15</t>
+          <t>2026-06-24</t>
+        </is>
+      </c>
+      <c r="AB84" t="inlineStr">
+        <is>
+          <t>16:20</t>
         </is>
       </c>
       <c r="AD84" t="b">
@@ -9791,51 +9781,50 @@
       <c r="AE84" t="b">
         <v>0</v>
       </c>
-      <c r="AF84" t="inlineStr"/>
       <c r="AG84" t="b">
         <v>0</v>
       </c>
       <c r="AT84" t="inlineStr"/>
       <c r="AW84" t="inlineStr">
         <is>
-          <t>Kjell Eriksson</t>
+          <t>Margaret Rainey</t>
         </is>
       </c>
       <c r="AX84" t="inlineStr">
         <is>
-          <t>Kjell Eriksson, Ulla Eriksson</t>
+          <t>Via Margaret Rainey</t>
         </is>
       </c>
       <c r="AY84" t="inlineStr"/>
     </row>
     <row r="85">
       <c r="A85" t="n">
-        <v>116259087</v>
+        <v>111589164</v>
       </c>
       <c r="B85" t="n">
-        <v>99035</v>
+        <v>5479</v>
       </c>
       <c r="D85" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E85" t="n">
-        <v>219790</v>
+        <v>105894</v>
       </c>
       <c r="F85" t="inlineStr">
         <is>
-          <t>Fläcknycklar</t>
+          <t>Smedbock</t>
         </is>
       </c>
       <c r="G85" t="inlineStr">
         <is>
-          <t>Dactylorhiza maculata</t>
+          <t>Ergates faber</t>
         </is>
       </c>
       <c r="H85" t="inlineStr">
         <is>
-          <t>(L.) Soó</t>
+          <t>(Linnaeus, 1761)</t>
         </is>
       </c>
       <c r="I85" t="inlineStr">
@@ -9845,27 +9834,38 @@
       </c>
       <c r="J85" t="inlineStr">
         <is>
-          <t>plantor/tuvor</t>
+          <t>ex.</t>
         </is>
       </c>
       <c r="K85" t="inlineStr">
         <is>
-          <t>fullt utvecklade blad</t>
-        </is>
-      </c>
+          <t>imago/adult</t>
+        </is>
+      </c>
+      <c r="L85" t="inlineStr">
+        <is>
+          <t>hona</t>
+        </is>
+      </c>
+      <c r="M85" t="inlineStr">
+        <is>
+          <t>frispringande/krypande</t>
+        </is>
+      </c>
+      <c r="N85" t="inlineStr"/>
       <c r="P85" t="inlineStr">
         <is>
-          <t>Gerum Likmunds 1:2 (4), Gtl</t>
+          <t>Botes källmyr, vägen, Gtl</t>
         </is>
       </c>
       <c r="Q85" t="n">
-        <v>700256</v>
+        <v>700322</v>
       </c>
       <c r="R85" t="n">
-        <v>6359045</v>
+        <v>6359100</v>
       </c>
       <c r="S85" t="n">
-        <v>3</v>
+        <v>50</v>
       </c>
       <c r="T85" t="inlineStr">
         <is>
@@ -9889,12 +9889,12 @@
       </c>
       <c r="Y85" t="inlineStr">
         <is>
-          <t>2024-04-23</t>
+          <t>2023-08-15</t>
         </is>
       </c>
       <c r="AA85" t="inlineStr">
         <is>
-          <t>2024-04-23</t>
+          <t>2023-08-15</t>
         </is>
       </c>
       <c r="AD85" t="b">
@@ -9903,33 +9903,29 @@
       <c r="AE85" t="b">
         <v>0</v>
       </c>
+      <c r="AF85" t="inlineStr"/>
       <c r="AG85" t="b">
         <v>0</v>
-      </c>
-      <c r="AI85" t="inlineStr">
-        <is>
-          <t>Kalktallskog något fuktigare, träd på socklar, hästbetad.</t>
-        </is>
       </c>
       <c r="AT85" t="inlineStr"/>
       <c r="AW85" t="inlineStr">
         <is>
-          <t>Jörgen Petersson</t>
+          <t>Kjell Eriksson</t>
         </is>
       </c>
       <c r="AX85" t="inlineStr">
         <is>
-          <t>Jörgen Petersson</t>
+          <t>Kjell Eriksson, Ulla Eriksson</t>
         </is>
       </c>
       <c r="AY85" t="inlineStr"/>
     </row>
     <row r="86">
       <c r="A86" t="n">
-        <v>126300257</v>
+        <v>116259087</v>
       </c>
       <c r="B86" t="n">
-        <v>99096</v>
+        <v>99035</v>
       </c>
       <c r="D86" t="inlineStr">
         <is>
@@ -9937,21 +9933,21 @@
         </is>
       </c>
       <c r="E86" t="n">
-        <v>219798</v>
+        <v>219790</v>
       </c>
       <c r="F86" t="inlineStr">
         <is>
-          <t>Skogsknipprot</t>
+          <t>Fläcknycklar</t>
         </is>
       </c>
       <c r="G86" t="inlineStr">
         <is>
-          <t>Epipactis helleborine</t>
+          <t>Dactylorhiza maculata</t>
         </is>
       </c>
       <c r="H86" t="inlineStr">
         <is>
-          <t>(L.) Crantz</t>
+          <t>(L.) Soó</t>
         </is>
       </c>
       <c r="I86" t="inlineStr">
@@ -9959,19 +9955,29 @@
           <t>1</t>
         </is>
       </c>
+      <c r="J86" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="K86" t="inlineStr">
+        <is>
+          <t>fullt utvecklade blad</t>
+        </is>
+      </c>
       <c r="P86" t="inlineStr">
         <is>
-          <t>Gerum, Likmunds 1:2 (4), Gtl</t>
+          <t>Gerum Likmunds 1:2 (4), Gtl</t>
         </is>
       </c>
       <c r="Q86" t="n">
-        <v>700247</v>
+        <v>700256</v>
       </c>
       <c r="R86" t="n">
-        <v>6359114</v>
+        <v>6359045</v>
       </c>
       <c r="S86" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="T86" t="inlineStr">
         <is>
@@ -9995,12 +10001,12 @@
       </c>
       <c r="Y86" t="inlineStr">
         <is>
-          <t>2025-06-29</t>
+          <t>2024-04-23</t>
         </is>
       </c>
       <c r="AA86" t="inlineStr">
         <is>
-          <t>2025-06-29</t>
+          <t>2024-04-23</t>
         </is>
       </c>
       <c r="AD86" t="b">
@@ -10014,25 +10020,25 @@
       </c>
       <c r="AI86" t="inlineStr">
         <is>
-          <t>Hästbetad blandskog</t>
+          <t>Kalktallskog något fuktigare, träd på socklar, hästbetad.</t>
         </is>
       </c>
       <c r="AT86" t="inlineStr"/>
       <c r="AW86" t="inlineStr">
         <is>
-          <t>Gun Ingmansson</t>
+          <t>Jörgen Petersson</t>
         </is>
       </c>
       <c r="AX86" t="inlineStr">
         <is>
-          <t>Gun Ingmansson, Jörgen Petersson, Björn Larsson</t>
+          <t>Jörgen Petersson</t>
         </is>
       </c>
       <c r="AY86" t="inlineStr"/>
     </row>
     <row r="87">
       <c r="A87" t="n">
-        <v>126514044</v>
+        <v>126300257</v>
       </c>
       <c r="B87" t="n">
         <v>99096</v>
@@ -10071,13 +10077,13 @@
         </is>
       </c>
       <c r="Q87" t="n">
-        <v>700215</v>
+        <v>700247</v>
       </c>
       <c r="R87" t="n">
-        <v>6359155</v>
+        <v>6359114</v>
       </c>
       <c r="S87" t="n">
-        <v>8</v>
+        <v>4</v>
       </c>
       <c r="T87" t="inlineStr">
         <is>
@@ -10138,10 +10144,10 @@
     </row>
     <row r="88">
       <c r="A88" t="n">
-        <v>126300256</v>
+        <v>126514044</v>
       </c>
       <c r="B88" t="n">
-        <v>99142</v>
+        <v>99096</v>
       </c>
       <c r="D88" t="inlineStr">
         <is>
@@ -10149,37 +10155,41 @@
         </is>
       </c>
       <c r="E88" t="n">
-        <v>219847</v>
+        <v>219798</v>
       </c>
       <c r="F88" t="inlineStr">
         <is>
-          <t>Tvåblad</t>
+          <t>Skogsknipprot</t>
         </is>
       </c>
       <c r="G88" t="inlineStr">
         <is>
-          <t>Neottia ovata</t>
+          <t>Epipactis helleborine</t>
         </is>
       </c>
       <c r="H88" t="inlineStr">
         <is>
-          <t>(L.) Buff. &amp; Fingerh.</t>
-        </is>
-      </c>
-      <c r="I88" t="inlineStr"/>
+          <t>(L.) Crantz</t>
+        </is>
+      </c>
+      <c r="I88" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="P88" t="inlineStr">
         <is>
           <t>Gerum, Likmunds 1:2 (4), Gtl</t>
         </is>
       </c>
       <c r="Q88" t="n">
-        <v>700247</v>
+        <v>700215</v>
       </c>
       <c r="R88" t="n">
-        <v>6359114</v>
+        <v>6359155</v>
       </c>
       <c r="S88" t="n">
-        <v>4</v>
+        <v>8</v>
       </c>
       <c r="T88" t="inlineStr">
         <is>
@@ -10240,7 +10250,7 @@
     </row>
     <row r="89">
       <c r="A89" t="n">
-        <v>126300258</v>
+        <v>126300256</v>
       </c>
       <c r="B89" t="n">
         <v>99142</v>
@@ -10268,11 +10278,7 @@
           <t>(L.) Buff. &amp; Fingerh.</t>
         </is>
       </c>
-      <c r="I89" t="inlineStr">
-        <is>
-          <t>7</t>
-        </is>
-      </c>
+      <c r="I89" t="inlineStr"/>
       <c r="P89" t="inlineStr">
         <is>
           <t>Gerum, Likmunds 1:2 (4), Gtl</t>
@@ -10282,10 +10288,10 @@
         <v>700247</v>
       </c>
       <c r="R89" t="n">
-        <v>6359105</v>
+        <v>6359114</v>
       </c>
       <c r="S89" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="T89" t="inlineStr">
         <is>
@@ -10346,7 +10352,7 @@
     </row>
     <row r="90">
       <c r="A90" t="n">
-        <v>126300265</v>
+        <v>126300258</v>
       </c>
       <c r="B90" t="n">
         <v>99142</v>
@@ -10374,7 +10380,11 @@
           <t>(L.) Buff. &amp; Fingerh.</t>
         </is>
       </c>
-      <c r="I90" t="inlineStr"/>
+      <c r="I90" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
       <c r="P90" t="inlineStr">
         <is>
           <t>Gerum, Likmunds 1:2 (4), Gtl</t>
@@ -10384,10 +10394,10 @@
         <v>700247</v>
       </c>
       <c r="R90" t="n">
-        <v>6359082</v>
+        <v>6359105</v>
       </c>
       <c r="S90" t="n">
-        <v>8</v>
+        <v>5</v>
       </c>
       <c r="T90" t="inlineStr">
         <is>
@@ -10448,7 +10458,7 @@
     </row>
     <row r="91">
       <c r="A91" t="n">
-        <v>126300268</v>
+        <v>126300265</v>
       </c>
       <c r="B91" t="n">
         <v>99142</v>
@@ -10483,13 +10493,13 @@
         </is>
       </c>
       <c r="Q91" t="n">
-        <v>700265</v>
+        <v>700247</v>
       </c>
       <c r="R91" t="n">
-        <v>6359056</v>
+        <v>6359082</v>
       </c>
       <c r="S91" t="n">
-        <v>4</v>
+        <v>8</v>
       </c>
       <c r="T91" t="inlineStr">
         <is>
@@ -10550,7 +10560,7 @@
     </row>
     <row r="92">
       <c r="A92" t="n">
-        <v>126300273</v>
+        <v>126300268</v>
       </c>
       <c r="B92" t="n">
         <v>99142</v>
@@ -10578,21 +10588,17 @@
           <t>(L.) Buff. &amp; Fingerh.</t>
         </is>
       </c>
-      <c r="I92" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
+      <c r="I92" t="inlineStr"/>
       <c r="P92" t="inlineStr">
         <is>
           <t>Gerum, Likmunds 1:2 (4), Gtl</t>
         </is>
       </c>
       <c r="Q92" t="n">
-        <v>700275</v>
+        <v>700265</v>
       </c>
       <c r="R92" t="n">
-        <v>6359045</v>
+        <v>6359056</v>
       </c>
       <c r="S92" t="n">
         <v>4</v>
@@ -10656,7 +10662,7 @@
     </row>
     <row r="93">
       <c r="A93" t="n">
-        <v>126514045</v>
+        <v>126300273</v>
       </c>
       <c r="B93" t="n">
         <v>99142</v>
@@ -10684,20 +10690,24 @@
           <t>(L.) Buff. &amp; Fingerh.</t>
         </is>
       </c>
-      <c r="I93" t="inlineStr"/>
+      <c r="I93" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
       <c r="P93" t="inlineStr">
         <is>
           <t>Gerum, Likmunds 1:2 (4), Gtl</t>
         </is>
       </c>
       <c r="Q93" t="n">
-        <v>700215</v>
+        <v>700275</v>
       </c>
       <c r="R93" t="n">
-        <v>6359155</v>
+        <v>6359045</v>
       </c>
       <c r="S93" t="n">
-        <v>8</v>
+        <v>4</v>
       </c>
       <c r="T93" t="inlineStr">
         <is>
@@ -10758,7 +10768,7 @@
     </row>
     <row r="94">
       <c r="A94" t="n">
-        <v>126514049</v>
+        <v>126514045</v>
       </c>
       <c r="B94" t="n">
         <v>99142</v>
@@ -10793,13 +10803,13 @@
         </is>
       </c>
       <c r="Q94" t="n">
-        <v>700235</v>
+        <v>700215</v>
       </c>
       <c r="R94" t="n">
-        <v>6359147</v>
+        <v>6359155</v>
       </c>
       <c r="S94" t="n">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="T94" t="inlineStr">
         <is>
@@ -10860,10 +10870,10 @@
     </row>
     <row r="95">
       <c r="A95" t="n">
-        <v>134628528</v>
+        <v>126514049</v>
       </c>
       <c r="B95" t="n">
-        <v>99219</v>
+        <v>99142</v>
       </c>
       <c r="D95" t="inlineStr">
         <is>
@@ -10891,17 +10901,17 @@
       <c r="I95" t="inlineStr"/>
       <c r="P95" t="inlineStr">
         <is>
-          <t>Gerum Likmunds, Gtl</t>
+          <t>Gerum, Likmunds 1:2 (4), Gtl</t>
         </is>
       </c>
       <c r="Q95" t="n">
-        <v>700250</v>
+        <v>700235</v>
       </c>
       <c r="R95" t="n">
-        <v>6359173</v>
+        <v>6359147</v>
       </c>
       <c r="S95" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T95" t="inlineStr">
         <is>
@@ -10925,22 +10935,12 @@
       </c>
       <c r="Y95" t="inlineStr">
         <is>
-          <t>2026-06-24</t>
-        </is>
-      </c>
-      <c r="Z95" t="inlineStr">
-        <is>
-          <t>15:58</t>
+          <t>2025-06-29</t>
         </is>
       </c>
       <c r="AA95" t="inlineStr">
         <is>
-          <t>2026-06-24</t>
-        </is>
-      </c>
-      <c r="AB95" t="inlineStr">
-        <is>
-          <t>15:58</t>
+          <t>2025-06-29</t>
         </is>
       </c>
       <c r="AD95" t="b">
@@ -10951,23 +10951,28 @@
       </c>
       <c r="AG95" t="b">
         <v>0</v>
+      </c>
+      <c r="AI95" t="inlineStr">
+        <is>
+          <t>Hästbetad blandskog</t>
+        </is>
       </c>
       <c r="AT95" t="inlineStr"/>
       <c r="AW95" t="inlineStr">
         <is>
-          <t>Anna Helmersson</t>
+          <t>Gun Ingmansson</t>
         </is>
       </c>
       <c r="AX95" t="inlineStr">
         <is>
-          <t>Anna Helmersson, Margaret Rainey, Esmeralda  Svanberg</t>
+          <t>Gun Ingmansson, Jörgen Petersson, Björn Larsson</t>
         </is>
       </c>
       <c r="AY95" t="inlineStr"/>
     </row>
     <row r="96">
       <c r="A96" t="n">
-        <v>134629174</v>
+        <v>134628528</v>
       </c>
       <c r="B96" t="n">
         <v>99219</v>
@@ -10998,14 +11003,14 @@
       <c r="I96" t="inlineStr"/>
       <c r="P96" t="inlineStr">
         <is>
-          <t>Gerums Likmunds, Gtl</t>
+          <t>Gerum Likmunds, Gtl</t>
         </is>
       </c>
       <c r="Q96" t="n">
-        <v>700262</v>
+        <v>700250</v>
       </c>
       <c r="R96" t="n">
-        <v>6359042</v>
+        <v>6359173</v>
       </c>
       <c r="S96" t="n">
         <v>5</v>
@@ -11037,7 +11042,7 @@
       </c>
       <c r="Z96" t="inlineStr">
         <is>
-          <t>15:53</t>
+          <t>15:58</t>
         </is>
       </c>
       <c r="AA96" t="inlineStr">
@@ -11047,7 +11052,7 @@
       </c>
       <c r="AB96" t="inlineStr">
         <is>
-          <t>15:53</t>
+          <t>15:58</t>
         </is>
       </c>
       <c r="AD96" t="b">
@@ -11062,19 +11067,19 @@
       <c r="AT96" t="inlineStr"/>
       <c r="AW96" t="inlineStr">
         <is>
-          <t>Margaret Rainey</t>
+          <t>Anna Helmersson</t>
         </is>
       </c>
       <c r="AX96" t="inlineStr">
         <is>
-          <t>Margaret Rainey</t>
+          <t>Anna Helmersson, Margaret Rainey, Esmeralda  Svanberg</t>
         </is>
       </c>
       <c r="AY96" t="inlineStr"/>
     </row>
     <row r="97">
       <c r="A97" t="n">
-        <v>134629183</v>
+        <v>134629174</v>
       </c>
       <c r="B97" t="n">
         <v>99219</v>
@@ -11109,10 +11114,10 @@
         </is>
       </c>
       <c r="Q97" t="n">
-        <v>700205</v>
+        <v>700262</v>
       </c>
       <c r="R97" t="n">
-        <v>6359141</v>
+        <v>6359042</v>
       </c>
       <c r="S97" t="n">
         <v>5</v>
@@ -11144,7 +11149,7 @@
       </c>
       <c r="Z97" t="inlineStr">
         <is>
-          <t>16:11</t>
+          <t>15:53</t>
         </is>
       </c>
       <c r="AA97" t="inlineStr">
@@ -11154,7 +11159,7 @@
       </c>
       <c r="AB97" t="inlineStr">
         <is>
-          <t>16:11</t>
+          <t>15:53</t>
         </is>
       </c>
       <c r="AD97" t="b">
@@ -11181,7 +11186,7 @@
     </row>
     <row r="98">
       <c r="A98" t="n">
-        <v>134629187</v>
+        <v>134629183</v>
       </c>
       <c r="B98" t="n">
         <v>99219</v>
@@ -11216,10 +11221,10 @@
         </is>
       </c>
       <c r="Q98" t="n">
-        <v>700230</v>
+        <v>700205</v>
       </c>
       <c r="R98" t="n">
-        <v>6359151</v>
+        <v>6359141</v>
       </c>
       <c r="S98" t="n">
         <v>5</v>
@@ -11251,7 +11256,7 @@
       </c>
       <c r="Z98" t="inlineStr">
         <is>
-          <t>16:16</t>
+          <t>16:11</t>
         </is>
       </c>
       <c r="AA98" t="inlineStr">
@@ -11261,12 +11266,7 @@
       </c>
       <c r="AB98" t="inlineStr">
         <is>
-          <t>16:16</t>
-        </is>
-      </c>
-      <c r="AC98" t="inlineStr">
-        <is>
-          <t>3 st</t>
+          <t>16:11</t>
         </is>
       </c>
       <c r="AD98" t="b">
@@ -11293,10 +11293,10 @@
     </row>
     <row r="99">
       <c r="A99" t="n">
-        <v>126300267</v>
+        <v>134629187</v>
       </c>
       <c r="B99" t="n">
-        <v>99141</v>
+        <v>99219</v>
       </c>
       <c r="D99" t="inlineStr">
         <is>
@@ -11304,41 +11304,37 @@
         </is>
       </c>
       <c r="E99" t="n">
-        <v>219862</v>
+        <v>219847</v>
       </c>
       <c r="F99" t="inlineStr">
         <is>
-          <t>Nästrot</t>
+          <t>Tvåblad</t>
         </is>
       </c>
       <c r="G99" t="inlineStr">
         <is>
-          <t>Neottia nidus-avis</t>
+          <t>Neottia ovata</t>
         </is>
       </c>
       <c r="H99" t="inlineStr">
         <is>
-          <t>(L.) Rich.</t>
-        </is>
-      </c>
-      <c r="I99" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
+          <t>(L.) Buff. &amp; Fingerh.</t>
+        </is>
+      </c>
+      <c r="I99" t="inlineStr"/>
       <c r="P99" t="inlineStr">
         <is>
-          <t>Gerum, Likmunds 1:2 (4), Gtl</t>
+          <t>Gerums Likmunds, Gtl</t>
         </is>
       </c>
       <c r="Q99" t="n">
-        <v>700257</v>
+        <v>700230</v>
       </c>
       <c r="R99" t="n">
-        <v>6359067</v>
+        <v>6359151</v>
       </c>
       <c r="S99" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T99" t="inlineStr">
         <is>
@@ -11362,12 +11358,27 @@
       </c>
       <c r="Y99" t="inlineStr">
         <is>
-          <t>2025-06-29</t>
+          <t>2026-06-24</t>
+        </is>
+      </c>
+      <c r="Z99" t="inlineStr">
+        <is>
+          <t>16:16</t>
         </is>
       </c>
       <c r="AA99" t="inlineStr">
         <is>
-          <t>2025-06-29</t>
+          <t>2026-06-24</t>
+        </is>
+      </c>
+      <c r="AB99" t="inlineStr">
+        <is>
+          <t>16:16</t>
+        </is>
+      </c>
+      <c r="AC99" t="inlineStr">
+        <is>
+          <t>3 st</t>
         </is>
       </c>
       <c r="AD99" t="b">
@@ -11378,31 +11389,26 @@
       </c>
       <c r="AG99" t="b">
         <v>0</v>
-      </c>
-      <c r="AI99" t="inlineStr">
-        <is>
-          <t>Hästbetad blandskog</t>
-        </is>
       </c>
       <c r="AT99" t="inlineStr"/>
       <c r="AW99" t="inlineStr">
         <is>
-          <t>Gun Ingmansson</t>
+          <t>Margaret Rainey</t>
         </is>
       </c>
       <c r="AX99" t="inlineStr">
         <is>
-          <t>Gun Ingmansson, Jörgen Petersson, Björn Larsson</t>
+          <t>Margaret Rainey</t>
         </is>
       </c>
       <c r="AY99" t="inlineStr"/>
     </row>
     <row r="100">
       <c r="A100" t="n">
-        <v>134629170</v>
+        <v>126300267</v>
       </c>
       <c r="B100" t="n">
-        <v>99230</v>
+        <v>99141</v>
       </c>
       <c r="D100" t="inlineStr">
         <is>
@@ -11410,16 +11416,16 @@
         </is>
       </c>
       <c r="E100" t="n">
-        <v>219874</v>
+        <v>219862</v>
       </c>
       <c r="F100" t="inlineStr">
         <is>
-          <t>Nattviol</t>
+          <t>Nästrot</t>
         </is>
       </c>
       <c r="G100" t="inlineStr">
         <is>
-          <t>Platanthera bifolia</t>
+          <t>Neottia nidus-avis</t>
         </is>
       </c>
       <c r="H100" t="inlineStr">
@@ -11427,20 +11433,24 @@
           <t>(L.) Rich.</t>
         </is>
       </c>
-      <c r="I100" t="inlineStr"/>
+      <c r="I100" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
       <c r="P100" t="inlineStr">
         <is>
-          <t>Gerums Likmunds, Gtl</t>
+          <t>Gerum, Likmunds 1:2 (4), Gtl</t>
         </is>
       </c>
       <c r="Q100" t="n">
-        <v>700270</v>
+        <v>700257</v>
       </c>
       <c r="R100" t="n">
-        <v>6359038</v>
+        <v>6359067</v>
       </c>
       <c r="S100" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T100" t="inlineStr">
         <is>
@@ -11464,22 +11474,12 @@
       </c>
       <c r="Y100" t="inlineStr">
         <is>
-          <t>2026-06-24</t>
-        </is>
-      </c>
-      <c r="Z100" t="inlineStr">
-        <is>
-          <t>15:48</t>
+          <t>2025-06-29</t>
         </is>
       </c>
       <c r="AA100" t="inlineStr">
         <is>
-          <t>2026-06-24</t>
-        </is>
-      </c>
-      <c r="AB100" t="inlineStr">
-        <is>
-          <t>15:48</t>
+          <t>2025-06-29</t>
         </is>
       </c>
       <c r="AD100" t="b">
@@ -11490,72 +11490,69 @@
       </c>
       <c r="AG100" t="b">
         <v>0</v>
+      </c>
+      <c r="AI100" t="inlineStr">
+        <is>
+          <t>Hästbetad blandskog</t>
+        </is>
       </c>
       <c r="AT100" t="inlineStr"/>
       <c r="AW100" t="inlineStr">
         <is>
-          <t>Margaret Rainey</t>
+          <t>Gun Ingmansson</t>
         </is>
       </c>
       <c r="AX100" t="inlineStr">
         <is>
-          <t>Margaret Rainey</t>
+          <t>Gun Ingmansson, Jörgen Petersson, Björn Larsson</t>
         </is>
       </c>
       <c r="AY100" t="inlineStr"/>
     </row>
     <row r="101">
       <c r="A101" t="n">
-        <v>97960624</v>
+        <v>134629170</v>
       </c>
       <c r="B101" t="n">
-        <v>110078</v>
+        <v>99230</v>
       </c>
       <c r="D101" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E101" t="n">
-        <v>220299</v>
+        <v>219874</v>
       </c>
       <c r="F101" t="inlineStr">
         <is>
-          <t>Svinrot</t>
+          <t>Nattviol</t>
         </is>
       </c>
       <c r="G101" t="inlineStr">
         <is>
-          <t>Scorzonera humilis</t>
+          <t>Platanthera bifolia</t>
         </is>
       </c>
       <c r="H101" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(L.) Rich.</t>
         </is>
       </c>
       <c r="I101" t="inlineStr"/>
-      <c r="J101" t="inlineStr"/>
-      <c r="K101" t="inlineStr">
-        <is>
-          <t>vinterståndare</t>
-        </is>
-      </c>
-      <c r="L101" t="inlineStr"/>
-      <c r="N101" t="inlineStr"/>
       <c r="P101" t="inlineStr">
         <is>
-          <t>Russparken, parkeringen 100m N, Gtl</t>
+          <t>Gerums Likmunds, Gtl</t>
         </is>
       </c>
       <c r="Q101" t="n">
-        <v>700333</v>
+        <v>700270</v>
       </c>
       <c r="R101" t="n">
-        <v>6359040</v>
+        <v>6359038</v>
       </c>
       <c r="S101" t="n">
-        <v>25</v>
+        <v>5</v>
       </c>
       <c r="T101" t="inlineStr">
         <is>
@@ -11579,12 +11576,22 @@
       </c>
       <c r="Y101" t="inlineStr">
         <is>
-          <t>2022-01-06</t>
+          <t>2026-06-24</t>
+        </is>
+      </c>
+      <c r="Z101" t="inlineStr">
+        <is>
+          <t>15:48</t>
         </is>
       </c>
       <c r="AA101" t="inlineStr">
         <is>
-          <t>2022-01-06</t>
+          <t>2026-06-24</t>
+        </is>
+      </c>
+      <c r="AB101" t="inlineStr">
+        <is>
+          <t>15:48</t>
         </is>
       </c>
       <c r="AD101" t="b">
@@ -11593,29 +11600,28 @@
       <c r="AE101" t="b">
         <v>0</v>
       </c>
-      <c r="AF101" t="inlineStr"/>
       <c r="AG101" t="b">
         <v>0</v>
       </c>
       <c r="AT101" t="inlineStr"/>
       <c r="AW101" t="inlineStr">
         <is>
-          <t>Dennis Nyström</t>
+          <t>Margaret Rainey</t>
         </is>
       </c>
       <c r="AX101" t="inlineStr">
         <is>
-          <t>Dennis Nyström</t>
+          <t>Margaret Rainey</t>
         </is>
       </c>
       <c r="AY101" t="inlineStr"/>
     </row>
     <row r="102">
       <c r="A102" t="n">
-        <v>2760594</v>
+        <v>97960624</v>
       </c>
       <c r="B102" t="n">
-        <v>110117</v>
+        <v>110078</v>
       </c>
       <c r="D102" t="inlineStr">
         <is>
@@ -11623,16 +11629,16 @@
         </is>
       </c>
       <c r="E102" t="n">
-        <v>220320</v>
+        <v>220299</v>
       </c>
       <c r="F102" t="inlineStr">
         <is>
-          <t>Ängsskära</t>
+          <t>Svinrot</t>
         </is>
       </c>
       <c r="G102" t="inlineStr">
         <is>
-          <t>Serratula tinctoria</t>
+          <t>Scorzonera humilis</t>
         </is>
       </c>
       <c r="H102" t="inlineStr">
@@ -11640,34 +11646,28 @@
           <t>L.</t>
         </is>
       </c>
-      <c r="I102" t="inlineStr">
-        <is>
-          <t>49</t>
-        </is>
-      </c>
-      <c r="J102" t="inlineStr">
-        <is>
-          <t>stjälkar/strån/skott</t>
-        </is>
-      </c>
+      <c r="I102" t="inlineStr"/>
+      <c r="J102" t="inlineStr"/>
       <c r="K102" t="inlineStr">
         <is>
-          <t>frukt-/fröspridning</t>
-        </is>
-      </c>
+          <t>vinterståndare</t>
+        </is>
+      </c>
+      <c r="L102" t="inlineStr"/>
+      <c r="N102" t="inlineStr"/>
       <c r="P102" t="inlineStr">
         <is>
-          <t>Lojsta hed, Botes källmyr S-ut, Gtl</t>
+          <t>Russparken, parkeringen 100m N, Gtl</t>
         </is>
       </c>
       <c r="Q102" t="n">
-        <v>700332</v>
+        <v>700333</v>
       </c>
       <c r="R102" t="n">
-        <v>6359036</v>
+        <v>6359040</v>
       </c>
       <c r="S102" t="n">
-        <v>5</v>
+        <v>25</v>
       </c>
       <c r="T102" t="inlineStr">
         <is>
@@ -11691,17 +11691,12 @@
       </c>
       <c r="Y102" t="inlineStr">
         <is>
-          <t>2008-09-04</t>
+          <t>2022-01-06</t>
         </is>
       </c>
       <c r="AA102" t="inlineStr">
         <is>
-          <t>2008-09-04</t>
-        </is>
-      </c>
-      <c r="AC102" t="inlineStr">
-        <is>
-          <t>Återfynd.</t>
+          <t>2022-01-06</t>
         </is>
       </c>
       <c r="AD102" t="b">
@@ -11710,30 +11705,26 @@
       <c r="AE102" t="b">
         <v>0</v>
       </c>
+      <c r="AF102" t="inlineStr"/>
       <c r="AG102" t="b">
         <v>0</v>
-      </c>
-      <c r="AI102" t="inlineStr">
-        <is>
-          <t>Stigkant</t>
-        </is>
       </c>
       <c r="AT102" t="inlineStr"/>
       <c r="AW102" t="inlineStr">
         <is>
-          <t>Joakim Ekman</t>
+          <t>Dennis Nyström</t>
         </is>
       </c>
       <c r="AX102" t="inlineStr">
         <is>
-          <t>Joakim Ekman, Gabriel Ekman</t>
+          <t>Dennis Nyström</t>
         </is>
       </c>
       <c r="AY102" t="inlineStr"/>
     </row>
     <row r="103">
       <c r="A103" t="n">
-        <v>16230167</v>
+        <v>2760594</v>
       </c>
       <c r="B103" t="n">
         <v>110117</v>
@@ -11761,27 +11752,34 @@
           <t>L.</t>
         </is>
       </c>
-      <c r="I103" t="inlineStr"/>
-      <c r="J103" t="inlineStr"/>
+      <c r="I103" t="inlineStr">
+        <is>
+          <t>49</t>
+        </is>
+      </c>
+      <c r="J103" t="inlineStr">
+        <is>
+          <t>stjälkar/strån/skott</t>
+        </is>
+      </c>
       <c r="K103" t="inlineStr">
         <is>
-          <t>blomning</t>
-        </is>
-      </c>
-      <c r="L103" t="inlineStr"/>
+          <t>frukt-/fröspridning</t>
+        </is>
+      </c>
       <c r="P103" t="inlineStr">
         <is>
-          <t>Russparken, parkeringen 100m N, Gtl</t>
+          <t>Lojsta hed, Botes källmyr S-ut, Gtl</t>
         </is>
       </c>
       <c r="Q103" t="n">
-        <v>700333</v>
+        <v>700332</v>
       </c>
       <c r="R103" t="n">
-        <v>6359040</v>
+        <v>6359036</v>
       </c>
       <c r="S103" t="n">
-        <v>25</v>
+        <v>5</v>
       </c>
       <c r="T103" t="inlineStr">
         <is>
@@ -11805,12 +11803,17 @@
       </c>
       <c r="Y103" t="inlineStr">
         <is>
-          <t>2014-07-21</t>
+          <t>2008-09-04</t>
         </is>
       </c>
       <c r="AA103" t="inlineStr">
         <is>
-          <t>2014-07-21</t>
+          <t>2008-09-04</t>
+        </is>
+      </c>
+      <c r="AC103" t="inlineStr">
+        <is>
+          <t>Återfynd.</t>
         </is>
       </c>
       <c r="AD103" t="b">
@@ -11821,23 +11824,28 @@
       </c>
       <c r="AG103" t="b">
         <v>0</v>
+      </c>
+      <c r="AI103" t="inlineStr">
+        <is>
+          <t>Stigkant</t>
+        </is>
       </c>
       <c r="AT103" t="inlineStr"/>
       <c r="AW103" t="inlineStr">
         <is>
-          <t>Dennis Nyström</t>
+          <t>Joakim Ekman</t>
         </is>
       </c>
       <c r="AX103" t="inlineStr">
         <is>
-          <t>Dennis Nyström</t>
+          <t>Joakim Ekman, Gabriel Ekman</t>
         </is>
       </c>
       <c r="AY103" t="inlineStr"/>
     </row>
     <row r="104">
       <c r="A104" t="n">
-        <v>16500486</v>
+        <v>16230167</v>
       </c>
       <c r="B104" t="n">
         <v>110117</v>
@@ -11867,18 +11875,22 @@
       </c>
       <c r="I104" t="inlineStr"/>
       <c r="J104" t="inlineStr"/>
-      <c r="K104" t="inlineStr"/>
+      <c r="K104" t="inlineStr">
+        <is>
+          <t>blomning</t>
+        </is>
+      </c>
       <c r="L104" t="inlineStr"/>
       <c r="P104" t="inlineStr">
         <is>
-          <t>Lojsta, Gtl</t>
+          <t>Russparken, parkeringen 100m N, Gtl</t>
         </is>
       </c>
       <c r="Q104" t="n">
-        <v>700339</v>
+        <v>700333</v>
       </c>
       <c r="R104" t="n">
-        <v>6359017</v>
+        <v>6359040</v>
       </c>
       <c r="S104" t="n">
         <v>25</v>
@@ -11900,17 +11912,17 @@
       </c>
       <c r="W104" t="inlineStr">
         <is>
-          <t>Fardhem</t>
+          <t>Gerum</t>
         </is>
       </c>
       <c r="Y104" t="inlineStr">
         <is>
-          <t>2014-08-12</t>
+          <t>2014-07-21</t>
         </is>
       </c>
       <c r="AA104" t="inlineStr">
         <is>
-          <t>2014-08-12</t>
+          <t>2014-07-21</t>
         </is>
       </c>
       <c r="AD104" t="b">
@@ -11925,19 +11937,19 @@
       <c r="AT104" t="inlineStr"/>
       <c r="AW104" t="inlineStr">
         <is>
-          <t>Thomas Strid</t>
+          <t>Dennis Nyström</t>
         </is>
       </c>
       <c r="AX104" t="inlineStr">
         <is>
-          <t>Thomas Strid, Tiina Laantee, Melica Strid</t>
+          <t>Dennis Nyström</t>
         </is>
       </c>
       <c r="AY104" t="inlineStr"/>
     </row>
     <row r="105">
       <c r="A105" t="n">
-        <v>69716937</v>
+        <v>16500486</v>
       </c>
       <c r="B105" t="n">
         <v>110117</v>
@@ -11966,24 +11978,22 @@
         </is>
       </c>
       <c r="I105" t="inlineStr"/>
-      <c r="K105" t="inlineStr">
-        <is>
-          <t>blomning</t>
-        </is>
-      </c>
+      <c r="J105" t="inlineStr"/>
+      <c r="K105" t="inlineStr"/>
+      <c r="L105" t="inlineStr"/>
       <c r="P105" t="inlineStr">
         <is>
-          <t>Lojsta hed, S om Botes källmyrs NR, Gtl</t>
+          <t>Lojsta, Gtl</t>
         </is>
       </c>
       <c r="Q105" t="n">
-        <v>700329</v>
+        <v>700339</v>
       </c>
       <c r="R105" t="n">
-        <v>6359034</v>
+        <v>6359017</v>
       </c>
       <c r="S105" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T105" t="inlineStr">
         <is>
@@ -12002,17 +12012,17 @@
       </c>
       <c r="W105" t="inlineStr">
         <is>
-          <t>Gerum</t>
+          <t>Fardhem</t>
         </is>
       </c>
       <c r="Y105" t="inlineStr">
         <is>
-          <t>2009-07-23</t>
+          <t>2014-08-12</t>
         </is>
       </c>
       <c r="AA105" t="inlineStr">
         <is>
-          <t>2009-07-23</t>
+          <t>2014-08-12</t>
         </is>
       </c>
       <c r="AD105" t="b">
@@ -12023,28 +12033,23 @@
       </c>
       <c r="AG105" t="b">
         <v>0</v>
-      </c>
-      <c r="AI105" t="inlineStr">
-        <is>
-          <t>Fuktig ängsmark</t>
-        </is>
       </c>
       <c r="AT105" t="inlineStr"/>
       <c r="AW105" t="inlineStr">
         <is>
-          <t>Jan Yngve Andersson</t>
+          <t>Thomas Strid</t>
         </is>
       </c>
       <c r="AX105" t="inlineStr">
         <is>
-          <t>Jan Yngve Andersson</t>
+          <t>Thomas Strid, Tiina Laantee, Melica Strid</t>
         </is>
       </c>
       <c r="AY105" t="inlineStr"/>
     </row>
     <row r="106">
       <c r="A106" t="n">
-        <v>105024185</v>
+        <v>69716937</v>
       </c>
       <c r="B106" t="n">
         <v>110117</v>
@@ -12072,26 +12077,22 @@
           <t>L.</t>
         </is>
       </c>
-      <c r="I106" t="inlineStr">
-        <is>
-          <t>57</t>
-        </is>
-      </c>
-      <c r="J106" t="inlineStr">
-        <is>
-          <t>stjälkar/strån/skott</t>
+      <c r="I106" t="inlineStr"/>
+      <c r="K106" t="inlineStr">
+        <is>
+          <t>blomning</t>
         </is>
       </c>
       <c r="P106" t="inlineStr">
         <is>
-          <t>Lilla Korsgatan N, Gtl</t>
+          <t>Lojsta hed, S om Botes källmyrs NR, Gtl</t>
         </is>
       </c>
       <c r="Q106" t="n">
-        <v>700333</v>
+        <v>700329</v>
       </c>
       <c r="R106" t="n">
-        <v>6359035</v>
+        <v>6359034</v>
       </c>
       <c r="S106" t="n">
         <v>10</v>
@@ -12118,17 +12119,12 @@
       </c>
       <c r="Y106" t="inlineStr">
         <is>
-          <t>2008-07-26</t>
+          <t>2009-07-23</t>
         </is>
       </c>
       <c r="AA106" t="inlineStr">
         <is>
-          <t>2008-07-26</t>
-        </is>
-      </c>
-      <c r="AC106" t="inlineStr">
-        <is>
-          <t>57 stänglar, ca 25 ex. Tidigare känd lokal. - xkoord = 1651946, ykoord = 6358867</t>
+          <t>2009-07-23</t>
         </is>
       </c>
       <c r="AD106" t="b">
@@ -12139,27 +12135,28 @@
       </c>
       <c r="AG106" t="b">
         <v>0</v>
+      </c>
+      <c r="AI106" t="inlineStr">
+        <is>
+          <t>Fuktig ängsmark</t>
+        </is>
       </c>
       <c r="AT106" t="inlineStr"/>
       <c r="AW106" t="inlineStr">
         <is>
-          <t>Jörgen Petersson</t>
+          <t>Jan Yngve Andersson</t>
         </is>
       </c>
       <c r="AX106" t="inlineStr">
         <is>
-          <t>Jörgen Petersson</t>
-        </is>
-      </c>
-      <c r="AY106" t="inlineStr">
-        <is>
-          <t>Projekt Gotlands Flora</t>
-        </is>
-      </c>
+          <t>Jan Yngve Andersson</t>
+        </is>
+      </c>
+      <c r="AY106" t="inlineStr"/>
     </row>
     <row r="107">
       <c r="A107" t="n">
-        <v>105024186</v>
+        <v>105024185</v>
       </c>
       <c r="B107" t="n">
         <v>110117</v>
@@ -12189,21 +12186,21 @@
       </c>
       <c r="I107" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>57</t>
         </is>
       </c>
       <c r="J107" t="inlineStr">
         <is>
-          <t>m²</t>
+          <t>stjälkar/strån/skott</t>
         </is>
       </c>
       <c r="P107" t="inlineStr">
         <is>
-          <t>Lilla Korsgatan 100 m N, vid stig mot Botes källmyr, Gtl</t>
+          <t>Lilla Korsgatan N, Gtl</t>
         </is>
       </c>
       <c r="Q107" t="n">
-        <v>700323</v>
+        <v>700333</v>
       </c>
       <c r="R107" t="n">
         <v>6359035</v>
@@ -12233,12 +12230,17 @@
       </c>
       <c r="Y107" t="inlineStr">
         <is>
-          <t>2003-08-30</t>
+          <t>2008-07-26</t>
         </is>
       </c>
       <c r="AA107" t="inlineStr">
         <is>
-          <t>2003-08-30</t>
+          <t>2008-07-26</t>
+        </is>
+      </c>
+      <c r="AC107" t="inlineStr">
+        <is>
+          <t>57 stänglar, ca 25 ex. Tidigare känd lokal. - xkoord = 1651946, ykoord = 6358867</t>
         </is>
       </c>
       <c r="AD107" t="b">
@@ -12249,11 +12251,6 @@
       </c>
       <c r="AG107" t="b">
         <v>0</v>
-      </c>
-      <c r="AI107" t="inlineStr">
-        <is>
-          <t>Körvägkant.</t>
-        </is>
       </c>
       <c r="AT107" t="inlineStr"/>
       <c r="AW107" t="inlineStr">
@@ -12274,7 +12271,7 @@
     </row>
     <row r="108">
       <c r="A108" t="n">
-        <v>105024198</v>
+        <v>105024186</v>
       </c>
       <c r="B108" t="n">
         <v>110117</v>
@@ -12304,27 +12301,27 @@
       </c>
       <c r="I108" t="inlineStr">
         <is>
-          <t>57</t>
+          <t>1</t>
         </is>
       </c>
       <c r="J108" t="inlineStr">
         <is>
-          <t>stjälkar/strån/skott</t>
+          <t>m²</t>
         </is>
       </c>
       <c r="P108" t="inlineStr">
         <is>
-          <t>Lilla Korsgatan N, vid stig mot Botes källmyr, Gtl</t>
+          <t>Lilla Korsgatan 100 m N, vid stig mot Botes källmyr, Gtl</t>
         </is>
       </c>
       <c r="Q108" t="n">
-        <v>700333</v>
+        <v>700323</v>
       </c>
       <c r="R108" t="n">
-        <v>6359015</v>
+        <v>6359035</v>
       </c>
       <c r="S108" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T108" t="inlineStr">
         <is>
@@ -12343,22 +12340,17 @@
       </c>
       <c r="W108" t="inlineStr">
         <is>
-          <t>Fardhem</t>
+          <t>Gerum</t>
         </is>
       </c>
       <c r="Y108" t="inlineStr">
         <is>
-          <t>2006-07-04</t>
+          <t>2003-08-30</t>
         </is>
       </c>
       <c r="AA108" t="inlineStr">
         <is>
-          <t>2006-07-04</t>
-        </is>
-      </c>
-      <c r="AC108" t="inlineStr">
-        <is>
-          <t>57 stänglar. Ungefärlig koordinat.</t>
+          <t>2003-08-30</t>
         </is>
       </c>
       <c r="AD108" t="b">
@@ -12372,7 +12364,7 @@
       </c>
       <c r="AI108" t="inlineStr">
         <is>
-          <t>Stig i kalktallskog, delvis sandunderlag</t>
+          <t>Körvägkant.</t>
         </is>
       </c>
       <c r="AT108" t="inlineStr"/>
@@ -12394,7 +12386,7 @@
     </row>
     <row r="109">
       <c r="A109" t="n">
-        <v>111587690</v>
+        <v>105024198</v>
       </c>
       <c r="B109" t="n">
         <v>110117</v>
@@ -12424,7 +12416,7 @@
       </c>
       <c r="I109" t="inlineStr">
         <is>
-          <t>37</t>
+          <t>57</t>
         </is>
       </c>
       <c r="J109" t="inlineStr">
@@ -12432,23 +12424,16 @@
           <t>stjälkar/strån/skott</t>
         </is>
       </c>
-      <c r="K109" t="inlineStr">
-        <is>
-          <t>överblommad</t>
-        </is>
-      </c>
-      <c r="L109" t="inlineStr"/>
-      <c r="N109" t="inlineStr"/>
       <c r="P109" t="inlineStr">
         <is>
-          <t>Botes källmyr, vägen, Gtl</t>
+          <t>Lilla Korsgatan N, vid stig mot Botes källmyr, Gtl</t>
         </is>
       </c>
       <c r="Q109" t="n">
-        <v>700319</v>
+        <v>700333</v>
       </c>
       <c r="R109" t="n">
-        <v>6359038</v>
+        <v>6359015</v>
       </c>
       <c r="S109" t="n">
         <v>25</v>
@@ -12470,17 +12455,22 @@
       </c>
       <c r="W109" t="inlineStr">
         <is>
-          <t>Gerum</t>
+          <t>Fardhem</t>
         </is>
       </c>
       <c r="Y109" t="inlineStr">
         <is>
-          <t>2023-08-15</t>
+          <t>2006-07-04</t>
         </is>
       </c>
       <c r="AA109" t="inlineStr">
         <is>
-          <t>2023-08-15</t>
+          <t>2006-07-04</t>
+        </is>
+      </c>
+      <c r="AC109" t="inlineStr">
+        <is>
+          <t>57 stänglar. Ungefärlig koordinat.</t>
         </is>
       </c>
       <c r="AD109" t="b">
@@ -12489,26 +12479,34 @@
       <c r="AE109" t="b">
         <v>0</v>
       </c>
-      <c r="AF109" t="inlineStr"/>
       <c r="AG109" t="b">
         <v>0</v>
+      </c>
+      <c r="AI109" t="inlineStr">
+        <is>
+          <t>Stig i kalktallskog, delvis sandunderlag</t>
+        </is>
       </c>
       <c r="AT109" t="inlineStr"/>
       <c r="AW109" t="inlineStr">
         <is>
-          <t>Kjell Eriksson</t>
+          <t>Jörgen Petersson</t>
         </is>
       </c>
       <c r="AX109" t="inlineStr">
         <is>
-          <t>Kjell Eriksson, Ulla Eriksson</t>
-        </is>
-      </c>
-      <c r="AY109" t="inlineStr"/>
+          <t>Jörgen Petersson</t>
+        </is>
+      </c>
+      <c r="AY109" t="inlineStr">
+        <is>
+          <t>Projekt Gotlands Flora</t>
+        </is>
+      </c>
     </row>
     <row r="110">
       <c r="A110" t="n">
-        <v>126312506</v>
+        <v>111587690</v>
       </c>
       <c r="B110" t="n">
         <v>110117</v>
@@ -12538,7 +12536,7 @@
       </c>
       <c r="I110" t="inlineStr">
         <is>
-          <t>34</t>
+          <t>37</t>
         </is>
       </c>
       <c r="J110" t="inlineStr">
@@ -12548,19 +12546,21 @@
       </c>
       <c r="K110" t="inlineStr">
         <is>
-          <t>blomknopp</t>
-        </is>
-      </c>
+          <t>överblommad</t>
+        </is>
+      </c>
+      <c r="L110" t="inlineStr"/>
+      <c r="N110" t="inlineStr"/>
       <c r="P110" t="inlineStr">
         <is>
-          <t>Lilla Korsgatan, Gtl</t>
+          <t>Botes källmyr, vägen, Gtl</t>
         </is>
       </c>
       <c r="Q110" t="n">
-        <v>700335</v>
+        <v>700319</v>
       </c>
       <c r="R110" t="n">
-        <v>6359040</v>
+        <v>6359038</v>
       </c>
       <c r="S110" t="n">
         <v>25</v>
@@ -12587,12 +12587,12 @@
       </c>
       <c r="Y110" t="inlineStr">
         <is>
-          <t>2025-06-30</t>
+          <t>2023-08-15</t>
         </is>
       </c>
       <c r="AA110" t="inlineStr">
         <is>
-          <t>2025-06-30</t>
+          <t>2023-08-15</t>
         </is>
       </c>
       <c r="AD110" t="b">
@@ -12601,66 +12601,81 @@
       <c r="AE110" t="b">
         <v>0</v>
       </c>
+      <c r="AF110" t="inlineStr"/>
       <c r="AG110" t="b">
         <v>0</v>
       </c>
       <c r="AT110" t="inlineStr"/>
       <c r="AW110" t="inlineStr">
         <is>
-          <t>Felicia Wikinger</t>
+          <t>Kjell Eriksson</t>
         </is>
       </c>
       <c r="AX110" t="inlineStr">
         <is>
-          <t>Felicia Wikinger, Teo Jernkvist</t>
+          <t>Kjell Eriksson, Ulla Eriksson</t>
         </is>
       </c>
       <c r="AY110" t="inlineStr"/>
     </row>
     <row r="111">
       <c r="A111" t="n">
-        <v>116259105</v>
+        <v>126312506</v>
       </c>
       <c r="B111" t="n">
-        <v>101326</v>
+        <v>110117</v>
       </c>
       <c r="D111" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E111" t="n">
-        <v>222498</v>
+        <v>220320</v>
       </c>
       <c r="F111" t="inlineStr">
         <is>
-          <t>Blåsippa</t>
+          <t>Ängsskära</t>
         </is>
       </c>
       <c r="G111" t="inlineStr">
         <is>
-          <t>Hepatica nobilis</t>
+          <t>Serratula tinctoria</t>
         </is>
       </c>
       <c r="H111" t="inlineStr">
         <is>
-          <t>Schreb.</t>
-        </is>
-      </c>
-      <c r="I111" t="inlineStr"/>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I111" t="inlineStr">
+        <is>
+          <t>34</t>
+        </is>
+      </c>
+      <c r="J111" t="inlineStr">
+        <is>
+          <t>stjälkar/strån/skott</t>
+        </is>
+      </c>
+      <c r="K111" t="inlineStr">
+        <is>
+          <t>blomknopp</t>
+        </is>
+      </c>
       <c r="P111" t="inlineStr">
         <is>
-          <t>Gerum Likmunds 1:2 (4), Gtl</t>
+          <t>Lilla Korsgatan, Gtl</t>
         </is>
       </c>
       <c r="Q111" t="n">
-        <v>700330</v>
+        <v>700335</v>
       </c>
       <c r="R111" t="n">
-        <v>6359014</v>
+        <v>6359040</v>
       </c>
       <c r="S111" t="n">
-        <v>5</v>
+        <v>25</v>
       </c>
       <c r="T111" t="inlineStr">
         <is>
@@ -12684,17 +12699,12 @@
       </c>
       <c r="Y111" t="inlineStr">
         <is>
-          <t>2024-04-23</t>
+          <t>2025-06-30</t>
         </is>
       </c>
       <c r="AA111" t="inlineStr">
         <is>
-          <t>2024-04-23</t>
-        </is>
-      </c>
-      <c r="AC111" t="inlineStr">
-        <is>
-          <t>Spridd i hela skogen.</t>
+          <t>2025-06-30</t>
         </is>
       </c>
       <c r="AD111" t="b">
@@ -12709,22 +12719,22 @@
       <c r="AT111" t="inlineStr"/>
       <c r="AW111" t="inlineStr">
         <is>
-          <t>Jörgen Petersson</t>
+          <t>Felicia Wikinger</t>
         </is>
       </c>
       <c r="AX111" t="inlineStr">
         <is>
-          <t>Jörgen Petersson</t>
+          <t>Felicia Wikinger, Teo Jernkvist</t>
         </is>
       </c>
       <c r="AY111" t="inlineStr"/>
     </row>
     <row r="112">
       <c r="A112" t="n">
-        <v>126300259</v>
+        <v>116259105</v>
       </c>
       <c r="B112" t="n">
-        <v>99036</v>
+        <v>101326</v>
       </c>
       <c r="D112" t="inlineStr">
         <is>
@@ -12732,38 +12742,34 @@
         </is>
       </c>
       <c r="E112" t="n">
-        <v>223591</v>
+        <v>222498</v>
       </c>
       <c r="F112" t="inlineStr">
         <is>
-          <t>Skogsnycklar</t>
+          <t>Blåsippa</t>
         </is>
       </c>
       <c r="G112" t="inlineStr">
         <is>
-          <t>Dactylorhiza maculata subsp. fuchsii</t>
+          <t>Hepatica nobilis</t>
         </is>
       </c>
       <c r="H112" t="inlineStr">
         <is>
-          <t>(Druce) Hyl.</t>
-        </is>
-      </c>
-      <c r="I112" t="inlineStr">
-        <is>
-          <t>7</t>
-        </is>
-      </c>
+          <t>Schreb.</t>
+        </is>
+      </c>
+      <c r="I112" t="inlineStr"/>
       <c r="P112" t="inlineStr">
         <is>
-          <t>Gerum, Likmunds 1:2 (4), Gtl</t>
+          <t>Gerum Likmunds 1:2 (4), Gtl</t>
         </is>
       </c>
       <c r="Q112" t="n">
-        <v>700247</v>
+        <v>700330</v>
       </c>
       <c r="R112" t="n">
-        <v>6359105</v>
+        <v>6359014</v>
       </c>
       <c r="S112" t="n">
         <v>5</v>
@@ -12790,12 +12796,17 @@
       </c>
       <c r="Y112" t="inlineStr">
         <is>
-          <t>2025-06-29</t>
+          <t>2024-04-23</t>
         </is>
       </c>
       <c r="AA112" t="inlineStr">
         <is>
-          <t>2025-06-29</t>
+          <t>2024-04-23</t>
+        </is>
+      </c>
+      <c r="AC112" t="inlineStr">
+        <is>
+          <t>Spridd i hela skogen.</t>
         </is>
       </c>
       <c r="AD112" t="b">
@@ -12806,28 +12817,23 @@
       </c>
       <c r="AG112" t="b">
         <v>0</v>
-      </c>
-      <c r="AI112" t="inlineStr">
-        <is>
-          <t>Hästbetad blandskog</t>
-        </is>
       </c>
       <c r="AT112" t="inlineStr"/>
       <c r="AW112" t="inlineStr">
         <is>
-          <t>Gun Ingmansson</t>
+          <t>Jörgen Petersson</t>
         </is>
       </c>
       <c r="AX112" t="inlineStr">
         <is>
-          <t>Gun Ingmansson, Jörgen Petersson, Björn Larsson</t>
+          <t>Jörgen Petersson</t>
         </is>
       </c>
       <c r="AY112" t="inlineStr"/>
     </row>
     <row r="113">
       <c r="A113" t="n">
-        <v>126300263</v>
+        <v>126300259</v>
       </c>
       <c r="B113" t="n">
         <v>99036</v>
@@ -12857,7 +12863,7 @@
       </c>
       <c r="I113" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>7</t>
         </is>
       </c>
       <c r="P113" t="inlineStr">
@@ -12866,13 +12872,13 @@
         </is>
       </c>
       <c r="Q113" t="n">
-        <v>700253</v>
+        <v>700247</v>
       </c>
       <c r="R113" t="n">
-        <v>6359086</v>
+        <v>6359105</v>
       </c>
       <c r="S113" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="T113" t="inlineStr">
         <is>
@@ -12933,7 +12939,7 @@
     </row>
     <row r="114">
       <c r="A114" t="n">
-        <v>126300266</v>
+        <v>126300263</v>
       </c>
       <c r="B114" t="n">
         <v>99036</v>
@@ -12963,7 +12969,7 @@
       </c>
       <c r="I114" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>10</t>
         </is>
       </c>
       <c r="P114" t="inlineStr">
@@ -12972,13 +12978,13 @@
         </is>
       </c>
       <c r="Q114" t="n">
-        <v>700247</v>
+        <v>700253</v>
       </c>
       <c r="R114" t="n">
-        <v>6359082</v>
+        <v>6359086</v>
       </c>
       <c r="S114" t="n">
-        <v>8</v>
+        <v>4</v>
       </c>
       <c r="T114" t="inlineStr">
         <is>
@@ -13039,7 +13045,7 @@
     </row>
     <row r="115">
       <c r="A115" t="n">
-        <v>126300270</v>
+        <v>126300266</v>
       </c>
       <c r="B115" t="n">
         <v>99036</v>
@@ -13067,20 +13073,24 @@
           <t>(Druce) Hyl.</t>
         </is>
       </c>
-      <c r="I115" t="inlineStr"/>
+      <c r="I115" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
       <c r="P115" t="inlineStr">
         <is>
           <t>Gerum, Likmunds 1:2 (4), Gtl</t>
         </is>
       </c>
       <c r="Q115" t="n">
-        <v>700265</v>
+        <v>700247</v>
       </c>
       <c r="R115" t="n">
-        <v>6359056</v>
+        <v>6359082</v>
       </c>
       <c r="S115" t="n">
-        <v>4</v>
+        <v>8</v>
       </c>
       <c r="T115" t="inlineStr">
         <is>
@@ -13141,7 +13151,7 @@
     </row>
     <row r="116">
       <c r="A116" t="n">
-        <v>126300272</v>
+        <v>126300270</v>
       </c>
       <c r="B116" t="n">
         <v>99036</v>
@@ -13169,21 +13179,17 @@
           <t>(Druce) Hyl.</t>
         </is>
       </c>
-      <c r="I116" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
-      </c>
+      <c r="I116" t="inlineStr"/>
       <c r="P116" t="inlineStr">
         <is>
           <t>Gerum, Likmunds 1:2 (4), Gtl</t>
         </is>
       </c>
       <c r="Q116" t="n">
-        <v>700275</v>
+        <v>700265</v>
       </c>
       <c r="R116" t="n">
-        <v>6359045</v>
+        <v>6359056</v>
       </c>
       <c r="S116" t="n">
         <v>4</v>
@@ -13247,7 +13253,7 @@
     </row>
     <row r="117">
       <c r="A117" t="n">
-        <v>126514047</v>
+        <v>126300272</v>
       </c>
       <c r="B117" t="n">
         <v>99036</v>
@@ -13275,20 +13281,24 @@
           <t>(Druce) Hyl.</t>
         </is>
       </c>
-      <c r="I117" t="inlineStr"/>
+      <c r="I117" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
       <c r="P117" t="inlineStr">
         <is>
           <t>Gerum, Likmunds 1:2 (4), Gtl</t>
         </is>
       </c>
       <c r="Q117" t="n">
-        <v>700215</v>
+        <v>700275</v>
       </c>
       <c r="R117" t="n">
-        <v>6359155</v>
+        <v>6359045</v>
       </c>
       <c r="S117" t="n">
-        <v>8</v>
+        <v>4</v>
       </c>
       <c r="T117" t="inlineStr">
         <is>
@@ -13349,10 +13359,10 @@
     </row>
     <row r="118">
       <c r="A118" t="n">
-        <v>134628531</v>
+        <v>126514047</v>
       </c>
       <c r="B118" t="n">
-        <v>99113</v>
+        <v>99036</v>
       </c>
       <c r="D118" t="inlineStr">
         <is>
@@ -13380,17 +13390,17 @@
       <c r="I118" t="inlineStr"/>
       <c r="P118" t="inlineStr">
         <is>
-          <t>Gerum Likmunds, Gtl</t>
+          <t>Gerum, Likmunds 1:2 (4), Gtl</t>
         </is>
       </c>
       <c r="Q118" t="n">
-        <v>700192</v>
+        <v>700215</v>
       </c>
       <c r="R118" t="n">
-        <v>6359150</v>
+        <v>6359155</v>
       </c>
       <c r="S118" t="n">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="T118" t="inlineStr">
         <is>
@@ -13414,22 +13424,12 @@
       </c>
       <c r="Y118" t="inlineStr">
         <is>
-          <t>2026-06-24</t>
-        </is>
-      </c>
-      <c r="Z118" t="inlineStr">
-        <is>
-          <t>16:09</t>
+          <t>2025-06-29</t>
         </is>
       </c>
       <c r="AA118" t="inlineStr">
         <is>
-          <t>2026-06-24</t>
-        </is>
-      </c>
-      <c r="AB118" t="inlineStr">
-        <is>
-          <t>16:09</t>
+          <t>2025-06-29</t>
         </is>
       </c>
       <c r="AD118" t="b">
@@ -13440,23 +13440,28 @@
       </c>
       <c r="AG118" t="b">
         <v>0</v>
+      </c>
+      <c r="AI118" t="inlineStr">
+        <is>
+          <t>Hästbetad blandskog</t>
+        </is>
       </c>
       <c r="AT118" t="inlineStr"/>
       <c r="AW118" t="inlineStr">
         <is>
-          <t>Anna Helmersson</t>
+          <t>Gun Ingmansson</t>
         </is>
       </c>
       <c r="AX118" t="inlineStr">
         <is>
-          <t>Anna Helmersson, Margaret Rainey, Esmeralda  Svanberg</t>
+          <t>Gun Ingmansson, Jörgen Petersson, Björn Larsson</t>
         </is>
       </c>
       <c r="AY118" t="inlineStr"/>
     </row>
     <row r="119">
       <c r="A119" t="n">
-        <v>134629175</v>
+        <v>134628531</v>
       </c>
       <c r="B119" t="n">
         <v>99113</v>
@@ -13487,17 +13492,17 @@
       <c r="I119" t="inlineStr"/>
       <c r="P119" t="inlineStr">
         <is>
-          <t>Gerums Likmunds, Gtl</t>
+          <t>Gerum Likmunds, Gtl</t>
         </is>
       </c>
       <c r="Q119" t="n">
-        <v>700259</v>
+        <v>700192</v>
       </c>
       <c r="R119" t="n">
-        <v>6359029</v>
+        <v>6359150</v>
       </c>
       <c r="S119" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="T119" t="inlineStr">
         <is>
@@ -13526,7 +13531,7 @@
       </c>
       <c r="Z119" t="inlineStr">
         <is>
-          <t>15:54</t>
+          <t>16:09</t>
         </is>
       </c>
       <c r="AA119" t="inlineStr">
@@ -13536,7 +13541,7 @@
       </c>
       <c r="AB119" t="inlineStr">
         <is>
-          <t>15:54</t>
+          <t>16:09</t>
         </is>
       </c>
       <c r="AD119" t="b">
@@ -13551,19 +13556,19 @@
       <c r="AT119" t="inlineStr"/>
       <c r="AW119" t="inlineStr">
         <is>
-          <t>Margaret Rainey</t>
+          <t>Anna Helmersson</t>
         </is>
       </c>
       <c r="AX119" t="inlineStr">
         <is>
-          <t>Margaret Rainey</t>
+          <t>Anna Helmersson, Margaret Rainey, Esmeralda  Svanberg</t>
         </is>
       </c>
       <c r="AY119" t="inlineStr"/>
     </row>
     <row r="120">
       <c r="A120" t="n">
-        <v>134629176</v>
+        <v>134629175</v>
       </c>
       <c r="B120" t="n">
         <v>99113</v>
@@ -13598,13 +13603,13 @@
         </is>
       </c>
       <c r="Q120" t="n">
-        <v>700225</v>
+        <v>700259</v>
       </c>
       <c r="R120" t="n">
-        <v>6359027</v>
+        <v>6359029</v>
       </c>
       <c r="S120" t="n">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="T120" t="inlineStr">
         <is>
@@ -13633,7 +13638,7 @@
       </c>
       <c r="Z120" t="inlineStr">
         <is>
-          <t>15:57</t>
+          <t>15:54</t>
         </is>
       </c>
       <c r="AA120" t="inlineStr">
@@ -13643,7 +13648,7 @@
       </c>
       <c r="AB120" t="inlineStr">
         <is>
-          <t>15:57</t>
+          <t>15:54</t>
         </is>
       </c>
       <c r="AD120" t="b">
@@ -13670,7 +13675,7 @@
     </row>
     <row r="121">
       <c r="A121" t="n">
-        <v>134629180</v>
+        <v>134629176</v>
       </c>
       <c r="B121" t="n">
         <v>99113</v>
@@ -13705,13 +13710,13 @@
         </is>
       </c>
       <c r="Q121" t="n">
-        <v>700189</v>
+        <v>700225</v>
       </c>
       <c r="R121" t="n">
-        <v>6359091</v>
+        <v>6359027</v>
       </c>
       <c r="S121" t="n">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="T121" t="inlineStr">
         <is>
@@ -13740,7 +13745,7 @@
       </c>
       <c r="Z121" t="inlineStr">
         <is>
-          <t>16:04</t>
+          <t>15:57</t>
         </is>
       </c>
       <c r="AA121" t="inlineStr">
@@ -13750,7 +13755,7 @@
       </c>
       <c r="AB121" t="inlineStr">
         <is>
-          <t>16:04</t>
+          <t>15:57</t>
         </is>
       </c>
       <c r="AD121" t="b">
@@ -13777,7 +13782,7 @@
     </row>
     <row r="122">
       <c r="A122" t="n">
-        <v>134629194</v>
+        <v>134629180</v>
       </c>
       <c r="B122" t="n">
         <v>99113</v>
@@ -13812,13 +13817,13 @@
         </is>
       </c>
       <c r="Q122" t="n">
-        <v>700257</v>
+        <v>700189</v>
       </c>
       <c r="R122" t="n">
         <v>6359091</v>
       </c>
       <c r="S122" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="T122" t="inlineStr">
         <is>
@@ -13847,7 +13852,7 @@
       </c>
       <c r="Z122" t="inlineStr">
         <is>
-          <t>16:24</t>
+          <t>16:04</t>
         </is>
       </c>
       <c r="AA122" t="inlineStr">
@@ -13857,7 +13862,7 @@
       </c>
       <c r="AB122" t="inlineStr">
         <is>
-          <t>16:24</t>
+          <t>16:04</t>
         </is>
       </c>
       <c r="AD122" t="b">
@@ -13884,10 +13889,10 @@
     </row>
     <row r="123">
       <c r="A123" t="n">
-        <v>126300254</v>
+        <v>134629194</v>
       </c>
       <c r="B123" t="n">
-        <v>99155</v>
+        <v>99113</v>
       </c>
       <c r="D123" t="inlineStr">
         <is>
@@ -13895,41 +13900,37 @@
         </is>
       </c>
       <c r="E123" t="n">
-        <v>223621</v>
+        <v>223591</v>
       </c>
       <c r="F123" t="inlineStr">
         <is>
-          <t>Skogsnattviol</t>
+          <t>Skogsnycklar</t>
         </is>
       </c>
       <c r="G123" t="inlineStr">
         <is>
-          <t>Platanthera bifolia subsp. latiflora</t>
+          <t>Dactylorhiza maculata subsp. fuchsii</t>
         </is>
       </c>
       <c r="H123" t="inlineStr">
         <is>
-          <t>(Drejer) Løjtnant</t>
-        </is>
-      </c>
-      <c r="I123" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+          <t>(Druce) Hyl.</t>
+        </is>
+      </c>
+      <c r="I123" t="inlineStr"/>
       <c r="P123" t="inlineStr">
         <is>
-          <t>Gerum, Likmunds 1:2 (4), Gtl</t>
+          <t>Gerums Likmunds, Gtl</t>
         </is>
       </c>
       <c r="Q123" t="n">
-        <v>700231</v>
+        <v>700257</v>
       </c>
       <c r="R123" t="n">
-        <v>6359136</v>
+        <v>6359091</v>
       </c>
       <c r="S123" t="n">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="T123" t="inlineStr">
         <is>
@@ -13953,12 +13954,22 @@
       </c>
       <c r="Y123" t="inlineStr">
         <is>
-          <t>2025-06-29</t>
+          <t>2026-06-24</t>
+        </is>
+      </c>
+      <c r="Z123" t="inlineStr">
+        <is>
+          <t>16:24</t>
         </is>
       </c>
       <c r="AA123" t="inlineStr">
         <is>
-          <t>2025-06-29</t>
+          <t>2026-06-24</t>
+        </is>
+      </c>
+      <c r="AB123" t="inlineStr">
+        <is>
+          <t>16:24</t>
         </is>
       </c>
       <c r="AD123" t="b">
@@ -13969,24 +13980,125 @@
       </c>
       <c r="AG123" t="b">
         <v>0</v>
-      </c>
-      <c r="AI123" t="inlineStr">
-        <is>
-          <t>Hästbetad blandskog</t>
-        </is>
       </c>
       <c r="AT123" t="inlineStr"/>
       <c r="AW123" t="inlineStr">
         <is>
+          <t>Margaret Rainey</t>
+        </is>
+      </c>
+      <c r="AX123" t="inlineStr">
+        <is>
+          <t>Margaret Rainey</t>
+        </is>
+      </c>
+      <c r="AY123" t="inlineStr"/>
+    </row>
+    <row r="124">
+      <c r="A124" t="n">
+        <v>126300254</v>
+      </c>
+      <c r="B124" t="n">
+        <v>99155</v>
+      </c>
+      <c r="D124" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E124" t="n">
+        <v>223621</v>
+      </c>
+      <c r="F124" t="inlineStr">
+        <is>
+          <t>Skogsnattviol</t>
+        </is>
+      </c>
+      <c r="G124" t="inlineStr">
+        <is>
+          <t>Platanthera bifolia subsp. latiflora</t>
+        </is>
+      </c>
+      <c r="H124" t="inlineStr">
+        <is>
+          <t>(Drejer) Løjtnant</t>
+        </is>
+      </c>
+      <c r="I124" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="P124" t="inlineStr">
+        <is>
+          <t>Gerum, Likmunds 1:2 (4), Gtl</t>
+        </is>
+      </c>
+      <c r="Q124" t="n">
+        <v>700231</v>
+      </c>
+      <c r="R124" t="n">
+        <v>6359136</v>
+      </c>
+      <c r="S124" t="n">
+        <v>4</v>
+      </c>
+      <c r="T124" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="U124" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="V124" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="W124" t="inlineStr">
+        <is>
+          <t>Gerum</t>
+        </is>
+      </c>
+      <c r="Y124" t="inlineStr">
+        <is>
+          <t>2025-06-29</t>
+        </is>
+      </c>
+      <c r="AA124" t="inlineStr">
+        <is>
+          <t>2025-06-29</t>
+        </is>
+      </c>
+      <c r="AD124" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE124" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG124" t="b">
+        <v>0</v>
+      </c>
+      <c r="AI124" t="inlineStr">
+        <is>
+          <t>Hästbetad blandskog</t>
+        </is>
+      </c>
+      <c r="AT124" t="inlineStr"/>
+      <c r="AW124" t="inlineStr">
+        <is>
           <t>Gun Ingmansson</t>
         </is>
       </c>
-      <c r="AX123" t="inlineStr">
+      <c r="AX124" t="inlineStr">
         <is>
           <t>Gun Ingmansson, Jörgen Petersson, Björn Larsson</t>
         </is>
       </c>
-      <c r="AY123" t="inlineStr"/>
+      <c r="AY124" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/artfynd/A 14354-2024 artfynd.xlsx
+++ b/artfynd/A 14354-2024 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY124"/>
+  <dimension ref="A1:AZ124"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -672,6 +672,11 @@
           <t>Projektnamn</t>
         </is>
       </c>
+      <c r="AZ1" t="inlineStr">
+        <is>
+          <t>Artportalenlänk</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="n">
@@ -774,6 +779,11 @@
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
+      <c r="AZ2" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/126514041</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
@@ -885,6 +895,11 @@
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
+      <c r="AZ3" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/116259490</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
@@ -999,6 +1014,11 @@
         </is>
       </c>
       <c r="AY4" t="inlineStr"/>
+      <c r="AZ4" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/60293979</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="n">
@@ -1117,6 +1137,11 @@
           <t>Biogeografisk uppföljning av fjärilar</t>
         </is>
       </c>
+      <c r="AZ5" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/68587789</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="n">
@@ -1232,6 +1257,11 @@
           <t>Biogeografisk uppföljning av fjärilar</t>
         </is>
       </c>
+      <c r="AZ6" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/88866474</t>
+        </is>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="n">
@@ -1347,6 +1377,11 @@
           <t>Biogeografisk uppföljning av fjärilar</t>
         </is>
       </c>
+      <c r="AZ7" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/95822755</t>
+        </is>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="n">
@@ -1462,6 +1497,11 @@
           <t>Biogeografisk uppföljning av fjärilar</t>
         </is>
       </c>
+      <c r="AZ8" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/95822757</t>
+        </is>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="n">
@@ -1577,6 +1617,11 @@
           <t>Biogeografisk uppföljning av fjärilar</t>
         </is>
       </c>
+      <c r="AZ9" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/111758809</t>
+        </is>
+      </c>
     </row>
     <row r="10">
       <c r="A10" t="n">
@@ -1692,6 +1737,11 @@
           <t>Biogeografisk uppföljning av fjärilar</t>
         </is>
       </c>
+      <c r="AZ10" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/111758817</t>
+        </is>
+      </c>
     </row>
     <row r="11">
       <c r="A11" t="n">
@@ -1807,6 +1857,11 @@
           <t>Biogeografisk uppföljning av fjärilar</t>
         </is>
       </c>
+      <c r="AZ11" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/111758822</t>
+        </is>
+      </c>
     </row>
     <row r="12">
       <c r="A12" t="n">
@@ -1922,6 +1977,11 @@
           <t>Biogeografisk uppföljning av fjärilar</t>
         </is>
       </c>
+      <c r="AZ12" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/118077502</t>
+        </is>
+      </c>
     </row>
     <row r="13">
       <c r="A13" t="n">
@@ -2037,6 +2097,11 @@
           <t>Biogeografisk uppföljning av fjärilar</t>
         </is>
       </c>
+      <c r="AZ13" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/118077514</t>
+        </is>
+      </c>
     </row>
     <row r="14">
       <c r="A14" t="n">
@@ -2143,6 +2208,11 @@
         </is>
       </c>
       <c r="AY14" t="inlineStr"/>
+      <c r="AZ14" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/126300253</t>
+        </is>
+      </c>
     </row>
     <row r="15">
       <c r="A15" t="n">
@@ -2249,6 +2319,11 @@
         </is>
       </c>
       <c r="AY15" t="inlineStr"/>
+      <c r="AZ15" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/126300255</t>
+        </is>
+      </c>
     </row>
     <row r="16">
       <c r="A16" t="n">
@@ -2355,6 +2430,11 @@
         </is>
       </c>
       <c r="AY16" t="inlineStr"/>
+      <c r="AZ16" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/126300260</t>
+        </is>
+      </c>
     </row>
     <row r="17">
       <c r="A17" t="n">
@@ -2461,6 +2541,11 @@
         </is>
       </c>
       <c r="AY17" t="inlineStr"/>
+      <c r="AZ17" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/126300262</t>
+        </is>
+      </c>
     </row>
     <row r="18">
       <c r="A18" t="n">
@@ -2567,6 +2652,11 @@
         </is>
       </c>
       <c r="AY18" t="inlineStr"/>
+      <c r="AZ18" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/126300264</t>
+        </is>
+      </c>
     </row>
     <row r="19">
       <c r="A19" t="n">
@@ -2673,6 +2763,11 @@
         </is>
       </c>
       <c r="AY19" t="inlineStr"/>
+      <c r="AZ19" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/126300269</t>
+        </is>
+      </c>
     </row>
     <row r="20">
       <c r="A20" t="n">
@@ -2779,6 +2874,11 @@
         </is>
       </c>
       <c r="AY20" t="inlineStr"/>
+      <c r="AZ20" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/126300274</t>
+        </is>
+      </c>
     </row>
     <row r="21">
       <c r="A21" t="n">
@@ -2885,6 +2985,11 @@
         </is>
       </c>
       <c r="AY21" t="inlineStr"/>
+      <c r="AZ21" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/126300275</t>
+        </is>
+      </c>
     </row>
     <row r="22">
       <c r="A22" t="n">
@@ -2991,6 +3096,11 @@
         </is>
       </c>
       <c r="AY22" t="inlineStr"/>
+      <c r="AZ22" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/126300276</t>
+        </is>
+      </c>
     </row>
     <row r="23">
       <c r="A23" t="n">
@@ -3097,6 +3207,11 @@
         </is>
       </c>
       <c r="AY23" t="inlineStr"/>
+      <c r="AZ23" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/126514033</t>
+        </is>
+      </c>
     </row>
     <row r="24">
       <c r="A24" t="n">
@@ -3203,6 +3318,11 @@
         </is>
       </c>
       <c r="AY24" t="inlineStr"/>
+      <c r="AZ24" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/126514034</t>
+        </is>
+      </c>
     </row>
     <row r="25">
       <c r="A25" t="n">
@@ -3309,6 +3429,11 @@
         </is>
       </c>
       <c r="AY25" t="inlineStr"/>
+      <c r="AZ25" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/126514036</t>
+        </is>
+      </c>
     </row>
     <row r="26">
       <c r="A26" t="n">
@@ -3415,6 +3540,11 @@
         </is>
       </c>
       <c r="AY26" t="inlineStr"/>
+      <c r="AZ26" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/126514037</t>
+        </is>
+      </c>
     </row>
     <row r="27">
       <c r="A27" t="n">
@@ -3521,6 +3651,11 @@
         </is>
       </c>
       <c r="AY27" t="inlineStr"/>
+      <c r="AZ27" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/126514038</t>
+        </is>
+      </c>
     </row>
     <row r="28">
       <c r="A28" t="n">
@@ -3627,6 +3762,11 @@
         </is>
       </c>
       <c r="AY28" t="inlineStr"/>
+      <c r="AZ28" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/126514039</t>
+        </is>
+      </c>
     </row>
     <row r="29">
       <c r="A29" t="n">
@@ -3733,6 +3873,11 @@
         </is>
       </c>
       <c r="AY29" t="inlineStr"/>
+      <c r="AZ29" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/126514040</t>
+        </is>
+      </c>
     </row>
     <row r="30">
       <c r="A30" t="n">
@@ -3839,6 +3984,11 @@
         </is>
       </c>
       <c r="AY30" t="inlineStr"/>
+      <c r="AZ30" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/126514042</t>
+        </is>
+      </c>
     </row>
     <row r="31">
       <c r="A31" t="n">
@@ -3945,6 +4095,11 @@
         </is>
       </c>
       <c r="AY31" t="inlineStr"/>
+      <c r="AZ31" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/126514043</t>
+        </is>
+      </c>
     </row>
     <row r="32">
       <c r="A32" t="n">
@@ -4051,6 +4206,11 @@
         </is>
       </c>
       <c r="AY32" t="inlineStr"/>
+      <c r="AZ32" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/126514046</t>
+        </is>
+      </c>
     </row>
     <row r="33">
       <c r="A33" t="n">
@@ -4166,6 +4326,11 @@
           <t>Biogeografisk uppföljning av fjärilar</t>
         </is>
       </c>
+      <c r="AZ33" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/126992149</t>
+        </is>
+      </c>
     </row>
     <row r="34">
       <c r="A34" t="n">
@@ -4281,6 +4446,11 @@
           <t>Biogeografisk uppföljning av fjärilar</t>
         </is>
       </c>
+      <c r="AZ34" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/126992159</t>
+        </is>
+      </c>
     </row>
     <row r="35">
       <c r="A35" t="n">
@@ -4393,6 +4563,11 @@
         </is>
       </c>
       <c r="AY35" t="inlineStr"/>
+      <c r="AZ35" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134628521</t>
+        </is>
+      </c>
     </row>
     <row r="36">
       <c r="A36" t="n">
@@ -4500,6 +4675,11 @@
         </is>
       </c>
       <c r="AY36" t="inlineStr"/>
+      <c r="AZ36" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134628522</t>
+        </is>
+      </c>
     </row>
     <row r="37">
       <c r="A37" t="n">
@@ -4612,6 +4792,11 @@
         </is>
       </c>
       <c r="AY37" t="inlineStr"/>
+      <c r="AZ37" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134628523</t>
+        </is>
+      </c>
     </row>
     <row r="38">
       <c r="A38" t="n">
@@ -4719,6 +4904,11 @@
         </is>
       </c>
       <c r="AY38" t="inlineStr"/>
+      <c r="AZ38" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134628524</t>
+        </is>
+      </c>
     </row>
     <row r="39">
       <c r="A39" t="n">
@@ -4826,6 +5016,11 @@
         </is>
       </c>
       <c r="AY39" t="inlineStr"/>
+      <c r="AZ39" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134628525</t>
+        </is>
+      </c>
     </row>
     <row r="40">
       <c r="A40" t="n">
@@ -4938,6 +5133,11 @@
         </is>
       </c>
       <c r="AY40" t="inlineStr"/>
+      <c r="AZ40" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134628526</t>
+        </is>
+      </c>
     </row>
     <row r="41">
       <c r="A41" t="n">
@@ -5045,6 +5245,11 @@
         </is>
       </c>
       <c r="AY41" t="inlineStr"/>
+      <c r="AZ41" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134628529</t>
+        </is>
+      </c>
     </row>
     <row r="42">
       <c r="A42" t="n">
@@ -5157,6 +5362,11 @@
         </is>
       </c>
       <c r="AY42" t="inlineStr"/>
+      <c r="AZ42" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134628530</t>
+        </is>
+      </c>
     </row>
     <row r="43">
       <c r="A43" t="n">
@@ -5264,6 +5474,11 @@
         </is>
       </c>
       <c r="AY43" t="inlineStr"/>
+      <c r="AZ43" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134628532</t>
+        </is>
+      </c>
     </row>
     <row r="44">
       <c r="A44" t="n">
@@ -5371,6 +5586,11 @@
         </is>
       </c>
       <c r="AY44" t="inlineStr"/>
+      <c r="AZ44" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134628533</t>
+        </is>
+      </c>
     </row>
     <row r="45">
       <c r="A45" t="n">
@@ -5483,6 +5703,11 @@
         </is>
       </c>
       <c r="AY45" t="inlineStr"/>
+      <c r="AZ45" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134628534</t>
+        </is>
+      </c>
     </row>
     <row r="46">
       <c r="A46" t="n">
@@ -5595,6 +5820,11 @@
         </is>
       </c>
       <c r="AY46" t="inlineStr"/>
+      <c r="AZ46" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134628535</t>
+        </is>
+      </c>
     </row>
     <row r="47">
       <c r="A47" t="n">
@@ -5707,6 +5937,11 @@
         </is>
       </c>
       <c r="AY47" t="inlineStr"/>
+      <c r="AZ47" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134628536</t>
+        </is>
+      </c>
     </row>
     <row r="48">
       <c r="A48" t="n">
@@ -5819,6 +6054,11 @@
         </is>
       </c>
       <c r="AY48" t="inlineStr"/>
+      <c r="AZ48" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134628537</t>
+        </is>
+      </c>
     </row>
     <row r="49">
       <c r="A49" t="n">
@@ -5926,6 +6166,11 @@
         </is>
       </c>
       <c r="AY49" t="inlineStr"/>
+      <c r="AZ49" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134629166</t>
+        </is>
+      </c>
     </row>
     <row r="50">
       <c r="A50" t="n">
@@ -6033,6 +6278,11 @@
         </is>
       </c>
       <c r="AY50" t="inlineStr"/>
+      <c r="AZ50" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134629167</t>
+        </is>
+      </c>
     </row>
     <row r="51">
       <c r="A51" t="n">
@@ -6145,6 +6395,11 @@
         </is>
       </c>
       <c r="AY51" t="inlineStr"/>
+      <c r="AZ51" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134629169</t>
+        </is>
+      </c>
     </row>
     <row r="52">
       <c r="A52" t="n">
@@ -6257,6 +6512,11 @@
         </is>
       </c>
       <c r="AY52" t="inlineStr"/>
+      <c r="AZ52" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134629172</t>
+        </is>
+      </c>
     </row>
     <row r="53">
       <c r="A53" t="n">
@@ -6364,6 +6624,11 @@
         </is>
       </c>
       <c r="AY53" t="inlineStr"/>
+      <c r="AZ53" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134629173</t>
+        </is>
+      </c>
     </row>
     <row r="54">
       <c r="A54" t="n">
@@ -6476,6 +6741,11 @@
         </is>
       </c>
       <c r="AY54" t="inlineStr"/>
+      <c r="AZ54" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134629178</t>
+        </is>
+      </c>
     </row>
     <row r="55">
       <c r="A55" t="n">
@@ -6583,6 +6853,11 @@
         </is>
       </c>
       <c r="AY55" t="inlineStr"/>
+      <c r="AZ55" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134629181</t>
+        </is>
+      </c>
     </row>
     <row r="56">
       <c r="A56" t="n">
@@ -6690,6 +6965,11 @@
         </is>
       </c>
       <c r="AY56" t="inlineStr"/>
+      <c r="AZ56" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134629182</t>
+        </is>
+      </c>
     </row>
     <row r="57">
       <c r="A57" t="n">
@@ -6797,6 +7077,11 @@
         </is>
       </c>
       <c r="AY57" t="inlineStr"/>
+      <c r="AZ57" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134629184</t>
+        </is>
+      </c>
     </row>
     <row r="58">
       <c r="A58" t="n">
@@ -6904,6 +7189,11 @@
         </is>
       </c>
       <c r="AY58" t="inlineStr"/>
+      <c r="AZ58" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134629186</t>
+        </is>
+      </c>
     </row>
     <row r="59">
       <c r="A59" t="n">
@@ -7011,6 +7301,11 @@
         </is>
       </c>
       <c r="AY59" t="inlineStr"/>
+      <c r="AZ59" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134629191</t>
+        </is>
+      </c>
     </row>
     <row r="60">
       <c r="A60" t="n">
@@ -7118,6 +7413,11 @@
         </is>
       </c>
       <c r="AY60" t="inlineStr"/>
+      <c r="AZ60" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134629196</t>
+        </is>
+      </c>
     </row>
     <row r="61">
       <c r="A61" t="n">
@@ -7230,6 +7530,11 @@
         </is>
       </c>
       <c r="AY61" t="inlineStr"/>
+      <c r="AZ61" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134629641</t>
+        </is>
+      </c>
     </row>
     <row r="62">
       <c r="A62" t="n">
@@ -7342,6 +7647,11 @@
         </is>
       </c>
       <c r="AY62" t="inlineStr"/>
+      <c r="AZ62" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134629642</t>
+        </is>
+      </c>
     </row>
     <row r="63">
       <c r="A63" t="n">
@@ -7454,6 +7764,11 @@
         </is>
       </c>
       <c r="AY63" t="inlineStr"/>
+      <c r="AZ63" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134629644</t>
+        </is>
+      </c>
     </row>
     <row r="64">
       <c r="A64" t="n">
@@ -7566,6 +7881,11 @@
         </is>
       </c>
       <c r="AY64" t="inlineStr"/>
+      <c r="AZ64" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134629645</t>
+        </is>
+      </c>
     </row>
     <row r="65">
       <c r="A65" t="n">
@@ -7678,6 +7998,11 @@
         </is>
       </c>
       <c r="AY65" t="inlineStr"/>
+      <c r="AZ65" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134629647</t>
+        </is>
+      </c>
     </row>
     <row r="66">
       <c r="A66" t="n">
@@ -7790,6 +8115,11 @@
         </is>
       </c>
       <c r="AY66" t="inlineStr"/>
+      <c r="AZ66" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134629648</t>
+        </is>
+      </c>
     </row>
     <row r="67">
       <c r="A67" t="n">
@@ -7902,6 +8232,11 @@
         </is>
       </c>
       <c r="AY67" t="inlineStr"/>
+      <c r="AZ67" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134629650</t>
+        </is>
+      </c>
     </row>
     <row r="68">
       <c r="A68" t="n">
@@ -8014,6 +8349,11 @@
         </is>
       </c>
       <c r="AY68" t="inlineStr"/>
+      <c r="AZ68" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134629652</t>
+        </is>
+      </c>
     </row>
     <row r="69">
       <c r="A69" t="n">
@@ -8126,6 +8466,11 @@
         </is>
       </c>
       <c r="AY69" t="inlineStr"/>
+      <c r="AZ69" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134629655</t>
+        </is>
+      </c>
     </row>
     <row r="70">
       <c r="A70" t="n">
@@ -8238,6 +8583,11 @@
         </is>
       </c>
       <c r="AY70" t="inlineStr"/>
+      <c r="AZ70" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134629656</t>
+        </is>
+      </c>
     </row>
     <row r="71">
       <c r="A71" t="n">
@@ -8350,6 +8700,11 @@
         </is>
       </c>
       <c r="AY71" t="inlineStr"/>
+      <c r="AZ71" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134629658</t>
+        </is>
+      </c>
     </row>
     <row r="72">
       <c r="A72" t="n">
@@ -8462,6 +8817,11 @@
         </is>
       </c>
       <c r="AY72" t="inlineStr"/>
+      <c r="AZ72" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134629659</t>
+        </is>
+      </c>
     </row>
     <row r="73">
       <c r="A73" t="n">
@@ -8574,6 +8934,11 @@
         </is>
       </c>
       <c r="AY73" t="inlineStr"/>
+      <c r="AZ73" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134629661</t>
+        </is>
+      </c>
     </row>
     <row r="74">
       <c r="A74" t="n">
@@ -8686,6 +9051,11 @@
         </is>
       </c>
       <c r="AY74" t="inlineStr"/>
+      <c r="AZ74" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134629662</t>
+        </is>
+      </c>
     </row>
     <row r="75">
       <c r="A75" t="n">
@@ -8798,6 +9168,11 @@
         </is>
       </c>
       <c r="AY75" t="inlineStr"/>
+      <c r="AZ75" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134629664</t>
+        </is>
+      </c>
     </row>
     <row r="76">
       <c r="A76" t="n">
@@ -8910,6 +9285,11 @@
         </is>
       </c>
       <c r="AY76" t="inlineStr"/>
+      <c r="AZ76" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134629665</t>
+        </is>
+      </c>
     </row>
     <row r="77">
       <c r="A77" t="n">
@@ -9022,6 +9402,11 @@
         </is>
       </c>
       <c r="AY77" t="inlineStr"/>
+      <c r="AZ77" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134629666</t>
+        </is>
+      </c>
     </row>
     <row r="78">
       <c r="A78" t="n">
@@ -9134,6 +9519,11 @@
         </is>
       </c>
       <c r="AY78" t="inlineStr"/>
+      <c r="AZ78" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134629667</t>
+        </is>
+      </c>
     </row>
     <row r="79">
       <c r="A79" t="n">
@@ -9246,6 +9636,11 @@
         </is>
       </c>
       <c r="AY79" t="inlineStr"/>
+      <c r="AZ79" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134629668</t>
+        </is>
+      </c>
     </row>
     <row r="80">
       <c r="A80" t="n">
@@ -9358,6 +9753,11 @@
         </is>
       </c>
       <c r="AY80" t="inlineStr"/>
+      <c r="AZ80" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134629671</t>
+        </is>
+      </c>
     </row>
     <row r="81">
       <c r="A81" t="n">
@@ -9470,6 +9870,11 @@
         </is>
       </c>
       <c r="AY81" t="inlineStr"/>
+      <c r="AZ81" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134629673</t>
+        </is>
+      </c>
     </row>
     <row r="82">
       <c r="A82" t="n">
@@ -9582,6 +9987,11 @@
         </is>
       </c>
       <c r="AY82" t="inlineStr"/>
+      <c r="AZ82" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134629674</t>
+        </is>
+      </c>
     </row>
     <row r="83">
       <c r="A83" t="n">
@@ -9689,6 +10099,11 @@
         </is>
       </c>
       <c r="AY83" t="inlineStr"/>
+      <c r="AZ83" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134629192</t>
+        </is>
+      </c>
     </row>
     <row r="84">
       <c r="A84" t="n">
@@ -9796,6 +10211,11 @@
         </is>
       </c>
       <c r="AY84" t="inlineStr"/>
+      <c r="AZ84" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134629189</t>
+        </is>
+      </c>
     </row>
     <row r="85">
       <c r="A85" t="n">
@@ -9919,6 +10339,11 @@
         </is>
       </c>
       <c r="AY85" t="inlineStr"/>
+      <c r="AZ85" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/111589164</t>
+        </is>
+      </c>
     </row>
     <row r="86">
       <c r="A86" t="n">
@@ -10035,6 +10460,11 @@
         </is>
       </c>
       <c r="AY86" t="inlineStr"/>
+      <c r="AZ86" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/116259087</t>
+        </is>
+      </c>
     </row>
     <row r="87">
       <c r="A87" t="n">
@@ -10141,6 +10571,11 @@
         </is>
       </c>
       <c r="AY87" t="inlineStr"/>
+      <c r="AZ87" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/126300257</t>
+        </is>
+      </c>
     </row>
     <row r="88">
       <c r="A88" t="n">
@@ -10247,6 +10682,11 @@
         </is>
       </c>
       <c r="AY88" t="inlineStr"/>
+      <c r="AZ88" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/126514044</t>
+        </is>
+      </c>
     </row>
     <row r="89">
       <c r="A89" t="n">
@@ -10349,6 +10789,11 @@
         </is>
       </c>
       <c r="AY89" t="inlineStr"/>
+      <c r="AZ89" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/126300256</t>
+        </is>
+      </c>
     </row>
     <row r="90">
       <c r="A90" t="n">
@@ -10455,6 +10900,11 @@
         </is>
       </c>
       <c r="AY90" t="inlineStr"/>
+      <c r="AZ90" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/126300258</t>
+        </is>
+      </c>
     </row>
     <row r="91">
       <c r="A91" t="n">
@@ -10557,6 +11007,11 @@
         </is>
       </c>
       <c r="AY91" t="inlineStr"/>
+      <c r="AZ91" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/126300265</t>
+        </is>
+      </c>
     </row>
     <row r="92">
       <c r="A92" t="n">
@@ -10659,6 +11114,11 @@
         </is>
       </c>
       <c r="AY92" t="inlineStr"/>
+      <c r="AZ92" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/126300268</t>
+        </is>
+      </c>
     </row>
     <row r="93">
       <c r="A93" t="n">
@@ -10765,6 +11225,11 @@
         </is>
       </c>
       <c r="AY93" t="inlineStr"/>
+      <c r="AZ93" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/126300273</t>
+        </is>
+      </c>
     </row>
     <row r="94">
       <c r="A94" t="n">
@@ -10867,6 +11332,11 @@
         </is>
       </c>
       <c r="AY94" t="inlineStr"/>
+      <c r="AZ94" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/126514045</t>
+        </is>
+      </c>
     </row>
     <row r="95">
       <c r="A95" t="n">
@@ -10969,6 +11439,11 @@
         </is>
       </c>
       <c r="AY95" t="inlineStr"/>
+      <c r="AZ95" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/126514049</t>
+        </is>
+      </c>
     </row>
     <row r="96">
       <c r="A96" t="n">
@@ -11076,6 +11551,11 @@
         </is>
       </c>
       <c r="AY96" t="inlineStr"/>
+      <c r="AZ96" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134628528</t>
+        </is>
+      </c>
     </row>
     <row r="97">
       <c r="A97" t="n">
@@ -11183,6 +11663,11 @@
         </is>
       </c>
       <c r="AY97" t="inlineStr"/>
+      <c r="AZ97" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134629174</t>
+        </is>
+      </c>
     </row>
     <row r="98">
       <c r="A98" t="n">
@@ -11290,6 +11775,11 @@
         </is>
       </c>
       <c r="AY98" t="inlineStr"/>
+      <c r="AZ98" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134629183</t>
+        </is>
+      </c>
     </row>
     <row r="99">
       <c r="A99" t="n">
@@ -11402,6 +11892,11 @@
         </is>
       </c>
       <c r="AY99" t="inlineStr"/>
+      <c r="AZ99" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134629187</t>
+        </is>
+      </c>
     </row>
     <row r="100">
       <c r="A100" t="n">
@@ -11508,6 +12003,11 @@
         </is>
       </c>
       <c r="AY100" t="inlineStr"/>
+      <c r="AZ100" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/126300267</t>
+        </is>
+      </c>
     </row>
     <row r="101">
       <c r="A101" t="n">
@@ -11615,6 +12115,11 @@
         </is>
       </c>
       <c r="AY101" t="inlineStr"/>
+      <c r="AZ101" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134629170</t>
+        </is>
+      </c>
     </row>
     <row r="102">
       <c r="A102" t="n">
@@ -11721,6 +12226,11 @@
         </is>
       </c>
       <c r="AY102" t="inlineStr"/>
+      <c r="AZ102" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/97960624</t>
+        </is>
+      </c>
     </row>
     <row r="103">
       <c r="A103" t="n">
@@ -11842,6 +12352,11 @@
         </is>
       </c>
       <c r="AY103" t="inlineStr"/>
+      <c r="AZ103" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/2760594</t>
+        </is>
+      </c>
     </row>
     <row r="104">
       <c r="A104" t="n">
@@ -11946,6 +12461,11 @@
         </is>
       </c>
       <c r="AY104" t="inlineStr"/>
+      <c r="AZ104" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/16230167</t>
+        </is>
+      </c>
     </row>
     <row r="105">
       <c r="A105" t="n">
@@ -12046,6 +12566,11 @@
         </is>
       </c>
       <c r="AY105" t="inlineStr"/>
+      <c r="AZ105" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/16500486</t>
+        </is>
+      </c>
     </row>
     <row r="106">
       <c r="A106" t="n">
@@ -12153,6 +12678,11 @@
         </is>
       </c>
       <c r="AY106" t="inlineStr"/>
+      <c r="AZ106" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/69716937</t>
+        </is>
+      </c>
     </row>
     <row r="107">
       <c r="A107" t="n">
@@ -12268,6 +12798,11 @@
           <t>Projekt Gotlands Flora</t>
         </is>
       </c>
+      <c r="AZ107" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/105024185</t>
+        </is>
+      </c>
     </row>
     <row r="108">
       <c r="A108" t="n">
@@ -12383,6 +12918,11 @@
           <t>Projekt Gotlands Flora</t>
         </is>
       </c>
+      <c r="AZ108" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/105024186</t>
+        </is>
+      </c>
     </row>
     <row r="109">
       <c r="A109" t="n">
@@ -12503,6 +13043,11 @@
           <t>Projekt Gotlands Flora</t>
         </is>
       </c>
+      <c r="AZ109" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/105024198</t>
+        </is>
+      </c>
     </row>
     <row r="110">
       <c r="A110" t="n">
@@ -12617,6 +13162,11 @@
         </is>
       </c>
       <c r="AY110" t="inlineStr"/>
+      <c r="AZ110" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/111587690</t>
+        </is>
+      </c>
     </row>
     <row r="111">
       <c r="A111" t="n">
@@ -12728,6 +13278,11 @@
         </is>
       </c>
       <c r="AY111" t="inlineStr"/>
+      <c r="AZ111" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/126312506</t>
+        </is>
+      </c>
     </row>
     <row r="112">
       <c r="A112" t="n">
@@ -12830,6 +13385,11 @@
         </is>
       </c>
       <c r="AY112" t="inlineStr"/>
+      <c r="AZ112" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/116259105</t>
+        </is>
+      </c>
     </row>
     <row r="113">
       <c r="A113" t="n">
@@ -12936,6 +13496,11 @@
         </is>
       </c>
       <c r="AY113" t="inlineStr"/>
+      <c r="AZ113" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/126300259</t>
+        </is>
+      </c>
     </row>
     <row r="114">
       <c r="A114" t="n">
@@ -13042,6 +13607,11 @@
         </is>
       </c>
       <c r="AY114" t="inlineStr"/>
+      <c r="AZ114" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/126300263</t>
+        </is>
+      </c>
     </row>
     <row r="115">
       <c r="A115" t="n">
@@ -13148,6 +13718,11 @@
         </is>
       </c>
       <c r="AY115" t="inlineStr"/>
+      <c r="AZ115" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/126300266</t>
+        </is>
+      </c>
     </row>
     <row r="116">
       <c r="A116" t="n">
@@ -13250,6 +13825,11 @@
         </is>
       </c>
       <c r="AY116" t="inlineStr"/>
+      <c r="AZ116" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/126300270</t>
+        </is>
+      </c>
     </row>
     <row r="117">
       <c r="A117" t="n">
@@ -13356,6 +13936,11 @@
         </is>
       </c>
       <c r="AY117" t="inlineStr"/>
+      <c r="AZ117" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/126300272</t>
+        </is>
+      </c>
     </row>
     <row r="118">
       <c r="A118" t="n">
@@ -13458,6 +14043,11 @@
         </is>
       </c>
       <c r="AY118" t="inlineStr"/>
+      <c r="AZ118" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/126514047</t>
+        </is>
+      </c>
     </row>
     <row r="119">
       <c r="A119" t="n">
@@ -13565,6 +14155,11 @@
         </is>
       </c>
       <c r="AY119" t="inlineStr"/>
+      <c r="AZ119" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134628531</t>
+        </is>
+      </c>
     </row>
     <row r="120">
       <c r="A120" t="n">
@@ -13672,6 +14267,11 @@
         </is>
       </c>
       <c r="AY120" t="inlineStr"/>
+      <c r="AZ120" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134629175</t>
+        </is>
+      </c>
     </row>
     <row r="121">
       <c r="A121" t="n">
@@ -13779,6 +14379,11 @@
         </is>
       </c>
       <c r="AY121" t="inlineStr"/>
+      <c r="AZ121" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134629176</t>
+        </is>
+      </c>
     </row>
     <row r="122">
       <c r="A122" t="n">
@@ -13886,6 +14491,11 @@
         </is>
       </c>
       <c r="AY122" t="inlineStr"/>
+      <c r="AZ122" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134629180</t>
+        </is>
+      </c>
     </row>
     <row r="123">
       <c r="A123" t="n">
@@ -13993,6 +14603,11 @@
         </is>
       </c>
       <c r="AY123" t="inlineStr"/>
+      <c r="AZ123" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134629194</t>
+        </is>
+      </c>
     </row>
     <row r="124">
       <c r="A124" t="n">
@@ -14099,8 +14714,138 @@
         </is>
       </c>
       <c r="AY124" t="inlineStr"/>
+      <c r="AZ124" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/126300254</t>
+        </is>
+      </c>
     </row>
   </sheetData>
+  <hyperlinks>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ2" r:id="rId1"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ3" r:id="rId2"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ4" r:id="rId3"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ5" r:id="rId4"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ6" r:id="rId5"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ7" r:id="rId6"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ8" r:id="rId7"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ9" r:id="rId8"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ10" r:id="rId9"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ11" r:id="rId10"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ12" r:id="rId11"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ13" r:id="rId12"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ14" r:id="rId13"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ15" r:id="rId14"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ16" r:id="rId15"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ17" r:id="rId16"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ18" r:id="rId17"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ19" r:id="rId18"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ20" r:id="rId19"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ21" r:id="rId20"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ22" r:id="rId21"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ23" r:id="rId22"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ24" r:id="rId23"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ25" r:id="rId24"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ26" r:id="rId25"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ27" r:id="rId26"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ28" r:id="rId27"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ29" r:id="rId28"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ30" r:id="rId29"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ31" r:id="rId30"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ32" r:id="rId31"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ33" r:id="rId32"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ34" r:id="rId33"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ35" r:id="rId34"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ36" r:id="rId35"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ37" r:id="rId36"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ38" r:id="rId37"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ39" r:id="rId38"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ40" r:id="rId39"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ41" r:id="rId40"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ42" r:id="rId41"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ43" r:id="rId42"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ44" r:id="rId43"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ45" r:id="rId44"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ46" r:id="rId45"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ47" r:id="rId46"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ48" r:id="rId47"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ49" r:id="rId48"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ50" r:id="rId49"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ51" r:id="rId50"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ52" r:id="rId51"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ53" r:id="rId52"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ54" r:id="rId53"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ55" r:id="rId54"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ56" r:id="rId55"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ57" r:id="rId56"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ58" r:id="rId57"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ59" r:id="rId58"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ60" r:id="rId59"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ61" r:id="rId60"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ62" r:id="rId61"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ63" r:id="rId62"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ64" r:id="rId63"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ65" r:id="rId64"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ66" r:id="rId65"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ67" r:id="rId66"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ68" r:id="rId67"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ69" r:id="rId68"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ70" r:id="rId69"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ71" r:id="rId70"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ72" r:id="rId71"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ73" r:id="rId72"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ74" r:id="rId73"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ75" r:id="rId74"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ76" r:id="rId75"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ77" r:id="rId76"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ78" r:id="rId77"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ79" r:id="rId78"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ80" r:id="rId79"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ81" r:id="rId80"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ82" r:id="rId81"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ83" r:id="rId82"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ84" r:id="rId83"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ85" r:id="rId84"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ86" r:id="rId85"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ87" r:id="rId86"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ88" r:id="rId87"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ89" r:id="rId88"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ90" r:id="rId89"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ91" r:id="rId90"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ92" r:id="rId91"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ93" r:id="rId92"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ94" r:id="rId93"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ95" r:id="rId94"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ96" r:id="rId95"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ97" r:id="rId96"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ98" r:id="rId97"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ99" r:id="rId98"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ100" r:id="rId99"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ101" r:id="rId100"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ102" r:id="rId101"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ103" r:id="rId102"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ104" r:id="rId103"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ105" r:id="rId104"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ106" r:id="rId105"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ107" r:id="rId106"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ108" r:id="rId107"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ109" r:id="rId108"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ110" r:id="rId109"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ111" r:id="rId110"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ112" r:id="rId111"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ113" r:id="rId112"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ114" r:id="rId113"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ115" r:id="rId114"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ116" r:id="rId115"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ117" r:id="rId116"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ118" r:id="rId117"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ119" r:id="rId118"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ120" r:id="rId119"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ121" r:id="rId120"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ122" r:id="rId121"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ123" r:id="rId122"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ124" r:id="rId123"/>
+  </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>